--- a/class_excel/temp_midterm.xlsx
+++ b/class_excel/temp_midterm.xlsx
@@ -1,89 +1,219 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\T00229\Documents\GitHub\DADS7102\class_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FEA6F27-3E5F-450A-B189-D5E460E65C37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9FB1999-D2C3-4B61-BC64-81BC6F1A62B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{962D6ACA-47B2-4C7E-82D5-0F5476EE75BF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="9" xr2:uid="{962D6ACA-47B2-4C7E-82D5-0F5476EE75BF}"/>
   </bookViews>
   <sheets>
-    <sheet name="lesson_1_Sensitivity Report" sheetId="3" r:id="rId1"/>
-    <sheet name="lesson_1" sheetId="1" r:id="rId2"/>
-    <sheet name="lesson_2" sheetId="4" r:id="rId3"/>
+    <sheet name="ch_1_1_Sensitivity Report" sheetId="3" r:id="rId1"/>
+    <sheet name="ch_1_1" sheetId="1" r:id="rId2"/>
+    <sheet name="ch_1_2" sheetId="5" r:id="rId3"/>
+    <sheet name="ch_2_1_Sensitivity Report 1" sheetId="7" r:id="rId4"/>
+    <sheet name="ch_2_1" sheetId="4" r:id="rId5"/>
+    <sheet name="Sensitivity Report 1" sheetId="10" r:id="rId6"/>
+    <sheet name="ch_2_2" sheetId="9" r:id="rId7"/>
+    <sheet name="Sensitivity Report 3" sheetId="14" r:id="rId8"/>
+    <sheet name="ch_2_3" sheetId="11" r:id="rId9"/>
+    <sheet name="ch_3_1" sheetId="15" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="solver_adj" localSheetId="1" hidden="1">lesson_1!$L$2:$N$2</definedName>
-    <definedName name="solver_adj" localSheetId="2" hidden="1">lesson_2!$B$2:$I$3</definedName>
+    <definedName name="solver_adj" localSheetId="1" hidden="1">ch_1_1!$L$2:$N$2</definedName>
+    <definedName name="solver_adj" localSheetId="2" hidden="1">ch_1_2!$B$2:$C$2</definedName>
+    <definedName name="solver_adj" localSheetId="4" hidden="1">ch_2_1!$B$2:$I$3</definedName>
+    <definedName name="solver_adj" localSheetId="6" hidden="1">ch_2_2!$B$2:$C$2</definedName>
+    <definedName name="solver_adj" localSheetId="8" hidden="1">ch_2_3!$B$2:$E$4</definedName>
+    <definedName name="solver_adj" localSheetId="9" hidden="1">ch_3_1!$B$2:$H$2</definedName>
     <definedName name="solver_cvg" localSheetId="1" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="2" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="4" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="6" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="8" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="9" hidden="1">0.0001</definedName>
     <definedName name="solver_drv" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="4" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="6" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="8" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="9" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_eng" localSheetId="4" hidden="1">2</definedName>
+    <definedName name="solver_eng" localSheetId="6" hidden="1">2</definedName>
+    <definedName name="solver_eng" localSheetId="8" hidden="1">2</definedName>
+    <definedName name="solver_eng" localSheetId="9" hidden="1">2</definedName>
     <definedName name="solver_est" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="4" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="6" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="8" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="9" hidden="1">1</definedName>
     <definedName name="solver_itr" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="2" hidden="1">2147483647</definedName>
-    <definedName name="solver_lhs1" localSheetId="1" hidden="1">lesson_1!$B$3:$B$5</definedName>
-    <definedName name="solver_lhs1" localSheetId="2" hidden="1">lesson_2!$B$4:$I$4</definedName>
-    <definedName name="solver_lhs2" localSheetId="1" hidden="1">lesson_1!$B$8:$B$9</definedName>
-    <definedName name="solver_lhs2" localSheetId="2" hidden="1">lesson_2!$O$2:$O$4</definedName>
+    <definedName name="solver_itr" localSheetId="4" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="6" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="8" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="9" hidden="1">2147483647</definedName>
+    <definedName name="solver_lhs1" localSheetId="1" hidden="1">ch_1_1!$B$3:$B$5</definedName>
+    <definedName name="solver_lhs1" localSheetId="2" hidden="1">ch_1_2!$F$5:$F$7</definedName>
+    <definedName name="solver_lhs1" localSheetId="4" hidden="1">ch_2_1!$B$4:$I$4</definedName>
+    <definedName name="solver_lhs1" localSheetId="6" hidden="1">ch_2_2!$E$4:$E$6</definedName>
+    <definedName name="solver_lhs1" localSheetId="8" hidden="1">ch_2_3!$G$2:$G$6</definedName>
+    <definedName name="solver_lhs1" localSheetId="9" hidden="1">ch_3_1!$B$2:$H$2</definedName>
+    <definedName name="solver_lhs2" localSheetId="1" hidden="1">ch_1_1!$B$8:$B$9</definedName>
+    <definedName name="solver_lhs2" localSheetId="4" hidden="1">ch_2_1!$O$2:$O$4</definedName>
+    <definedName name="solver_lhs2" localSheetId="9" hidden="1">ch_3_1!$J$3</definedName>
     <definedName name="solver_mip" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="2" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="4" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="6" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="8" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="9" hidden="1">2147483647</definedName>
     <definedName name="solver_mni" localSheetId="1" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="2" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="4" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="6" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="8" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="9" hidden="1">30</definedName>
     <definedName name="solver_mrt" localSheetId="1" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="2" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="4" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="6" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="8" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="9" hidden="1">0.075</definedName>
     <definedName name="solver_msl" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="4" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="6" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="8" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="9" hidden="1">2</definedName>
     <definedName name="solver_neg" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="4" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="6" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="8" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="9" hidden="1">1</definedName>
     <definedName name="solver_nod" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="2" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="4" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="6" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="8" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="9" hidden="1">2147483647</definedName>
     <definedName name="solver_num" localSheetId="1" hidden="1">2</definedName>
-    <definedName name="solver_num" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_num" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_num" localSheetId="4" hidden="1">2</definedName>
+    <definedName name="solver_num" localSheetId="6" hidden="1">1</definedName>
+    <definedName name="solver_num" localSheetId="8" hidden="1">1</definedName>
+    <definedName name="solver_num" localSheetId="9" hidden="1">2</definedName>
     <definedName name="solver_nwt" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="2" hidden="1">1</definedName>
-    <definedName name="solver_opt" localSheetId="1" hidden="1">lesson_1!$B$17</definedName>
-    <definedName name="solver_opt" localSheetId="2" hidden="1">lesson_2!$J$22</definedName>
+    <definedName name="solver_nwt" localSheetId="4" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="6" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="8" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="9" hidden="1">1</definedName>
+    <definedName name="solver_opt" localSheetId="1" hidden="1">ch_1_1!$B$17</definedName>
+    <definedName name="solver_opt" localSheetId="2" hidden="1">ch_1_2!$B$10</definedName>
+    <definedName name="solver_opt" localSheetId="4" hidden="1">ch_2_1!$J$22</definedName>
+    <definedName name="solver_opt" localSheetId="6" hidden="1">ch_2_2!$B$10</definedName>
+    <definedName name="solver_opt" localSheetId="8" hidden="1">ch_2_3!$B$14</definedName>
+    <definedName name="solver_opt" localSheetId="9" hidden="1">ch_3_1!$B$8</definedName>
     <definedName name="solver_pre" localSheetId="1" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="2" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="4" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="6" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="8" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="9" hidden="1">0.000001</definedName>
     <definedName name="solver_rbv" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="4" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="6" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="8" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="9" hidden="1">2</definedName>
     <definedName name="solver_rel1" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_rel1" localSheetId="4" hidden="1">1</definedName>
+    <definedName name="solver_rel1" localSheetId="6" hidden="1">3</definedName>
+    <definedName name="solver_rel1" localSheetId="8" hidden="1">1</definedName>
+    <definedName name="solver_rel1" localSheetId="9" hidden="1">1</definedName>
     <definedName name="solver_rel2" localSheetId="1" hidden="1">1</definedName>
-    <definedName name="solver_rel2" localSheetId="2" hidden="1">1</definedName>
-    <definedName name="solver_rhs1" localSheetId="1" hidden="1">lesson_1!$D$3:$D$5</definedName>
-    <definedName name="solver_rhs1" localSheetId="2" hidden="1">lesson_2!$B$6:$I$6</definedName>
-    <definedName name="solver_rhs2" localSheetId="1" hidden="1">lesson_1!$D$8:$D$9</definedName>
-    <definedName name="solver_rhs2" localSheetId="2" hidden="1">lesson_2!$Q$2:$Q$4</definedName>
+    <definedName name="solver_rel2" localSheetId="4" hidden="1">1</definedName>
+    <definedName name="solver_rel2" localSheetId="9" hidden="1">1</definedName>
+    <definedName name="solver_rhs1" localSheetId="1" hidden="1">ch_1_1!$D$3:$D$5</definedName>
+    <definedName name="solver_rhs1" localSheetId="2" hidden="1">ch_1_2!$H$5:$H$7</definedName>
+    <definedName name="solver_rhs1" localSheetId="4" hidden="1">ch_2_1!$B$6:$I$6</definedName>
+    <definedName name="solver_rhs1" localSheetId="6" hidden="1">ch_2_2!$G$4:$G$6</definedName>
+    <definedName name="solver_rhs1" localSheetId="8" hidden="1">ch_2_3!$I$2:$I$6</definedName>
+    <definedName name="solver_rhs1" localSheetId="9" hidden="1">1</definedName>
+    <definedName name="solver_rhs2" localSheetId="1" hidden="1">ch_1_1!$D$8:$D$9</definedName>
+    <definedName name="solver_rhs2" localSheetId="4" hidden="1">ch_2_1!$Q$2:$Q$4</definedName>
+    <definedName name="solver_rhs2" localSheetId="9" hidden="1">ch_3_1!$L$3</definedName>
     <definedName name="solver_rlx" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="4" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="6" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="8" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="9" hidden="1">2</definedName>
     <definedName name="solver_rsd" localSheetId="1" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="2" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="4" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="6" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="8" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="9" hidden="1">0</definedName>
     <definedName name="solver_scl" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_scl" localSheetId="4" hidden="1">1</definedName>
+    <definedName name="solver_scl" localSheetId="6" hidden="1">1</definedName>
+    <definedName name="solver_scl" localSheetId="8" hidden="1">1</definedName>
+    <definedName name="solver_scl" localSheetId="9" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="4" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="6" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="8" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="9" hidden="1">2</definedName>
     <definedName name="solver_ssz" localSheetId="1" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="2" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="4" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="6" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="8" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="9" hidden="1">100</definedName>
     <definedName name="solver_tim" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="2" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="4" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="6" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="8" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="9" hidden="1">2147483647</definedName>
     <definedName name="solver_tol" localSheetId="1" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="2" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="4" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="6" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="8" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="9" hidden="1">0.01</definedName>
     <definedName name="solver_typ" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_typ" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_typ" localSheetId="4" hidden="1">1</definedName>
+    <definedName name="solver_typ" localSheetId="6" hidden="1">2</definedName>
+    <definedName name="solver_typ" localSheetId="8" hidden="1">1</definedName>
+    <definedName name="solver_typ" localSheetId="9" hidden="1">1</definedName>
     <definedName name="solver_val" localSheetId="1" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="2" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="4" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="6" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="8" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="9" hidden="1">0</definedName>
     <definedName name="solver_ver" localSheetId="1" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="2" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="4" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="6" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="8" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="9" hidden="1">3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -99,12 +229,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="154">
   <si>
     <t xml:space="preserve">basic </t>
   </si>
@@ -332,13 +465,247 @@
   </si>
   <si>
     <t>total_labor_line_2</t>
+  </si>
+  <si>
+    <t>var</t>
+  </si>
+  <si>
+    <t>rolltop</t>
+  </si>
+  <si>
+    <t>regular</t>
+  </si>
+  <si>
+    <t>oak</t>
+  </si>
+  <si>
+    <t>cedar</t>
+  </si>
+  <si>
+    <t>maple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;= </t>
+  </si>
+  <si>
+    <t>each profit</t>
+  </si>
+  <si>
+    <t>total profit</t>
+  </si>
+  <si>
+    <t>Worksheet: [temp_midterm.xlsx]ch_1_2</t>
+  </si>
+  <si>
+    <t>Report Created: 9/18/2026 8:24:49 AM</t>
+  </si>
+  <si>
+    <t>$B$2</t>
+  </si>
+  <si>
+    <t>var rolltop</t>
+  </si>
+  <si>
+    <t>$C$2</t>
+  </si>
+  <si>
+    <t>var regular</t>
+  </si>
+  <si>
+    <t>$F$5</t>
+  </si>
+  <si>
+    <t>$F$6</t>
+  </si>
+  <si>
+    <t>$F$7</t>
+  </si>
+  <si>
+    <t>pine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">x1 </t>
+  </si>
+  <si>
+    <t>x2</t>
+  </si>
+  <si>
+    <t>HIM</t>
+  </si>
+  <si>
+    <t>LIP</t>
+  </si>
+  <si>
+    <t>HIW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total_cost </t>
+  </si>
+  <si>
+    <t>&gt;=</t>
+  </si>
+  <si>
+    <t>Worksheet: [temp_midterm.xlsx]ch_2_2</t>
+  </si>
+  <si>
+    <t>Report Created: 9/18/2026 8:55:10 AM</t>
+  </si>
+  <si>
+    <t>$E$4</t>
+  </si>
+  <si>
+    <t>$E$5</t>
+  </si>
+  <si>
+    <t>$E$6</t>
+  </si>
+  <si>
+    <t>wheat</t>
+  </si>
+  <si>
+    <t>corn</t>
+  </si>
+  <si>
+    <t>plant</t>
+  </si>
+  <si>
+    <t>buy</t>
+  </si>
+  <si>
+    <t>yield</t>
+  </si>
+  <si>
+    <t xml:space="preserve">plant_cost </t>
+  </si>
+  <si>
+    <t>sell_price</t>
+  </si>
+  <si>
+    <t>buy_price</t>
+  </si>
+  <si>
+    <t>cost</t>
+  </si>
+  <si>
+    <t>Worksheet: [temp_midterm.xlsx]ch_2_3</t>
+  </si>
+  <si>
+    <t>plant wheat</t>
+  </si>
+  <si>
+    <t>plant corn</t>
+  </si>
+  <si>
+    <t>$D$2</t>
+  </si>
+  <si>
+    <t>$E$2</t>
+  </si>
+  <si>
+    <t>sell wheat</t>
+  </si>
+  <si>
+    <t>$C$3</t>
+  </si>
+  <si>
+    <t>sell corn</t>
+  </si>
+  <si>
+    <t>$D$3</t>
+  </si>
+  <si>
+    <t>$E$3</t>
+  </si>
+  <si>
+    <t>buy wheat</t>
+  </si>
+  <si>
+    <t>$C$4</t>
+  </si>
+  <si>
+    <t>buy corn</t>
+  </si>
+  <si>
+    <t>$D$4</t>
+  </si>
+  <si>
+    <t>$G$2</t>
+  </si>
+  <si>
+    <t>$G$3</t>
+  </si>
+  <si>
+    <t>$G$4</t>
+  </si>
+  <si>
+    <t>$G$5</t>
+  </si>
+  <si>
+    <t>$G$6</t>
+  </si>
+  <si>
+    <t>sugar_1</t>
+  </si>
+  <si>
+    <t>sugar_2</t>
+  </si>
+  <si>
+    <t>Report Created: 9/18/2026 9:39:27 AM</t>
+  </si>
+  <si>
+    <t>plant sugar_1</t>
+  </si>
+  <si>
+    <t>plant sugar_2</t>
+  </si>
+  <si>
+    <t>sell sugar_1</t>
+  </si>
+  <si>
+    <t>sell sugar_2</t>
+  </si>
+  <si>
+    <t>buy sugar_1</t>
+  </si>
+  <si>
+    <t>buy sugar_2</t>
+  </si>
+  <si>
+    <t>invest_1</t>
+  </si>
+  <si>
+    <t>invest_2</t>
+  </si>
+  <si>
+    <t>invest_3</t>
+  </si>
+  <si>
+    <t>invest_4</t>
+  </si>
+  <si>
+    <t>invest_5</t>
+  </si>
+  <si>
+    <t>invest_6</t>
+  </si>
+  <si>
+    <t>invest_7</t>
+  </si>
+  <si>
+    <t>return</t>
+  </si>
+  <si>
+    <t>percent_return</t>
+  </si>
+  <si>
+    <t>percet_port</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -364,6 +731,14 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="18"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -478,7 +853,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -504,6 +879,19 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1128,6 +1516,179 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{663BCE4E-1681-441F-8DE6-2742A5A66B94}">
+  <dimension ref="A1:L8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E1" t="s">
+        <v>147</v>
+      </c>
+      <c r="F1" t="s">
+        <v>148</v>
+      </c>
+      <c r="G1" t="s">
+        <v>149</v>
+      </c>
+      <c r="H1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B2" s="1">
+        <v>0.44000000000000028</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0</v>
+      </c>
+      <c r="J2" s="21"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="21"/>
+    </row>
+    <row r="3" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J3" s="4">
+        <f>SUMPRODUCT(B2:H2, B4:H4)</f>
+        <v>15.000000000000002</v>
+      </c>
+      <c r="K3" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="L3" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>2.4</v>
+      </c>
+      <c r="D4">
+        <v>3.5</v>
+      </c>
+      <c r="E4">
+        <v>5.9</v>
+      </c>
+      <c r="F4">
+        <v>6.9</v>
+      </c>
+      <c r="G4">
+        <v>4.5</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>151</v>
+      </c>
+      <c r="B5">
+        <v>5.6</v>
+      </c>
+      <c r="C5">
+        <v>2.7</v>
+      </c>
+      <c r="D5">
+        <v>3.9</v>
+      </c>
+      <c r="E5">
+        <v>6.8</v>
+      </c>
+      <c r="F5">
+        <v>7.7</v>
+      </c>
+      <c r="G5">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="H5">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>152</v>
+      </c>
+      <c r="B6">
+        <f>(B5-B4)/B4</f>
+        <v>0.11999999999999993</v>
+      </c>
+      <c r="C6">
+        <f t="shared" ref="C6:H6" si="0">(C5-C4)/C4</f>
+        <v>0.12500000000000011</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="0"/>
+        <v>0.11428571428571425</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="0"/>
+        <v>0.15254237288135583</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="0"/>
+        <v>0.11594202898550722</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="0"/>
+        <v>0.13333333333333325</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="0"/>
+        <v>9.9999999999999936E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B8" s="2">
+        <f>SUMPRODUCT(B2:H2,B5:H5)</f>
+        <v>17.064</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C764809-11C3-4C28-A777-28C2126910BA}">
   <dimension ref="A1:N18"/>
@@ -1368,6 +1929,384 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8ED592CD-86CB-44D4-97B2-69C4BC78FBD6}">
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B2" s="1">
+        <v>14.499999999999998</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0.25000000000000072</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B5">
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
+        <v>94</v>
+      </c>
+      <c r="F5">
+        <f>SUMPRODUCT(B5:C5,$B$2:$C$2)</f>
+        <v>150</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="H5" s="3">
+        <f>200-50</f>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>16</v>
+      </c>
+      <c r="E6" t="s">
+        <v>80</v>
+      </c>
+      <c r="F6">
+        <f t="shared" ref="F6:F7" si="0">SUMPRODUCT(B6:C6,$B$2:$C$2)</f>
+        <v>62.000000000000007</v>
+      </c>
+      <c r="G6" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="H6" s="3">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>81</v>
+      </c>
+      <c r="B7">
+        <v>15</v>
+      </c>
+      <c r="C7">
+        <v>10</v>
+      </c>
+      <c r="E7" t="s">
+        <v>81</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="0"/>
+        <v>219.99999999999997</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="H7" s="3">
+        <f>220</f>
+        <v>220</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9">
+        <v>115</v>
+      </c>
+      <c r="C9">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>84</v>
+      </c>
+      <c r="B10" s="2">
+        <f>SUMPRODUCT(B2:C2,B9:C9)</f>
+        <v>1689.9999999999998</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5FE0CDD-01E0-4554-B5DF-18449D62CE2F}">
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="2.28515625" customWidth="1"/>
+    <col min="2" max="2" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7" s="19" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" s="20" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B9" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="D9" s="17">
+        <v>12</v>
+      </c>
+      <c r="E9" s="17">
+        <v>0</v>
+      </c>
+      <c r="F9" s="17">
+        <v>115</v>
+      </c>
+      <c r="G9" s="17">
+        <v>20.000000000000014</v>
+      </c>
+      <c r="H9" s="17">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="D10" s="18">
+        <v>4.0000000000000009</v>
+      </c>
+      <c r="E10" s="18">
+        <v>0</v>
+      </c>
+      <c r="F10" s="18">
+        <v>90</v>
+      </c>
+      <c r="G10" s="18">
+        <v>140</v>
+      </c>
+      <c r="H10" s="18">
+        <v>13.333333333333343</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="G13" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="H13" s="19" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="F14" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="G14" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="H14" s="20" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B15" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="D15" s="17">
+        <v>200</v>
+      </c>
+      <c r="E15" s="17">
+        <v>1.0000000000000007</v>
+      </c>
+      <c r="F15" s="17">
+        <v>200</v>
+      </c>
+      <c r="G15" s="17">
+        <v>15.999999999999993</v>
+      </c>
+      <c r="H15" s="17">
+        <v>53.33333333333335</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B16" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="D16" s="17">
+        <v>112.00000000000001</v>
+      </c>
+      <c r="E16" s="17">
+        <v>0</v>
+      </c>
+      <c r="F16" s="17">
+        <v>128</v>
+      </c>
+      <c r="G16" s="17">
+        <v>1E+30</v>
+      </c>
+      <c r="H16" s="17">
+        <v>15.999999999999993</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="C17" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="D17" s="18">
+        <v>220</v>
+      </c>
+      <c r="E17" s="18">
+        <v>7</v>
+      </c>
+      <c r="F17" s="18">
+        <v>220</v>
+      </c>
+      <c r="G17" s="18">
+        <v>80.000000000000028</v>
+      </c>
+      <c r="H17" s="18">
+        <v>39.999999999999986</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{383545CA-8758-49BF-B735-9E5D292B0FF0}">
   <dimension ref="A1:Q22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1499,7 +2438,7 @@
         <v>1500</v>
       </c>
       <c r="C4" s="12">
-        <f t="shared" ref="C4:I4" si="0">SUM(C2:C3)</f>
+        <f t="shared" ref="C4:H4" si="0">SUM(C2:C3)</f>
         <v>0</v>
       </c>
       <c r="D4" s="12">
@@ -2009,6 +2948,1109 @@
         <v>615812.5</v>
       </c>
       <c r="M22" s="14"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3F00459-BDC7-4CA1-B921-E7450FB211D5}">
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="2.28515625" customWidth="1"/>
+    <col min="2" max="2" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7" s="19" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" s="20" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B9" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="D9" s="17">
+        <v>4.3333333333333339</v>
+      </c>
+      <c r="E9" s="17">
+        <v>0</v>
+      </c>
+      <c r="F9" s="17">
+        <v>100</v>
+      </c>
+      <c r="G9" s="17">
+        <v>20.000000000000004</v>
+      </c>
+      <c r="H9" s="17">
+        <v>24.999999999999996</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="D10" s="18">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="E10" s="18">
+        <v>0</v>
+      </c>
+      <c r="F10" s="18">
+        <v>60</v>
+      </c>
+      <c r="G10" s="18">
+        <v>20</v>
+      </c>
+      <c r="H10" s="18">
+        <v>10.000000000000002</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="G13" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="H13" s="19" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="F14" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="G14" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="H14" s="20" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B15" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="D15" s="17">
+        <v>40.333333333333336</v>
+      </c>
+      <c r="E15" s="17">
+        <v>0</v>
+      </c>
+      <c r="F15" s="17">
+        <v>40</v>
+      </c>
+      <c r="G15" s="17">
+        <v>0.33333333333333748</v>
+      </c>
+      <c r="H15" s="17">
+        <v>1E+30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B16" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="D16" s="17">
+        <v>60.000000000000007</v>
+      </c>
+      <c r="E16" s="17">
+        <v>6.6666666666666661</v>
+      </c>
+      <c r="F16" s="17">
+        <v>60</v>
+      </c>
+      <c r="G16" s="17">
+        <v>10</v>
+      </c>
+      <c r="H16" s="17">
+        <v>0.38461538461538941</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="C17" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="D17" s="18">
+        <v>35</v>
+      </c>
+      <c r="E17" s="18">
+        <v>6.6666666666666679</v>
+      </c>
+      <c r="F17" s="18">
+        <v>35</v>
+      </c>
+      <c r="G17" s="18">
+        <v>1.0000000000000127</v>
+      </c>
+      <c r="H17" s="18">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0E7EC63-9A54-4477-BBCB-EE695471FCE4}">
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B2" s="1">
+        <v>4.3333333333333339</v>
+      </c>
+      <c r="C2" s="1">
+        <v>3.333333333333333</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B4">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="E4" s="4">
+        <f>SUMPRODUCT(B4:C4,$B$2:$C$2)</f>
+        <v>40.333333333333336</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="G4" s="3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B5">
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="E5" s="4">
+        <f t="shared" ref="E5:E6" si="0">SUMPRODUCT(B5:C5,$B$2:$C$2)</f>
+        <v>60.000000000000007</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="G5" s="3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="E6" s="4">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="G6" s="3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F7" s="15"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9">
+        <v>100</v>
+      </c>
+      <c r="C9">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>100</v>
+      </c>
+      <c r="B10" s="2">
+        <f>SUMPRODUCT(B9:C9,B2:C2)</f>
+        <v>633.33333333333337</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5C7CA85-32B5-46DC-AA68-134E32F2459F}">
+  <dimension ref="A1:H29"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="2.28515625" customWidth="1"/>
+    <col min="2" max="2" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7" s="19" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" s="20" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B9" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="D9" s="17">
+        <v>120</v>
+      </c>
+      <c r="E9" s="17">
+        <v>0</v>
+      </c>
+      <c r="F9" s="17">
+        <v>-150</v>
+      </c>
+      <c r="G9" s="17">
+        <v>125.00000000000006</v>
+      </c>
+      <c r="H9" s="17">
+        <v>54.999999999999943</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B10" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="D10" s="17">
+        <v>80</v>
+      </c>
+      <c r="E10" s="17">
+        <v>0</v>
+      </c>
+      <c r="F10" s="17">
+        <v>-230</v>
+      </c>
+      <c r="G10" s="17">
+        <v>54.999999999999943</v>
+      </c>
+      <c r="H10" s="17">
+        <v>125.00000000000006</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B11" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="D11" s="17">
+        <v>300</v>
+      </c>
+      <c r="E11" s="17">
+        <v>0</v>
+      </c>
+      <c r="F11" s="17">
+        <v>-260</v>
+      </c>
+      <c r="G11" s="17">
+        <v>335</v>
+      </c>
+      <c r="H11" s="17">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B12" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="D12" s="17">
+        <v>0</v>
+      </c>
+      <c r="E12" s="17">
+        <v>0</v>
+      </c>
+      <c r="F12" s="17">
+        <v>0</v>
+      </c>
+      <c r="G12" s="17">
+        <v>0</v>
+      </c>
+      <c r="H12" s="17">
+        <v>1E+30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B13" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="D13" s="17">
+        <v>100</v>
+      </c>
+      <c r="E13" s="17">
+        <v>0</v>
+      </c>
+      <c r="F13" s="17">
+        <v>170</v>
+      </c>
+      <c r="G13" s="17">
+        <v>50.000000000000028</v>
+      </c>
+      <c r="H13" s="17">
+        <v>21.999999999999979</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B14" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="D14" s="17">
+        <v>0</v>
+      </c>
+      <c r="E14" s="17">
+        <v>-18.333333333333314</v>
+      </c>
+      <c r="F14" s="17">
+        <v>150</v>
+      </c>
+      <c r="G14" s="17">
+        <v>18.333333333333314</v>
+      </c>
+      <c r="H14" s="17">
+        <v>1E+30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B15" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="D15" s="17">
+        <v>6000</v>
+      </c>
+      <c r="E15" s="17">
+        <v>0</v>
+      </c>
+      <c r="F15" s="17">
+        <v>36</v>
+      </c>
+      <c r="G15" s="17">
+        <v>1E+30</v>
+      </c>
+      <c r="H15" s="17">
+        <v>9.25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B16" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>141</v>
+      </c>
+      <c r="D16" s="17">
+        <v>0</v>
+      </c>
+      <c r="E16" s="17">
+        <v>-16.75</v>
+      </c>
+      <c r="F16" s="17">
+        <v>10</v>
+      </c>
+      <c r="G16" s="17">
+        <v>16.75</v>
+      </c>
+      <c r="H16" s="17">
+        <v>1E+30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="D17" s="17">
+        <v>0</v>
+      </c>
+      <c r="E17" s="17">
+        <v>-68</v>
+      </c>
+      <c r="F17" s="17">
+        <v>-238</v>
+      </c>
+      <c r="G17" s="17">
+        <v>68</v>
+      </c>
+      <c r="H17" s="17">
+        <v>1E+30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="D18" s="17">
+        <v>0</v>
+      </c>
+      <c r="E18" s="17">
+        <v>-41.666666666666686</v>
+      </c>
+      <c r="F18" s="17">
+        <v>-210</v>
+      </c>
+      <c r="G18" s="17">
+        <v>41.666666666666686</v>
+      </c>
+      <c r="H18" s="17">
+        <v>1E+30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="D19" s="17">
+        <v>0</v>
+      </c>
+      <c r="E19" s="17">
+        <v>0</v>
+      </c>
+      <c r="F19" s="17">
+        <v>0</v>
+      </c>
+      <c r="G19" s="17">
+        <v>0</v>
+      </c>
+      <c r="H19" s="17">
+        <v>1E+30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="D20" s="18">
+        <v>0</v>
+      </c>
+      <c r="E20" s="18">
+        <v>0</v>
+      </c>
+      <c r="F20" s="18">
+        <v>0</v>
+      </c>
+      <c r="G20" s="18">
+        <v>0</v>
+      </c>
+      <c r="H20" s="18">
+        <v>1E+30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="E23" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="F23" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="G23" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="H23" s="19" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="E24" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="F24" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="G24" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="H24" s="20" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="D25" s="17">
+        <v>500</v>
+      </c>
+      <c r="E25" s="17">
+        <v>275</v>
+      </c>
+      <c r="F25" s="17">
+        <v>0</v>
+      </c>
+      <c r="G25" s="17">
+        <v>1E+30</v>
+      </c>
+      <c r="H25" s="17">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="C26" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="D26" s="17">
+        <v>-200</v>
+      </c>
+      <c r="E26" s="17">
+        <v>170</v>
+      </c>
+      <c r="F26" s="17">
+        <v>0</v>
+      </c>
+      <c r="G26" s="17">
+        <v>1E+30</v>
+      </c>
+      <c r="H26" s="17">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="C27" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="D27" s="17">
+        <v>-240</v>
+      </c>
+      <c r="E27" s="17">
+        <v>168.33333333333331</v>
+      </c>
+      <c r="F27" s="17">
+        <v>0</v>
+      </c>
+      <c r="G27" s="17">
+        <v>240</v>
+      </c>
+      <c r="H27" s="17">
+        <v>120.00000000000001</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="C28" s="17"/>
+      <c r="D28" s="17">
+        <v>6000</v>
+      </c>
+      <c r="E28" s="17">
+        <v>26.75</v>
+      </c>
+      <c r="F28" s="17">
+        <v>0</v>
+      </c>
+      <c r="G28" s="17">
+        <v>6000</v>
+      </c>
+      <c r="H28" s="17">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="C29" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="D29" s="18">
+        <v>6000</v>
+      </c>
+      <c r="E29" s="18">
+        <v>9.25</v>
+      </c>
+      <c r="F29" s="18">
+        <v>0</v>
+      </c>
+      <c r="G29" s="18">
+        <v>800</v>
+      </c>
+      <c r="H29" s="18">
+        <v>6000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{252464CB-7E70-452A-88CC-BE24E3E0118E}">
+  <dimension ref="A1:I14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" customWidth="1"/>
+    <col min="3" max="3" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.42578125" customWidth="1"/>
+    <col min="8" max="8" width="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B2" s="1">
+        <v>120</v>
+      </c>
+      <c r="C2" s="1">
+        <v>80</v>
+      </c>
+      <c r="D2" s="1">
+        <v>300</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <f>SUM(B2:D2)</f>
+        <v>500</v>
+      </c>
+      <c r="H2" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="I2" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B3" s="1">
+        <v>100</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0</v>
+      </c>
+      <c r="D3" s="1">
+        <v>6000</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <f>-(B2 * B6) - B4 + B3</f>
+        <v>-200</v>
+      </c>
+      <c r="H3" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" s="3">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B4" s="1">
+        <v>0</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <f>-(C2*C6) - C4 + C3</f>
+        <v>-240</v>
+      </c>
+      <c r="H4" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="I4" s="3">
+        <v>-240</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G5">
+        <f>D3 + E3</f>
+        <v>6000</v>
+      </c>
+      <c r="H5" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="I5" s="3">
+        <f>D2*D6</f>
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>111</v>
+      </c>
+      <c r="B6">
+        <v>2.5</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>20</v>
+      </c>
+      <c r="G6">
+        <f>$D$3</f>
+        <v>6000</v>
+      </c>
+      <c r="H6" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="I6" s="3">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>112</v>
+      </c>
+      <c r="B7" s="21">
+        <v>150</v>
+      </c>
+      <c r="C7" s="21">
+        <v>230</v>
+      </c>
+      <c r="D7" s="21">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>113</v>
+      </c>
+      <c r="B8" s="21">
+        <v>170</v>
+      </c>
+      <c r="C8" s="21">
+        <v>150</v>
+      </c>
+      <c r="D8" s="21">
+        <v>36</v>
+      </c>
+      <c r="E8" s="21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>114</v>
+      </c>
+      <c r="B9" s="21">
+        <v>238</v>
+      </c>
+      <c r="C9" s="21">
+        <v>210</v>
+      </c>
+      <c r="D9" s="21"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11">
+        <f>SUMPRODUCT(B3:E3,B8:E8)</f>
+        <v>233000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>110</v>
+      </c>
+      <c r="B12">
+        <f>SUMPRODUCT(B4:C4,B9:C9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>115</v>
+      </c>
+      <c r="B13">
+        <f>SUMPRODUCT(B7:D7,B2:D2)</f>
+        <v>114400</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>69</v>
+      </c>
+      <c r="B14" s="22">
+        <f>B11 - B12 - B13</f>
+        <v>118600</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/class_excel/temp_midterm.xlsx
+++ b/class_excel/temp_midterm.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\DADS7102\class_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3CE1B8C-61F3-436E-965F-F24741E7636A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{709CDB1A-C542-4C86-8419-C52931AC18FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="7" xr2:uid="{962D6ACA-47B2-4C7E-82D5-0F5476EE75BF}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="3" xr2:uid="{962D6ACA-47B2-4C7E-82D5-0F5476EE75BF}"/>
   </bookViews>
   <sheets>
     <sheet name="ch_1_1" sheetId="1" r:id="rId1"/>
@@ -21,8 +21,27 @@
     <sheet name="ch_2_4" sheetId="15" r:id="rId6"/>
     <sheet name="ch_3_1" sheetId="16" r:id="rId7"/>
     <sheet name="ch_3_2" sheetId="17" r:id="rId8"/>
+    <sheet name="ch_3_3" sheetId="18" r:id="rId9"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId10"/>
+  </externalReferences>
   <definedNames>
+    <definedName name="AFinish">[1]project!$K$6</definedName>
+    <definedName name="BFinish">[1]project!$K$7</definedName>
+    <definedName name="CFinish">[1]project!$K$8</definedName>
+    <definedName name="DFinish">[1]project!$K$9</definedName>
+    <definedName name="EFinish">[1]project!$K$10</definedName>
+    <definedName name="FFinish">[1]project!$K$11</definedName>
+    <definedName name="GFinish">[1]project!$K$12</definedName>
+    <definedName name="HFinish">[1]project!$K$13</definedName>
+    <definedName name="IFinish">[1]project!$K$14</definedName>
+    <definedName name="invLevels">[1]CapitalBudget!$B$10:$H$10</definedName>
+    <definedName name="JFinish">[1]project!$K$15</definedName>
+    <definedName name="KFinish">[1]project!$K$16</definedName>
+    <definedName name="LFinish">[1]project!$K$17</definedName>
+    <definedName name="MFinish">[1]project!$K$18</definedName>
+    <definedName name="NFinish">[1]project!$K$19</definedName>
     <definedName name="solver_adj" localSheetId="0" hidden="1">ch_1_1!$L$2:$N$2</definedName>
     <definedName name="solver_adj" localSheetId="1" hidden="1">ch_1_2!$B$2:$C$2</definedName>
     <definedName name="solver_adj" localSheetId="2" hidden="1">ch_2_1!$B$2:$I$3</definedName>
@@ -31,6 +50,7 @@
     <definedName name="solver_adj" localSheetId="5" hidden="1">ch_2_4!$B$2:$H$2</definedName>
     <definedName name="solver_adj" localSheetId="6" hidden="1">ch_3_1!$D$3:$D$28</definedName>
     <definedName name="solver_adj" localSheetId="7" hidden="1">ch_3_2!$D$3:$D$8</definedName>
+    <definedName name="solver_adj" localSheetId="8" hidden="1">ch_3_3!$B$12:$G$12</definedName>
     <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="1" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="2" hidden="1">0.0001</definedName>
@@ -39,6 +59,7 @@
     <definedName name="solver_cvg" localSheetId="5" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="6" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="7" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="8" hidden="1">0.0001</definedName>
     <definedName name="solver_drv" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="2" hidden="1">1</definedName>
@@ -47,6 +68,7 @@
     <definedName name="solver_drv" localSheetId="5" hidden="1">2</definedName>
     <definedName name="solver_drv" localSheetId="6" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="7" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="8" hidden="1">1</definedName>
     <definedName name="solver_eng" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="2" hidden="1">2</definedName>
@@ -55,6 +77,7 @@
     <definedName name="solver_eng" localSheetId="5" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="6" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="7" hidden="1">2</definedName>
+    <definedName name="solver_eng" localSheetId="8" hidden="1">2</definedName>
     <definedName name="solver_est" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="2" hidden="1">1</definedName>
@@ -63,6 +86,7 @@
     <definedName name="solver_est" localSheetId="5" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="6" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="7" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="8" hidden="1">1</definedName>
     <definedName name="solver_itr" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="2" hidden="1">2147483647</definedName>
@@ -71,6 +95,7 @@
     <definedName name="solver_itr" localSheetId="5" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="6" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="7" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="8" hidden="1">2147483647</definedName>
     <definedName name="solver_lhs1" localSheetId="0" hidden="1">ch_1_1!$B$3:$B$5</definedName>
     <definedName name="solver_lhs1" localSheetId="1" hidden="1">ch_1_2!$F$5:$F$7</definedName>
     <definedName name="solver_lhs1" localSheetId="2" hidden="1">ch_2_1!$B$4:$I$4</definedName>
@@ -79,11 +104,14 @@
     <definedName name="solver_lhs1" localSheetId="5" hidden="1">ch_2_4!$B$2:$H$2</definedName>
     <definedName name="solver_lhs1" localSheetId="6" hidden="1">ch_3_1!$D$3:$D$28</definedName>
     <definedName name="solver_lhs1" localSheetId="7" hidden="1">ch_3_2!$D$3:$D$8</definedName>
+    <definedName name="solver_lhs1" localSheetId="8" hidden="1">ch_3_3!$B$12:$G$12</definedName>
     <definedName name="solver_lhs2" localSheetId="0" hidden="1">ch_1_1!$B$8:$B$9</definedName>
     <definedName name="solver_lhs2" localSheetId="2" hidden="1">ch_2_1!$O$2:$O$4</definedName>
     <definedName name="solver_lhs2" localSheetId="5" hidden="1">ch_2_4!$J$3</definedName>
     <definedName name="solver_lhs2" localSheetId="6" hidden="1">ch_3_1!$K$3:$K$9</definedName>
     <definedName name="solver_lhs2" localSheetId="7" hidden="1">ch_3_2!$K$3:$K$7</definedName>
+    <definedName name="solver_lhs2" localSheetId="8" hidden="1">ch_3_3!$B$20:$G$20</definedName>
+    <definedName name="solver_lhs3" localSheetId="8" hidden="1">ch_3_3!$B$20:$G$20</definedName>
     <definedName name="solver_mip" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="2" hidden="1">2147483647</definedName>
@@ -92,6 +120,7 @@
     <definedName name="solver_mip" localSheetId="5" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="6" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="7" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="8" hidden="1">2147483647</definedName>
     <definedName name="solver_mni" localSheetId="0" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="1" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="2" hidden="1">30</definedName>
@@ -100,6 +129,7 @@
     <definedName name="solver_mni" localSheetId="5" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="6" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="7" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="8" hidden="1">30</definedName>
     <definedName name="solver_mrt" localSheetId="0" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="1" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="2" hidden="1">0.075</definedName>
@@ -108,6 +138,7 @@
     <definedName name="solver_mrt" localSheetId="5" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="6" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="7" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="8" hidden="1">0.075</definedName>
     <definedName name="solver_msl" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="2" hidden="1">2</definedName>
@@ -116,6 +147,7 @@
     <definedName name="solver_msl" localSheetId="5" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="6" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="7" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="8" hidden="1">2</definedName>
     <definedName name="solver_neg" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="2" hidden="1">1</definedName>
@@ -124,6 +156,7 @@
     <definedName name="solver_neg" localSheetId="5" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="6" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="7" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="8" hidden="1">1</definedName>
     <definedName name="solver_nod" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="2" hidden="1">2147483647</definedName>
@@ -132,6 +165,7 @@
     <definedName name="solver_nod" localSheetId="5" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="6" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="7" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="8" hidden="1">2147483647</definedName>
     <definedName name="solver_num" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_num" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_num" localSheetId="2" hidden="1">2</definedName>
@@ -140,6 +174,7 @@
     <definedName name="solver_num" localSheetId="5" hidden="1">2</definedName>
     <definedName name="solver_num" localSheetId="6" hidden="1">2</definedName>
     <definedName name="solver_num" localSheetId="7" hidden="1">2</definedName>
+    <definedName name="solver_num" localSheetId="8" hidden="1">3</definedName>
     <definedName name="solver_nwt" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="2" hidden="1">1</definedName>
@@ -148,6 +183,7 @@
     <definedName name="solver_nwt" localSheetId="5" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="6" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="7" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="8" hidden="1">1</definedName>
     <definedName name="solver_opt" localSheetId="0" hidden="1">ch_1_1!$B$17</definedName>
     <definedName name="solver_opt" localSheetId="1" hidden="1">ch_1_2!$B$10</definedName>
     <definedName name="solver_opt" localSheetId="2" hidden="1">ch_2_1!$J$22</definedName>
@@ -156,6 +192,7 @@
     <definedName name="solver_opt" localSheetId="5" hidden="1">ch_2_4!$B$8</definedName>
     <definedName name="solver_opt" localSheetId="6" hidden="1">ch_3_1!$I$11</definedName>
     <definedName name="solver_opt" localSheetId="7" hidden="1">ch_3_2!$B$11</definedName>
+    <definedName name="solver_opt" localSheetId="8" hidden="1">ch_3_3!$N$4</definedName>
     <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="1" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="2" hidden="1">0.000001</definedName>
@@ -164,6 +201,7 @@
     <definedName name="solver_pre" localSheetId="5" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="6" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="7" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="8" hidden="1">0.000001</definedName>
     <definedName name="solver_rbv" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="2" hidden="1">1</definedName>
@@ -172,6 +210,7 @@
     <definedName name="solver_rbv" localSheetId="5" hidden="1">2</definedName>
     <definedName name="solver_rbv" localSheetId="6" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="7" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="8" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="2" hidden="1">1</definedName>
@@ -180,11 +219,14 @@
     <definedName name="solver_rel1" localSheetId="5" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="6" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="7" hidden="1">1</definedName>
+    <definedName name="solver_rel1" localSheetId="8" hidden="1">1</definedName>
     <definedName name="solver_rel2" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rel2" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_rel2" localSheetId="5" hidden="1">1</definedName>
     <definedName name="solver_rel2" localSheetId="6" hidden="1">1</definedName>
     <definedName name="solver_rel2" localSheetId="7" hidden="1">1</definedName>
+    <definedName name="solver_rel2" localSheetId="8" hidden="1">1</definedName>
+    <definedName name="solver_rel3" localSheetId="8" hidden="1">3</definedName>
     <definedName name="solver_rhs1" localSheetId="0" hidden="1">ch_1_1!$D$3:$D$5</definedName>
     <definedName name="solver_rhs1" localSheetId="1" hidden="1">ch_1_2!$H$5:$H$7</definedName>
     <definedName name="solver_rhs1" localSheetId="2" hidden="1">ch_2_1!$B$6:$I$6</definedName>
@@ -193,11 +235,14 @@
     <definedName name="solver_rhs1" localSheetId="5" hidden="1">1</definedName>
     <definedName name="solver_rhs1" localSheetId="6" hidden="1">ch_3_1!$F$3:$F$28</definedName>
     <definedName name="solver_rhs1" localSheetId="7" hidden="1">ch_3_2!$F$3:$F$8</definedName>
+    <definedName name="solver_rhs1" localSheetId="8" hidden="1">ch_3_3!$B$14:$G$14</definedName>
     <definedName name="solver_rhs2" localSheetId="0" hidden="1">ch_1_1!$D$8:$D$9</definedName>
     <definedName name="solver_rhs2" localSheetId="2" hidden="1">ch_2_1!$Q$2:$Q$4</definedName>
     <definedName name="solver_rhs2" localSheetId="5" hidden="1">ch_2_4!$L$3</definedName>
     <definedName name="solver_rhs2" localSheetId="6" hidden="1">ch_3_1!$M$3:$M$9</definedName>
     <definedName name="solver_rhs2" localSheetId="7" hidden="1">ch_3_2!$M$3:$M$7</definedName>
+    <definedName name="solver_rhs2" localSheetId="8" hidden="1">ch_3_3!$B$22:$G$22</definedName>
+    <definedName name="solver_rhs3" localSheetId="8" hidden="1">0</definedName>
     <definedName name="solver_rlx" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="2" hidden="1">2</definedName>
@@ -206,6 +251,7 @@
     <definedName name="solver_rlx" localSheetId="5" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="6" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="7" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="8" hidden="1">2</definedName>
     <definedName name="solver_rsd" localSheetId="0" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="1" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="2" hidden="1">0</definedName>
@@ -214,6 +260,7 @@
     <definedName name="solver_rsd" localSheetId="5" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="6" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="7" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="8" hidden="1">0</definedName>
     <definedName name="solver_scl" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="2" hidden="1">1</definedName>
@@ -222,6 +269,7 @@
     <definedName name="solver_scl" localSheetId="5" hidden="1">2</definedName>
     <definedName name="solver_scl" localSheetId="6" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="7" hidden="1">1</definedName>
+    <definedName name="solver_scl" localSheetId="8" hidden="1">1</definedName>
     <definedName name="solver_sho" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="2" hidden="1">2</definedName>
@@ -230,6 +278,7 @@
     <definedName name="solver_sho" localSheetId="5" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="6" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="7" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="8" hidden="1">2</definedName>
     <definedName name="solver_ssz" localSheetId="0" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="1" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="2" hidden="1">100</definedName>
@@ -238,6 +287,7 @@
     <definedName name="solver_ssz" localSheetId="5" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="6" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="7" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="8" hidden="1">100</definedName>
     <definedName name="solver_tim" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="2" hidden="1">2147483647</definedName>
@@ -246,6 +296,7 @@
     <definedName name="solver_tim" localSheetId="5" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="6" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="7" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="8" hidden="1">2147483647</definedName>
     <definedName name="solver_tol" localSheetId="0" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="1" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="2" hidden="1">0.01</definedName>
@@ -254,6 +305,7 @@
     <definedName name="solver_tol" localSheetId="5" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="6" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="7" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="8" hidden="1">0.01</definedName>
     <definedName name="solver_typ" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_typ" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_typ" localSheetId="2" hidden="1">1</definedName>
@@ -262,6 +314,7 @@
     <definedName name="solver_typ" localSheetId="5" hidden="1">1</definedName>
     <definedName name="solver_typ" localSheetId="6" hidden="1">2</definedName>
     <definedName name="solver_typ" localSheetId="7" hidden="1">2</definedName>
+    <definedName name="solver_typ" localSheetId="8" hidden="1">2</definedName>
     <definedName name="solver_val" localSheetId="0" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="1" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="2" hidden="1">0</definedName>
@@ -270,6 +323,7 @@
     <definedName name="solver_val" localSheetId="5" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="6" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="7" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="8" hidden="1">0</definedName>
     <definedName name="solver_ver" localSheetId="0" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="1" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="2" hidden="1">3</definedName>
@@ -278,6 +332,7 @@
     <definedName name="solver_ver" localSheetId="5" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="6" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="7" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="8" hidden="1">3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -298,7 +353,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="121">
   <si>
     <t xml:space="preserve">basic </t>
   </si>
@@ -595,13 +650,86 @@
   </si>
   <si>
     <t>net</t>
+  </si>
+  <si>
+    <t>Multiperiod production model</t>
+  </si>
+  <si>
+    <t>Input data</t>
+  </si>
+  <si>
+    <t>Initial inventory</t>
+  </si>
+  <si>
+    <t>Holding cost as % of prod cost</t>
+  </si>
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>Production cost/unit</t>
+  </si>
+  <si>
+    <t>Holding cost/unit</t>
+  </si>
+  <si>
+    <t>Production plan (all quantities are in 100s of footballs)</t>
+  </si>
+  <si>
+    <t>Units produced</t>
+  </si>
+  <si>
+    <t>Production capacity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">produce capacity </t>
+  </si>
+  <si>
+    <t>On hand after production</t>
+  </si>
+  <si>
+    <t>Demand</t>
+  </si>
+  <si>
+    <t>Ending inventory</t>
+  </si>
+  <si>
+    <t>&gt;= 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">for shortage condition </t>
+  </si>
+  <si>
+    <t>Storage capacity</t>
+  </si>
+  <si>
+    <t>inventory condition</t>
+  </si>
+  <si>
+    <t>Summary of costs (all costs are in hundreds of dollars)</t>
+  </si>
+  <si>
+    <t>Totals</t>
+  </si>
+  <si>
+    <t>Holding cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production cost </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="5">
+    <numFmt numFmtId="187" formatCode="0.0000"/>
+    <numFmt numFmtId="188" formatCode="0.000"/>
+    <numFmt numFmtId="189" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
+    <numFmt numFmtId="190" formatCode="&quot;$&quot;#,##0.000_);\(&quot;$&quot;#,##0.000\)"/>
+    <numFmt numFmtId="191" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -620,8 +748,28 @@
       <name val="MS Sans Serif"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -664,6 +812,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -689,11 +843,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="189" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="191" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -705,8 +861,45 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="187" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="5" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="188" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="189" fontId="5" fillId="8" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="190" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="191" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="191" fontId="5" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="5" fillId="2" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="4">
+    <cellStyle name="Comma 2" xfId="3" xr:uid="{C9C68EFB-DC8B-4BBD-B2A4-694D3E58E673}"/>
+    <cellStyle name="Currency 2" xfId="2" xr:uid="{A9BDFC23-AFF7-42B4-B5DA-AB895D831664}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{67581A20-F69A-473C-AA9B-FD9B097B2E83}"/>
   </cellStyles>
@@ -721,6 +914,191 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Advertising "/>
+      <sheetName val="Advertising _Sensitivity Report"/>
+      <sheetName val="monopolist"/>
+      <sheetName val="Sensitivity Report 1"/>
+      <sheetName val="ProductMix"/>
+      <sheetName val="ProductMix_add_on"/>
+      <sheetName val="ProductMix2 Sensitivity"/>
+      <sheetName val="ProductMix2"/>
+      <sheetName val="LM_2"/>
+      <sheetName val="Dual"/>
+      <sheetName val="ProdPlanning"/>
+      <sheetName val="project"/>
+      <sheetName val="BlendingOil"/>
+      <sheetName val="Transport1"/>
+      <sheetName val="AssignmentProblem"/>
+      <sheetName val="BinPacking"/>
+      <sheetName val="cuttingStock"/>
+      <sheetName val="MCNF"/>
+      <sheetName val="RedBrandLogistics"/>
+      <sheetName val="HW3"/>
+      <sheetName val="set_covering_model"/>
+      <sheetName val="ShortestPath"/>
+      <sheetName val="Aggregate1"/>
+      <sheetName val="CapitalBudget"/>
+      <sheetName val="FixedCost"/>
+      <sheetName val="Hub"/>
+      <sheetName val="WorkerScheduling"/>
+      <sheetName val="Transport1-2"/>
+      <sheetName val="MMULT"/>
+      <sheetName val="MDETERM"/>
+      <sheetName val="Peakload"/>
+      <sheetName val="GameTheory"/>
+      <sheetName val="Portfolio"/>
+      <sheetName val="EOQ"/>
+      <sheetName val="SVM1"/>
+      <sheetName val="MLE"/>
+      <sheetName val="OLS"/>
+      <sheetName val="Location"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11">
+        <row r="6">
+          <cell r="K6">
+            <v>2</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="K7">
+            <v>6</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="K8">
+            <v>16</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="K9">
+            <v>22</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="K10">
+            <v>20</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="K11">
+            <v>23</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="K12">
+            <v>29</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="K13">
+            <v>38</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="K14">
+            <v>23</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="K15">
+            <v>29</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="K16">
+            <v>34</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="K17">
+            <v>34</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="K18">
+            <v>40</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="K19">
+            <v>40</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
+      <sheetData sheetId="22"/>
+      <sheetData sheetId="23">
+        <row r="10">
+          <cell r="B10">
+            <v>0</v>
+          </cell>
+          <cell r="C10">
+            <v>1</v>
+          </cell>
+          <cell r="D10">
+            <v>1</v>
+          </cell>
+          <cell r="E10">
+            <v>1</v>
+          </cell>
+          <cell r="F10">
+            <v>0</v>
+          </cell>
+          <cell r="G10">
+            <v>0</v>
+          </cell>
+          <cell r="H10">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="24"/>
+      <sheetData sheetId="25"/>
+      <sheetData sheetId="26"/>
+      <sheetData sheetId="27"/>
+      <sheetData sheetId="28"/>
+      <sheetData sheetId="29"/>
+      <sheetData sheetId="30"/>
+      <sheetData sheetId="31"/>
+      <sheetData sheetId="32"/>
+      <sheetData sheetId="33"/>
+      <sheetData sheetId="34"/>
+      <sheetData sheetId="35"/>
+      <sheetData sheetId="36"/>
+      <sheetData sheetId="37"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2695,11 +3073,11 @@
         <v>3</v>
       </c>
       <c r="I5">
-        <f t="shared" ref="I4:I9" si="1">SUMIF($A$3:$A$28,H5,$D$3:$D$28)</f>
+        <f t="shared" ref="I5:I9" si="1">SUMIF($A$3:$A$28,H5,$D$3:$D$28)</f>
         <v>280</v>
       </c>
       <c r="J5">
-        <f t="shared" ref="J4:J9" si="2">SUMIF($B$3:$B$28,H5,$D$3:$D$28)</f>
+        <f t="shared" ref="J5:J9" si="2">SUMIF($B$3:$B$28,H5,$D$3:$D$28)</f>
         <v>180</v>
       </c>
       <c r="K5" s="4">
@@ -3371,15 +3749,15 @@
         <v>2</v>
       </c>
       <c r="I4">
-        <f t="shared" ref="I4:I8" si="0">SUMIF($A$3:$A$8, H4, $D$3:$D$8)</f>
+        <f t="shared" ref="I4:I7" si="0">SUMIF($A$3:$A$8, H4, $D$3:$D$8)</f>
         <v>70</v>
       </c>
       <c r="J4">
-        <f t="shared" ref="J4:J8" si="1">SUMIF($B$3:$B$8, H4, $D$3:$D$8)</f>
+        <f t="shared" ref="J4:J7" si="1">SUMIF($B$3:$B$8, H4, $D$3:$D$8)</f>
         <v>0</v>
       </c>
       <c r="K4" s="4">
-        <f t="shared" ref="K4:K8" si="2">I4-J4</f>
+        <f t="shared" ref="K4:K7" si="2">I4-J4</f>
         <v>70</v>
       </c>
       <c r="L4" s="7" t="s">
@@ -3541,6 +3919,960 @@
       <c r="B11" s="2">
         <f>SUMPRODUCT(D3:D8,C3:C8)</f>
         <v>117000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E76634E4-7D20-4A0E-A622-BD83CBE54980}">
+  <dimension ref="A1:I28"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="28.5625" style="10" customWidth="1"/>
+    <col min="2" max="2" width="13.125" style="10" customWidth="1"/>
+    <col min="3" max="7" width="9" style="10"/>
+    <col min="8" max="8" width="12.875" style="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19" style="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="243" width="9" style="10"/>
+    <col min="244" max="244" width="26.5625" style="10" customWidth="1"/>
+    <col min="245" max="245" width="13.125" style="10" customWidth="1"/>
+    <col min="246" max="250" width="9" style="10"/>
+    <col min="251" max="251" width="10.875" style="10" customWidth="1"/>
+    <col min="252" max="252" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="253" max="253" width="10.5625" style="10" customWidth="1"/>
+    <col min="254" max="254" width="10.875" style="10" customWidth="1"/>
+    <col min="255" max="499" width="9" style="10"/>
+    <col min="500" max="500" width="26.5625" style="10" customWidth="1"/>
+    <col min="501" max="501" width="13.125" style="10" customWidth="1"/>
+    <col min="502" max="506" width="9" style="10"/>
+    <col min="507" max="507" width="10.875" style="10" customWidth="1"/>
+    <col min="508" max="508" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="509" max="509" width="10.5625" style="10" customWidth="1"/>
+    <col min="510" max="510" width="10.875" style="10" customWidth="1"/>
+    <col min="511" max="755" width="9" style="10"/>
+    <col min="756" max="756" width="26.5625" style="10" customWidth="1"/>
+    <col min="757" max="757" width="13.125" style="10" customWidth="1"/>
+    <col min="758" max="762" width="9" style="10"/>
+    <col min="763" max="763" width="10.875" style="10" customWidth="1"/>
+    <col min="764" max="764" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="765" max="765" width="10.5625" style="10" customWidth="1"/>
+    <col min="766" max="766" width="10.875" style="10" customWidth="1"/>
+    <col min="767" max="1011" width="9" style="10"/>
+    <col min="1012" max="1012" width="26.5625" style="10" customWidth="1"/>
+    <col min="1013" max="1013" width="13.125" style="10" customWidth="1"/>
+    <col min="1014" max="1018" width="9" style="10"/>
+    <col min="1019" max="1019" width="10.875" style="10" customWidth="1"/>
+    <col min="1020" max="1020" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="1021" max="1021" width="10.5625" style="10" customWidth="1"/>
+    <col min="1022" max="1022" width="10.875" style="10" customWidth="1"/>
+    <col min="1023" max="1267" width="9" style="10"/>
+    <col min="1268" max="1268" width="26.5625" style="10" customWidth="1"/>
+    <col min="1269" max="1269" width="13.125" style="10" customWidth="1"/>
+    <col min="1270" max="1274" width="9" style="10"/>
+    <col min="1275" max="1275" width="10.875" style="10" customWidth="1"/>
+    <col min="1276" max="1276" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="1277" max="1277" width="10.5625" style="10" customWidth="1"/>
+    <col min="1278" max="1278" width="10.875" style="10" customWidth="1"/>
+    <col min="1279" max="1523" width="9" style="10"/>
+    <col min="1524" max="1524" width="26.5625" style="10" customWidth="1"/>
+    <col min="1525" max="1525" width="13.125" style="10" customWidth="1"/>
+    <col min="1526" max="1530" width="9" style="10"/>
+    <col min="1531" max="1531" width="10.875" style="10" customWidth="1"/>
+    <col min="1532" max="1532" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="1533" max="1533" width="10.5625" style="10" customWidth="1"/>
+    <col min="1534" max="1534" width="10.875" style="10" customWidth="1"/>
+    <col min="1535" max="1779" width="9" style="10"/>
+    <col min="1780" max="1780" width="26.5625" style="10" customWidth="1"/>
+    <col min="1781" max="1781" width="13.125" style="10" customWidth="1"/>
+    <col min="1782" max="1786" width="9" style="10"/>
+    <col min="1787" max="1787" width="10.875" style="10" customWidth="1"/>
+    <col min="1788" max="1788" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="1789" max="1789" width="10.5625" style="10" customWidth="1"/>
+    <col min="1790" max="1790" width="10.875" style="10" customWidth="1"/>
+    <col min="1791" max="2035" width="9" style="10"/>
+    <col min="2036" max="2036" width="26.5625" style="10" customWidth="1"/>
+    <col min="2037" max="2037" width="13.125" style="10" customWidth="1"/>
+    <col min="2038" max="2042" width="9" style="10"/>
+    <col min="2043" max="2043" width="10.875" style="10" customWidth="1"/>
+    <col min="2044" max="2044" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="2045" max="2045" width="10.5625" style="10" customWidth="1"/>
+    <col min="2046" max="2046" width="10.875" style="10" customWidth="1"/>
+    <col min="2047" max="2291" width="9" style="10"/>
+    <col min="2292" max="2292" width="26.5625" style="10" customWidth="1"/>
+    <col min="2293" max="2293" width="13.125" style="10" customWidth="1"/>
+    <col min="2294" max="2298" width="9" style="10"/>
+    <col min="2299" max="2299" width="10.875" style="10" customWidth="1"/>
+    <col min="2300" max="2300" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="2301" max="2301" width="10.5625" style="10" customWidth="1"/>
+    <col min="2302" max="2302" width="10.875" style="10" customWidth="1"/>
+    <col min="2303" max="2547" width="9" style="10"/>
+    <col min="2548" max="2548" width="26.5625" style="10" customWidth="1"/>
+    <col min="2549" max="2549" width="13.125" style="10" customWidth="1"/>
+    <col min="2550" max="2554" width="9" style="10"/>
+    <col min="2555" max="2555" width="10.875" style="10" customWidth="1"/>
+    <col min="2556" max="2556" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="2557" max="2557" width="10.5625" style="10" customWidth="1"/>
+    <col min="2558" max="2558" width="10.875" style="10" customWidth="1"/>
+    <col min="2559" max="2803" width="9" style="10"/>
+    <col min="2804" max="2804" width="26.5625" style="10" customWidth="1"/>
+    <col min="2805" max="2805" width="13.125" style="10" customWidth="1"/>
+    <col min="2806" max="2810" width="9" style="10"/>
+    <col min="2811" max="2811" width="10.875" style="10" customWidth="1"/>
+    <col min="2812" max="2812" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="2813" max="2813" width="10.5625" style="10" customWidth="1"/>
+    <col min="2814" max="2814" width="10.875" style="10" customWidth="1"/>
+    <col min="2815" max="3059" width="9" style="10"/>
+    <col min="3060" max="3060" width="26.5625" style="10" customWidth="1"/>
+    <col min="3061" max="3061" width="13.125" style="10" customWidth="1"/>
+    <col min="3062" max="3066" width="9" style="10"/>
+    <col min="3067" max="3067" width="10.875" style="10" customWidth="1"/>
+    <col min="3068" max="3068" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="3069" max="3069" width="10.5625" style="10" customWidth="1"/>
+    <col min="3070" max="3070" width="10.875" style="10" customWidth="1"/>
+    <col min="3071" max="3315" width="9" style="10"/>
+    <col min="3316" max="3316" width="26.5625" style="10" customWidth="1"/>
+    <col min="3317" max="3317" width="13.125" style="10" customWidth="1"/>
+    <col min="3318" max="3322" width="9" style="10"/>
+    <col min="3323" max="3323" width="10.875" style="10" customWidth="1"/>
+    <col min="3324" max="3324" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="3325" max="3325" width="10.5625" style="10" customWidth="1"/>
+    <col min="3326" max="3326" width="10.875" style="10" customWidth="1"/>
+    <col min="3327" max="3571" width="9" style="10"/>
+    <col min="3572" max="3572" width="26.5625" style="10" customWidth="1"/>
+    <col min="3573" max="3573" width="13.125" style="10" customWidth="1"/>
+    <col min="3574" max="3578" width="9" style="10"/>
+    <col min="3579" max="3579" width="10.875" style="10" customWidth="1"/>
+    <col min="3580" max="3580" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="3581" max="3581" width="10.5625" style="10" customWidth="1"/>
+    <col min="3582" max="3582" width="10.875" style="10" customWidth="1"/>
+    <col min="3583" max="3827" width="9" style="10"/>
+    <col min="3828" max="3828" width="26.5625" style="10" customWidth="1"/>
+    <col min="3829" max="3829" width="13.125" style="10" customWidth="1"/>
+    <col min="3830" max="3834" width="9" style="10"/>
+    <col min="3835" max="3835" width="10.875" style="10" customWidth="1"/>
+    <col min="3836" max="3836" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="3837" max="3837" width="10.5625" style="10" customWidth="1"/>
+    <col min="3838" max="3838" width="10.875" style="10" customWidth="1"/>
+    <col min="3839" max="4083" width="9" style="10"/>
+    <col min="4084" max="4084" width="26.5625" style="10" customWidth="1"/>
+    <col min="4085" max="4085" width="13.125" style="10" customWidth="1"/>
+    <col min="4086" max="4090" width="9" style="10"/>
+    <col min="4091" max="4091" width="10.875" style="10" customWidth="1"/>
+    <col min="4092" max="4092" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="4093" max="4093" width="10.5625" style="10" customWidth="1"/>
+    <col min="4094" max="4094" width="10.875" style="10" customWidth="1"/>
+    <col min="4095" max="4339" width="9" style="10"/>
+    <col min="4340" max="4340" width="26.5625" style="10" customWidth="1"/>
+    <col min="4341" max="4341" width="13.125" style="10" customWidth="1"/>
+    <col min="4342" max="4346" width="9" style="10"/>
+    <col min="4347" max="4347" width="10.875" style="10" customWidth="1"/>
+    <col min="4348" max="4348" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="4349" max="4349" width="10.5625" style="10" customWidth="1"/>
+    <col min="4350" max="4350" width="10.875" style="10" customWidth="1"/>
+    <col min="4351" max="4595" width="9" style="10"/>
+    <col min="4596" max="4596" width="26.5625" style="10" customWidth="1"/>
+    <col min="4597" max="4597" width="13.125" style="10" customWidth="1"/>
+    <col min="4598" max="4602" width="9" style="10"/>
+    <col min="4603" max="4603" width="10.875" style="10" customWidth="1"/>
+    <col min="4604" max="4604" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="4605" max="4605" width="10.5625" style="10" customWidth="1"/>
+    <col min="4606" max="4606" width="10.875" style="10" customWidth="1"/>
+    <col min="4607" max="4851" width="9" style="10"/>
+    <col min="4852" max="4852" width="26.5625" style="10" customWidth="1"/>
+    <col min="4853" max="4853" width="13.125" style="10" customWidth="1"/>
+    <col min="4854" max="4858" width="9" style="10"/>
+    <col min="4859" max="4859" width="10.875" style="10" customWidth="1"/>
+    <col min="4860" max="4860" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="4861" max="4861" width="10.5625" style="10" customWidth="1"/>
+    <col min="4862" max="4862" width="10.875" style="10" customWidth="1"/>
+    <col min="4863" max="5107" width="9" style="10"/>
+    <col min="5108" max="5108" width="26.5625" style="10" customWidth="1"/>
+    <col min="5109" max="5109" width="13.125" style="10" customWidth="1"/>
+    <col min="5110" max="5114" width="9" style="10"/>
+    <col min="5115" max="5115" width="10.875" style="10" customWidth="1"/>
+    <col min="5116" max="5116" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="5117" max="5117" width="10.5625" style="10" customWidth="1"/>
+    <col min="5118" max="5118" width="10.875" style="10" customWidth="1"/>
+    <col min="5119" max="5363" width="9" style="10"/>
+    <col min="5364" max="5364" width="26.5625" style="10" customWidth="1"/>
+    <col min="5365" max="5365" width="13.125" style="10" customWidth="1"/>
+    <col min="5366" max="5370" width="9" style="10"/>
+    <col min="5371" max="5371" width="10.875" style="10" customWidth="1"/>
+    <col min="5372" max="5372" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="5373" max="5373" width="10.5625" style="10" customWidth="1"/>
+    <col min="5374" max="5374" width="10.875" style="10" customWidth="1"/>
+    <col min="5375" max="5619" width="9" style="10"/>
+    <col min="5620" max="5620" width="26.5625" style="10" customWidth="1"/>
+    <col min="5621" max="5621" width="13.125" style="10" customWidth="1"/>
+    <col min="5622" max="5626" width="9" style="10"/>
+    <col min="5627" max="5627" width="10.875" style="10" customWidth="1"/>
+    <col min="5628" max="5628" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="5629" max="5629" width="10.5625" style="10" customWidth="1"/>
+    <col min="5630" max="5630" width="10.875" style="10" customWidth="1"/>
+    <col min="5631" max="5875" width="9" style="10"/>
+    <col min="5876" max="5876" width="26.5625" style="10" customWidth="1"/>
+    <col min="5877" max="5877" width="13.125" style="10" customWidth="1"/>
+    <col min="5878" max="5882" width="9" style="10"/>
+    <col min="5883" max="5883" width="10.875" style="10" customWidth="1"/>
+    <col min="5884" max="5884" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="5885" max="5885" width="10.5625" style="10" customWidth="1"/>
+    <col min="5886" max="5886" width="10.875" style="10" customWidth="1"/>
+    <col min="5887" max="6131" width="9" style="10"/>
+    <col min="6132" max="6132" width="26.5625" style="10" customWidth="1"/>
+    <col min="6133" max="6133" width="13.125" style="10" customWidth="1"/>
+    <col min="6134" max="6138" width="9" style="10"/>
+    <col min="6139" max="6139" width="10.875" style="10" customWidth="1"/>
+    <col min="6140" max="6140" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="6141" max="6141" width="10.5625" style="10" customWidth="1"/>
+    <col min="6142" max="6142" width="10.875" style="10" customWidth="1"/>
+    <col min="6143" max="6387" width="9" style="10"/>
+    <col min="6388" max="6388" width="26.5625" style="10" customWidth="1"/>
+    <col min="6389" max="6389" width="13.125" style="10" customWidth="1"/>
+    <col min="6390" max="6394" width="9" style="10"/>
+    <col min="6395" max="6395" width="10.875" style="10" customWidth="1"/>
+    <col min="6396" max="6396" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="6397" max="6397" width="10.5625" style="10" customWidth="1"/>
+    <col min="6398" max="6398" width="10.875" style="10" customWidth="1"/>
+    <col min="6399" max="6643" width="9" style="10"/>
+    <col min="6644" max="6644" width="26.5625" style="10" customWidth="1"/>
+    <col min="6645" max="6645" width="13.125" style="10" customWidth="1"/>
+    <col min="6646" max="6650" width="9" style="10"/>
+    <col min="6651" max="6651" width="10.875" style="10" customWidth="1"/>
+    <col min="6652" max="6652" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="6653" max="6653" width="10.5625" style="10" customWidth="1"/>
+    <col min="6654" max="6654" width="10.875" style="10" customWidth="1"/>
+    <col min="6655" max="6899" width="9" style="10"/>
+    <col min="6900" max="6900" width="26.5625" style="10" customWidth="1"/>
+    <col min="6901" max="6901" width="13.125" style="10" customWidth="1"/>
+    <col min="6902" max="6906" width="9" style="10"/>
+    <col min="6907" max="6907" width="10.875" style="10" customWidth="1"/>
+    <col min="6908" max="6908" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="6909" max="6909" width="10.5625" style="10" customWidth="1"/>
+    <col min="6910" max="6910" width="10.875" style="10" customWidth="1"/>
+    <col min="6911" max="7155" width="9" style="10"/>
+    <col min="7156" max="7156" width="26.5625" style="10" customWidth="1"/>
+    <col min="7157" max="7157" width="13.125" style="10" customWidth="1"/>
+    <col min="7158" max="7162" width="9" style="10"/>
+    <col min="7163" max="7163" width="10.875" style="10" customWidth="1"/>
+    <col min="7164" max="7164" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="7165" max="7165" width="10.5625" style="10" customWidth="1"/>
+    <col min="7166" max="7166" width="10.875" style="10" customWidth="1"/>
+    <col min="7167" max="7411" width="9" style="10"/>
+    <col min="7412" max="7412" width="26.5625" style="10" customWidth="1"/>
+    <col min="7413" max="7413" width="13.125" style="10" customWidth="1"/>
+    <col min="7414" max="7418" width="9" style="10"/>
+    <col min="7419" max="7419" width="10.875" style="10" customWidth="1"/>
+    <col min="7420" max="7420" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="7421" max="7421" width="10.5625" style="10" customWidth="1"/>
+    <col min="7422" max="7422" width="10.875" style="10" customWidth="1"/>
+    <col min="7423" max="7667" width="9" style="10"/>
+    <col min="7668" max="7668" width="26.5625" style="10" customWidth="1"/>
+    <col min="7669" max="7669" width="13.125" style="10" customWidth="1"/>
+    <col min="7670" max="7674" width="9" style="10"/>
+    <col min="7675" max="7675" width="10.875" style="10" customWidth="1"/>
+    <col min="7676" max="7676" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="7677" max="7677" width="10.5625" style="10" customWidth="1"/>
+    <col min="7678" max="7678" width="10.875" style="10" customWidth="1"/>
+    <col min="7679" max="7923" width="9" style="10"/>
+    <col min="7924" max="7924" width="26.5625" style="10" customWidth="1"/>
+    <col min="7925" max="7925" width="13.125" style="10" customWidth="1"/>
+    <col min="7926" max="7930" width="9" style="10"/>
+    <col min="7931" max="7931" width="10.875" style="10" customWidth="1"/>
+    <col min="7932" max="7932" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="7933" max="7933" width="10.5625" style="10" customWidth="1"/>
+    <col min="7934" max="7934" width="10.875" style="10" customWidth="1"/>
+    <col min="7935" max="8179" width="9" style="10"/>
+    <col min="8180" max="8180" width="26.5625" style="10" customWidth="1"/>
+    <col min="8181" max="8181" width="13.125" style="10" customWidth="1"/>
+    <col min="8182" max="8186" width="9" style="10"/>
+    <col min="8187" max="8187" width="10.875" style="10" customWidth="1"/>
+    <col min="8188" max="8188" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="8189" max="8189" width="10.5625" style="10" customWidth="1"/>
+    <col min="8190" max="8190" width="10.875" style="10" customWidth="1"/>
+    <col min="8191" max="8435" width="9" style="10"/>
+    <col min="8436" max="8436" width="26.5625" style="10" customWidth="1"/>
+    <col min="8437" max="8437" width="13.125" style="10" customWidth="1"/>
+    <col min="8438" max="8442" width="9" style="10"/>
+    <col min="8443" max="8443" width="10.875" style="10" customWidth="1"/>
+    <col min="8444" max="8444" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="8445" max="8445" width="10.5625" style="10" customWidth="1"/>
+    <col min="8446" max="8446" width="10.875" style="10" customWidth="1"/>
+    <col min="8447" max="8691" width="9" style="10"/>
+    <col min="8692" max="8692" width="26.5625" style="10" customWidth="1"/>
+    <col min="8693" max="8693" width="13.125" style="10" customWidth="1"/>
+    <col min="8694" max="8698" width="9" style="10"/>
+    <col min="8699" max="8699" width="10.875" style="10" customWidth="1"/>
+    <col min="8700" max="8700" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="8701" max="8701" width="10.5625" style="10" customWidth="1"/>
+    <col min="8702" max="8702" width="10.875" style="10" customWidth="1"/>
+    <col min="8703" max="8947" width="9" style="10"/>
+    <col min="8948" max="8948" width="26.5625" style="10" customWidth="1"/>
+    <col min="8949" max="8949" width="13.125" style="10" customWidth="1"/>
+    <col min="8950" max="8954" width="9" style="10"/>
+    <col min="8955" max="8955" width="10.875" style="10" customWidth="1"/>
+    <col min="8956" max="8956" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="8957" max="8957" width="10.5625" style="10" customWidth="1"/>
+    <col min="8958" max="8958" width="10.875" style="10" customWidth="1"/>
+    <col min="8959" max="9203" width="9" style="10"/>
+    <col min="9204" max="9204" width="26.5625" style="10" customWidth="1"/>
+    <col min="9205" max="9205" width="13.125" style="10" customWidth="1"/>
+    <col min="9206" max="9210" width="9" style="10"/>
+    <col min="9211" max="9211" width="10.875" style="10" customWidth="1"/>
+    <col min="9212" max="9212" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="9213" max="9213" width="10.5625" style="10" customWidth="1"/>
+    <col min="9214" max="9214" width="10.875" style="10" customWidth="1"/>
+    <col min="9215" max="9459" width="9" style="10"/>
+    <col min="9460" max="9460" width="26.5625" style="10" customWidth="1"/>
+    <col min="9461" max="9461" width="13.125" style="10" customWidth="1"/>
+    <col min="9462" max="9466" width="9" style="10"/>
+    <col min="9467" max="9467" width="10.875" style="10" customWidth="1"/>
+    <col min="9468" max="9468" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="9469" max="9469" width="10.5625" style="10" customWidth="1"/>
+    <col min="9470" max="9470" width="10.875" style="10" customWidth="1"/>
+    <col min="9471" max="9715" width="9" style="10"/>
+    <col min="9716" max="9716" width="26.5625" style="10" customWidth="1"/>
+    <col min="9717" max="9717" width="13.125" style="10" customWidth="1"/>
+    <col min="9718" max="9722" width="9" style="10"/>
+    <col min="9723" max="9723" width="10.875" style="10" customWidth="1"/>
+    <col min="9724" max="9724" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="9725" max="9725" width="10.5625" style="10" customWidth="1"/>
+    <col min="9726" max="9726" width="10.875" style="10" customWidth="1"/>
+    <col min="9727" max="9971" width="9" style="10"/>
+    <col min="9972" max="9972" width="26.5625" style="10" customWidth="1"/>
+    <col min="9973" max="9973" width="13.125" style="10" customWidth="1"/>
+    <col min="9974" max="9978" width="9" style="10"/>
+    <col min="9979" max="9979" width="10.875" style="10" customWidth="1"/>
+    <col min="9980" max="9980" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="9981" max="9981" width="10.5625" style="10" customWidth="1"/>
+    <col min="9982" max="9982" width="10.875" style="10" customWidth="1"/>
+    <col min="9983" max="10227" width="9" style="10"/>
+    <col min="10228" max="10228" width="26.5625" style="10" customWidth="1"/>
+    <col min="10229" max="10229" width="13.125" style="10" customWidth="1"/>
+    <col min="10230" max="10234" width="9" style="10"/>
+    <col min="10235" max="10235" width="10.875" style="10" customWidth="1"/>
+    <col min="10236" max="10236" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="10237" max="10237" width="10.5625" style="10" customWidth="1"/>
+    <col min="10238" max="10238" width="10.875" style="10" customWidth="1"/>
+    <col min="10239" max="10483" width="9" style="10"/>
+    <col min="10484" max="10484" width="26.5625" style="10" customWidth="1"/>
+    <col min="10485" max="10485" width="13.125" style="10" customWidth="1"/>
+    <col min="10486" max="10490" width="9" style="10"/>
+    <col min="10491" max="10491" width="10.875" style="10" customWidth="1"/>
+    <col min="10492" max="10492" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="10493" max="10493" width="10.5625" style="10" customWidth="1"/>
+    <col min="10494" max="10494" width="10.875" style="10" customWidth="1"/>
+    <col min="10495" max="10739" width="9" style="10"/>
+    <col min="10740" max="10740" width="26.5625" style="10" customWidth="1"/>
+    <col min="10741" max="10741" width="13.125" style="10" customWidth="1"/>
+    <col min="10742" max="10746" width="9" style="10"/>
+    <col min="10747" max="10747" width="10.875" style="10" customWidth="1"/>
+    <col min="10748" max="10748" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="10749" max="10749" width="10.5625" style="10" customWidth="1"/>
+    <col min="10750" max="10750" width="10.875" style="10" customWidth="1"/>
+    <col min="10751" max="10995" width="9" style="10"/>
+    <col min="10996" max="10996" width="26.5625" style="10" customWidth="1"/>
+    <col min="10997" max="10997" width="13.125" style="10" customWidth="1"/>
+    <col min="10998" max="11002" width="9" style="10"/>
+    <col min="11003" max="11003" width="10.875" style="10" customWidth="1"/>
+    <col min="11004" max="11004" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="11005" max="11005" width="10.5625" style="10" customWidth="1"/>
+    <col min="11006" max="11006" width="10.875" style="10" customWidth="1"/>
+    <col min="11007" max="11251" width="9" style="10"/>
+    <col min="11252" max="11252" width="26.5625" style="10" customWidth="1"/>
+    <col min="11253" max="11253" width="13.125" style="10" customWidth="1"/>
+    <col min="11254" max="11258" width="9" style="10"/>
+    <col min="11259" max="11259" width="10.875" style="10" customWidth="1"/>
+    <col min="11260" max="11260" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="11261" max="11261" width="10.5625" style="10" customWidth="1"/>
+    <col min="11262" max="11262" width="10.875" style="10" customWidth="1"/>
+    <col min="11263" max="11507" width="9" style="10"/>
+    <col min="11508" max="11508" width="26.5625" style="10" customWidth="1"/>
+    <col min="11509" max="11509" width="13.125" style="10" customWidth="1"/>
+    <col min="11510" max="11514" width="9" style="10"/>
+    <col min="11515" max="11515" width="10.875" style="10" customWidth="1"/>
+    <col min="11516" max="11516" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="11517" max="11517" width="10.5625" style="10" customWidth="1"/>
+    <col min="11518" max="11518" width="10.875" style="10" customWidth="1"/>
+    <col min="11519" max="11763" width="9" style="10"/>
+    <col min="11764" max="11764" width="26.5625" style="10" customWidth="1"/>
+    <col min="11765" max="11765" width="13.125" style="10" customWidth="1"/>
+    <col min="11766" max="11770" width="9" style="10"/>
+    <col min="11771" max="11771" width="10.875" style="10" customWidth="1"/>
+    <col min="11772" max="11772" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="11773" max="11773" width="10.5625" style="10" customWidth="1"/>
+    <col min="11774" max="11774" width="10.875" style="10" customWidth="1"/>
+    <col min="11775" max="12019" width="9" style="10"/>
+    <col min="12020" max="12020" width="26.5625" style="10" customWidth="1"/>
+    <col min="12021" max="12021" width="13.125" style="10" customWidth="1"/>
+    <col min="12022" max="12026" width="9" style="10"/>
+    <col min="12027" max="12027" width="10.875" style="10" customWidth="1"/>
+    <col min="12028" max="12028" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="12029" max="12029" width="10.5625" style="10" customWidth="1"/>
+    <col min="12030" max="12030" width="10.875" style="10" customWidth="1"/>
+    <col min="12031" max="12275" width="9" style="10"/>
+    <col min="12276" max="12276" width="26.5625" style="10" customWidth="1"/>
+    <col min="12277" max="12277" width="13.125" style="10" customWidth="1"/>
+    <col min="12278" max="12282" width="9" style="10"/>
+    <col min="12283" max="12283" width="10.875" style="10" customWidth="1"/>
+    <col min="12284" max="12284" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="12285" max="12285" width="10.5625" style="10" customWidth="1"/>
+    <col min="12286" max="12286" width="10.875" style="10" customWidth="1"/>
+    <col min="12287" max="12531" width="9" style="10"/>
+    <col min="12532" max="12532" width="26.5625" style="10" customWidth="1"/>
+    <col min="12533" max="12533" width="13.125" style="10" customWidth="1"/>
+    <col min="12534" max="12538" width="9" style="10"/>
+    <col min="12539" max="12539" width="10.875" style="10" customWidth="1"/>
+    <col min="12540" max="12540" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="12541" max="12541" width="10.5625" style="10" customWidth="1"/>
+    <col min="12542" max="12542" width="10.875" style="10" customWidth="1"/>
+    <col min="12543" max="12787" width="9" style="10"/>
+    <col min="12788" max="12788" width="26.5625" style="10" customWidth="1"/>
+    <col min="12789" max="12789" width="13.125" style="10" customWidth="1"/>
+    <col min="12790" max="12794" width="9" style="10"/>
+    <col min="12795" max="12795" width="10.875" style="10" customWidth="1"/>
+    <col min="12796" max="12796" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="12797" max="12797" width="10.5625" style="10" customWidth="1"/>
+    <col min="12798" max="12798" width="10.875" style="10" customWidth="1"/>
+    <col min="12799" max="13043" width="9" style="10"/>
+    <col min="13044" max="13044" width="26.5625" style="10" customWidth="1"/>
+    <col min="13045" max="13045" width="13.125" style="10" customWidth="1"/>
+    <col min="13046" max="13050" width="9" style="10"/>
+    <col min="13051" max="13051" width="10.875" style="10" customWidth="1"/>
+    <col min="13052" max="13052" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="13053" max="13053" width="10.5625" style="10" customWidth="1"/>
+    <col min="13054" max="13054" width="10.875" style="10" customWidth="1"/>
+    <col min="13055" max="13299" width="9" style="10"/>
+    <col min="13300" max="13300" width="26.5625" style="10" customWidth="1"/>
+    <col min="13301" max="13301" width="13.125" style="10" customWidth="1"/>
+    <col min="13302" max="13306" width="9" style="10"/>
+    <col min="13307" max="13307" width="10.875" style="10" customWidth="1"/>
+    <col min="13308" max="13308" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="13309" max="13309" width="10.5625" style="10" customWidth="1"/>
+    <col min="13310" max="13310" width="10.875" style="10" customWidth="1"/>
+    <col min="13311" max="13555" width="9" style="10"/>
+    <col min="13556" max="13556" width="26.5625" style="10" customWidth="1"/>
+    <col min="13557" max="13557" width="13.125" style="10" customWidth="1"/>
+    <col min="13558" max="13562" width="9" style="10"/>
+    <col min="13563" max="13563" width="10.875" style="10" customWidth="1"/>
+    <col min="13564" max="13564" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="13565" max="13565" width="10.5625" style="10" customWidth="1"/>
+    <col min="13566" max="13566" width="10.875" style="10" customWidth="1"/>
+    <col min="13567" max="13811" width="9" style="10"/>
+    <col min="13812" max="13812" width="26.5625" style="10" customWidth="1"/>
+    <col min="13813" max="13813" width="13.125" style="10" customWidth="1"/>
+    <col min="13814" max="13818" width="9" style="10"/>
+    <col min="13819" max="13819" width="10.875" style="10" customWidth="1"/>
+    <col min="13820" max="13820" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="13821" max="13821" width="10.5625" style="10" customWidth="1"/>
+    <col min="13822" max="13822" width="10.875" style="10" customWidth="1"/>
+    <col min="13823" max="14067" width="9" style="10"/>
+    <col min="14068" max="14068" width="26.5625" style="10" customWidth="1"/>
+    <col min="14069" max="14069" width="13.125" style="10" customWidth="1"/>
+    <col min="14070" max="14074" width="9" style="10"/>
+    <col min="14075" max="14075" width="10.875" style="10" customWidth="1"/>
+    <col min="14076" max="14076" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="14077" max="14077" width="10.5625" style="10" customWidth="1"/>
+    <col min="14078" max="14078" width="10.875" style="10" customWidth="1"/>
+    <col min="14079" max="14323" width="9" style="10"/>
+    <col min="14324" max="14324" width="26.5625" style="10" customWidth="1"/>
+    <col min="14325" max="14325" width="13.125" style="10" customWidth="1"/>
+    <col min="14326" max="14330" width="9" style="10"/>
+    <col min="14331" max="14331" width="10.875" style="10" customWidth="1"/>
+    <col min="14332" max="14332" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="14333" max="14333" width="10.5625" style="10" customWidth="1"/>
+    <col min="14334" max="14334" width="10.875" style="10" customWidth="1"/>
+    <col min="14335" max="14579" width="9" style="10"/>
+    <col min="14580" max="14580" width="26.5625" style="10" customWidth="1"/>
+    <col min="14581" max="14581" width="13.125" style="10" customWidth="1"/>
+    <col min="14582" max="14586" width="9" style="10"/>
+    <col min="14587" max="14587" width="10.875" style="10" customWidth="1"/>
+    <col min="14588" max="14588" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="14589" max="14589" width="10.5625" style="10" customWidth="1"/>
+    <col min="14590" max="14590" width="10.875" style="10" customWidth="1"/>
+    <col min="14591" max="14835" width="9" style="10"/>
+    <col min="14836" max="14836" width="26.5625" style="10" customWidth="1"/>
+    <col min="14837" max="14837" width="13.125" style="10" customWidth="1"/>
+    <col min="14838" max="14842" width="9" style="10"/>
+    <col min="14843" max="14843" width="10.875" style="10" customWidth="1"/>
+    <col min="14844" max="14844" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="14845" max="14845" width="10.5625" style="10" customWidth="1"/>
+    <col min="14846" max="14846" width="10.875" style="10" customWidth="1"/>
+    <col min="14847" max="15091" width="9" style="10"/>
+    <col min="15092" max="15092" width="26.5625" style="10" customWidth="1"/>
+    <col min="15093" max="15093" width="13.125" style="10" customWidth="1"/>
+    <col min="15094" max="15098" width="9" style="10"/>
+    <col min="15099" max="15099" width="10.875" style="10" customWidth="1"/>
+    <col min="15100" max="15100" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="15101" max="15101" width="10.5625" style="10" customWidth="1"/>
+    <col min="15102" max="15102" width="10.875" style="10" customWidth="1"/>
+    <col min="15103" max="15347" width="9" style="10"/>
+    <col min="15348" max="15348" width="26.5625" style="10" customWidth="1"/>
+    <col min="15349" max="15349" width="13.125" style="10" customWidth="1"/>
+    <col min="15350" max="15354" width="9" style="10"/>
+    <col min="15355" max="15355" width="10.875" style="10" customWidth="1"/>
+    <col min="15356" max="15356" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="15357" max="15357" width="10.5625" style="10" customWidth="1"/>
+    <col min="15358" max="15358" width="10.875" style="10" customWidth="1"/>
+    <col min="15359" max="15603" width="9" style="10"/>
+    <col min="15604" max="15604" width="26.5625" style="10" customWidth="1"/>
+    <col min="15605" max="15605" width="13.125" style="10" customWidth="1"/>
+    <col min="15606" max="15610" width="9" style="10"/>
+    <col min="15611" max="15611" width="10.875" style="10" customWidth="1"/>
+    <col min="15612" max="15612" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="15613" max="15613" width="10.5625" style="10" customWidth="1"/>
+    <col min="15614" max="15614" width="10.875" style="10" customWidth="1"/>
+    <col min="15615" max="15859" width="9" style="10"/>
+    <col min="15860" max="15860" width="26.5625" style="10" customWidth="1"/>
+    <col min="15861" max="15861" width="13.125" style="10" customWidth="1"/>
+    <col min="15862" max="15866" width="9" style="10"/>
+    <col min="15867" max="15867" width="10.875" style="10" customWidth="1"/>
+    <col min="15868" max="15868" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="15869" max="15869" width="10.5625" style="10" customWidth="1"/>
+    <col min="15870" max="15870" width="10.875" style="10" customWidth="1"/>
+    <col min="15871" max="16115" width="9" style="10"/>
+    <col min="16116" max="16116" width="26.5625" style="10" customWidth="1"/>
+    <col min="16117" max="16117" width="13.125" style="10" customWidth="1"/>
+    <col min="16118" max="16122" width="9" style="10"/>
+    <col min="16123" max="16123" width="10.875" style="10" customWidth="1"/>
+    <col min="16124" max="16124" width="23" style="10" bestFit="1" customWidth="1"/>
+    <col min="16125" max="16125" width="10.5625" style="10" customWidth="1"/>
+    <col min="16126" max="16126" width="10.875" style="10" customWidth="1"/>
+    <col min="16127" max="16384" width="9" style="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1" s="9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="E3" s="11"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="B4" s="12">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="B5" s="13">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="B7" s="14">
+        <v>1</v>
+      </c>
+      <c r="C7" s="14">
+        <v>2</v>
+      </c>
+      <c r="D7" s="14">
+        <v>3</v>
+      </c>
+      <c r="E7" s="14">
+        <v>4</v>
+      </c>
+      <c r="F7" s="14">
+        <v>5</v>
+      </c>
+      <c r="G7" s="14">
+        <v>6</v>
+      </c>
+      <c r="H7" s="15"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="B8" s="17">
+        <v>12.5</v>
+      </c>
+      <c r="C8" s="17">
+        <v>12.55</v>
+      </c>
+      <c r="D8" s="17">
+        <v>12.7</v>
+      </c>
+      <c r="E8" s="17">
+        <v>12.8</v>
+      </c>
+      <c r="F8" s="17">
+        <v>12.85</v>
+      </c>
+      <c r="G8" s="17">
+        <v>12.95</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="B9" s="18">
+        <f>B8* $B$5</f>
+        <v>0.625</v>
+      </c>
+      <c r="C9" s="18">
+        <f t="shared" ref="C9:G9" si="0">C8* $B$5</f>
+        <v>0.62750000000000006</v>
+      </c>
+      <c r="D9" s="18">
+        <f t="shared" si="0"/>
+        <v>0.63500000000000001</v>
+      </c>
+      <c r="E9" s="18">
+        <f t="shared" si="0"/>
+        <v>0.64000000000000012</v>
+      </c>
+      <c r="F9" s="18">
+        <f t="shared" si="0"/>
+        <v>0.64250000000000007</v>
+      </c>
+      <c r="G9" s="18">
+        <f t="shared" si="0"/>
+        <v>0.64749999999999996</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10" s="19" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A11" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="B11" s="14">
+        <v>1</v>
+      </c>
+      <c r="C11" s="14">
+        <v>2</v>
+      </c>
+      <c r="D11" s="14">
+        <v>3</v>
+      </c>
+      <c r="E11" s="14">
+        <v>4</v>
+      </c>
+      <c r="F11" s="14">
+        <v>5</v>
+      </c>
+      <c r="G11" s="14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A12" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="B12" s="20">
+        <v>5000</v>
+      </c>
+      <c r="C12" s="20">
+        <v>20000</v>
+      </c>
+      <c r="D12" s="20">
+        <v>30000</v>
+      </c>
+      <c r="E12" s="20">
+        <v>30000</v>
+      </c>
+      <c r="F12" s="20">
+        <v>25000</v>
+      </c>
+      <c r="G12" s="20">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B13" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="E13" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="F13" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="G13" s="21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A14" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="B14" s="12">
+        <v>30000</v>
+      </c>
+      <c r="C14" s="12">
+        <v>30000</v>
+      </c>
+      <c r="D14" s="12">
+        <v>30000</v>
+      </c>
+      <c r="E14" s="12">
+        <v>30000</v>
+      </c>
+      <c r="F14" s="12">
+        <v>30000</v>
+      </c>
+      <c r="G14" s="12">
+        <v>30000</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A16" s="22" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B17" s="23"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="23"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A18" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="B18" s="12">
+        <v>10000</v>
+      </c>
+      <c r="C18" s="12">
+        <v>15000</v>
+      </c>
+      <c r="D18" s="12">
+        <v>30000</v>
+      </c>
+      <c r="E18" s="12">
+        <v>35000</v>
+      </c>
+      <c r="F18" s="12">
+        <v>25000</v>
+      </c>
+      <c r="G18" s="12">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B19" s="21"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A20" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="B20" s="27">
+        <f>B12-B18+B4</f>
+        <v>0</v>
+      </c>
+      <c r="C20" s="27">
+        <f>C12-C18+B20</f>
+        <v>5000</v>
+      </c>
+      <c r="D20" s="27">
+        <f t="shared" ref="D20:G20" si="1">D12-D18+C20</f>
+        <v>5000</v>
+      </c>
+      <c r="E20" s="27">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F20" s="27">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G20" s="27">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H20" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="I20" s="10" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B21" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="C21" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="D21" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="E21" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="F21" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="G21" s="23" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A22" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="B22" s="12">
+        <v>10000</v>
+      </c>
+      <c r="C22" s="12">
+        <v>10000</v>
+      </c>
+      <c r="D22" s="12">
+        <v>10000</v>
+      </c>
+      <c r="E22" s="12">
+        <v>10000</v>
+      </c>
+      <c r="F22" s="12">
+        <v>10000</v>
+      </c>
+      <c r="G22" s="12">
+        <v>10000</v>
+      </c>
+      <c r="I22" s="10" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A23" s="19"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A24" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="B24" s="18"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A25" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="B25" s="14">
+        <v>1</v>
+      </c>
+      <c r="C25" s="14">
+        <v>2</v>
+      </c>
+      <c r="D25" s="14">
+        <v>3</v>
+      </c>
+      <c r="E25" s="14">
+        <v>4</v>
+      </c>
+      <c r="F25" s="14">
+        <v>5</v>
+      </c>
+      <c r="G25" s="14">
+        <v>6</v>
+      </c>
+      <c r="H25" s="23" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A26" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="B26" s="10">
+        <f>B20*B9</f>
+        <v>0</v>
+      </c>
+      <c r="C26" s="10">
+        <f t="shared" ref="C26:G26" si="2">C20*C9</f>
+        <v>3137.5000000000005</v>
+      </c>
+      <c r="D26" s="10">
+        <f t="shared" si="2"/>
+        <v>3175</v>
+      </c>
+      <c r="E26" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F26" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G26" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H26" s="25">
+        <f>SUM(B26:G26)</f>
+        <v>6312.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A27" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B27" s="10">
+        <f>B12*B8</f>
+        <v>62500</v>
+      </c>
+      <c r="C27" s="10">
+        <f t="shared" ref="C27:G27" si="3">C12*C8</f>
+        <v>251000</v>
+      </c>
+      <c r="D27" s="10">
+        <f t="shared" si="3"/>
+        <v>381000</v>
+      </c>
+      <c r="E27" s="10">
+        <f t="shared" si="3"/>
+        <v>384000</v>
+      </c>
+      <c r="F27" s="10">
+        <f t="shared" si="3"/>
+        <v>321250</v>
+      </c>
+      <c r="G27" s="10">
+        <f t="shared" si="3"/>
+        <v>129500</v>
+      </c>
+      <c r="H27" s="25">
+        <f>SUM(B27:G27)</f>
+        <v>1529250</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H28" s="26">
+        <f>SUM(H26:H27)</f>
+        <v>1535562.5</v>
       </c>
     </row>
   </sheetData>

--- a/class_excel/temp_midterm.xlsx
+++ b/class_excel/temp_midterm.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\DADS7102\class_excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\T00229\Documents\GitHub\DADS7102\class_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{709CDB1A-C542-4C86-8419-C52931AC18FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{096B21DD-E272-4CBA-85A1-A6582E4189E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="3" xr2:uid="{962D6ACA-47B2-4C7E-82D5-0F5476EE75BF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="11" xr2:uid="{962D6ACA-47B2-4C7E-82D5-0F5476EE75BF}"/>
   </bookViews>
   <sheets>
     <sheet name="ch_1_1" sheetId="1" r:id="rId1"/>
@@ -22,9 +22,12 @@
     <sheet name="ch_3_1" sheetId="16" r:id="rId7"/>
     <sheet name="ch_3_2" sheetId="17" r:id="rId8"/>
     <sheet name="ch_3_3" sheetId="18" r:id="rId9"/>
+    <sheet name="ch_3_4" sheetId="19" r:id="rId10"/>
+    <sheet name="ch4_1" sheetId="20" r:id="rId11"/>
+    <sheet name="ch4_2" sheetId="21" r:id="rId12"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId10"/>
+    <externalReference r:id="rId13"/>
   </externalReferences>
   <definedNames>
     <definedName name="AFinish">[1]project!$K$6</definedName>
@@ -51,6 +54,8 @@
     <definedName name="solver_adj" localSheetId="6" hidden="1">ch_3_1!$D$3:$D$28</definedName>
     <definedName name="solver_adj" localSheetId="7" hidden="1">ch_3_2!$D$3:$D$8</definedName>
     <definedName name="solver_adj" localSheetId="8" hidden="1">ch_3_3!$B$12:$G$12</definedName>
+    <definedName name="solver_adj" localSheetId="9" hidden="1">ch_3_4!$E$2:$E$11</definedName>
+    <definedName name="solver_adj" localSheetId="10" hidden="1">ch4_1!$B$11:$F$12</definedName>
     <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="1" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="2" hidden="1">0.0001</definedName>
@@ -60,6 +65,8 @@
     <definedName name="solver_cvg" localSheetId="6" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="7" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="8" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="9" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="10" hidden="1">0.0001</definedName>
     <definedName name="solver_drv" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="2" hidden="1">1</definedName>
@@ -69,6 +76,8 @@
     <definedName name="solver_drv" localSheetId="6" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="7" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="8" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="9" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="10" hidden="1">1</definedName>
     <definedName name="solver_eng" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="2" hidden="1">2</definedName>
@@ -78,6 +87,8 @@
     <definedName name="solver_eng" localSheetId="6" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="7" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="8" hidden="1">2</definedName>
+    <definedName name="solver_eng" localSheetId="9" hidden="1">2</definedName>
+    <definedName name="solver_eng" localSheetId="10" hidden="1">2</definedName>
     <definedName name="solver_est" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="2" hidden="1">1</definedName>
@@ -87,6 +98,8 @@
     <definedName name="solver_est" localSheetId="6" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="7" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="8" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="9" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="10" hidden="1">1</definedName>
     <definedName name="solver_itr" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="2" hidden="1">2147483647</definedName>
@@ -96,6 +109,8 @@
     <definedName name="solver_itr" localSheetId="6" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="7" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="8" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="9" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="10" hidden="1">2147483647</definedName>
     <definedName name="solver_lhs1" localSheetId="0" hidden="1">ch_1_1!$B$3:$B$5</definedName>
     <definedName name="solver_lhs1" localSheetId="1" hidden="1">ch_1_2!$F$5:$F$7</definedName>
     <definedName name="solver_lhs1" localSheetId="2" hidden="1">ch_2_1!$B$4:$I$4</definedName>
@@ -105,13 +120,18 @@
     <definedName name="solver_lhs1" localSheetId="6" hidden="1">ch_3_1!$D$3:$D$28</definedName>
     <definedName name="solver_lhs1" localSheetId="7" hidden="1">ch_3_2!$D$3:$D$8</definedName>
     <definedName name="solver_lhs1" localSheetId="8" hidden="1">ch_3_3!$B$12:$G$12</definedName>
+    <definedName name="solver_lhs1" localSheetId="9" hidden="1">ch_3_4!$E$2:$E$3</definedName>
+    <definedName name="solver_lhs1" localSheetId="10" hidden="1">ch4_1!$B$11:$F$11</definedName>
     <definedName name="solver_lhs2" localSheetId="0" hidden="1">ch_1_1!$B$8:$B$9</definedName>
     <definedName name="solver_lhs2" localSheetId="2" hidden="1">ch_2_1!$O$2:$O$4</definedName>
     <definedName name="solver_lhs2" localSheetId="5" hidden="1">ch_2_4!$J$3</definedName>
     <definedName name="solver_lhs2" localSheetId="6" hidden="1">ch_3_1!$K$3:$K$9</definedName>
     <definedName name="solver_lhs2" localSheetId="7" hidden="1">ch_3_2!$K$3:$K$7</definedName>
     <definedName name="solver_lhs2" localSheetId="8" hidden="1">ch_3_3!$B$20:$G$20</definedName>
+    <definedName name="solver_lhs2" localSheetId="9" hidden="1">ch_3_4!$L$2:$L$8</definedName>
+    <definedName name="solver_lhs2" localSheetId="10" hidden="1">ch4_1!$B$12:$F$12</definedName>
     <definedName name="solver_lhs3" localSheetId="8" hidden="1">ch_3_3!$B$20:$G$20</definedName>
+    <definedName name="solver_lhs3" localSheetId="10" hidden="1">ch4_1!$B$16:$B$17</definedName>
     <definedName name="solver_mip" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="2" hidden="1">2147483647</definedName>
@@ -121,6 +141,8 @@
     <definedName name="solver_mip" localSheetId="6" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="7" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="8" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="9" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="10" hidden="1">2147483647</definedName>
     <definedName name="solver_mni" localSheetId="0" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="1" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="2" hidden="1">30</definedName>
@@ -130,6 +152,8 @@
     <definedName name="solver_mni" localSheetId="6" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="7" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="8" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="9" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="10" hidden="1">30</definedName>
     <definedName name="solver_mrt" localSheetId="0" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="1" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="2" hidden="1">0.075</definedName>
@@ -139,6 +163,8 @@
     <definedName name="solver_mrt" localSheetId="6" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="7" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="8" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="9" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="10" hidden="1">0.075</definedName>
     <definedName name="solver_msl" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="2" hidden="1">2</definedName>
@@ -148,6 +174,8 @@
     <definedName name="solver_msl" localSheetId="6" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="7" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="8" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="9" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="10" hidden="1">2</definedName>
     <definedName name="solver_neg" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="2" hidden="1">1</definedName>
@@ -157,6 +185,8 @@
     <definedName name="solver_neg" localSheetId="6" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="7" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="8" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="9" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="10" hidden="1">1</definedName>
     <definedName name="solver_nod" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="2" hidden="1">2147483647</definedName>
@@ -166,6 +196,8 @@
     <definedName name="solver_nod" localSheetId="6" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="7" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="8" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="9" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="10" hidden="1">2147483647</definedName>
     <definedName name="solver_num" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_num" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_num" localSheetId="2" hidden="1">2</definedName>
@@ -175,6 +207,8 @@
     <definedName name="solver_num" localSheetId="6" hidden="1">2</definedName>
     <definedName name="solver_num" localSheetId="7" hidden="1">2</definedName>
     <definedName name="solver_num" localSheetId="8" hidden="1">3</definedName>
+    <definedName name="solver_num" localSheetId="9" hidden="1">2</definedName>
+    <definedName name="solver_num" localSheetId="10" hidden="1">3</definedName>
     <definedName name="solver_nwt" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="2" hidden="1">1</definedName>
@@ -184,6 +218,8 @@
     <definedName name="solver_nwt" localSheetId="6" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="7" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="8" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="9" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="10" hidden="1">1</definedName>
     <definedName name="solver_opt" localSheetId="0" hidden="1">ch_1_1!$B$17</definedName>
     <definedName name="solver_opt" localSheetId="1" hidden="1">ch_1_2!$B$10</definedName>
     <definedName name="solver_opt" localSheetId="2" hidden="1">ch_2_1!$J$22</definedName>
@@ -193,6 +229,8 @@
     <definedName name="solver_opt" localSheetId="6" hidden="1">ch_3_1!$I$11</definedName>
     <definedName name="solver_opt" localSheetId="7" hidden="1">ch_3_2!$B$11</definedName>
     <definedName name="solver_opt" localSheetId="8" hidden="1">ch_3_3!$N$4</definedName>
+    <definedName name="solver_opt" localSheetId="9" hidden="1">ch_3_4!$E$13</definedName>
+    <definedName name="solver_opt" localSheetId="10" hidden="1">ch4_1!$B$22</definedName>
     <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="1" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="2" hidden="1">0.000001</definedName>
@@ -202,6 +240,8 @@
     <definedName name="solver_pre" localSheetId="6" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="7" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="8" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="9" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="10" hidden="1">0.000001</definedName>
     <definedName name="solver_rbv" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="2" hidden="1">1</definedName>
@@ -211,6 +251,8 @@
     <definedName name="solver_rbv" localSheetId="6" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="7" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="8" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="9" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="10" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="2" hidden="1">1</definedName>
@@ -220,13 +262,18 @@
     <definedName name="solver_rel1" localSheetId="6" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="7" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="8" hidden="1">1</definedName>
+    <definedName name="solver_rel1" localSheetId="9" hidden="1">1</definedName>
+    <definedName name="solver_rel1" localSheetId="10" hidden="1">5</definedName>
     <definedName name="solver_rel2" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rel2" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_rel2" localSheetId="5" hidden="1">1</definedName>
     <definedName name="solver_rel2" localSheetId="6" hidden="1">1</definedName>
     <definedName name="solver_rel2" localSheetId="7" hidden="1">1</definedName>
     <definedName name="solver_rel2" localSheetId="8" hidden="1">1</definedName>
+    <definedName name="solver_rel2" localSheetId="9" hidden="1">1</definedName>
+    <definedName name="solver_rel2" localSheetId="10" hidden="1">1</definedName>
     <definedName name="solver_rel3" localSheetId="8" hidden="1">3</definedName>
+    <definedName name="solver_rel3" localSheetId="10" hidden="1">1</definedName>
     <definedName name="solver_rhs1" localSheetId="0" hidden="1">ch_1_1!$D$3:$D$5</definedName>
     <definedName name="solver_rhs1" localSheetId="1" hidden="1">ch_1_2!$H$5:$H$7</definedName>
     <definedName name="solver_rhs1" localSheetId="2" hidden="1">ch_2_1!$B$6:$I$6</definedName>
@@ -236,13 +283,18 @@
     <definedName name="solver_rhs1" localSheetId="6" hidden="1">ch_3_1!$F$3:$F$28</definedName>
     <definedName name="solver_rhs1" localSheetId="7" hidden="1">ch_3_2!$F$3:$F$8</definedName>
     <definedName name="solver_rhs1" localSheetId="8" hidden="1">ch_3_3!$B$14:$G$14</definedName>
+    <definedName name="solver_rhs1" localSheetId="9" hidden="1">ch_3_4!$G$2:$G$3</definedName>
+    <definedName name="solver_rhs1" localSheetId="10" hidden="1">"binary"</definedName>
     <definedName name="solver_rhs2" localSheetId="0" hidden="1">ch_1_1!$D$8:$D$9</definedName>
     <definedName name="solver_rhs2" localSheetId="2" hidden="1">ch_2_1!$Q$2:$Q$4</definedName>
     <definedName name="solver_rhs2" localSheetId="5" hidden="1">ch_2_4!$L$3</definedName>
     <definedName name="solver_rhs2" localSheetId="6" hidden="1">ch_3_1!$M$3:$M$9</definedName>
     <definedName name="solver_rhs2" localSheetId="7" hidden="1">ch_3_2!$M$3:$M$7</definedName>
     <definedName name="solver_rhs2" localSheetId="8" hidden="1">ch_3_3!$B$22:$G$22</definedName>
+    <definedName name="solver_rhs2" localSheetId="9" hidden="1">ch_3_4!$N$2:$N$8</definedName>
+    <definedName name="solver_rhs2" localSheetId="10" hidden="1">ch4_1!$B$14:$F$14</definedName>
     <definedName name="solver_rhs3" localSheetId="8" hidden="1">0</definedName>
+    <definedName name="solver_rhs3" localSheetId="10" hidden="1">ch4_1!$D$16:$D$17</definedName>
     <definedName name="solver_rlx" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="2" hidden="1">2</definedName>
@@ -252,6 +304,8 @@
     <definedName name="solver_rlx" localSheetId="6" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="7" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="8" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="9" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="10" hidden="1">2</definedName>
     <definedName name="solver_rsd" localSheetId="0" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="1" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="2" hidden="1">0</definedName>
@@ -261,6 +315,8 @@
     <definedName name="solver_rsd" localSheetId="6" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="7" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="8" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="9" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="10" hidden="1">0</definedName>
     <definedName name="solver_scl" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="2" hidden="1">1</definedName>
@@ -270,6 +326,8 @@
     <definedName name="solver_scl" localSheetId="6" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="7" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="8" hidden="1">1</definedName>
+    <definedName name="solver_scl" localSheetId="9" hidden="1">1</definedName>
+    <definedName name="solver_scl" localSheetId="10" hidden="1">1</definedName>
     <definedName name="solver_sho" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="2" hidden="1">2</definedName>
@@ -279,6 +337,8 @@
     <definedName name="solver_sho" localSheetId="6" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="7" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="8" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="9" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="10" hidden="1">2</definedName>
     <definedName name="solver_ssz" localSheetId="0" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="1" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="2" hidden="1">100</definedName>
@@ -288,6 +348,8 @@
     <definedName name="solver_ssz" localSheetId="6" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="7" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="8" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="9" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="10" hidden="1">100</definedName>
     <definedName name="solver_tim" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="2" hidden="1">2147483647</definedName>
@@ -297,6 +359,8 @@
     <definedName name="solver_tim" localSheetId="6" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="7" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="8" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="9" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="10" hidden="1">2147483647</definedName>
     <definedName name="solver_tol" localSheetId="0" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="1" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="2" hidden="1">0.01</definedName>
@@ -306,6 +370,8 @@
     <definedName name="solver_tol" localSheetId="6" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="7" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="8" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="9" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="10" hidden="1">0.01</definedName>
     <definedName name="solver_typ" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_typ" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_typ" localSheetId="2" hidden="1">1</definedName>
@@ -315,6 +381,8 @@
     <definedName name="solver_typ" localSheetId="6" hidden="1">2</definedName>
     <definedName name="solver_typ" localSheetId="7" hidden="1">2</definedName>
     <definedName name="solver_typ" localSheetId="8" hidden="1">2</definedName>
+    <definedName name="solver_typ" localSheetId="9" hidden="1">2</definedName>
+    <definedName name="solver_typ" localSheetId="10" hidden="1">1</definedName>
     <definedName name="solver_val" localSheetId="0" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="1" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="2" hidden="1">0</definedName>
@@ -324,6 +392,8 @@
     <definedName name="solver_val" localSheetId="6" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="7" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="8" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="9" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="10" hidden="1">0</definedName>
     <definedName name="solver_ver" localSheetId="0" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="1" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="2" hidden="1">3</definedName>
@@ -333,6 +403,8 @@
     <definedName name="solver_ver" localSheetId="6" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="7" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="8" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="9" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="10" hidden="1">3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -348,12 +420,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="142">
   <si>
     <t xml:space="preserve">basic </t>
   </si>
@@ -716,30 +791,95 @@
   </si>
   <si>
     <t xml:space="preserve">Production cost </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>des</t>
+  </si>
+  <si>
+    <t xml:space="preserve">flow </t>
+  </si>
+  <si>
+    <t>lim</t>
+  </si>
+  <si>
+    <t>x1</t>
+  </si>
+  <si>
+    <t>x3</t>
+  </si>
+  <si>
+    <t>x4</t>
+  </si>
+  <si>
+    <t>x5</t>
+  </si>
+  <si>
+    <t>produce?</t>
+  </si>
+  <si>
+    <t># produce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fix cost </t>
+  </si>
+  <si>
+    <t xml:space="preserve">labor hour 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cloth use </t>
+  </si>
+  <si>
+    <t>sell price</t>
+  </si>
+  <si>
+    <t>cost price</t>
+  </si>
+  <si>
+    <t>total revenue</t>
+  </si>
+  <si>
+    <t>total fix cost</t>
+  </si>
+  <si>
+    <t>revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">big M </t>
+  </si>
+  <si>
+    <t xml:space="preserve">total labor </t>
+  </si>
+  <si>
+    <t>total cloth</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
-    <numFmt numFmtId="187" formatCode="0.0000"/>
-    <numFmt numFmtId="188" formatCode="0.000"/>
-    <numFmt numFmtId="189" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
-    <numFmt numFmtId="190" formatCode="&quot;$&quot;#,##0.000_);\(&quot;$&quot;#,##0.000\)"/>
-    <numFmt numFmtId="191" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+  <numFmts count="6">
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.000_);\(&quot;$&quot;#,##0.000\)"/>
+    <numFmt numFmtId="168" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Tahoma"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Tahoma"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -751,20 +891,20 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Tahoma"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Tahoma"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="Tahoma"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -843,13 +983,14 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="189" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="191" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="8" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -865,18 +1006,18 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="5" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="188" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="189" fontId="5" fillId="8" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="190" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="8" fontId="5" fillId="8" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -891,13 +1032,19 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="191" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1"/>
-    <xf numFmtId="191" fontId="5" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="43" fontId="5" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="5" fillId="2" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="168" fontId="0" fillId="3" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="5">
+    <cellStyle name="Comma" xfId="4" builtinId="3"/>
     <cellStyle name="Comma 2" xfId="3" xr:uid="{C9C68EFB-DC8B-4BBD-B2A4-694D3E58E673}"/>
     <cellStyle name="Currency 2" xfId="2" xr:uid="{A9BDFC23-AFF7-42B4-B5DA-AB895D831664}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -917,11 +1064,8 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Advertising "/>
       <sheetName val="Advertising _Sensitivity Report"/>
@@ -1102,9 +1246,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1142,7 +1286,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1248,7 +1392,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1390,7 +1534,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1399,13 +1543,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C764809-11C3-4C28-A777-28C2126910BA}">
   <dimension ref="A1:N18"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.6875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.4375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="H1" t="s">
         <v>0</v>
       </c>
@@ -1425,7 +1569,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="G2" t="s">
         <v>3</v>
       </c>
@@ -1448,7 +1592,7 @@
         <v>28.571428571428573</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1484,7 +1628,7 @@
         <v>28.571428571428573</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1511,7 +1655,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -1538,7 +1682,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -1559,7 +1703,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -1580,7 +1724,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -1589,7 +1733,7 @@
         <v>718514.28571428568</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -1598,7 +1742,7 @@
         <v>355000</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -1607,7 +1751,7 @@
         <v>110000</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -1616,7 +1760,7 @@
         <v>45000</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>12</v>
       </c>
@@ -1625,12 +1769,695 @@
         <v>208514.28571428568</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B18">
         <v>200285.71428571432</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68278018-F2A2-4894-8531-388098B52F99}">
+  <dimension ref="A1:N13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="13.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1" t="s">
+        <v>88</v>
+      </c>
+      <c r="J1" t="s">
+        <v>94</v>
+      </c>
+      <c r="K1" t="s">
+        <v>122</v>
+      </c>
+      <c r="L1" t="s">
+        <v>98</v>
+      </c>
+      <c r="N1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>24.5</v>
+      </c>
+      <c r="E2" s="1">
+        <v>150000</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="7">
+        <v>150000</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <f>SUMIF($B$2:$B$11, $I2, $E$2:$E$11)</f>
+        <v>290000</v>
+      </c>
+      <c r="K2">
+        <f>SUMIF($C$2:$C$11, $I2, $E$2:$E$11)</f>
+        <v>0</v>
+      </c>
+      <c r="L2" s="4">
+        <f>J2-K2</f>
+        <v>290000</v>
+      </c>
+      <c r="M2" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="N2" s="3">
+        <v>290000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>26</v>
+      </c>
+      <c r="E3" s="1">
+        <v>140000</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="7">
+        <v>150000</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <f t="shared" ref="J3:J8" si="0">SUMIF($B$2:$B$11, $I3, $E$2:$E$11)</f>
+        <v>150000</v>
+      </c>
+      <c r="K3">
+        <f>SUMIF($C$2:$C$11, $I3, $E$2:$E$11)</f>
+        <v>150000</v>
+      </c>
+      <c r="L3" s="4">
+        <f t="shared" ref="L3:L8" si="1">J3-K3</f>
+        <v>0</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="N3" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>4</v>
+      </c>
+      <c r="D4">
+        <v>9.6</v>
+      </c>
+      <c r="E4" s="1">
+        <v>90000</v>
+      </c>
+      <c r="I4">
+        <v>3</v>
+      </c>
+      <c r="J4">
+        <f t="shared" si="0"/>
+        <v>140000</v>
+      </c>
+      <c r="K4">
+        <f>SUMIF($C$2:$C$11, $I4, $E$2:$E$11)</f>
+        <v>140000</v>
+      </c>
+      <c r="L4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="N4" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <v>7</v>
+      </c>
+      <c r="E5" s="1">
+        <v>60000</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <f>SUMIF($C$2:$C$11, $I5, $E$2:$E$11)</f>
+        <v>90000</v>
+      </c>
+      <c r="L5" s="4">
+        <f t="shared" si="1"/>
+        <v>-90000</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="N5" s="3">
+        <v>-90000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+      <c r="D6">
+        <v>15.2</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="J6">
+        <f>SUMIF($B$2:$B$11, $I6, $E$2:$E$11)</f>
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <f>SUMIF($C$2:$C$11, $I6, $E$2:$E$11)</f>
+        <v>80000</v>
+      </c>
+      <c r="L6" s="4">
+        <f t="shared" si="1"/>
+        <v>-80000</v>
+      </c>
+      <c r="M6" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="N6" s="3">
+        <v>-80000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>7</v>
+      </c>
+      <c r="D7">
+        <v>28.5</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>6</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <f>SUMIF($C$2:$C$11, $I7, $E$2:$E$11)</f>
+        <v>50000</v>
+      </c>
+      <c r="L7" s="4">
+        <f t="shared" si="1"/>
+        <v>-50000</v>
+      </c>
+      <c r="M7" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="N7" s="3">
+        <v>-50000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B8">
+        <v>3</v>
+      </c>
+      <c r="C8">
+        <v>4</v>
+      </c>
+      <c r="D8">
+        <v>19.5</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>7</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <f>SUMIF($C$2:$C$11, $I8, $E$2:$E$11)</f>
+        <v>70000</v>
+      </c>
+      <c r="L8" s="4">
+        <f t="shared" si="1"/>
+        <v>-70000</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="N8" s="3">
+        <v>-70000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B9">
+        <v>3</v>
+      </c>
+      <c r="C9">
+        <v>5</v>
+      </c>
+      <c r="D9">
+        <v>13.3</v>
+      </c>
+      <c r="E9" s="1">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B10">
+        <v>3</v>
+      </c>
+      <c r="C10">
+        <v>6</v>
+      </c>
+      <c r="D10">
+        <v>5</v>
+      </c>
+      <c r="E10" s="1">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B11">
+        <v>3</v>
+      </c>
+      <c r="C11">
+        <v>7</v>
+      </c>
+      <c r="D11">
+        <v>11.3</v>
+      </c>
+      <c r="E11" s="1">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="D13" t="s">
+        <v>70</v>
+      </c>
+      <c r="E13" s="28">
+        <f>SUMPRODUCT(E2:E11, D2:D11)</f>
+        <v>9906000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D286B17C-5944-46CA-B76E-D859AC09B597}">
+  <dimension ref="A2:F22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.140625" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E2" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B3">
+        <v>1500</v>
+      </c>
+      <c r="C3">
+        <v>1200</v>
+      </c>
+      <c r="D3">
+        <v>1600</v>
+      </c>
+      <c r="E3">
+        <v>1500</v>
+      </c>
+      <c r="F3">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="29" t="s">
+        <v>132</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>6</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+      <c r="F4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>2.5</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>4.5</v>
+      </c>
+      <c r="F5">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B6">
+        <v>35</v>
+      </c>
+      <c r="C6">
+        <v>40</v>
+      </c>
+      <c r="D6">
+        <v>65</v>
+      </c>
+      <c r="E6">
+        <v>70</v>
+      </c>
+      <c r="F6">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B7">
+        <v>20</v>
+      </c>
+      <c r="C7">
+        <v>10</v>
+      </c>
+      <c r="D7">
+        <v>25</v>
+      </c>
+      <c r="E7">
+        <v>30</v>
+      </c>
+      <c r="F7">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>138</v>
+      </c>
+      <c r="B8">
+        <f>B6-B7</f>
+        <v>15</v>
+      </c>
+      <c r="C8">
+        <f>C6-C7</f>
+        <v>30</v>
+      </c>
+      <c r="D8">
+        <f>D6-D7</f>
+        <v>40</v>
+      </c>
+      <c r="E8">
+        <f>E6-E7</f>
+        <v>40</v>
+      </c>
+      <c r="F8">
+        <f>F6-F7</f>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>125</v>
+      </c>
+      <c r="C10" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" t="s">
+        <v>126</v>
+      </c>
+      <c r="E10" t="s">
+        <v>127</v>
+      </c>
+      <c r="F10" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>129</v>
+      </c>
+      <c r="B11" s="30">
+        <v>0</v>
+      </c>
+      <c r="C11" s="30">
+        <v>1</v>
+      </c>
+      <c r="D11" s="30">
+        <v>0</v>
+      </c>
+      <c r="E11" s="30">
+        <v>0</v>
+      </c>
+      <c r="F11" s="30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>130</v>
+      </c>
+      <c r="B12" s="30">
+        <v>0</v>
+      </c>
+      <c r="C12" s="30">
+        <v>965.51724137931024</v>
+      </c>
+      <c r="D12" s="30">
+        <v>0</v>
+      </c>
+      <c r="E12" s="30">
+        <v>0</v>
+      </c>
+      <c r="F12" s="30">
+        <v>379.31034482758622</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B13" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B14">
+        <f>B11 * $B$19</f>
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <f>C11 * $B$19</f>
+        <v>1000000</v>
+      </c>
+      <c r="D14">
+        <f>D11 * $B$19</f>
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <f>E11 * $B$19</f>
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <f>F11 * $B$19</f>
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>140</v>
+      </c>
+      <c r="B16" s="4">
+        <f>SUMPRODUCT(B4:F4,B12:F12)</f>
+        <v>4000</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="3">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>141</v>
+      </c>
+      <c r="B17" s="4">
+        <f>SUMPRODUCT(B5:F5, B12:F12)</f>
+        <v>4500</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D17" s="3">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>139</v>
+      </c>
+      <c r="B19">
+        <f>1000000</f>
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>136</v>
+      </c>
+      <c r="B20">
+        <f>SUMPRODUCT(B8:F8, B12:F12)</f>
+        <v>57413.793103448275</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>137</v>
+      </c>
+      <c r="B21">
+        <f>SUMPRODUCT(B3:F3, B11:F11)</f>
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" s="2">
+        <f>B20-B21</f>
+        <v>54613.793103448275</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA6CB6CF-31AC-43B2-BABC-B89D4F5C3C26}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1638,12 +2465,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8ED592CD-86CB-44D4-97B2-69C4BC78FBD6}">
   <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.5625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>47</v>
       </c>
@@ -1651,7 +2478,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>46</v>
       </c>
@@ -1662,7 +2489,7 @@
         <v>0.25000000000000072</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>47</v>
       </c>
@@ -1670,7 +2497,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>54</v>
       </c>
@@ -1695,7 +2522,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>49</v>
       </c>
@@ -1719,7 +2546,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>50</v>
       </c>
@@ -1744,7 +2571,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>52</v>
       </c>
@@ -1755,7 +2582,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>53</v>
       </c>
@@ -1772,14 +2599,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{383545CA-8758-49BF-B735-9E5D292B0FF0}">
   <dimension ref="A1:Q22"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.6875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.4375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>19</v>
       </c>
@@ -1806,7 +2633,7 @@
       </c>
       <c r="M1" s="8"/>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>27</v>
       </c>
@@ -1849,7 +2676,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>28</v>
       </c>
@@ -1892,7 +2719,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>40</v>
       </c>
@@ -1943,7 +2770,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B5" s="7" t="s">
         <v>2</v>
       </c>
@@ -1970,7 +2797,7 @@
       </c>
       <c r="M5" s="8"/>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="3">
         <v>1500</v>
       </c>
@@ -1997,13 +2824,13 @@
       </c>
       <c r="M6" s="8"/>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M7" s="8"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="M8" s="8"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -2039,7 +2866,7 @@
       </c>
       <c r="M9" s="8"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>42</v>
       </c>
@@ -2075,7 +2902,7 @@
       </c>
       <c r="M10" s="8"/>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>43</v>
       </c>
@@ -2111,10 +2938,10 @@
       </c>
       <c r="M11" s="8"/>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="M12" s="8"/>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>29</v>
       </c>
@@ -2144,7 +2971,7 @@
       </c>
       <c r="M13" s="8"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>30</v>
       </c>
@@ -2174,7 +3001,7 @@
       </c>
       <c r="M14" s="8"/>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -2212,7 +3039,7 @@
       </c>
       <c r="M15" s="8"/>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>37</v>
       </c>
@@ -2250,7 +3077,7 @@
       </c>
       <c r="M16" s="8"/>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>38</v>
       </c>
@@ -2288,10 +3115,10 @@
       </c>
       <c r="M17" s="8"/>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="M18" s="8"/>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>31</v>
       </c>
@@ -2329,7 +3156,7 @@
       </c>
       <c r="M19" s="8"/>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>32</v>
       </c>
@@ -2367,10 +3194,10 @@
       </c>
       <c r="M20" s="8"/>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="M21" s="8"/>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>39</v>
       </c>
@@ -2421,9 +3248,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0E7EC63-9A54-4477-BBCB-EE695471FCE4}">
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>55</v>
       </c>
@@ -2431,7 +3258,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B2" s="1">
         <v>4.3333333333333339</v>
       </c>
@@ -2439,7 +3266,7 @@
         <v>3.333333333333333</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>57</v>
       </c>
@@ -2460,7 +3287,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>58</v>
       </c>
@@ -2481,7 +3308,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>59</v>
       </c>
@@ -2502,10 +3329,10 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F7" s="7"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -2516,7 +3343,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>60</v>
       </c>
@@ -2533,18 +3360,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{252464CB-7E70-452A-88CC-BE24E3E0118E}">
   <dimension ref="A1:I14"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.5625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.4375" customWidth="1"/>
-    <col min="3" max="3" width="4.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="7.6875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.4375" customWidth="1"/>
+    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" customWidth="1"/>
+    <col min="3" max="3" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.42578125" customWidth="1"/>
     <col min="8" max="8" width="3" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>62</v>
       </c>
@@ -2558,7 +3385,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>64</v>
       </c>
@@ -2585,7 +3412,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>30</v>
       </c>
@@ -2612,7 +3439,7 @@
         <v>-200</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>65</v>
       </c>
@@ -2639,7 +3466,7 @@
         <v>-240</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="G5">
         <f>D3 + E3</f>
         <v>6000</v>
@@ -2652,7 +3479,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>66</v>
       </c>
@@ -2676,7 +3503,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>67</v>
       </c>
@@ -2690,7 +3517,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>68</v>
       </c>
@@ -2707,7 +3534,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>69</v>
       </c>
@@ -2718,7 +3545,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -2727,7 +3554,7 @@
         <v>233000</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>65</v>
       </c>
@@ -2736,7 +3563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>70</v>
       </c>
@@ -2745,7 +3572,7 @@
         <v>114400</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -2763,13 +3590,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{663BCE4E-1681-441F-8DE6-2742A5A66B94}">
   <dimension ref="A1:L8"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.5625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>73</v>
       </c>
@@ -2792,7 +3619,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>82</v>
       </c>
@@ -2819,7 +3646,7 @@
       </c>
       <c r="K2" s="7"/>
     </row>
-    <row r="3" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J3" s="4">
         <f>SUMPRODUCT(B2:H2, B4:H4)</f>
         <v>15.000000000000002</v>
@@ -2831,7 +3658,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>70</v>
       </c>
@@ -2857,7 +3684,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>80</v>
       </c>
@@ -2883,7 +3710,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>81</v>
       </c>
@@ -2916,7 +3743,7 @@
         <v>9.9999999999999936E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>39</v>
       </c>
@@ -2934,9 +3761,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9416A4A6-16E8-44A6-ABD2-65E95D8954DD}">
   <dimension ref="A2:M28"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>83</v>
       </c>
@@ -2968,7 +3795,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -3009,7 +3836,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
@@ -3050,7 +3877,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1</v>
       </c>
@@ -3091,7 +3918,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1</v>
       </c>
@@ -3132,7 +3959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>1</v>
       </c>
@@ -3173,7 +4000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>1</v>
       </c>
@@ -3214,7 +4041,7 @@
         <v>-400</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2</v>
       </c>
@@ -3255,7 +4082,7 @@
         <v>-180</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2</v>
       </c>
@@ -3275,7 +4102,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2</v>
       </c>
@@ -3302,7 +4129,7 @@
         <v>3260</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2</v>
       </c>
@@ -3322,7 +4149,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2</v>
       </c>
@@ -3342,7 +4169,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2</v>
       </c>
@@ -3362,7 +4189,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>3</v>
       </c>
@@ -3382,7 +4209,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>3</v>
       </c>
@@ -3402,7 +4229,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>3</v>
       </c>
@@ -3422,7 +4249,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>3</v>
       </c>
@@ -3442,7 +4269,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>3</v>
       </c>
@@ -3462,7 +4289,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>3</v>
       </c>
@@ -3482,7 +4309,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>4</v>
       </c>
@@ -3502,7 +4329,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>4</v>
       </c>
@@ -3522,7 +4349,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>4</v>
       </c>
@@ -3542,7 +4369,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>5</v>
       </c>
@@ -3562,7 +4389,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>5</v>
       </c>
@@ -3582,7 +4409,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>5</v>
       </c>
@@ -3602,7 +4429,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>6</v>
       </c>
@@ -3622,7 +4449,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>7</v>
       </c>
@@ -3650,9 +4477,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B2F4BAA-45A2-4B9F-8DB4-EA5599549413}">
   <dimension ref="A2:M11"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>94</v>
       </c>
@@ -3684,7 +4511,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -3725,7 +4552,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
@@ -3767,7 +4594,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2</v>
       </c>
@@ -3808,7 +4635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2</v>
       </c>
@@ -3850,7 +4677,7 @@
         <v>-60</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>3</v>
       </c>
@@ -3891,7 +4718,7 @@
         <v>-90</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>3</v>
       </c>
@@ -3912,7 +4739,7 @@
       </c>
       <c r="L8" s="7"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>70</v>
       </c>
@@ -3929,532 +4756,532 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E76634E4-7D20-4A0E-A622-BD83CBE54980}">
   <dimension ref="A1:I28"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.5625" style="10" customWidth="1"/>
-    <col min="2" max="2" width="13.125" style="10" customWidth="1"/>
+    <col min="1" max="1" width="28.5703125" style="10" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" style="10" customWidth="1"/>
     <col min="3" max="7" width="9" style="10"/>
-    <col min="8" max="8" width="12.875" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.85546875" style="10" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19" style="10" bestFit="1" customWidth="1"/>
     <col min="10" max="243" width="9" style="10"/>
-    <col min="244" max="244" width="26.5625" style="10" customWidth="1"/>
-    <col min="245" max="245" width="13.125" style="10" customWidth="1"/>
+    <col min="244" max="244" width="26.5703125" style="10" customWidth="1"/>
+    <col min="245" max="245" width="13.140625" style="10" customWidth="1"/>
     <col min="246" max="250" width="9" style="10"/>
-    <col min="251" max="251" width="10.875" style="10" customWidth="1"/>
+    <col min="251" max="251" width="10.85546875" style="10" customWidth="1"/>
     <col min="252" max="252" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="253" max="253" width="10.5625" style="10" customWidth="1"/>
-    <col min="254" max="254" width="10.875" style="10" customWidth="1"/>
+    <col min="253" max="253" width="10.5703125" style="10" customWidth="1"/>
+    <col min="254" max="254" width="10.85546875" style="10" customWidth="1"/>
     <col min="255" max="499" width="9" style="10"/>
-    <col min="500" max="500" width="26.5625" style="10" customWidth="1"/>
-    <col min="501" max="501" width="13.125" style="10" customWidth="1"/>
+    <col min="500" max="500" width="26.5703125" style="10" customWidth="1"/>
+    <col min="501" max="501" width="13.140625" style="10" customWidth="1"/>
     <col min="502" max="506" width="9" style="10"/>
-    <col min="507" max="507" width="10.875" style="10" customWidth="1"/>
+    <col min="507" max="507" width="10.85546875" style="10" customWidth="1"/>
     <col min="508" max="508" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="509" max="509" width="10.5625" style="10" customWidth="1"/>
-    <col min="510" max="510" width="10.875" style="10" customWidth="1"/>
+    <col min="509" max="509" width="10.5703125" style="10" customWidth="1"/>
+    <col min="510" max="510" width="10.85546875" style="10" customWidth="1"/>
     <col min="511" max="755" width="9" style="10"/>
-    <col min="756" max="756" width="26.5625" style="10" customWidth="1"/>
-    <col min="757" max="757" width="13.125" style="10" customWidth="1"/>
+    <col min="756" max="756" width="26.5703125" style="10" customWidth="1"/>
+    <col min="757" max="757" width="13.140625" style="10" customWidth="1"/>
     <col min="758" max="762" width="9" style="10"/>
-    <col min="763" max="763" width="10.875" style="10" customWidth="1"/>
+    <col min="763" max="763" width="10.85546875" style="10" customWidth="1"/>
     <col min="764" max="764" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="765" max="765" width="10.5625" style="10" customWidth="1"/>
-    <col min="766" max="766" width="10.875" style="10" customWidth="1"/>
+    <col min="765" max="765" width="10.5703125" style="10" customWidth="1"/>
+    <col min="766" max="766" width="10.85546875" style="10" customWidth="1"/>
     <col min="767" max="1011" width="9" style="10"/>
-    <col min="1012" max="1012" width="26.5625" style="10" customWidth="1"/>
-    <col min="1013" max="1013" width="13.125" style="10" customWidth="1"/>
+    <col min="1012" max="1012" width="26.5703125" style="10" customWidth="1"/>
+    <col min="1013" max="1013" width="13.140625" style="10" customWidth="1"/>
     <col min="1014" max="1018" width="9" style="10"/>
-    <col min="1019" max="1019" width="10.875" style="10" customWidth="1"/>
+    <col min="1019" max="1019" width="10.85546875" style="10" customWidth="1"/>
     <col min="1020" max="1020" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="1021" max="1021" width="10.5625" style="10" customWidth="1"/>
-    <col min="1022" max="1022" width="10.875" style="10" customWidth="1"/>
+    <col min="1021" max="1021" width="10.5703125" style="10" customWidth="1"/>
+    <col min="1022" max="1022" width="10.85546875" style="10" customWidth="1"/>
     <col min="1023" max="1267" width="9" style="10"/>
-    <col min="1268" max="1268" width="26.5625" style="10" customWidth="1"/>
-    <col min="1269" max="1269" width="13.125" style="10" customWidth="1"/>
+    <col min="1268" max="1268" width="26.5703125" style="10" customWidth="1"/>
+    <col min="1269" max="1269" width="13.140625" style="10" customWidth="1"/>
     <col min="1270" max="1274" width="9" style="10"/>
-    <col min="1275" max="1275" width="10.875" style="10" customWidth="1"/>
+    <col min="1275" max="1275" width="10.85546875" style="10" customWidth="1"/>
     <col min="1276" max="1276" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="1277" max="1277" width="10.5625" style="10" customWidth="1"/>
-    <col min="1278" max="1278" width="10.875" style="10" customWidth="1"/>
+    <col min="1277" max="1277" width="10.5703125" style="10" customWidth="1"/>
+    <col min="1278" max="1278" width="10.85546875" style="10" customWidth="1"/>
     <col min="1279" max="1523" width="9" style="10"/>
-    <col min="1524" max="1524" width="26.5625" style="10" customWidth="1"/>
-    <col min="1525" max="1525" width="13.125" style="10" customWidth="1"/>
+    <col min="1524" max="1524" width="26.5703125" style="10" customWidth="1"/>
+    <col min="1525" max="1525" width="13.140625" style="10" customWidth="1"/>
     <col min="1526" max="1530" width="9" style="10"/>
-    <col min="1531" max="1531" width="10.875" style="10" customWidth="1"/>
+    <col min="1531" max="1531" width="10.85546875" style="10" customWidth="1"/>
     <col min="1532" max="1532" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="1533" max="1533" width="10.5625" style="10" customWidth="1"/>
-    <col min="1534" max="1534" width="10.875" style="10" customWidth="1"/>
+    <col min="1533" max="1533" width="10.5703125" style="10" customWidth="1"/>
+    <col min="1534" max="1534" width="10.85546875" style="10" customWidth="1"/>
     <col min="1535" max="1779" width="9" style="10"/>
-    <col min="1780" max="1780" width="26.5625" style="10" customWidth="1"/>
-    <col min="1781" max="1781" width="13.125" style="10" customWidth="1"/>
+    <col min="1780" max="1780" width="26.5703125" style="10" customWidth="1"/>
+    <col min="1781" max="1781" width="13.140625" style="10" customWidth="1"/>
     <col min="1782" max="1786" width="9" style="10"/>
-    <col min="1787" max="1787" width="10.875" style="10" customWidth="1"/>
+    <col min="1787" max="1787" width="10.85546875" style="10" customWidth="1"/>
     <col min="1788" max="1788" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="1789" max="1789" width="10.5625" style="10" customWidth="1"/>
-    <col min="1790" max="1790" width="10.875" style="10" customWidth="1"/>
+    <col min="1789" max="1789" width="10.5703125" style="10" customWidth="1"/>
+    <col min="1790" max="1790" width="10.85546875" style="10" customWidth="1"/>
     <col min="1791" max="2035" width="9" style="10"/>
-    <col min="2036" max="2036" width="26.5625" style="10" customWidth="1"/>
-    <col min="2037" max="2037" width="13.125" style="10" customWidth="1"/>
+    <col min="2036" max="2036" width="26.5703125" style="10" customWidth="1"/>
+    <col min="2037" max="2037" width="13.140625" style="10" customWidth="1"/>
     <col min="2038" max="2042" width="9" style="10"/>
-    <col min="2043" max="2043" width="10.875" style="10" customWidth="1"/>
+    <col min="2043" max="2043" width="10.85546875" style="10" customWidth="1"/>
     <col min="2044" max="2044" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="2045" max="2045" width="10.5625" style="10" customWidth="1"/>
-    <col min="2046" max="2046" width="10.875" style="10" customWidth="1"/>
+    <col min="2045" max="2045" width="10.5703125" style="10" customWidth="1"/>
+    <col min="2046" max="2046" width="10.85546875" style="10" customWidth="1"/>
     <col min="2047" max="2291" width="9" style="10"/>
-    <col min="2292" max="2292" width="26.5625" style="10" customWidth="1"/>
-    <col min="2293" max="2293" width="13.125" style="10" customWidth="1"/>
+    <col min="2292" max="2292" width="26.5703125" style="10" customWidth="1"/>
+    <col min="2293" max="2293" width="13.140625" style="10" customWidth="1"/>
     <col min="2294" max="2298" width="9" style="10"/>
-    <col min="2299" max="2299" width="10.875" style="10" customWidth="1"/>
+    <col min="2299" max="2299" width="10.85546875" style="10" customWidth="1"/>
     <col min="2300" max="2300" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="2301" max="2301" width="10.5625" style="10" customWidth="1"/>
-    <col min="2302" max="2302" width="10.875" style="10" customWidth="1"/>
+    <col min="2301" max="2301" width="10.5703125" style="10" customWidth="1"/>
+    <col min="2302" max="2302" width="10.85546875" style="10" customWidth="1"/>
     <col min="2303" max="2547" width="9" style="10"/>
-    <col min="2548" max="2548" width="26.5625" style="10" customWidth="1"/>
-    <col min="2549" max="2549" width="13.125" style="10" customWidth="1"/>
+    <col min="2548" max="2548" width="26.5703125" style="10" customWidth="1"/>
+    <col min="2549" max="2549" width="13.140625" style="10" customWidth="1"/>
     <col min="2550" max="2554" width="9" style="10"/>
-    <col min="2555" max="2555" width="10.875" style="10" customWidth="1"/>
+    <col min="2555" max="2555" width="10.85546875" style="10" customWidth="1"/>
     <col min="2556" max="2556" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="2557" max="2557" width="10.5625" style="10" customWidth="1"/>
-    <col min="2558" max="2558" width="10.875" style="10" customWidth="1"/>
+    <col min="2557" max="2557" width="10.5703125" style="10" customWidth="1"/>
+    <col min="2558" max="2558" width="10.85546875" style="10" customWidth="1"/>
     <col min="2559" max="2803" width="9" style="10"/>
-    <col min="2804" max="2804" width="26.5625" style="10" customWidth="1"/>
-    <col min="2805" max="2805" width="13.125" style="10" customWidth="1"/>
+    <col min="2804" max="2804" width="26.5703125" style="10" customWidth="1"/>
+    <col min="2805" max="2805" width="13.140625" style="10" customWidth="1"/>
     <col min="2806" max="2810" width="9" style="10"/>
-    <col min="2811" max="2811" width="10.875" style="10" customWidth="1"/>
+    <col min="2811" max="2811" width="10.85546875" style="10" customWidth="1"/>
     <col min="2812" max="2812" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="2813" max="2813" width="10.5625" style="10" customWidth="1"/>
-    <col min="2814" max="2814" width="10.875" style="10" customWidth="1"/>
+    <col min="2813" max="2813" width="10.5703125" style="10" customWidth="1"/>
+    <col min="2814" max="2814" width="10.85546875" style="10" customWidth="1"/>
     <col min="2815" max="3059" width="9" style="10"/>
-    <col min="3060" max="3060" width="26.5625" style="10" customWidth="1"/>
-    <col min="3061" max="3061" width="13.125" style="10" customWidth="1"/>
+    <col min="3060" max="3060" width="26.5703125" style="10" customWidth="1"/>
+    <col min="3061" max="3061" width="13.140625" style="10" customWidth="1"/>
     <col min="3062" max="3066" width="9" style="10"/>
-    <col min="3067" max="3067" width="10.875" style="10" customWidth="1"/>
+    <col min="3067" max="3067" width="10.85546875" style="10" customWidth="1"/>
     <col min="3068" max="3068" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="3069" max="3069" width="10.5625" style="10" customWidth="1"/>
-    <col min="3070" max="3070" width="10.875" style="10" customWidth="1"/>
+    <col min="3069" max="3069" width="10.5703125" style="10" customWidth="1"/>
+    <col min="3070" max="3070" width="10.85546875" style="10" customWidth="1"/>
     <col min="3071" max="3315" width="9" style="10"/>
-    <col min="3316" max="3316" width="26.5625" style="10" customWidth="1"/>
-    <col min="3317" max="3317" width="13.125" style="10" customWidth="1"/>
+    <col min="3316" max="3316" width="26.5703125" style="10" customWidth="1"/>
+    <col min="3317" max="3317" width="13.140625" style="10" customWidth="1"/>
     <col min="3318" max="3322" width="9" style="10"/>
-    <col min="3323" max="3323" width="10.875" style="10" customWidth="1"/>
+    <col min="3323" max="3323" width="10.85546875" style="10" customWidth="1"/>
     <col min="3324" max="3324" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="3325" max="3325" width="10.5625" style="10" customWidth="1"/>
-    <col min="3326" max="3326" width="10.875" style="10" customWidth="1"/>
+    <col min="3325" max="3325" width="10.5703125" style="10" customWidth="1"/>
+    <col min="3326" max="3326" width="10.85546875" style="10" customWidth="1"/>
     <col min="3327" max="3571" width="9" style="10"/>
-    <col min="3572" max="3572" width="26.5625" style="10" customWidth="1"/>
-    <col min="3573" max="3573" width="13.125" style="10" customWidth="1"/>
+    <col min="3572" max="3572" width="26.5703125" style="10" customWidth="1"/>
+    <col min="3573" max="3573" width="13.140625" style="10" customWidth="1"/>
     <col min="3574" max="3578" width="9" style="10"/>
-    <col min="3579" max="3579" width="10.875" style="10" customWidth="1"/>
+    <col min="3579" max="3579" width="10.85546875" style="10" customWidth="1"/>
     <col min="3580" max="3580" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="3581" max="3581" width="10.5625" style="10" customWidth="1"/>
-    <col min="3582" max="3582" width="10.875" style="10" customWidth="1"/>
+    <col min="3581" max="3581" width="10.5703125" style="10" customWidth="1"/>
+    <col min="3582" max="3582" width="10.85546875" style="10" customWidth="1"/>
     <col min="3583" max="3827" width="9" style="10"/>
-    <col min="3828" max="3828" width="26.5625" style="10" customWidth="1"/>
-    <col min="3829" max="3829" width="13.125" style="10" customWidth="1"/>
+    <col min="3828" max="3828" width="26.5703125" style="10" customWidth="1"/>
+    <col min="3829" max="3829" width="13.140625" style="10" customWidth="1"/>
     <col min="3830" max="3834" width="9" style="10"/>
-    <col min="3835" max="3835" width="10.875" style="10" customWidth="1"/>
+    <col min="3835" max="3835" width="10.85546875" style="10" customWidth="1"/>
     <col min="3836" max="3836" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="3837" max="3837" width="10.5625" style="10" customWidth="1"/>
-    <col min="3838" max="3838" width="10.875" style="10" customWidth="1"/>
+    <col min="3837" max="3837" width="10.5703125" style="10" customWidth="1"/>
+    <col min="3838" max="3838" width="10.85546875" style="10" customWidth="1"/>
     <col min="3839" max="4083" width="9" style="10"/>
-    <col min="4084" max="4084" width="26.5625" style="10" customWidth="1"/>
-    <col min="4085" max="4085" width="13.125" style="10" customWidth="1"/>
+    <col min="4084" max="4084" width="26.5703125" style="10" customWidth="1"/>
+    <col min="4085" max="4085" width="13.140625" style="10" customWidth="1"/>
     <col min="4086" max="4090" width="9" style="10"/>
-    <col min="4091" max="4091" width="10.875" style="10" customWidth="1"/>
+    <col min="4091" max="4091" width="10.85546875" style="10" customWidth="1"/>
     <col min="4092" max="4092" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="4093" max="4093" width="10.5625" style="10" customWidth="1"/>
-    <col min="4094" max="4094" width="10.875" style="10" customWidth="1"/>
+    <col min="4093" max="4093" width="10.5703125" style="10" customWidth="1"/>
+    <col min="4094" max="4094" width="10.85546875" style="10" customWidth="1"/>
     <col min="4095" max="4339" width="9" style="10"/>
-    <col min="4340" max="4340" width="26.5625" style="10" customWidth="1"/>
-    <col min="4341" max="4341" width="13.125" style="10" customWidth="1"/>
+    <col min="4340" max="4340" width="26.5703125" style="10" customWidth="1"/>
+    <col min="4341" max="4341" width="13.140625" style="10" customWidth="1"/>
     <col min="4342" max="4346" width="9" style="10"/>
-    <col min="4347" max="4347" width="10.875" style="10" customWidth="1"/>
+    <col min="4347" max="4347" width="10.85546875" style="10" customWidth="1"/>
     <col min="4348" max="4348" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="4349" max="4349" width="10.5625" style="10" customWidth="1"/>
-    <col min="4350" max="4350" width="10.875" style="10" customWidth="1"/>
+    <col min="4349" max="4349" width="10.5703125" style="10" customWidth="1"/>
+    <col min="4350" max="4350" width="10.85546875" style="10" customWidth="1"/>
     <col min="4351" max="4595" width="9" style="10"/>
-    <col min="4596" max="4596" width="26.5625" style="10" customWidth="1"/>
-    <col min="4597" max="4597" width="13.125" style="10" customWidth="1"/>
+    <col min="4596" max="4596" width="26.5703125" style="10" customWidth="1"/>
+    <col min="4597" max="4597" width="13.140625" style="10" customWidth="1"/>
     <col min="4598" max="4602" width="9" style="10"/>
-    <col min="4603" max="4603" width="10.875" style="10" customWidth="1"/>
+    <col min="4603" max="4603" width="10.85546875" style="10" customWidth="1"/>
     <col min="4604" max="4604" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="4605" max="4605" width="10.5625" style="10" customWidth="1"/>
-    <col min="4606" max="4606" width="10.875" style="10" customWidth="1"/>
+    <col min="4605" max="4605" width="10.5703125" style="10" customWidth="1"/>
+    <col min="4606" max="4606" width="10.85546875" style="10" customWidth="1"/>
     <col min="4607" max="4851" width="9" style="10"/>
-    <col min="4852" max="4852" width="26.5625" style="10" customWidth="1"/>
-    <col min="4853" max="4853" width="13.125" style="10" customWidth="1"/>
+    <col min="4852" max="4852" width="26.5703125" style="10" customWidth="1"/>
+    <col min="4853" max="4853" width="13.140625" style="10" customWidth="1"/>
     <col min="4854" max="4858" width="9" style="10"/>
-    <col min="4859" max="4859" width="10.875" style="10" customWidth="1"/>
+    <col min="4859" max="4859" width="10.85546875" style="10" customWidth="1"/>
     <col min="4860" max="4860" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="4861" max="4861" width="10.5625" style="10" customWidth="1"/>
-    <col min="4862" max="4862" width="10.875" style="10" customWidth="1"/>
+    <col min="4861" max="4861" width="10.5703125" style="10" customWidth="1"/>
+    <col min="4862" max="4862" width="10.85546875" style="10" customWidth="1"/>
     <col min="4863" max="5107" width="9" style="10"/>
-    <col min="5108" max="5108" width="26.5625" style="10" customWidth="1"/>
-    <col min="5109" max="5109" width="13.125" style="10" customWidth="1"/>
+    <col min="5108" max="5108" width="26.5703125" style="10" customWidth="1"/>
+    <col min="5109" max="5109" width="13.140625" style="10" customWidth="1"/>
     <col min="5110" max="5114" width="9" style="10"/>
-    <col min="5115" max="5115" width="10.875" style="10" customWidth="1"/>
+    <col min="5115" max="5115" width="10.85546875" style="10" customWidth="1"/>
     <col min="5116" max="5116" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="5117" max="5117" width="10.5625" style="10" customWidth="1"/>
-    <col min="5118" max="5118" width="10.875" style="10" customWidth="1"/>
+    <col min="5117" max="5117" width="10.5703125" style="10" customWidth="1"/>
+    <col min="5118" max="5118" width="10.85546875" style="10" customWidth="1"/>
     <col min="5119" max="5363" width="9" style="10"/>
-    <col min="5364" max="5364" width="26.5625" style="10" customWidth="1"/>
-    <col min="5365" max="5365" width="13.125" style="10" customWidth="1"/>
+    <col min="5364" max="5364" width="26.5703125" style="10" customWidth="1"/>
+    <col min="5365" max="5365" width="13.140625" style="10" customWidth="1"/>
     <col min="5366" max="5370" width="9" style="10"/>
-    <col min="5371" max="5371" width="10.875" style="10" customWidth="1"/>
+    <col min="5371" max="5371" width="10.85546875" style="10" customWidth="1"/>
     <col min="5372" max="5372" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="5373" max="5373" width="10.5625" style="10" customWidth="1"/>
-    <col min="5374" max="5374" width="10.875" style="10" customWidth="1"/>
+    <col min="5373" max="5373" width="10.5703125" style="10" customWidth="1"/>
+    <col min="5374" max="5374" width="10.85546875" style="10" customWidth="1"/>
     <col min="5375" max="5619" width="9" style="10"/>
-    <col min="5620" max="5620" width="26.5625" style="10" customWidth="1"/>
-    <col min="5621" max="5621" width="13.125" style="10" customWidth="1"/>
+    <col min="5620" max="5620" width="26.5703125" style="10" customWidth="1"/>
+    <col min="5621" max="5621" width="13.140625" style="10" customWidth="1"/>
     <col min="5622" max="5626" width="9" style="10"/>
-    <col min="5627" max="5627" width="10.875" style="10" customWidth="1"/>
+    <col min="5627" max="5627" width="10.85546875" style="10" customWidth="1"/>
     <col min="5628" max="5628" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="5629" max="5629" width="10.5625" style="10" customWidth="1"/>
-    <col min="5630" max="5630" width="10.875" style="10" customWidth="1"/>
+    <col min="5629" max="5629" width="10.5703125" style="10" customWidth="1"/>
+    <col min="5630" max="5630" width="10.85546875" style="10" customWidth="1"/>
     <col min="5631" max="5875" width="9" style="10"/>
-    <col min="5876" max="5876" width="26.5625" style="10" customWidth="1"/>
-    <col min="5877" max="5877" width="13.125" style="10" customWidth="1"/>
+    <col min="5876" max="5876" width="26.5703125" style="10" customWidth="1"/>
+    <col min="5877" max="5877" width="13.140625" style="10" customWidth="1"/>
     <col min="5878" max="5882" width="9" style="10"/>
-    <col min="5883" max="5883" width="10.875" style="10" customWidth="1"/>
+    <col min="5883" max="5883" width="10.85546875" style="10" customWidth="1"/>
     <col min="5884" max="5884" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="5885" max="5885" width="10.5625" style="10" customWidth="1"/>
-    <col min="5886" max="5886" width="10.875" style="10" customWidth="1"/>
+    <col min="5885" max="5885" width="10.5703125" style="10" customWidth="1"/>
+    <col min="5886" max="5886" width="10.85546875" style="10" customWidth="1"/>
     <col min="5887" max="6131" width="9" style="10"/>
-    <col min="6132" max="6132" width="26.5625" style="10" customWidth="1"/>
-    <col min="6133" max="6133" width="13.125" style="10" customWidth="1"/>
+    <col min="6132" max="6132" width="26.5703125" style="10" customWidth="1"/>
+    <col min="6133" max="6133" width="13.140625" style="10" customWidth="1"/>
     <col min="6134" max="6138" width="9" style="10"/>
-    <col min="6139" max="6139" width="10.875" style="10" customWidth="1"/>
+    <col min="6139" max="6139" width="10.85546875" style="10" customWidth="1"/>
     <col min="6140" max="6140" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="6141" max="6141" width="10.5625" style="10" customWidth="1"/>
-    <col min="6142" max="6142" width="10.875" style="10" customWidth="1"/>
+    <col min="6141" max="6141" width="10.5703125" style="10" customWidth="1"/>
+    <col min="6142" max="6142" width="10.85546875" style="10" customWidth="1"/>
     <col min="6143" max="6387" width="9" style="10"/>
-    <col min="6388" max="6388" width="26.5625" style="10" customWidth="1"/>
-    <col min="6389" max="6389" width="13.125" style="10" customWidth="1"/>
+    <col min="6388" max="6388" width="26.5703125" style="10" customWidth="1"/>
+    <col min="6389" max="6389" width="13.140625" style="10" customWidth="1"/>
     <col min="6390" max="6394" width="9" style="10"/>
-    <col min="6395" max="6395" width="10.875" style="10" customWidth="1"/>
+    <col min="6395" max="6395" width="10.85546875" style="10" customWidth="1"/>
     <col min="6396" max="6396" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="6397" max="6397" width="10.5625" style="10" customWidth="1"/>
-    <col min="6398" max="6398" width="10.875" style="10" customWidth="1"/>
+    <col min="6397" max="6397" width="10.5703125" style="10" customWidth="1"/>
+    <col min="6398" max="6398" width="10.85546875" style="10" customWidth="1"/>
     <col min="6399" max="6643" width="9" style="10"/>
-    <col min="6644" max="6644" width="26.5625" style="10" customWidth="1"/>
-    <col min="6645" max="6645" width="13.125" style="10" customWidth="1"/>
+    <col min="6644" max="6644" width="26.5703125" style="10" customWidth="1"/>
+    <col min="6645" max="6645" width="13.140625" style="10" customWidth="1"/>
     <col min="6646" max="6650" width="9" style="10"/>
-    <col min="6651" max="6651" width="10.875" style="10" customWidth="1"/>
+    <col min="6651" max="6651" width="10.85546875" style="10" customWidth="1"/>
     <col min="6652" max="6652" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="6653" max="6653" width="10.5625" style="10" customWidth="1"/>
-    <col min="6654" max="6654" width="10.875" style="10" customWidth="1"/>
+    <col min="6653" max="6653" width="10.5703125" style="10" customWidth="1"/>
+    <col min="6654" max="6654" width="10.85546875" style="10" customWidth="1"/>
     <col min="6655" max="6899" width="9" style="10"/>
-    <col min="6900" max="6900" width="26.5625" style="10" customWidth="1"/>
-    <col min="6901" max="6901" width="13.125" style="10" customWidth="1"/>
+    <col min="6900" max="6900" width="26.5703125" style="10" customWidth="1"/>
+    <col min="6901" max="6901" width="13.140625" style="10" customWidth="1"/>
     <col min="6902" max="6906" width="9" style="10"/>
-    <col min="6907" max="6907" width="10.875" style="10" customWidth="1"/>
+    <col min="6907" max="6907" width="10.85546875" style="10" customWidth="1"/>
     <col min="6908" max="6908" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="6909" max="6909" width="10.5625" style="10" customWidth="1"/>
-    <col min="6910" max="6910" width="10.875" style="10" customWidth="1"/>
+    <col min="6909" max="6909" width="10.5703125" style="10" customWidth="1"/>
+    <col min="6910" max="6910" width="10.85546875" style="10" customWidth="1"/>
     <col min="6911" max="7155" width="9" style="10"/>
-    <col min="7156" max="7156" width="26.5625" style="10" customWidth="1"/>
-    <col min="7157" max="7157" width="13.125" style="10" customWidth="1"/>
+    <col min="7156" max="7156" width="26.5703125" style="10" customWidth="1"/>
+    <col min="7157" max="7157" width="13.140625" style="10" customWidth="1"/>
     <col min="7158" max="7162" width="9" style="10"/>
-    <col min="7163" max="7163" width="10.875" style="10" customWidth="1"/>
+    <col min="7163" max="7163" width="10.85546875" style="10" customWidth="1"/>
     <col min="7164" max="7164" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="7165" max="7165" width="10.5625" style="10" customWidth="1"/>
-    <col min="7166" max="7166" width="10.875" style="10" customWidth="1"/>
+    <col min="7165" max="7165" width="10.5703125" style="10" customWidth="1"/>
+    <col min="7166" max="7166" width="10.85546875" style="10" customWidth="1"/>
     <col min="7167" max="7411" width="9" style="10"/>
-    <col min="7412" max="7412" width="26.5625" style="10" customWidth="1"/>
-    <col min="7413" max="7413" width="13.125" style="10" customWidth="1"/>
+    <col min="7412" max="7412" width="26.5703125" style="10" customWidth="1"/>
+    <col min="7413" max="7413" width="13.140625" style="10" customWidth="1"/>
     <col min="7414" max="7418" width="9" style="10"/>
-    <col min="7419" max="7419" width="10.875" style="10" customWidth="1"/>
+    <col min="7419" max="7419" width="10.85546875" style="10" customWidth="1"/>
     <col min="7420" max="7420" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="7421" max="7421" width="10.5625" style="10" customWidth="1"/>
-    <col min="7422" max="7422" width="10.875" style="10" customWidth="1"/>
+    <col min="7421" max="7421" width="10.5703125" style="10" customWidth="1"/>
+    <col min="7422" max="7422" width="10.85546875" style="10" customWidth="1"/>
     <col min="7423" max="7667" width="9" style="10"/>
-    <col min="7668" max="7668" width="26.5625" style="10" customWidth="1"/>
-    <col min="7669" max="7669" width="13.125" style="10" customWidth="1"/>
+    <col min="7668" max="7668" width="26.5703125" style="10" customWidth="1"/>
+    <col min="7669" max="7669" width="13.140625" style="10" customWidth="1"/>
     <col min="7670" max="7674" width="9" style="10"/>
-    <col min="7675" max="7675" width="10.875" style="10" customWidth="1"/>
+    <col min="7675" max="7675" width="10.85546875" style="10" customWidth="1"/>
     <col min="7676" max="7676" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="7677" max="7677" width="10.5625" style="10" customWidth="1"/>
-    <col min="7678" max="7678" width="10.875" style="10" customWidth="1"/>
+    <col min="7677" max="7677" width="10.5703125" style="10" customWidth="1"/>
+    <col min="7678" max="7678" width="10.85546875" style="10" customWidth="1"/>
     <col min="7679" max="7923" width="9" style="10"/>
-    <col min="7924" max="7924" width="26.5625" style="10" customWidth="1"/>
-    <col min="7925" max="7925" width="13.125" style="10" customWidth="1"/>
+    <col min="7924" max="7924" width="26.5703125" style="10" customWidth="1"/>
+    <col min="7925" max="7925" width="13.140625" style="10" customWidth="1"/>
     <col min="7926" max="7930" width="9" style="10"/>
-    <col min="7931" max="7931" width="10.875" style="10" customWidth="1"/>
+    <col min="7931" max="7931" width="10.85546875" style="10" customWidth="1"/>
     <col min="7932" max="7932" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="7933" max="7933" width="10.5625" style="10" customWidth="1"/>
-    <col min="7934" max="7934" width="10.875" style="10" customWidth="1"/>
+    <col min="7933" max="7933" width="10.5703125" style="10" customWidth="1"/>
+    <col min="7934" max="7934" width="10.85546875" style="10" customWidth="1"/>
     <col min="7935" max="8179" width="9" style="10"/>
-    <col min="8180" max="8180" width="26.5625" style="10" customWidth="1"/>
-    <col min="8181" max="8181" width="13.125" style="10" customWidth="1"/>
+    <col min="8180" max="8180" width="26.5703125" style="10" customWidth="1"/>
+    <col min="8181" max="8181" width="13.140625" style="10" customWidth="1"/>
     <col min="8182" max="8186" width="9" style="10"/>
-    <col min="8187" max="8187" width="10.875" style="10" customWidth="1"/>
+    <col min="8187" max="8187" width="10.85546875" style="10" customWidth="1"/>
     <col min="8188" max="8188" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="8189" max="8189" width="10.5625" style="10" customWidth="1"/>
-    <col min="8190" max="8190" width="10.875" style="10" customWidth="1"/>
+    <col min="8189" max="8189" width="10.5703125" style="10" customWidth="1"/>
+    <col min="8190" max="8190" width="10.85546875" style="10" customWidth="1"/>
     <col min="8191" max="8435" width="9" style="10"/>
-    <col min="8436" max="8436" width="26.5625" style="10" customWidth="1"/>
-    <col min="8437" max="8437" width="13.125" style="10" customWidth="1"/>
+    <col min="8436" max="8436" width="26.5703125" style="10" customWidth="1"/>
+    <col min="8437" max="8437" width="13.140625" style="10" customWidth="1"/>
     <col min="8438" max="8442" width="9" style="10"/>
-    <col min="8443" max="8443" width="10.875" style="10" customWidth="1"/>
+    <col min="8443" max="8443" width="10.85546875" style="10" customWidth="1"/>
     <col min="8444" max="8444" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="8445" max="8445" width="10.5625" style="10" customWidth="1"/>
-    <col min="8446" max="8446" width="10.875" style="10" customWidth="1"/>
+    <col min="8445" max="8445" width="10.5703125" style="10" customWidth="1"/>
+    <col min="8446" max="8446" width="10.85546875" style="10" customWidth="1"/>
     <col min="8447" max="8691" width="9" style="10"/>
-    <col min="8692" max="8692" width="26.5625" style="10" customWidth="1"/>
-    <col min="8693" max="8693" width="13.125" style="10" customWidth="1"/>
+    <col min="8692" max="8692" width="26.5703125" style="10" customWidth="1"/>
+    <col min="8693" max="8693" width="13.140625" style="10" customWidth="1"/>
     <col min="8694" max="8698" width="9" style="10"/>
-    <col min="8699" max="8699" width="10.875" style="10" customWidth="1"/>
+    <col min="8699" max="8699" width="10.85546875" style="10" customWidth="1"/>
     <col min="8700" max="8700" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="8701" max="8701" width="10.5625" style="10" customWidth="1"/>
-    <col min="8702" max="8702" width="10.875" style="10" customWidth="1"/>
+    <col min="8701" max="8701" width="10.5703125" style="10" customWidth="1"/>
+    <col min="8702" max="8702" width="10.85546875" style="10" customWidth="1"/>
     <col min="8703" max="8947" width="9" style="10"/>
-    <col min="8948" max="8948" width="26.5625" style="10" customWidth="1"/>
-    <col min="8949" max="8949" width="13.125" style="10" customWidth="1"/>
+    <col min="8948" max="8948" width="26.5703125" style="10" customWidth="1"/>
+    <col min="8949" max="8949" width="13.140625" style="10" customWidth="1"/>
     <col min="8950" max="8954" width="9" style="10"/>
-    <col min="8955" max="8955" width="10.875" style="10" customWidth="1"/>
+    <col min="8955" max="8955" width="10.85546875" style="10" customWidth="1"/>
     <col min="8956" max="8956" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="8957" max="8957" width="10.5625" style="10" customWidth="1"/>
-    <col min="8958" max="8958" width="10.875" style="10" customWidth="1"/>
+    <col min="8957" max="8957" width="10.5703125" style="10" customWidth="1"/>
+    <col min="8958" max="8958" width="10.85546875" style="10" customWidth="1"/>
     <col min="8959" max="9203" width="9" style="10"/>
-    <col min="9204" max="9204" width="26.5625" style="10" customWidth="1"/>
-    <col min="9205" max="9205" width="13.125" style="10" customWidth="1"/>
+    <col min="9204" max="9204" width="26.5703125" style="10" customWidth="1"/>
+    <col min="9205" max="9205" width="13.140625" style="10" customWidth="1"/>
     <col min="9206" max="9210" width="9" style="10"/>
-    <col min="9211" max="9211" width="10.875" style="10" customWidth="1"/>
+    <col min="9211" max="9211" width="10.85546875" style="10" customWidth="1"/>
     <col min="9212" max="9212" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="9213" max="9213" width="10.5625" style="10" customWidth="1"/>
-    <col min="9214" max="9214" width="10.875" style="10" customWidth="1"/>
+    <col min="9213" max="9213" width="10.5703125" style="10" customWidth="1"/>
+    <col min="9214" max="9214" width="10.85546875" style="10" customWidth="1"/>
     <col min="9215" max="9459" width="9" style="10"/>
-    <col min="9460" max="9460" width="26.5625" style="10" customWidth="1"/>
-    <col min="9461" max="9461" width="13.125" style="10" customWidth="1"/>
+    <col min="9460" max="9460" width="26.5703125" style="10" customWidth="1"/>
+    <col min="9461" max="9461" width="13.140625" style="10" customWidth="1"/>
     <col min="9462" max="9466" width="9" style="10"/>
-    <col min="9467" max="9467" width="10.875" style="10" customWidth="1"/>
+    <col min="9467" max="9467" width="10.85546875" style="10" customWidth="1"/>
     <col min="9468" max="9468" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="9469" max="9469" width="10.5625" style="10" customWidth="1"/>
-    <col min="9470" max="9470" width="10.875" style="10" customWidth="1"/>
+    <col min="9469" max="9469" width="10.5703125" style="10" customWidth="1"/>
+    <col min="9470" max="9470" width="10.85546875" style="10" customWidth="1"/>
     <col min="9471" max="9715" width="9" style="10"/>
-    <col min="9716" max="9716" width="26.5625" style="10" customWidth="1"/>
-    <col min="9717" max="9717" width="13.125" style="10" customWidth="1"/>
+    <col min="9716" max="9716" width="26.5703125" style="10" customWidth="1"/>
+    <col min="9717" max="9717" width="13.140625" style="10" customWidth="1"/>
     <col min="9718" max="9722" width="9" style="10"/>
-    <col min="9723" max="9723" width="10.875" style="10" customWidth="1"/>
+    <col min="9723" max="9723" width="10.85546875" style="10" customWidth="1"/>
     <col min="9724" max="9724" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="9725" max="9725" width="10.5625" style="10" customWidth="1"/>
-    <col min="9726" max="9726" width="10.875" style="10" customWidth="1"/>
+    <col min="9725" max="9725" width="10.5703125" style="10" customWidth="1"/>
+    <col min="9726" max="9726" width="10.85546875" style="10" customWidth="1"/>
     <col min="9727" max="9971" width="9" style="10"/>
-    <col min="9972" max="9972" width="26.5625" style="10" customWidth="1"/>
-    <col min="9973" max="9973" width="13.125" style="10" customWidth="1"/>
+    <col min="9972" max="9972" width="26.5703125" style="10" customWidth="1"/>
+    <col min="9973" max="9973" width="13.140625" style="10" customWidth="1"/>
     <col min="9974" max="9978" width="9" style="10"/>
-    <col min="9979" max="9979" width="10.875" style="10" customWidth="1"/>
+    <col min="9979" max="9979" width="10.85546875" style="10" customWidth="1"/>
     <col min="9980" max="9980" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="9981" max="9981" width="10.5625" style="10" customWidth="1"/>
-    <col min="9982" max="9982" width="10.875" style="10" customWidth="1"/>
+    <col min="9981" max="9981" width="10.5703125" style="10" customWidth="1"/>
+    <col min="9982" max="9982" width="10.85546875" style="10" customWidth="1"/>
     <col min="9983" max="10227" width="9" style="10"/>
-    <col min="10228" max="10228" width="26.5625" style="10" customWidth="1"/>
-    <col min="10229" max="10229" width="13.125" style="10" customWidth="1"/>
+    <col min="10228" max="10228" width="26.5703125" style="10" customWidth="1"/>
+    <col min="10229" max="10229" width="13.140625" style="10" customWidth="1"/>
     <col min="10230" max="10234" width="9" style="10"/>
-    <col min="10235" max="10235" width="10.875" style="10" customWidth="1"/>
+    <col min="10235" max="10235" width="10.85546875" style="10" customWidth="1"/>
     <col min="10236" max="10236" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="10237" max="10237" width="10.5625" style="10" customWidth="1"/>
-    <col min="10238" max="10238" width="10.875" style="10" customWidth="1"/>
+    <col min="10237" max="10237" width="10.5703125" style="10" customWidth="1"/>
+    <col min="10238" max="10238" width="10.85546875" style="10" customWidth="1"/>
     <col min="10239" max="10483" width="9" style="10"/>
-    <col min="10484" max="10484" width="26.5625" style="10" customWidth="1"/>
-    <col min="10485" max="10485" width="13.125" style="10" customWidth="1"/>
+    <col min="10484" max="10484" width="26.5703125" style="10" customWidth="1"/>
+    <col min="10485" max="10485" width="13.140625" style="10" customWidth="1"/>
     <col min="10486" max="10490" width="9" style="10"/>
-    <col min="10491" max="10491" width="10.875" style="10" customWidth="1"/>
+    <col min="10491" max="10491" width="10.85546875" style="10" customWidth="1"/>
     <col min="10492" max="10492" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="10493" max="10493" width="10.5625" style="10" customWidth="1"/>
-    <col min="10494" max="10494" width="10.875" style="10" customWidth="1"/>
+    <col min="10493" max="10493" width="10.5703125" style="10" customWidth="1"/>
+    <col min="10494" max="10494" width="10.85546875" style="10" customWidth="1"/>
     <col min="10495" max="10739" width="9" style="10"/>
-    <col min="10740" max="10740" width="26.5625" style="10" customWidth="1"/>
-    <col min="10741" max="10741" width="13.125" style="10" customWidth="1"/>
+    <col min="10740" max="10740" width="26.5703125" style="10" customWidth="1"/>
+    <col min="10741" max="10741" width="13.140625" style="10" customWidth="1"/>
     <col min="10742" max="10746" width="9" style="10"/>
-    <col min="10747" max="10747" width="10.875" style="10" customWidth="1"/>
+    <col min="10747" max="10747" width="10.85546875" style="10" customWidth="1"/>
     <col min="10748" max="10748" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="10749" max="10749" width="10.5625" style="10" customWidth="1"/>
-    <col min="10750" max="10750" width="10.875" style="10" customWidth="1"/>
+    <col min="10749" max="10749" width="10.5703125" style="10" customWidth="1"/>
+    <col min="10750" max="10750" width="10.85546875" style="10" customWidth="1"/>
     <col min="10751" max="10995" width="9" style="10"/>
-    <col min="10996" max="10996" width="26.5625" style="10" customWidth="1"/>
-    <col min="10997" max="10997" width="13.125" style="10" customWidth="1"/>
+    <col min="10996" max="10996" width="26.5703125" style="10" customWidth="1"/>
+    <col min="10997" max="10997" width="13.140625" style="10" customWidth="1"/>
     <col min="10998" max="11002" width="9" style="10"/>
-    <col min="11003" max="11003" width="10.875" style="10" customWidth="1"/>
+    <col min="11003" max="11003" width="10.85546875" style="10" customWidth="1"/>
     <col min="11004" max="11004" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="11005" max="11005" width="10.5625" style="10" customWidth="1"/>
-    <col min="11006" max="11006" width="10.875" style="10" customWidth="1"/>
+    <col min="11005" max="11005" width="10.5703125" style="10" customWidth="1"/>
+    <col min="11006" max="11006" width="10.85546875" style="10" customWidth="1"/>
     <col min="11007" max="11251" width="9" style="10"/>
-    <col min="11252" max="11252" width="26.5625" style="10" customWidth="1"/>
-    <col min="11253" max="11253" width="13.125" style="10" customWidth="1"/>
+    <col min="11252" max="11252" width="26.5703125" style="10" customWidth="1"/>
+    <col min="11253" max="11253" width="13.140625" style="10" customWidth="1"/>
     <col min="11254" max="11258" width="9" style="10"/>
-    <col min="11259" max="11259" width="10.875" style="10" customWidth="1"/>
+    <col min="11259" max="11259" width="10.85546875" style="10" customWidth="1"/>
     <col min="11260" max="11260" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="11261" max="11261" width="10.5625" style="10" customWidth="1"/>
-    <col min="11262" max="11262" width="10.875" style="10" customWidth="1"/>
+    <col min="11261" max="11261" width="10.5703125" style="10" customWidth="1"/>
+    <col min="11262" max="11262" width="10.85546875" style="10" customWidth="1"/>
     <col min="11263" max="11507" width="9" style="10"/>
-    <col min="11508" max="11508" width="26.5625" style="10" customWidth="1"/>
-    <col min="11509" max="11509" width="13.125" style="10" customWidth="1"/>
+    <col min="11508" max="11508" width="26.5703125" style="10" customWidth="1"/>
+    <col min="11509" max="11509" width="13.140625" style="10" customWidth="1"/>
     <col min="11510" max="11514" width="9" style="10"/>
-    <col min="11515" max="11515" width="10.875" style="10" customWidth="1"/>
+    <col min="11515" max="11515" width="10.85546875" style="10" customWidth="1"/>
     <col min="11516" max="11516" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="11517" max="11517" width="10.5625" style="10" customWidth="1"/>
-    <col min="11518" max="11518" width="10.875" style="10" customWidth="1"/>
+    <col min="11517" max="11517" width="10.5703125" style="10" customWidth="1"/>
+    <col min="11518" max="11518" width="10.85546875" style="10" customWidth="1"/>
     <col min="11519" max="11763" width="9" style="10"/>
-    <col min="11764" max="11764" width="26.5625" style="10" customWidth="1"/>
-    <col min="11765" max="11765" width="13.125" style="10" customWidth="1"/>
+    <col min="11764" max="11764" width="26.5703125" style="10" customWidth="1"/>
+    <col min="11765" max="11765" width="13.140625" style="10" customWidth="1"/>
     <col min="11766" max="11770" width="9" style="10"/>
-    <col min="11771" max="11771" width="10.875" style="10" customWidth="1"/>
+    <col min="11771" max="11771" width="10.85546875" style="10" customWidth="1"/>
     <col min="11772" max="11772" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="11773" max="11773" width="10.5625" style="10" customWidth="1"/>
-    <col min="11774" max="11774" width="10.875" style="10" customWidth="1"/>
+    <col min="11773" max="11773" width="10.5703125" style="10" customWidth="1"/>
+    <col min="11774" max="11774" width="10.85546875" style="10" customWidth="1"/>
     <col min="11775" max="12019" width="9" style="10"/>
-    <col min="12020" max="12020" width="26.5625" style="10" customWidth="1"/>
-    <col min="12021" max="12021" width="13.125" style="10" customWidth="1"/>
+    <col min="12020" max="12020" width="26.5703125" style="10" customWidth="1"/>
+    <col min="12021" max="12021" width="13.140625" style="10" customWidth="1"/>
     <col min="12022" max="12026" width="9" style="10"/>
-    <col min="12027" max="12027" width="10.875" style="10" customWidth="1"/>
+    <col min="12027" max="12027" width="10.85546875" style="10" customWidth="1"/>
     <col min="12028" max="12028" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="12029" max="12029" width="10.5625" style="10" customWidth="1"/>
-    <col min="12030" max="12030" width="10.875" style="10" customWidth="1"/>
+    <col min="12029" max="12029" width="10.5703125" style="10" customWidth="1"/>
+    <col min="12030" max="12030" width="10.85546875" style="10" customWidth="1"/>
     <col min="12031" max="12275" width="9" style="10"/>
-    <col min="12276" max="12276" width="26.5625" style="10" customWidth="1"/>
-    <col min="12277" max="12277" width="13.125" style="10" customWidth="1"/>
+    <col min="12276" max="12276" width="26.5703125" style="10" customWidth="1"/>
+    <col min="12277" max="12277" width="13.140625" style="10" customWidth="1"/>
     <col min="12278" max="12282" width="9" style="10"/>
-    <col min="12283" max="12283" width="10.875" style="10" customWidth="1"/>
+    <col min="12283" max="12283" width="10.85546875" style="10" customWidth="1"/>
     <col min="12284" max="12284" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="12285" max="12285" width="10.5625" style="10" customWidth="1"/>
-    <col min="12286" max="12286" width="10.875" style="10" customWidth="1"/>
+    <col min="12285" max="12285" width="10.5703125" style="10" customWidth="1"/>
+    <col min="12286" max="12286" width="10.85546875" style="10" customWidth="1"/>
     <col min="12287" max="12531" width="9" style="10"/>
-    <col min="12532" max="12532" width="26.5625" style="10" customWidth="1"/>
-    <col min="12533" max="12533" width="13.125" style="10" customWidth="1"/>
+    <col min="12532" max="12532" width="26.5703125" style="10" customWidth="1"/>
+    <col min="12533" max="12533" width="13.140625" style="10" customWidth="1"/>
     <col min="12534" max="12538" width="9" style="10"/>
-    <col min="12539" max="12539" width="10.875" style="10" customWidth="1"/>
+    <col min="12539" max="12539" width="10.85546875" style="10" customWidth="1"/>
     <col min="12540" max="12540" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="12541" max="12541" width="10.5625" style="10" customWidth="1"/>
-    <col min="12542" max="12542" width="10.875" style="10" customWidth="1"/>
+    <col min="12541" max="12541" width="10.5703125" style="10" customWidth="1"/>
+    <col min="12542" max="12542" width="10.85546875" style="10" customWidth="1"/>
     <col min="12543" max="12787" width="9" style="10"/>
-    <col min="12788" max="12788" width="26.5625" style="10" customWidth="1"/>
-    <col min="12789" max="12789" width="13.125" style="10" customWidth="1"/>
+    <col min="12788" max="12788" width="26.5703125" style="10" customWidth="1"/>
+    <col min="12789" max="12789" width="13.140625" style="10" customWidth="1"/>
     <col min="12790" max="12794" width="9" style="10"/>
-    <col min="12795" max="12795" width="10.875" style="10" customWidth="1"/>
+    <col min="12795" max="12795" width="10.85546875" style="10" customWidth="1"/>
     <col min="12796" max="12796" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="12797" max="12797" width="10.5625" style="10" customWidth="1"/>
-    <col min="12798" max="12798" width="10.875" style="10" customWidth="1"/>
+    <col min="12797" max="12797" width="10.5703125" style="10" customWidth="1"/>
+    <col min="12798" max="12798" width="10.85546875" style="10" customWidth="1"/>
     <col min="12799" max="13043" width="9" style="10"/>
-    <col min="13044" max="13044" width="26.5625" style="10" customWidth="1"/>
-    <col min="13045" max="13045" width="13.125" style="10" customWidth="1"/>
+    <col min="13044" max="13044" width="26.5703125" style="10" customWidth="1"/>
+    <col min="13045" max="13045" width="13.140625" style="10" customWidth="1"/>
     <col min="13046" max="13050" width="9" style="10"/>
-    <col min="13051" max="13051" width="10.875" style="10" customWidth="1"/>
+    <col min="13051" max="13051" width="10.85546875" style="10" customWidth="1"/>
     <col min="13052" max="13052" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="13053" max="13053" width="10.5625" style="10" customWidth="1"/>
-    <col min="13054" max="13054" width="10.875" style="10" customWidth="1"/>
+    <col min="13053" max="13053" width="10.5703125" style="10" customWidth="1"/>
+    <col min="13054" max="13054" width="10.85546875" style="10" customWidth="1"/>
     <col min="13055" max="13299" width="9" style="10"/>
-    <col min="13300" max="13300" width="26.5625" style="10" customWidth="1"/>
-    <col min="13301" max="13301" width="13.125" style="10" customWidth="1"/>
+    <col min="13300" max="13300" width="26.5703125" style="10" customWidth="1"/>
+    <col min="13301" max="13301" width="13.140625" style="10" customWidth="1"/>
     <col min="13302" max="13306" width="9" style="10"/>
-    <col min="13307" max="13307" width="10.875" style="10" customWidth="1"/>
+    <col min="13307" max="13307" width="10.85546875" style="10" customWidth="1"/>
     <col min="13308" max="13308" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="13309" max="13309" width="10.5625" style="10" customWidth="1"/>
-    <col min="13310" max="13310" width="10.875" style="10" customWidth="1"/>
+    <col min="13309" max="13309" width="10.5703125" style="10" customWidth="1"/>
+    <col min="13310" max="13310" width="10.85546875" style="10" customWidth="1"/>
     <col min="13311" max="13555" width="9" style="10"/>
-    <col min="13556" max="13556" width="26.5625" style="10" customWidth="1"/>
-    <col min="13557" max="13557" width="13.125" style="10" customWidth="1"/>
+    <col min="13556" max="13556" width="26.5703125" style="10" customWidth="1"/>
+    <col min="13557" max="13557" width="13.140625" style="10" customWidth="1"/>
     <col min="13558" max="13562" width="9" style="10"/>
-    <col min="13563" max="13563" width="10.875" style="10" customWidth="1"/>
+    <col min="13563" max="13563" width="10.85546875" style="10" customWidth="1"/>
     <col min="13564" max="13564" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="13565" max="13565" width="10.5625" style="10" customWidth="1"/>
-    <col min="13566" max="13566" width="10.875" style="10" customWidth="1"/>
+    <col min="13565" max="13565" width="10.5703125" style="10" customWidth="1"/>
+    <col min="13566" max="13566" width="10.85546875" style="10" customWidth="1"/>
     <col min="13567" max="13811" width="9" style="10"/>
-    <col min="13812" max="13812" width="26.5625" style="10" customWidth="1"/>
-    <col min="13813" max="13813" width="13.125" style="10" customWidth="1"/>
+    <col min="13812" max="13812" width="26.5703125" style="10" customWidth="1"/>
+    <col min="13813" max="13813" width="13.140625" style="10" customWidth="1"/>
     <col min="13814" max="13818" width="9" style="10"/>
-    <col min="13819" max="13819" width="10.875" style="10" customWidth="1"/>
+    <col min="13819" max="13819" width="10.85546875" style="10" customWidth="1"/>
     <col min="13820" max="13820" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="13821" max="13821" width="10.5625" style="10" customWidth="1"/>
-    <col min="13822" max="13822" width="10.875" style="10" customWidth="1"/>
+    <col min="13821" max="13821" width="10.5703125" style="10" customWidth="1"/>
+    <col min="13822" max="13822" width="10.85546875" style="10" customWidth="1"/>
     <col min="13823" max="14067" width="9" style="10"/>
-    <col min="14068" max="14068" width="26.5625" style="10" customWidth="1"/>
-    <col min="14069" max="14069" width="13.125" style="10" customWidth="1"/>
+    <col min="14068" max="14068" width="26.5703125" style="10" customWidth="1"/>
+    <col min="14069" max="14069" width="13.140625" style="10" customWidth="1"/>
     <col min="14070" max="14074" width="9" style="10"/>
-    <col min="14075" max="14075" width="10.875" style="10" customWidth="1"/>
+    <col min="14075" max="14075" width="10.85546875" style="10" customWidth="1"/>
     <col min="14076" max="14076" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="14077" max="14077" width="10.5625" style="10" customWidth="1"/>
-    <col min="14078" max="14078" width="10.875" style="10" customWidth="1"/>
+    <col min="14077" max="14077" width="10.5703125" style="10" customWidth="1"/>
+    <col min="14078" max="14078" width="10.85546875" style="10" customWidth="1"/>
     <col min="14079" max="14323" width="9" style="10"/>
-    <col min="14324" max="14324" width="26.5625" style="10" customWidth="1"/>
-    <col min="14325" max="14325" width="13.125" style="10" customWidth="1"/>
+    <col min="14324" max="14324" width="26.5703125" style="10" customWidth="1"/>
+    <col min="14325" max="14325" width="13.140625" style="10" customWidth="1"/>
     <col min="14326" max="14330" width="9" style="10"/>
-    <col min="14331" max="14331" width="10.875" style="10" customWidth="1"/>
+    <col min="14331" max="14331" width="10.85546875" style="10" customWidth="1"/>
     <col min="14332" max="14332" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="14333" max="14333" width="10.5625" style="10" customWidth="1"/>
-    <col min="14334" max="14334" width="10.875" style="10" customWidth="1"/>
+    <col min="14333" max="14333" width="10.5703125" style="10" customWidth="1"/>
+    <col min="14334" max="14334" width="10.85546875" style="10" customWidth="1"/>
     <col min="14335" max="14579" width="9" style="10"/>
-    <col min="14580" max="14580" width="26.5625" style="10" customWidth="1"/>
-    <col min="14581" max="14581" width="13.125" style="10" customWidth="1"/>
+    <col min="14580" max="14580" width="26.5703125" style="10" customWidth="1"/>
+    <col min="14581" max="14581" width="13.140625" style="10" customWidth="1"/>
     <col min="14582" max="14586" width="9" style="10"/>
-    <col min="14587" max="14587" width="10.875" style="10" customWidth="1"/>
+    <col min="14587" max="14587" width="10.85546875" style="10" customWidth="1"/>
     <col min="14588" max="14588" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="14589" max="14589" width="10.5625" style="10" customWidth="1"/>
-    <col min="14590" max="14590" width="10.875" style="10" customWidth="1"/>
+    <col min="14589" max="14589" width="10.5703125" style="10" customWidth="1"/>
+    <col min="14590" max="14590" width="10.85546875" style="10" customWidth="1"/>
     <col min="14591" max="14835" width="9" style="10"/>
-    <col min="14836" max="14836" width="26.5625" style="10" customWidth="1"/>
-    <col min="14837" max="14837" width="13.125" style="10" customWidth="1"/>
+    <col min="14836" max="14836" width="26.5703125" style="10" customWidth="1"/>
+    <col min="14837" max="14837" width="13.140625" style="10" customWidth="1"/>
     <col min="14838" max="14842" width="9" style="10"/>
-    <col min="14843" max="14843" width="10.875" style="10" customWidth="1"/>
+    <col min="14843" max="14843" width="10.85546875" style="10" customWidth="1"/>
     <col min="14844" max="14844" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="14845" max="14845" width="10.5625" style="10" customWidth="1"/>
-    <col min="14846" max="14846" width="10.875" style="10" customWidth="1"/>
+    <col min="14845" max="14845" width="10.5703125" style="10" customWidth="1"/>
+    <col min="14846" max="14846" width="10.85546875" style="10" customWidth="1"/>
     <col min="14847" max="15091" width="9" style="10"/>
-    <col min="15092" max="15092" width="26.5625" style="10" customWidth="1"/>
-    <col min="15093" max="15093" width="13.125" style="10" customWidth="1"/>
+    <col min="15092" max="15092" width="26.5703125" style="10" customWidth="1"/>
+    <col min="15093" max="15093" width="13.140625" style="10" customWidth="1"/>
     <col min="15094" max="15098" width="9" style="10"/>
-    <col min="15099" max="15099" width="10.875" style="10" customWidth="1"/>
+    <col min="15099" max="15099" width="10.85546875" style="10" customWidth="1"/>
     <col min="15100" max="15100" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="15101" max="15101" width="10.5625" style="10" customWidth="1"/>
-    <col min="15102" max="15102" width="10.875" style="10" customWidth="1"/>
+    <col min="15101" max="15101" width="10.5703125" style="10" customWidth="1"/>
+    <col min="15102" max="15102" width="10.85546875" style="10" customWidth="1"/>
     <col min="15103" max="15347" width="9" style="10"/>
-    <col min="15348" max="15348" width="26.5625" style="10" customWidth="1"/>
-    <col min="15349" max="15349" width="13.125" style="10" customWidth="1"/>
+    <col min="15348" max="15348" width="26.5703125" style="10" customWidth="1"/>
+    <col min="15349" max="15349" width="13.140625" style="10" customWidth="1"/>
     <col min="15350" max="15354" width="9" style="10"/>
-    <col min="15355" max="15355" width="10.875" style="10" customWidth="1"/>
+    <col min="15355" max="15355" width="10.85546875" style="10" customWidth="1"/>
     <col min="15356" max="15356" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="15357" max="15357" width="10.5625" style="10" customWidth="1"/>
-    <col min="15358" max="15358" width="10.875" style="10" customWidth="1"/>
+    <col min="15357" max="15357" width="10.5703125" style="10" customWidth="1"/>
+    <col min="15358" max="15358" width="10.85546875" style="10" customWidth="1"/>
     <col min="15359" max="15603" width="9" style="10"/>
-    <col min="15604" max="15604" width="26.5625" style="10" customWidth="1"/>
-    <col min="15605" max="15605" width="13.125" style="10" customWidth="1"/>
+    <col min="15604" max="15604" width="26.5703125" style="10" customWidth="1"/>
+    <col min="15605" max="15605" width="13.140625" style="10" customWidth="1"/>
     <col min="15606" max="15610" width="9" style="10"/>
-    <col min="15611" max="15611" width="10.875" style="10" customWidth="1"/>
+    <col min="15611" max="15611" width="10.85546875" style="10" customWidth="1"/>
     <col min="15612" max="15612" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="15613" max="15613" width="10.5625" style="10" customWidth="1"/>
-    <col min="15614" max="15614" width="10.875" style="10" customWidth="1"/>
+    <col min="15613" max="15613" width="10.5703125" style="10" customWidth="1"/>
+    <col min="15614" max="15614" width="10.85546875" style="10" customWidth="1"/>
     <col min="15615" max="15859" width="9" style="10"/>
-    <col min="15860" max="15860" width="26.5625" style="10" customWidth="1"/>
-    <col min="15861" max="15861" width="13.125" style="10" customWidth="1"/>
+    <col min="15860" max="15860" width="26.5703125" style="10" customWidth="1"/>
+    <col min="15861" max="15861" width="13.140625" style="10" customWidth="1"/>
     <col min="15862" max="15866" width="9" style="10"/>
-    <col min="15867" max="15867" width="10.875" style="10" customWidth="1"/>
+    <col min="15867" max="15867" width="10.85546875" style="10" customWidth="1"/>
     <col min="15868" max="15868" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="15869" max="15869" width="10.5625" style="10" customWidth="1"/>
-    <col min="15870" max="15870" width="10.875" style="10" customWidth="1"/>
+    <col min="15869" max="15869" width="10.5703125" style="10" customWidth="1"/>
+    <col min="15870" max="15870" width="10.85546875" style="10" customWidth="1"/>
     <col min="15871" max="16115" width="9" style="10"/>
-    <col min="16116" max="16116" width="26.5625" style="10" customWidth="1"/>
-    <col min="16117" max="16117" width="13.125" style="10" customWidth="1"/>
+    <col min="16116" max="16116" width="26.5703125" style="10" customWidth="1"/>
+    <col min="16117" max="16117" width="13.140625" style="10" customWidth="1"/>
     <col min="16118" max="16122" width="9" style="10"/>
-    <col min="16123" max="16123" width="10.875" style="10" customWidth="1"/>
+    <col min="16123" max="16123" width="10.85546875" style="10" customWidth="1"/>
     <col min="16124" max="16124" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="16125" max="16125" width="10.5625" style="10" customWidth="1"/>
-    <col min="16126" max="16126" width="10.875" style="10" customWidth="1"/>
+    <col min="16125" max="16125" width="10.5703125" style="10" customWidth="1"/>
+    <col min="16126" max="16126" width="10.85546875" style="10" customWidth="1"/>
     <col min="16127" max="16384" width="9" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>100</v>
       </c>
       <c r="E3" s="11"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
         <v>101</v>
       </c>
@@ -4462,7 +5289,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>102</v>
       </c>
@@ -4470,7 +5297,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>103</v>
       </c>
@@ -4494,7 +5321,7 @@
       </c>
       <c r="H7" s="15"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
         <v>104</v>
       </c>
@@ -4517,7 +5344,7 @@
         <v>12.95</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
         <v>105</v>
       </c>
@@ -4546,12 +5373,12 @@
         <v>0.64749999999999996</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>103</v>
       </c>
@@ -4574,7 +5401,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
         <v>107</v>
       </c>
@@ -4597,7 +5424,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B13" s="21" t="s">
         <v>2</v>
       </c>
@@ -4617,7 +5444,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
         <v>108</v>
       </c>
@@ -4643,12 +5470,12 @@
         <v>109</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B17" s="23"/>
       <c r="C17" s="23"/>
       <c r="D17" s="23"/>
@@ -4656,7 +5483,7 @@
       <c r="F17" s="23"/>
       <c r="G17" s="23"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
         <v>111</v>
       </c>
@@ -4679,7 +5506,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B19" s="21"/>
       <c r="C19" s="21"/>
       <c r="D19" s="21"/>
@@ -4687,7 +5514,7 @@
       <c r="F19" s="21"/>
       <c r="G19" s="21"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
         <v>112</v>
       </c>
@@ -4722,7 +5549,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B21" s="23" t="s">
         <v>2</v>
       </c>
@@ -4742,7 +5569,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
         <v>115</v>
       </c>
@@ -4768,16 +5595,16 @@
         <v>116</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="19"/>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="24" t="s">
         <v>117</v>
       </c>
       <c r="B24" s="18"/>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>103</v>
       </c>
@@ -4803,7 +5630,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
         <v>119</v>
       </c>
@@ -4836,7 +5663,7 @@
         <v>6312.5</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>120</v>
       </c>
@@ -4869,7 +5696,7 @@
         <v>1529250</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="H28" s="26">
         <f>SUM(H26:H27)</f>
         <v>1535562.5</v>

--- a/class_excel/temp_midterm.xlsx
+++ b/class_excel/temp_midterm.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\T00229\Documents\GitHub\DADS7102\class_excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nuna\Documents\GitHub\DADS7102\class_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{096B21DD-E272-4CBA-85A1-A6582E4189E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{729ED7BC-EA08-4AE2-AB99-EA6C049BC5B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="11" xr2:uid="{962D6ACA-47B2-4C7E-82D5-0F5476EE75BF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="11" xr2:uid="{962D6ACA-47B2-4C7E-82D5-0F5476EE75BF}"/>
   </bookViews>
   <sheets>
     <sheet name="ch_1_1" sheetId="1" r:id="rId1"/>
@@ -56,6 +56,7 @@
     <definedName name="solver_adj" localSheetId="8" hidden="1">ch_3_3!$B$12:$G$12</definedName>
     <definedName name="solver_adj" localSheetId="9" hidden="1">ch_3_4!$E$2:$E$11</definedName>
     <definedName name="solver_adj" localSheetId="10" hidden="1">ch4_1!$B$11:$F$12</definedName>
+    <definedName name="solver_adj" localSheetId="11" hidden="1">ch4_2!$B$2:$H$2</definedName>
     <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="1" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="2" hidden="1">0.0001</definedName>
@@ -67,6 +68,7 @@
     <definedName name="solver_cvg" localSheetId="8" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="9" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="10" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="11" hidden="1">0.0001</definedName>
     <definedName name="solver_drv" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="2" hidden="1">1</definedName>
@@ -78,6 +80,7 @@
     <definedName name="solver_drv" localSheetId="8" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="9" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="10" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="11" hidden="1">1</definedName>
     <definedName name="solver_eng" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="2" hidden="1">2</definedName>
@@ -89,6 +92,7 @@
     <definedName name="solver_eng" localSheetId="8" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="9" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="10" hidden="1">2</definedName>
+    <definedName name="solver_eng" localSheetId="11" hidden="1">2</definedName>
     <definedName name="solver_est" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="2" hidden="1">1</definedName>
@@ -100,6 +104,7 @@
     <definedName name="solver_est" localSheetId="8" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="9" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="10" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="11" hidden="1">1</definedName>
     <definedName name="solver_itr" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="2" hidden="1">2147483647</definedName>
@@ -111,6 +116,7 @@
     <definedName name="solver_itr" localSheetId="8" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="9" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="10" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="11" hidden="1">2147483647</definedName>
     <definedName name="solver_lhs1" localSheetId="0" hidden="1">ch_1_1!$B$3:$B$5</definedName>
     <definedName name="solver_lhs1" localSheetId="1" hidden="1">ch_1_2!$F$5:$F$7</definedName>
     <definedName name="solver_lhs1" localSheetId="2" hidden="1">ch_2_1!$B$4:$I$4</definedName>
@@ -122,6 +128,7 @@
     <definedName name="solver_lhs1" localSheetId="8" hidden="1">ch_3_3!$B$12:$G$12</definedName>
     <definedName name="solver_lhs1" localSheetId="9" hidden="1">ch_3_4!$E$2:$E$3</definedName>
     <definedName name="solver_lhs1" localSheetId="10" hidden="1">ch4_1!$B$11:$F$11</definedName>
+    <definedName name="solver_lhs1" localSheetId="11" hidden="1">ch4_2!$B$2:$H$2</definedName>
     <definedName name="solver_lhs2" localSheetId="0" hidden="1">ch_1_1!$B$8:$B$9</definedName>
     <definedName name="solver_lhs2" localSheetId="2" hidden="1">ch_2_1!$O$2:$O$4</definedName>
     <definedName name="solver_lhs2" localSheetId="5" hidden="1">ch_2_4!$J$3</definedName>
@@ -130,6 +137,7 @@
     <definedName name="solver_lhs2" localSheetId="8" hidden="1">ch_3_3!$B$20:$G$20</definedName>
     <definedName name="solver_lhs2" localSheetId="9" hidden="1">ch_3_4!$L$2:$L$8</definedName>
     <definedName name="solver_lhs2" localSheetId="10" hidden="1">ch4_1!$B$12:$F$12</definedName>
+    <definedName name="solver_lhs2" localSheetId="11" hidden="1">ch4_2!$J$4</definedName>
     <definedName name="solver_lhs3" localSheetId="8" hidden="1">ch_3_3!$B$20:$G$20</definedName>
     <definedName name="solver_lhs3" localSheetId="10" hidden="1">ch4_1!$B$16:$B$17</definedName>
     <definedName name="solver_mip" localSheetId="0" hidden="1">2147483647</definedName>
@@ -143,6 +151,7 @@
     <definedName name="solver_mip" localSheetId="8" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="9" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="10" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="11" hidden="1">2147483647</definedName>
     <definedName name="solver_mni" localSheetId="0" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="1" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="2" hidden="1">30</definedName>
@@ -154,6 +163,7 @@
     <definedName name="solver_mni" localSheetId="8" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="9" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="10" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="11" hidden="1">30</definedName>
     <definedName name="solver_mrt" localSheetId="0" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="1" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="2" hidden="1">0.075</definedName>
@@ -165,6 +175,7 @@
     <definedName name="solver_mrt" localSheetId="8" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="9" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="10" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="11" hidden="1">0.075</definedName>
     <definedName name="solver_msl" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="2" hidden="1">2</definedName>
@@ -176,6 +187,7 @@
     <definedName name="solver_msl" localSheetId="8" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="9" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="10" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="11" hidden="1">2</definedName>
     <definedName name="solver_neg" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="2" hidden="1">1</definedName>
@@ -187,6 +199,7 @@
     <definedName name="solver_neg" localSheetId="8" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="9" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="10" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="11" hidden="1">1</definedName>
     <definedName name="solver_nod" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="2" hidden="1">2147483647</definedName>
@@ -198,6 +211,7 @@
     <definedName name="solver_nod" localSheetId="8" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="9" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="10" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="11" hidden="1">2147483647</definedName>
     <definedName name="solver_num" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_num" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_num" localSheetId="2" hidden="1">2</definedName>
@@ -209,6 +223,7 @@
     <definedName name="solver_num" localSheetId="8" hidden="1">3</definedName>
     <definedName name="solver_num" localSheetId="9" hidden="1">2</definedName>
     <definedName name="solver_num" localSheetId="10" hidden="1">3</definedName>
+    <definedName name="solver_num" localSheetId="11" hidden="1">2</definedName>
     <definedName name="solver_nwt" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="2" hidden="1">1</definedName>
@@ -220,6 +235,7 @@
     <definedName name="solver_nwt" localSheetId="8" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="9" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="10" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="11" hidden="1">1</definedName>
     <definedName name="solver_opt" localSheetId="0" hidden="1">ch_1_1!$B$17</definedName>
     <definedName name="solver_opt" localSheetId="1" hidden="1">ch_1_2!$B$10</definedName>
     <definedName name="solver_opt" localSheetId="2" hidden="1">ch_2_1!$J$22</definedName>
@@ -231,6 +247,7 @@
     <definedName name="solver_opt" localSheetId="8" hidden="1">ch_3_3!$N$4</definedName>
     <definedName name="solver_opt" localSheetId="9" hidden="1">ch_3_4!$E$13</definedName>
     <definedName name="solver_opt" localSheetId="10" hidden="1">ch4_1!$B$22</definedName>
+    <definedName name="solver_opt" localSheetId="11" hidden="1">ch4_2!$B$9</definedName>
     <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="1" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="2" hidden="1">0.000001</definedName>
@@ -242,6 +259,7 @@
     <definedName name="solver_pre" localSheetId="8" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="9" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="10" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="11" hidden="1">0.000001</definedName>
     <definedName name="solver_rbv" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="2" hidden="1">1</definedName>
@@ -253,6 +271,7 @@
     <definedName name="solver_rbv" localSheetId="8" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="9" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="10" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="11" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="2" hidden="1">1</definedName>
@@ -264,6 +283,7 @@
     <definedName name="solver_rel1" localSheetId="8" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="9" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="10" hidden="1">5</definedName>
+    <definedName name="solver_rel1" localSheetId="11" hidden="1">5</definedName>
     <definedName name="solver_rel2" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rel2" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_rel2" localSheetId="5" hidden="1">1</definedName>
@@ -272,6 +292,7 @@
     <definedName name="solver_rel2" localSheetId="8" hidden="1">1</definedName>
     <definedName name="solver_rel2" localSheetId="9" hidden="1">1</definedName>
     <definedName name="solver_rel2" localSheetId="10" hidden="1">1</definedName>
+    <definedName name="solver_rel2" localSheetId="11" hidden="1">1</definedName>
     <definedName name="solver_rel3" localSheetId="8" hidden="1">3</definedName>
     <definedName name="solver_rel3" localSheetId="10" hidden="1">1</definedName>
     <definedName name="solver_rhs1" localSheetId="0" hidden="1">ch_1_1!$D$3:$D$5</definedName>
@@ -285,6 +306,7 @@
     <definedName name="solver_rhs1" localSheetId="8" hidden="1">ch_3_3!$B$14:$G$14</definedName>
     <definedName name="solver_rhs1" localSheetId="9" hidden="1">ch_3_4!$G$2:$G$3</definedName>
     <definedName name="solver_rhs1" localSheetId="10" hidden="1">"binary"</definedName>
+    <definedName name="solver_rhs1" localSheetId="11" hidden="1">"binary"</definedName>
     <definedName name="solver_rhs2" localSheetId="0" hidden="1">ch_1_1!$D$8:$D$9</definedName>
     <definedName name="solver_rhs2" localSheetId="2" hidden="1">ch_2_1!$Q$2:$Q$4</definedName>
     <definedName name="solver_rhs2" localSheetId="5" hidden="1">ch_2_4!$L$3</definedName>
@@ -293,6 +315,7 @@
     <definedName name="solver_rhs2" localSheetId="8" hidden="1">ch_3_3!$B$22:$G$22</definedName>
     <definedName name="solver_rhs2" localSheetId="9" hidden="1">ch_3_4!$N$2:$N$8</definedName>
     <definedName name="solver_rhs2" localSheetId="10" hidden="1">ch4_1!$B$14:$F$14</definedName>
+    <definedName name="solver_rhs2" localSheetId="11" hidden="1">ch4_2!$L$4</definedName>
     <definedName name="solver_rhs3" localSheetId="8" hidden="1">0</definedName>
     <definedName name="solver_rhs3" localSheetId="10" hidden="1">ch4_1!$D$16:$D$17</definedName>
     <definedName name="solver_rlx" localSheetId="0" hidden="1">2</definedName>
@@ -306,6 +329,7 @@
     <definedName name="solver_rlx" localSheetId="8" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="9" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="10" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="11" hidden="1">2</definedName>
     <definedName name="solver_rsd" localSheetId="0" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="1" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="2" hidden="1">0</definedName>
@@ -317,6 +341,7 @@
     <definedName name="solver_rsd" localSheetId="8" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="9" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="10" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="11" hidden="1">0</definedName>
     <definedName name="solver_scl" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="2" hidden="1">1</definedName>
@@ -328,6 +353,7 @@
     <definedName name="solver_scl" localSheetId="8" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="9" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="10" hidden="1">1</definedName>
+    <definedName name="solver_scl" localSheetId="11" hidden="1">1</definedName>
     <definedName name="solver_sho" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="2" hidden="1">2</definedName>
@@ -339,6 +365,7 @@
     <definedName name="solver_sho" localSheetId="8" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="9" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="10" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="11" hidden="1">2</definedName>
     <definedName name="solver_ssz" localSheetId="0" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="1" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="2" hidden="1">100</definedName>
@@ -350,6 +377,7 @@
     <definedName name="solver_ssz" localSheetId="8" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="9" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="10" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="11" hidden="1">100</definedName>
     <definedName name="solver_tim" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="2" hidden="1">2147483647</definedName>
@@ -361,6 +389,7 @@
     <definedName name="solver_tim" localSheetId="8" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="9" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="10" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="11" hidden="1">2147483647</definedName>
     <definedName name="solver_tol" localSheetId="0" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="1" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="2" hidden="1">0.01</definedName>
@@ -372,6 +401,7 @@
     <definedName name="solver_tol" localSheetId="8" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="9" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="10" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="11" hidden="1">0.01</definedName>
     <definedName name="solver_typ" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_typ" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_typ" localSheetId="2" hidden="1">1</definedName>
@@ -383,6 +413,7 @@
     <definedName name="solver_typ" localSheetId="8" hidden="1">2</definedName>
     <definedName name="solver_typ" localSheetId="9" hidden="1">2</definedName>
     <definedName name="solver_typ" localSheetId="10" hidden="1">1</definedName>
+    <definedName name="solver_typ" localSheetId="11" hidden="1">1</definedName>
     <definedName name="solver_val" localSheetId="0" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="1" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="2" hidden="1">0</definedName>
@@ -394,6 +425,7 @@
     <definedName name="solver_val" localSheetId="8" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="9" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="10" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="11" hidden="1">0</definedName>
     <definedName name="solver_ver" localSheetId="0" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="1" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="2" hidden="1">3</definedName>
@@ -405,6 +437,7 @@
     <definedName name="solver_ver" localSheetId="8" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="9" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="10" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="11" hidden="1">3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -428,7 +461,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="142">
   <si>
     <t xml:space="preserve">basic </t>
   </si>
@@ -867,7 +900,7 @@
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.000_);\(&quot;$&quot;#,##0.000\)"/>
-    <numFmt numFmtId="168" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -1037,11 +1070,11 @@
     <xf numFmtId="1" fontId="5" fillId="2" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="3" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Comma" xfId="4" builtinId="3"/>
@@ -1064,7 +1097,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Advertising "/>
@@ -1846,7 +1879,7 @@
         <v>290000</v>
       </c>
       <c r="K2">
-        <f>SUMIF($C$2:$C$11, $I2, $E$2:$E$11)</f>
+        <f t="shared" ref="K2:K8" si="0">SUMIF($C$2:$C$11, $I2, $E$2:$E$11)</f>
         <v>0</v>
       </c>
       <c r="L2" s="4">
@@ -1883,15 +1916,15 @@
         <v>2</v>
       </c>
       <c r="J3">
-        <f t="shared" ref="J3:J8" si="0">SUMIF($B$2:$B$11, $I3, $E$2:$E$11)</f>
+        <f t="shared" ref="J3:J8" si="1">SUMIF($B$2:$B$11, $I3, $E$2:$E$11)</f>
         <v>150000</v>
       </c>
       <c r="K3">
-        <f>SUMIF($C$2:$C$11, $I3, $E$2:$E$11)</f>
+        <f t="shared" si="0"/>
         <v>150000</v>
       </c>
       <c r="L3" s="4">
-        <f t="shared" ref="L3:L8" si="1">J3-K3</f>
+        <f t="shared" ref="L3:L8" si="2">J3-K3</f>
         <v>0</v>
       </c>
       <c r="M3" s="7" t="s">
@@ -1918,15 +1951,15 @@
         <v>3</v>
       </c>
       <c r="J4">
+        <f t="shared" si="1"/>
+        <v>140000</v>
+      </c>
+      <c r="K4">
         <f t="shared" si="0"/>
         <v>140000</v>
       </c>
-      <c r="K4">
-        <f>SUMIF($C$2:$C$11, $I4, $E$2:$E$11)</f>
-        <v>140000</v>
-      </c>
       <c r="L4" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M4" s="7" t="s">
@@ -1953,15 +1986,15 @@
         <v>4</v>
       </c>
       <c r="J5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K5">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <f>SUMIF($C$2:$C$11, $I5, $E$2:$E$11)</f>
         <v>90000</v>
       </c>
       <c r="L5" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-90000</v>
       </c>
       <c r="M5" s="7" t="s">
@@ -1992,11 +2025,11 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <f>SUMIF($C$2:$C$11, $I6, $E$2:$E$11)</f>
+        <f t="shared" si="0"/>
         <v>80000</v>
       </c>
       <c r="L6" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-80000</v>
       </c>
       <c r="M6" s="7" t="s">
@@ -2023,15 +2056,15 @@
         <v>6</v>
       </c>
       <c r="J7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K7">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <f>SUMIF($C$2:$C$11, $I7, $E$2:$E$11)</f>
         <v>50000</v>
       </c>
       <c r="L7" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-50000</v>
       </c>
       <c r="M7" s="7" t="s">
@@ -2058,15 +2091,15 @@
         <v>7</v>
       </c>
       <c r="J8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K8">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <f>SUMIF($C$2:$C$11, $I8, $E$2:$E$11)</f>
         <v>70000</v>
       </c>
       <c r="L8" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-70000</v>
       </c>
       <c r="M8" s="7" t="s">
@@ -2305,19 +2338,19 @@
       <c r="A11" t="s">
         <v>129</v>
       </c>
-      <c r="B11" s="30">
-        <v>0</v>
-      </c>
-      <c r="C11" s="30">
+      <c r="B11" s="6">
+        <v>0</v>
+      </c>
+      <c r="C11" s="6">
         <v>1</v>
       </c>
-      <c r="D11" s="30">
-        <v>0</v>
-      </c>
-      <c r="E11" s="30">
-        <v>0</v>
-      </c>
-      <c r="F11" s="30">
+      <c r="D11" s="6">
+        <v>0</v>
+      </c>
+      <c r="E11" s="6">
+        <v>0</v>
+      </c>
+      <c r="F11" s="6">
         <v>1</v>
       </c>
     </row>
@@ -2325,19 +2358,19 @@
       <c r="A12" t="s">
         <v>130</v>
       </c>
-      <c r="B12" s="30">
-        <v>0</v>
-      </c>
-      <c r="C12" s="30">
+      <c r="B12" s="6">
+        <v>0</v>
+      </c>
+      <c r="C12" s="6">
         <v>965.51724137931024</v>
       </c>
-      <c r="D12" s="30">
-        <v>0</v>
-      </c>
-      <c r="E12" s="30">
-        <v>0</v>
-      </c>
-      <c r="F12" s="30">
+      <c r="D12" s="6">
+        <v>0</v>
+      </c>
+      <c r="E12" s="6">
+        <v>0</v>
+      </c>
+      <c r="F12" s="6">
         <v>379.31034482758622</v>
       </c>
     </row>
@@ -2455,9 +2488,180 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA6CB6CF-31AC-43B2-BABC-B89D4F5C3C26}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G1" t="s">
+        <v>78</v>
+      </c>
+      <c r="H1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B2" s="6">
+        <v>0</v>
+      </c>
+      <c r="C2" s="6">
+        <v>1</v>
+      </c>
+      <c r="D2" s="6">
+        <v>1</v>
+      </c>
+      <c r="E2" s="6">
+        <v>1</v>
+      </c>
+      <c r="F2" s="6">
+        <v>0</v>
+      </c>
+      <c r="G2" s="6">
+        <v>0</v>
+      </c>
+      <c r="H2" s="6">
+        <v>1</v>
+      </c>
+      <c r="K2" s="7"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
+      <c r="K3" s="7"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J4" s="4">
+        <f>SUMPRODUCT(B2:H2, B5:H5)</f>
+        <v>14.8</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="L4" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>2.4</v>
+      </c>
+      <c r="D5">
+        <v>3.5</v>
+      </c>
+      <c r="E5">
+        <v>5.9</v>
+      </c>
+      <c r="F5">
+        <v>6.9</v>
+      </c>
+      <c r="G5">
+        <v>4.5</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B6">
+        <v>5.6</v>
+      </c>
+      <c r="C6">
+        <v>2.7</v>
+      </c>
+      <c r="D6">
+        <v>3.9</v>
+      </c>
+      <c r="E6">
+        <v>6.8</v>
+      </c>
+      <c r="F6">
+        <v>7.7</v>
+      </c>
+      <c r="G6">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="H6">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>81</v>
+      </c>
+      <c r="B7">
+        <f>(B6-B5)/B5</f>
+        <v>0.11999999999999993</v>
+      </c>
+      <c r="C7">
+        <f t="shared" ref="C7:H7" si="0">(C6-C5)/C5</f>
+        <v>0.12500000000000011</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="0"/>
+        <v>0.11428571428571425</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="0"/>
+        <v>0.15254237288135583</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="0"/>
+        <v>0.11594202898550722</v>
+      </c>
+      <c r="G7">
+        <f t="shared" si="0"/>
+        <v>0.13333333333333325</v>
+      </c>
+      <c r="H7">
+        <f>(H6-H5)/H5</f>
+        <v>9.9999999999999936E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="2">
+        <f>SUMPRODUCT(B2:H2,B6:H6)</f>
+        <v>16.7</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/class_excel/temp_midterm.xlsx
+++ b/class_excel/temp_midterm.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nuna\Documents\GitHub\DADS7102\class_excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\T00229\Documents\GitHub\DADS7102\class_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{729ED7BC-EA08-4AE2-AB99-EA6C049BC5B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79984835-6A10-4A93-AF56-4D160F9500D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="11" xr2:uid="{962D6ACA-47B2-4C7E-82D5-0F5476EE75BF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="15" xr2:uid="{962D6ACA-47B2-4C7E-82D5-0F5476EE75BF}"/>
   </bookViews>
   <sheets>
     <sheet name="ch_1_1" sheetId="1" r:id="rId1"/>
@@ -24,10 +24,14 @@
     <sheet name="ch_3_3" sheetId="18" r:id="rId9"/>
     <sheet name="ch_3_4" sheetId="19" r:id="rId10"/>
     <sheet name="ch4_1" sheetId="20" r:id="rId11"/>
-    <sheet name="ch4_2" sheetId="21" r:id="rId12"/>
+    <sheet name="ch4_1 (2)" sheetId="27" r:id="rId12"/>
+    <sheet name="ch4_2" sheetId="21" r:id="rId13"/>
+    <sheet name="ch4_3" sheetId="22" r:id="rId14"/>
+    <sheet name="ch4_4" sheetId="23" r:id="rId15"/>
+    <sheet name="ch4_5" sheetId="28" r:id="rId16"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId13"/>
+    <externalReference r:id="rId17"/>
   </externalReferences>
   <definedNames>
     <definedName name="AFinish">[1]project!$K$6</definedName>
@@ -56,7 +60,11 @@
     <definedName name="solver_adj" localSheetId="8" hidden="1">ch_3_3!$B$12:$G$12</definedName>
     <definedName name="solver_adj" localSheetId="9" hidden="1">ch_3_4!$E$2:$E$11</definedName>
     <definedName name="solver_adj" localSheetId="10" hidden="1">ch4_1!$B$11:$F$12</definedName>
-    <definedName name="solver_adj" localSheetId="11" hidden="1">ch4_2!$B$2:$H$2</definedName>
+    <definedName name="solver_adj" localSheetId="11" hidden="1">'ch4_1 (2)'!$B$11:$G$12</definedName>
+    <definedName name="solver_adj" localSheetId="12" hidden="1">ch4_2!$B$2:$H$2</definedName>
+    <definedName name="solver_adj" localSheetId="13" hidden="1">ch4_3!$B$2:$G$2</definedName>
+    <definedName name="solver_adj" localSheetId="14" hidden="1">ch4_4!$B$2:$H$2</definedName>
+    <definedName name="solver_adj" localSheetId="15" hidden="1">ch4_5!$B$14:$G$15</definedName>
     <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="1" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="2" hidden="1">0.0001</definedName>
@@ -69,6 +77,10 @@
     <definedName name="solver_cvg" localSheetId="9" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="10" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="11" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="12" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="13" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="14" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="15" hidden="1">0.0001</definedName>
     <definedName name="solver_drv" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="2" hidden="1">1</definedName>
@@ -81,6 +93,10 @@
     <definedName name="solver_drv" localSheetId="9" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="10" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="11" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="12" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="13" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="14" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="15" hidden="1">1</definedName>
     <definedName name="solver_eng" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="2" hidden="1">2</definedName>
@@ -93,6 +109,10 @@
     <definedName name="solver_eng" localSheetId="9" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="10" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="11" hidden="1">2</definedName>
+    <definedName name="solver_eng" localSheetId="12" hidden="1">2</definedName>
+    <definedName name="solver_eng" localSheetId="13" hidden="1">2</definedName>
+    <definedName name="solver_eng" localSheetId="14" hidden="1">2</definedName>
+    <definedName name="solver_eng" localSheetId="15" hidden="1">2</definedName>
     <definedName name="solver_est" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="2" hidden="1">1</definedName>
@@ -105,6 +125,10 @@
     <definedName name="solver_est" localSheetId="9" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="10" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="11" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="12" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="13" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="14" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="15" hidden="1">1</definedName>
     <definedName name="solver_itr" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="2" hidden="1">2147483647</definedName>
@@ -117,6 +141,10 @@
     <definedName name="solver_itr" localSheetId="9" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="10" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="11" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="12" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="13" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="14" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="15" hidden="1">2147483647</definedName>
     <definedName name="solver_lhs1" localSheetId="0" hidden="1">ch_1_1!$B$3:$B$5</definedName>
     <definedName name="solver_lhs1" localSheetId="1" hidden="1">ch_1_2!$F$5:$F$7</definedName>
     <definedName name="solver_lhs1" localSheetId="2" hidden="1">ch_2_1!$B$4:$I$4</definedName>
@@ -128,7 +156,11 @@
     <definedName name="solver_lhs1" localSheetId="8" hidden="1">ch_3_3!$B$12:$G$12</definedName>
     <definedName name="solver_lhs1" localSheetId="9" hidden="1">ch_3_4!$E$2:$E$3</definedName>
     <definedName name="solver_lhs1" localSheetId="10" hidden="1">ch4_1!$B$11:$F$11</definedName>
-    <definedName name="solver_lhs1" localSheetId="11" hidden="1">ch4_2!$B$2:$H$2</definedName>
+    <definedName name="solver_lhs1" localSheetId="11" hidden="1">'ch4_1 (2)'!$B$11:$G$11</definedName>
+    <definedName name="solver_lhs1" localSheetId="12" hidden="1">ch4_2!$B$2:$H$2</definedName>
+    <definedName name="solver_lhs1" localSheetId="13" hidden="1">ch4_3!$B$2:$G$2</definedName>
+    <definedName name="solver_lhs1" localSheetId="14" hidden="1">ch4_4!$B$2:$H$2</definedName>
+    <definedName name="solver_lhs1" localSheetId="15" hidden="1">ch4_5!$B$14:$G$14</definedName>
     <definedName name="solver_lhs2" localSheetId="0" hidden="1">ch_1_1!$B$8:$B$9</definedName>
     <definedName name="solver_lhs2" localSheetId="2" hidden="1">ch_2_1!$O$2:$O$4</definedName>
     <definedName name="solver_lhs2" localSheetId="5" hidden="1">ch_2_4!$J$3</definedName>
@@ -137,9 +169,15 @@
     <definedName name="solver_lhs2" localSheetId="8" hidden="1">ch_3_3!$B$20:$G$20</definedName>
     <definedName name="solver_lhs2" localSheetId="9" hidden="1">ch_3_4!$L$2:$L$8</definedName>
     <definedName name="solver_lhs2" localSheetId="10" hidden="1">ch4_1!$B$12:$F$12</definedName>
-    <definedName name="solver_lhs2" localSheetId="11" hidden="1">ch4_2!$J$4</definedName>
+    <definedName name="solver_lhs2" localSheetId="11" hidden="1">'ch4_1 (2)'!$B$12:$G$12</definedName>
+    <definedName name="solver_lhs2" localSheetId="12" hidden="1">ch4_2!$J$4</definedName>
+    <definedName name="solver_lhs2" localSheetId="13" hidden="1">ch4_3!$H$4:$H$9</definedName>
+    <definedName name="solver_lhs2" localSheetId="14" hidden="1">ch4_4!$I$4:$I$10</definedName>
+    <definedName name="solver_lhs2" localSheetId="15" hidden="1">ch4_5!$B$15:$G$15</definedName>
     <definedName name="solver_lhs3" localSheetId="8" hidden="1">ch_3_3!$B$20:$G$20</definedName>
     <definedName name="solver_lhs3" localSheetId="10" hidden="1">ch4_1!$B$16:$B$17</definedName>
+    <definedName name="solver_lhs3" localSheetId="11" hidden="1">'ch4_1 (2)'!$B$16:$B$17</definedName>
+    <definedName name="solver_lhs3" localSheetId="15" hidden="1">ch4_5!$B$24:$G$24</definedName>
     <definedName name="solver_mip" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="2" hidden="1">2147483647</definedName>
@@ -152,6 +190,10 @@
     <definedName name="solver_mip" localSheetId="9" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="10" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="11" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="12" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="13" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="14" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="15" hidden="1">2147483647</definedName>
     <definedName name="solver_mni" localSheetId="0" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="1" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="2" hidden="1">30</definedName>
@@ -164,6 +206,10 @@
     <definedName name="solver_mni" localSheetId="9" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="10" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="11" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="12" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="13" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="14" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="15" hidden="1">30</definedName>
     <definedName name="solver_mrt" localSheetId="0" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="1" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="2" hidden="1">0.075</definedName>
@@ -176,6 +222,10 @@
     <definedName name="solver_mrt" localSheetId="9" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="10" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="11" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="12" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="13" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="14" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="15" hidden="1">0.075</definedName>
     <definedName name="solver_msl" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="2" hidden="1">2</definedName>
@@ -188,6 +238,10 @@
     <definedName name="solver_msl" localSheetId="9" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="10" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="11" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="12" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="13" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="14" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="15" hidden="1">2</definedName>
     <definedName name="solver_neg" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="2" hidden="1">1</definedName>
@@ -200,6 +254,10 @@
     <definedName name="solver_neg" localSheetId="9" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="10" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="11" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="12" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="13" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="14" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="15" hidden="1">1</definedName>
     <definedName name="solver_nod" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="2" hidden="1">2147483647</definedName>
@@ -212,6 +270,10 @@
     <definedName name="solver_nod" localSheetId="9" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="10" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="11" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="12" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="13" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="14" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="15" hidden="1">2147483647</definedName>
     <definedName name="solver_num" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_num" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_num" localSheetId="2" hidden="1">2</definedName>
@@ -223,7 +285,11 @@
     <definedName name="solver_num" localSheetId="8" hidden="1">3</definedName>
     <definedName name="solver_num" localSheetId="9" hidden="1">2</definedName>
     <definedName name="solver_num" localSheetId="10" hidden="1">3</definedName>
-    <definedName name="solver_num" localSheetId="11" hidden="1">2</definedName>
+    <definedName name="solver_num" localSheetId="11" hidden="1">3</definedName>
+    <definedName name="solver_num" localSheetId="12" hidden="1">2</definedName>
+    <definedName name="solver_num" localSheetId="13" hidden="1">2</definedName>
+    <definedName name="solver_num" localSheetId="14" hidden="1">2</definedName>
+    <definedName name="solver_num" localSheetId="15" hidden="1">3</definedName>
     <definedName name="solver_nwt" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="2" hidden="1">1</definedName>
@@ -236,6 +302,10 @@
     <definedName name="solver_nwt" localSheetId="9" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="10" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="11" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="12" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="13" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="14" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="15" hidden="1">1</definedName>
     <definedName name="solver_opt" localSheetId="0" hidden="1">ch_1_1!$B$17</definedName>
     <definedName name="solver_opt" localSheetId="1" hidden="1">ch_1_2!$B$10</definedName>
     <definedName name="solver_opt" localSheetId="2" hidden="1">ch_2_1!$J$22</definedName>
@@ -247,7 +317,11 @@
     <definedName name="solver_opt" localSheetId="8" hidden="1">ch_3_3!$N$4</definedName>
     <definedName name="solver_opt" localSheetId="9" hidden="1">ch_3_4!$E$13</definedName>
     <definedName name="solver_opt" localSheetId="10" hidden="1">ch4_1!$B$22</definedName>
-    <definedName name="solver_opt" localSheetId="11" hidden="1">ch4_2!$B$9</definedName>
+    <definedName name="solver_opt" localSheetId="11" hidden="1">'ch4_1 (2)'!$B$22</definedName>
+    <definedName name="solver_opt" localSheetId="12" hidden="1">ch4_2!$B$9</definedName>
+    <definedName name="solver_opt" localSheetId="13" hidden="1">ch4_3!$H$2</definedName>
+    <definedName name="solver_opt" localSheetId="14" hidden="1">ch4_4!$I$2</definedName>
+    <definedName name="solver_opt" localSheetId="15" hidden="1">ch4_5!$H$33</definedName>
     <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="1" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="2" hidden="1">0.000001</definedName>
@@ -260,6 +334,10 @@
     <definedName name="solver_pre" localSheetId="9" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="10" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="11" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="12" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="13" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="14" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="15" hidden="1">0.000001</definedName>
     <definedName name="solver_rbv" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="2" hidden="1">1</definedName>
@@ -272,6 +350,10 @@
     <definedName name="solver_rbv" localSheetId="9" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="10" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="11" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="12" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="13" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="14" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="15" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="2" hidden="1">1</definedName>
@@ -284,6 +366,10 @@
     <definedName name="solver_rel1" localSheetId="9" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="10" hidden="1">5</definedName>
     <definedName name="solver_rel1" localSheetId="11" hidden="1">5</definedName>
+    <definedName name="solver_rel1" localSheetId="12" hidden="1">5</definedName>
+    <definedName name="solver_rel1" localSheetId="13" hidden="1">5</definedName>
+    <definedName name="solver_rel1" localSheetId="14" hidden="1">4</definedName>
+    <definedName name="solver_rel1" localSheetId="15" hidden="1">5</definedName>
     <definedName name="solver_rel2" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rel2" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_rel2" localSheetId="5" hidden="1">1</definedName>
@@ -293,8 +379,14 @@
     <definedName name="solver_rel2" localSheetId="9" hidden="1">1</definedName>
     <definedName name="solver_rel2" localSheetId="10" hidden="1">1</definedName>
     <definedName name="solver_rel2" localSheetId="11" hidden="1">1</definedName>
+    <definedName name="solver_rel2" localSheetId="12" hidden="1">1</definedName>
+    <definedName name="solver_rel2" localSheetId="13" hidden="1">3</definedName>
+    <definedName name="solver_rel2" localSheetId="14" hidden="1">3</definedName>
+    <definedName name="solver_rel2" localSheetId="15" hidden="1">1</definedName>
     <definedName name="solver_rel3" localSheetId="8" hidden="1">3</definedName>
     <definedName name="solver_rel3" localSheetId="10" hidden="1">1</definedName>
+    <definedName name="solver_rel3" localSheetId="11" hidden="1">1</definedName>
+    <definedName name="solver_rel3" localSheetId="15" hidden="1">3</definedName>
     <definedName name="solver_rhs1" localSheetId="0" hidden="1">ch_1_1!$D$3:$D$5</definedName>
     <definedName name="solver_rhs1" localSheetId="1" hidden="1">ch_1_2!$H$5:$H$7</definedName>
     <definedName name="solver_rhs1" localSheetId="2" hidden="1">ch_2_1!$B$6:$I$6</definedName>
@@ -307,6 +399,10 @@
     <definedName name="solver_rhs1" localSheetId="9" hidden="1">ch_3_4!$G$2:$G$3</definedName>
     <definedName name="solver_rhs1" localSheetId="10" hidden="1">"binary"</definedName>
     <definedName name="solver_rhs1" localSheetId="11" hidden="1">"binary"</definedName>
+    <definedName name="solver_rhs1" localSheetId="12" hidden="1">"binary"</definedName>
+    <definedName name="solver_rhs1" localSheetId="13" hidden="1">"binary"</definedName>
+    <definedName name="solver_rhs1" localSheetId="14" hidden="1">"integer"</definedName>
+    <definedName name="solver_rhs1" localSheetId="15" hidden="1">"binary"</definedName>
     <definedName name="solver_rhs2" localSheetId="0" hidden="1">ch_1_1!$D$8:$D$9</definedName>
     <definedName name="solver_rhs2" localSheetId="2" hidden="1">ch_2_1!$Q$2:$Q$4</definedName>
     <definedName name="solver_rhs2" localSheetId="5" hidden="1">ch_2_4!$L$3</definedName>
@@ -315,9 +411,15 @@
     <definedName name="solver_rhs2" localSheetId="8" hidden="1">ch_3_3!$B$22:$G$22</definedName>
     <definedName name="solver_rhs2" localSheetId="9" hidden="1">ch_3_4!$N$2:$N$8</definedName>
     <definedName name="solver_rhs2" localSheetId="10" hidden="1">ch4_1!$B$14:$F$14</definedName>
-    <definedName name="solver_rhs2" localSheetId="11" hidden="1">ch4_2!$L$4</definedName>
+    <definedName name="solver_rhs2" localSheetId="11" hidden="1">'ch4_1 (2)'!$B$14:$G$14</definedName>
+    <definedName name="solver_rhs2" localSheetId="12" hidden="1">ch4_2!$L$4</definedName>
+    <definedName name="solver_rhs2" localSheetId="13" hidden="1">ch4_3!$J$4:$J$9</definedName>
+    <definedName name="solver_rhs2" localSheetId="14" hidden="1">ch4_4!$K$4:$K$10</definedName>
+    <definedName name="solver_rhs2" localSheetId="15" hidden="1">ch4_5!$B$18:$G$18</definedName>
     <definedName name="solver_rhs3" localSheetId="8" hidden="1">0</definedName>
     <definedName name="solver_rhs3" localSheetId="10" hidden="1">ch4_1!$D$16:$D$17</definedName>
+    <definedName name="solver_rhs3" localSheetId="11" hidden="1">'ch4_1 (2)'!$D$16:$D$17</definedName>
+    <definedName name="solver_rhs3" localSheetId="15" hidden="1">0</definedName>
     <definedName name="solver_rlx" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="2" hidden="1">2</definedName>
@@ -330,6 +432,10 @@
     <definedName name="solver_rlx" localSheetId="9" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="10" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="11" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="12" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="13" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="14" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="15" hidden="1">2</definedName>
     <definedName name="solver_rsd" localSheetId="0" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="1" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="2" hidden="1">0</definedName>
@@ -342,6 +448,10 @@
     <definedName name="solver_rsd" localSheetId="9" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="10" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="11" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="12" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="13" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="14" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="15" hidden="1">0</definedName>
     <definedName name="solver_scl" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="2" hidden="1">1</definedName>
@@ -354,6 +464,10 @@
     <definedName name="solver_scl" localSheetId="9" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="10" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="11" hidden="1">1</definedName>
+    <definedName name="solver_scl" localSheetId="12" hidden="1">1</definedName>
+    <definedName name="solver_scl" localSheetId="13" hidden="1">1</definedName>
+    <definedName name="solver_scl" localSheetId="14" hidden="1">1</definedName>
+    <definedName name="solver_scl" localSheetId="15" hidden="1">1</definedName>
     <definedName name="solver_sho" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="2" hidden="1">2</definedName>
@@ -366,6 +480,10 @@
     <definedName name="solver_sho" localSheetId="9" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="10" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="11" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="12" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="13" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="14" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="15" hidden="1">2</definedName>
     <definedName name="solver_ssz" localSheetId="0" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="1" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="2" hidden="1">100</definedName>
@@ -378,6 +496,10 @@
     <definedName name="solver_ssz" localSheetId="9" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="10" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="11" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="12" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="13" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="14" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="15" hidden="1">100</definedName>
     <definedName name="solver_tim" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="2" hidden="1">2147483647</definedName>
@@ -390,6 +512,10 @@
     <definedName name="solver_tim" localSheetId="9" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="10" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="11" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="12" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="13" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="14" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="15" hidden="1">2147483647</definedName>
     <definedName name="solver_tol" localSheetId="0" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="1" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="2" hidden="1">0.01</definedName>
@@ -402,6 +528,10 @@
     <definedName name="solver_tol" localSheetId="9" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="10" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="11" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="12" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="13" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="14" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="15" hidden="1">0</definedName>
     <definedName name="solver_typ" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_typ" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_typ" localSheetId="2" hidden="1">1</definedName>
@@ -414,6 +544,10 @@
     <definedName name="solver_typ" localSheetId="9" hidden="1">2</definedName>
     <definedName name="solver_typ" localSheetId="10" hidden="1">1</definedName>
     <definedName name="solver_typ" localSheetId="11" hidden="1">1</definedName>
+    <definedName name="solver_typ" localSheetId="12" hidden="1">1</definedName>
+    <definedName name="solver_typ" localSheetId="13" hidden="1">2</definedName>
+    <definedName name="solver_typ" localSheetId="14" hidden="1">2</definedName>
+    <definedName name="solver_typ" localSheetId="15" hidden="1">2</definedName>
     <definedName name="solver_val" localSheetId="0" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="1" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="2" hidden="1">0</definedName>
@@ -426,6 +560,10 @@
     <definedName name="solver_val" localSheetId="9" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="10" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="11" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="12" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="13" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="14" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="15" hidden="1">0</definedName>
     <definedName name="solver_ver" localSheetId="0" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="1" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="2" hidden="1">3</definedName>
@@ -438,6 +576,10 @@
     <definedName name="solver_ver" localSheetId="9" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="10" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="11" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="12" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="13" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="14" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="15" hidden="1">3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -461,7 +603,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="162">
   <si>
     <t xml:space="preserve">basic </t>
   </si>
@@ -888,6 +1030,66 @@
   </si>
   <si>
     <t>total cloth</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>decis var</t>
+  </si>
+  <si>
+    <t>&gt;&gt; (aij * xj) บังคับให้ 1  site ต้อง cover อย่างน้อย 1 จุด (ถ้าไม่ใส่ xj จะเลือกเป็น 0 ทั้งหมด)</t>
+  </si>
+  <si>
+    <t>Mon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tue </t>
+  </si>
+  <si>
+    <t>Wed</t>
+  </si>
+  <si>
+    <t>Thurs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fri </t>
+  </si>
+  <si>
+    <t>Sun</t>
+  </si>
+  <si>
+    <t>Sat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">decis var </t>
+  </si>
+  <si>
+    <t>fix cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shift start </t>
+  </si>
+  <si>
+    <t>x6</t>
+  </si>
+  <si>
+    <t>Big M</t>
   </si>
 </sst>
 </file>
@@ -942,7 +1144,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -991,6 +1193,24 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.749992370372631"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -1023,7 +1243,7 @@
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1075,6 +1295,29 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="5" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="5" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="5" fillId="3" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Comma" xfId="4" builtinId="3"/>
@@ -1097,7 +1340,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Advertising "/>
@@ -1140,16 +1383,16 @@
       <sheetName val="Location"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
       <sheetData sheetId="10"/>
       <sheetData sheetId="11">
         <row r="6">
@@ -1223,17 +1466,17 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-      <sheetData sheetId="19"/>
-      <sheetData sheetId="20"/>
-      <sheetData sheetId="21"/>
-      <sheetData sheetId="22"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
+      <sheetData sheetId="15" refreshError="1"/>
+      <sheetData sheetId="16" refreshError="1"/>
+      <sheetData sheetId="17" refreshError="1"/>
+      <sheetData sheetId="18" refreshError="1"/>
+      <sheetData sheetId="19" refreshError="1"/>
+      <sheetData sheetId="20" refreshError="1"/>
+      <sheetData sheetId="21" refreshError="1"/>
+      <sheetData sheetId="22" refreshError="1"/>
       <sheetData sheetId="23">
         <row r="10">
           <cell r="B10">
@@ -1259,20 +1502,20 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="24"/>
-      <sheetData sheetId="25"/>
-      <sheetData sheetId="26"/>
-      <sheetData sheetId="27"/>
-      <sheetData sheetId="28"/>
-      <sheetData sheetId="29"/>
-      <sheetData sheetId="30"/>
-      <sheetData sheetId="31"/>
-      <sheetData sheetId="32"/>
-      <sheetData sheetId="33"/>
-      <sheetData sheetId="34"/>
-      <sheetData sheetId="35"/>
-      <sheetData sheetId="36"/>
-      <sheetData sheetId="37"/>
+      <sheetData sheetId="24" refreshError="1"/>
+      <sheetData sheetId="25" refreshError="1"/>
+      <sheetData sheetId="26" refreshError="1"/>
+      <sheetData sheetId="27" refreshError="1"/>
+      <sheetData sheetId="28" refreshError="1"/>
+      <sheetData sheetId="29" refreshError="1"/>
+      <sheetData sheetId="30" refreshError="1"/>
+      <sheetData sheetId="31" refreshError="1"/>
+      <sheetData sheetId="32" refreshError="1"/>
+      <sheetData sheetId="33" refreshError="1"/>
+      <sheetData sheetId="34" refreshError="1"/>
+      <sheetData sheetId="35" refreshError="1"/>
+      <sheetData sheetId="36" refreshError="1"/>
+      <sheetData sheetId="37" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2487,6 +2730,364 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A8A5270-313A-4FDD-8229-6559A071CFF2}">
+  <dimension ref="A2:G22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.140625" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B2" s="31" t="s">
+        <v>125</v>
+      </c>
+      <c r="C2" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="E2" s="31" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="G2" s="31" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B3">
+        <v>1500</v>
+      </c>
+      <c r="C3">
+        <v>1200</v>
+      </c>
+      <c r="D3">
+        <v>1600</v>
+      </c>
+      <c r="E3">
+        <v>1500</v>
+      </c>
+      <c r="F3">
+        <v>1600</v>
+      </c>
+      <c r="G3">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="29" t="s">
+        <v>132</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>6</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+      <c r="F4">
+        <v>8</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>2.5</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>4.5</v>
+      </c>
+      <c r="F5">
+        <v>5.5</v>
+      </c>
+      <c r="G5">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B6">
+        <v>35</v>
+      </c>
+      <c r="C6">
+        <v>40</v>
+      </c>
+      <c r="D6">
+        <v>65</v>
+      </c>
+      <c r="E6">
+        <v>70</v>
+      </c>
+      <c r="F6">
+        <v>110</v>
+      </c>
+      <c r="G6">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B7">
+        <v>20</v>
+      </c>
+      <c r="C7">
+        <v>10</v>
+      </c>
+      <c r="D7">
+        <v>25</v>
+      </c>
+      <c r="E7">
+        <v>30</v>
+      </c>
+      <c r="F7">
+        <v>35</v>
+      </c>
+      <c r="G7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>138</v>
+      </c>
+      <c r="B8">
+        <f t="shared" ref="B8:G8" si="0">B6-B7</f>
+        <v>15</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="0"/>
+        <v>75</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>125</v>
+      </c>
+      <c r="C10" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" t="s">
+        <v>126</v>
+      </c>
+      <c r="E10" t="s">
+        <v>127</v>
+      </c>
+      <c r="F10" t="s">
+        <v>128</v>
+      </c>
+      <c r="G10" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>129</v>
+      </c>
+      <c r="B11" s="6">
+        <v>0</v>
+      </c>
+      <c r="C11" s="6">
+        <v>1</v>
+      </c>
+      <c r="D11" s="6">
+        <v>0</v>
+      </c>
+      <c r="E11" s="6">
+        <v>0</v>
+      </c>
+      <c r="F11" s="6">
+        <v>1</v>
+      </c>
+      <c r="G11" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>130</v>
+      </c>
+      <c r="B12" s="6">
+        <v>0</v>
+      </c>
+      <c r="C12" s="6">
+        <v>965.51724137931024</v>
+      </c>
+      <c r="D12" s="6">
+        <v>0</v>
+      </c>
+      <c r="E12" s="6">
+        <v>0</v>
+      </c>
+      <c r="F12" s="6">
+        <v>379.31034482758622</v>
+      </c>
+      <c r="G12" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B14">
+        <f t="shared" ref="B14:G14" si="1">B11 * $B$19</f>
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <f t="shared" si="1"/>
+        <v>1000000</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <f t="shared" si="1"/>
+        <v>1000000</v>
+      </c>
+      <c r="G14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>140</v>
+      </c>
+      <c r="B16" s="4">
+        <f>SUMPRODUCT(B4:G4,B12:G12)</f>
+        <v>4000</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="3">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>141</v>
+      </c>
+      <c r="B17" s="4">
+        <f>SUMPRODUCT(B5:G5, B12:G12)</f>
+        <v>4500</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D17" s="3">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>139</v>
+      </c>
+      <c r="B19">
+        <f>1000000</f>
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>136</v>
+      </c>
+      <c r="B20">
+        <f>SUMPRODUCT(B8:G8, B12:G12)</f>
+        <v>57413.793103448275</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>137</v>
+      </c>
+      <c r="B21">
+        <f>SUMPRODUCT(B3:G3, B11:G11)</f>
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" s="2">
+        <f>B20-B21</f>
+        <v>54613.793103448275</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA6CB6CF-31AC-43B2-BABC-B89D4F5C3C26}">
   <dimension ref="A1:L9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2627,7 +3228,7 @@
         <v>0.11999999999999993</v>
       </c>
       <c r="C7">
-        <f t="shared" ref="C7:H7" si="0">(C6-C5)/C5</f>
+        <f t="shared" ref="C7:G7" si="0">(C6-C5)/C5</f>
         <v>0.12500000000000011</v>
       </c>
       <c r="D7">
@@ -2662,6 +3263,1337 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BF078DC-633E-40D6-9FA8-AC14046EFECF}">
+  <dimension ref="A1:J14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E1" t="s">
+        <v>145</v>
+      </c>
+      <c r="F1" t="s">
+        <v>146</v>
+      </c>
+      <c r="G1" t="s">
+        <v>147</v>
+      </c>
+      <c r="H1" s="31"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B2" s="6">
+        <v>0</v>
+      </c>
+      <c r="C2" s="6">
+        <v>0</v>
+      </c>
+      <c r="D2" s="6">
+        <v>0</v>
+      </c>
+      <c r="E2" s="6">
+        <v>1</v>
+      </c>
+      <c r="F2" s="6">
+        <v>0</v>
+      </c>
+      <c r="G2" s="6">
+        <v>1</v>
+      </c>
+      <c r="H2" s="2">
+        <f>SUMPRODUCT(B11:G11,B2:G2)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="32"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <f>SUMPRODUCT(B4:G4,$B$2:$G$2)</f>
+        <v>1</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J4" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>143</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <f t="shared" ref="H5:H9" si="0">SUMPRODUCT(B5:G5,$B$2:$G$2)</f>
+        <v>1</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J5" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>144</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6" s="4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J6" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>145</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J7" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>146</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J8" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>147</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>10</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9" s="4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J9" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>131</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="33" t="s">
+        <v>149</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FFF8B83-9FAD-40FB-8E72-EC5CAC388E8C}">
+  <dimension ref="A1:K12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="34" t="s">
+        <v>159</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>150</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>151</v>
+      </c>
+      <c r="D1" s="31" t="s">
+        <v>152</v>
+      </c>
+      <c r="E1" s="31" t="s">
+        <v>153</v>
+      </c>
+      <c r="F1" s="31" t="s">
+        <v>154</v>
+      </c>
+      <c r="G1" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="H1" s="31" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B2" s="6">
+        <v>5</v>
+      </c>
+      <c r="C2" s="6">
+        <v>1</v>
+      </c>
+      <c r="D2" s="6">
+        <v>7</v>
+      </c>
+      <c r="E2" s="6">
+        <v>1</v>
+      </c>
+      <c r="F2" s="6">
+        <v>3</v>
+      </c>
+      <c r="G2" s="6">
+        <v>6</v>
+      </c>
+      <c r="H2" s="6">
+        <v>0</v>
+      </c>
+      <c r="I2" s="2">
+        <f>SUMPRODUCT(B2:H2,B12:H12)</f>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="31" t="s">
+        <v>150</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4" s="4">
+        <f>SUMPRODUCT($B$2:$H$2, B4:H4)</f>
+        <v>17</v>
+      </c>
+      <c r="J4" t="s">
+        <v>61</v>
+      </c>
+      <c r="K4" s="3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="31" t="s">
+        <v>151</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5" s="4">
+        <f>SUMPRODUCT($B$2:$H$2, B5:H5)</f>
+        <v>15</v>
+      </c>
+      <c r="J5" t="s">
+        <v>61</v>
+      </c>
+      <c r="K5" s="3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="31" t="s">
+        <v>152</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6" s="4">
+        <f>SUMPRODUCT($B$2:$H$2, B6:H6)</f>
+        <v>15</v>
+      </c>
+      <c r="J6" t="s">
+        <v>61</v>
+      </c>
+      <c r="K6" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="31" t="s">
+        <v>153</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7" s="4">
+        <f>SUMPRODUCT($B$2:$H$2, B7:H7)</f>
+        <v>19</v>
+      </c>
+      <c r="J7" t="s">
+        <v>61</v>
+      </c>
+      <c r="K7" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="31" t="s">
+        <v>154</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8" s="4">
+        <f>SUMPRODUCT($B$2:$H$2, B8:H8)</f>
+        <v>14</v>
+      </c>
+      <c r="J8" t="s">
+        <v>61</v>
+      </c>
+      <c r="K8" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9" s="4">
+        <f t="shared" ref="I9:I10" si="0">SUMPRODUCT($B$2:$H$2, B9:H9)</f>
+        <v>17</v>
+      </c>
+      <c r="J9" t="s">
+        <v>61</v>
+      </c>
+      <c r="K9" s="3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="31" t="s">
+        <v>155</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10" s="4">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="J10" t="s">
+        <v>61</v>
+      </c>
+      <c r="K10" s="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I11" s="32"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="31" t="s">
+        <v>158</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83770651-6A0E-4CA7-AD8F-E5D26ABE3557}">
+  <dimension ref="A1:I33"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="50" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="10"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="B4" s="12">
+        <v>5000</v>
+      </c>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="B5" s="13">
+        <v>0.05</v>
+      </c>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="B6" s="42">
+        <f>125000</f>
+        <v>125000</v>
+      </c>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="10"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="B8" s="14">
+        <v>1</v>
+      </c>
+      <c r="C8" s="14">
+        <v>2</v>
+      </c>
+      <c r="D8" s="14">
+        <v>3</v>
+      </c>
+      <c r="E8" s="14">
+        <v>4</v>
+      </c>
+      <c r="F8" s="14">
+        <v>5</v>
+      </c>
+      <c r="G8" s="14">
+        <v>6</v>
+      </c>
+      <c r="H8" s="15"/>
+      <c r="I8" s="10"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="B9" s="17">
+        <v>12.5</v>
+      </c>
+      <c r="C9" s="17">
+        <v>12.55</v>
+      </c>
+      <c r="D9" s="17">
+        <v>12.7</v>
+      </c>
+      <c r="E9" s="17">
+        <v>12.8</v>
+      </c>
+      <c r="F9" s="17">
+        <v>12.85</v>
+      </c>
+      <c r="G9" s="17">
+        <v>12.95</v>
+      </c>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="B10" s="18">
+        <f>B9* $B$5</f>
+        <v>0.625</v>
+      </c>
+      <c r="C10" s="18">
+        <f>C9* $B$5</f>
+        <v>0.62750000000000006</v>
+      </c>
+      <c r="D10" s="18">
+        <f>D9* $B$5</f>
+        <v>0.63500000000000001</v>
+      </c>
+      <c r="E10" s="18">
+        <f>E9* $B$5</f>
+        <v>0.64000000000000012</v>
+      </c>
+      <c r="F10" s="18">
+        <f>F9* $B$5</f>
+        <v>0.64250000000000007</v>
+      </c>
+      <c r="G10" s="18">
+        <f>G9* $B$5</f>
+        <v>0.64749999999999996</v>
+      </c>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="B13" s="14">
+        <v>1</v>
+      </c>
+      <c r="C13" s="14">
+        <v>2</v>
+      </c>
+      <c r="D13" s="14">
+        <v>3</v>
+      </c>
+      <c r="E13" s="14">
+        <v>4</v>
+      </c>
+      <c r="F13" s="14">
+        <v>5</v>
+      </c>
+      <c r="G13" s="14">
+        <v>6</v>
+      </c>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="B14" s="39">
+        <v>1</v>
+      </c>
+      <c r="C14" s="39">
+        <v>0</v>
+      </c>
+      <c r="D14" s="39">
+        <v>1</v>
+      </c>
+      <c r="E14" s="39">
+        <v>1</v>
+      </c>
+      <c r="F14" s="39">
+        <v>1</v>
+      </c>
+      <c r="G14" s="39">
+        <v>0</v>
+      </c>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="B15" s="40">
+        <v>20000</v>
+      </c>
+      <c r="C15" s="40">
+        <v>0</v>
+      </c>
+      <c r="D15" s="40">
+        <v>30000</v>
+      </c>
+      <c r="E15" s="40">
+        <v>35000</v>
+      </c>
+      <c r="F15" s="40">
+        <v>35000</v>
+      </c>
+      <c r="G15" s="40">
+        <v>0</v>
+      </c>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="10"/>
+      <c r="B16" s="45" t="s">
+        <v>2</v>
+      </c>
+      <c r="C16" s="45" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="45" t="s">
+        <v>2</v>
+      </c>
+      <c r="E16" s="45" t="s">
+        <v>2</v>
+      </c>
+      <c r="F16" s="45" t="s">
+        <v>2</v>
+      </c>
+      <c r="G16" s="45" t="s">
+        <v>2</v>
+      </c>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="B17" s="38">
+        <v>30000</v>
+      </c>
+      <c r="C17" s="38">
+        <v>30000</v>
+      </c>
+      <c r="D17" s="38">
+        <v>30000</v>
+      </c>
+      <c r="E17" s="38">
+        <v>30000</v>
+      </c>
+      <c r="F17" s="38">
+        <v>30000</v>
+      </c>
+      <c r="G17" s="38">
+        <v>30000</v>
+      </c>
+      <c r="H17" s="10"/>
+      <c r="I17" s="10"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="10"/>
+      <c r="B18" s="41">
+        <f>$B$6*B14</f>
+        <v>125000</v>
+      </c>
+      <c r="C18" s="41">
+        <f t="shared" ref="C18:F18" si="0">$B$6*C14</f>
+        <v>0</v>
+      </c>
+      <c r="D18" s="41">
+        <f>$B$6*D14</f>
+        <v>125000</v>
+      </c>
+      <c r="E18" s="41">
+        <f t="shared" si="0"/>
+        <v>125000</v>
+      </c>
+      <c r="F18" s="41">
+        <f t="shared" si="0"/>
+        <v>125000</v>
+      </c>
+      <c r="G18" s="41">
+        <f>$B$6*G14</f>
+        <v>0</v>
+      </c>
+      <c r="H18" s="10"/>
+      <c r="I18" s="10"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="10"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="10"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="B20" s="10"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="10"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="10"/>
+      <c r="B21" s="23"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="23"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="10"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="B22" s="12">
+        <v>10000</v>
+      </c>
+      <c r="C22" s="12">
+        <v>15000</v>
+      </c>
+      <c r="D22" s="12">
+        <v>30000</v>
+      </c>
+      <c r="E22" s="12">
+        <v>35000</v>
+      </c>
+      <c r="F22" s="12">
+        <v>25000</v>
+      </c>
+      <c r="G22" s="12">
+        <v>10000</v>
+      </c>
+      <c r="H22" s="10"/>
+      <c r="I22" s="10"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="10"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="B24" s="27">
+        <f>(B15)-B22+B4</f>
+        <v>15000</v>
+      </c>
+      <c r="C24" s="27">
+        <f>(C15)-C22+B24</f>
+        <v>0</v>
+      </c>
+      <c r="D24" s="27">
+        <f>(D15)-D22+C24</f>
+        <v>0</v>
+      </c>
+      <c r="E24" s="27">
+        <f t="shared" ref="D24:G24" si="1">(E15)-E22+D24</f>
+        <v>0</v>
+      </c>
+      <c r="F24" s="27">
+        <f>(F15)-F22+E24</f>
+        <v>10000</v>
+      </c>
+      <c r="G24" s="27">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H24" s="10"/>
+      <c r="I24" s="10"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="10"/>
+      <c r="B25" s="36" t="s">
+        <v>2</v>
+      </c>
+      <c r="C25" s="36" t="s">
+        <v>2</v>
+      </c>
+      <c r="D25" s="36" t="s">
+        <v>2</v>
+      </c>
+      <c r="E25" s="36" t="s">
+        <v>2</v>
+      </c>
+      <c r="F25" s="36" t="s">
+        <v>2</v>
+      </c>
+      <c r="G25" s="36" t="s">
+        <v>2</v>
+      </c>
+      <c r="H25" s="10"/>
+      <c r="I25" s="10" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="B26" s="37">
+        <v>10000</v>
+      </c>
+      <c r="C26" s="37">
+        <v>10000</v>
+      </c>
+      <c r="D26" s="37">
+        <v>10000</v>
+      </c>
+      <c r="E26" s="37">
+        <v>10000</v>
+      </c>
+      <c r="F26" s="37">
+        <v>10000</v>
+      </c>
+      <c r="G26" s="37">
+        <v>10000</v>
+      </c>
+      <c r="H26" s="10"/>
+      <c r="I26" s="10"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="19"/>
+      <c r="B27" s="10"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="10"/>
+      <c r="H27" s="10"/>
+      <c r="I27" s="10"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="B28" s="18"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="10"/>
+      <c r="I28" s="10"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="B29" s="14">
+        <v>1</v>
+      </c>
+      <c r="C29" s="14">
+        <v>2</v>
+      </c>
+      <c r="D29" s="14">
+        <v>3</v>
+      </c>
+      <c r="E29" s="14">
+        <v>4</v>
+      </c>
+      <c r="F29" s="14">
+        <v>5</v>
+      </c>
+      <c r="G29" s="14">
+        <v>6</v>
+      </c>
+      <c r="H29" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="I29" s="10"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="B30" s="35">
+        <f>B24*B10</f>
+        <v>9375</v>
+      </c>
+      <c r="C30" s="35">
+        <f>C24*C10</f>
+        <v>0</v>
+      </c>
+      <c r="D30" s="35">
+        <f>D24*D10</f>
+        <v>0</v>
+      </c>
+      <c r="E30" s="35">
+        <f>E24*E10</f>
+        <v>0</v>
+      </c>
+      <c r="F30" s="35">
+        <f>F24*F10</f>
+        <v>6425.0000000000009</v>
+      </c>
+      <c r="G30" s="35">
+        <f>G24*G10</f>
+        <v>0</v>
+      </c>
+      <c r="H30" s="43">
+        <f>SUMPRODUCT(B24:G24,B10:G10)</f>
+        <v>15800</v>
+      </c>
+      <c r="I30" s="10"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B31" s="35">
+        <f>B15*B9</f>
+        <v>250000</v>
+      </c>
+      <c r="C31" s="35">
+        <f>C15*C9</f>
+        <v>0</v>
+      </c>
+      <c r="D31" s="35">
+        <f>D15*D9</f>
+        <v>381000</v>
+      </c>
+      <c r="E31" s="35">
+        <f>E15*E9</f>
+        <v>448000</v>
+      </c>
+      <c r="F31" s="35">
+        <f>F15*F9</f>
+        <v>449750</v>
+      </c>
+      <c r="G31" s="35">
+        <f>G15*G9</f>
+        <v>0</v>
+      </c>
+      <c r="H31" s="43">
+        <f>SUMPRODUCT(B15:G15,B9:G9)</f>
+        <v>1528750</v>
+      </c>
+      <c r="I31" s="10"/>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="B32" s="35">
+        <v>15000</v>
+      </c>
+      <c r="C32" s="35">
+        <v>15000</v>
+      </c>
+      <c r="D32" s="35">
+        <v>15000</v>
+      </c>
+      <c r="E32" s="35">
+        <v>15000</v>
+      </c>
+      <c r="F32" s="35">
+        <v>15000</v>
+      </c>
+      <c r="G32" s="35">
+        <v>15000</v>
+      </c>
+      <c r="H32" s="43">
+        <f>SUMPRODUCT(B14:G14,B32:G32)</f>
+        <v>60000</v>
+      </c>
+      <c r="I32" s="10"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="10"/>
+      <c r="B33" s="10"/>
+      <c r="C33" s="10"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
+      <c r="G33" s="10"/>
+      <c r="H33" s="44">
+        <f>SUM(H30:H32)</f>
+        <v>1604550</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/class_excel/temp_midterm.xlsx
+++ b/class_excel/temp_midterm.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\T00229\Documents\GitHub\DADS7102\class_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79984835-6A10-4A93-AF56-4D160F9500D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1FEE5B8-7AB4-4062-8876-16A21AC25CEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="15" xr2:uid="{962D6ACA-47B2-4C7E-82D5-0F5476EE75BF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="18" xr2:uid="{962D6ACA-47B2-4C7E-82D5-0F5476EE75BF}"/>
   </bookViews>
   <sheets>
     <sheet name="ch_1_1" sheetId="1" r:id="rId1"/>
@@ -29,9 +29,12 @@
     <sheet name="ch4_3" sheetId="22" r:id="rId14"/>
     <sheet name="ch4_4" sheetId="23" r:id="rId15"/>
     <sheet name="ch4_5" sheetId="28" r:id="rId16"/>
+    <sheet name="ch5_1" sheetId="29" r:id="rId17"/>
+    <sheet name="ch5_2" sheetId="30" r:id="rId18"/>
+    <sheet name="ch5_3" sheetId="31" r:id="rId19"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId17"/>
+    <externalReference r:id="rId20"/>
   </externalReferences>
   <definedNames>
     <definedName name="AFinish">[1]project!$K$6</definedName>
@@ -65,6 +68,9 @@
     <definedName name="solver_adj" localSheetId="13" hidden="1">ch4_3!$B$2:$G$2</definedName>
     <definedName name="solver_adj" localSheetId="14" hidden="1">ch4_4!$B$2:$H$2</definedName>
     <definedName name="solver_adj" localSheetId="15" hidden="1">ch4_5!$B$14:$G$15</definedName>
+    <definedName name="solver_adj" localSheetId="16" hidden="1">ch5_1!$B$6:$C$6</definedName>
+    <definedName name="solver_adj" localSheetId="17" hidden="1">ch5_2!$B$13:$C$13,ch5_2!$B$15</definedName>
+    <definedName name="solver_adj" localSheetId="18" hidden="1">ch5_3!$B$7:$C$7,ch5_3!$I$3:$J$6</definedName>
     <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="1" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="2" hidden="1">0.0001</definedName>
@@ -81,6 +87,9 @@
     <definedName name="solver_cvg" localSheetId="13" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="14" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="15" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="16" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="17" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="18" hidden="1">0.0001</definedName>
     <definedName name="solver_drv" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="2" hidden="1">1</definedName>
@@ -97,6 +106,9 @@
     <definedName name="solver_drv" localSheetId="13" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="14" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="15" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="16" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="17" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="18" hidden="1">1</definedName>
     <definedName name="solver_eng" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="2" hidden="1">2</definedName>
@@ -113,6 +125,9 @@
     <definedName name="solver_eng" localSheetId="13" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="14" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="15" hidden="1">2</definedName>
+    <definedName name="solver_eng" localSheetId="16" hidden="1">1</definedName>
+    <definedName name="solver_eng" localSheetId="17" hidden="1">1</definedName>
+    <definedName name="solver_eng" localSheetId="18" hidden="1">2</definedName>
     <definedName name="solver_est" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="2" hidden="1">1</definedName>
@@ -129,6 +144,9 @@
     <definedName name="solver_est" localSheetId="13" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="14" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="15" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="16" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="17" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="18" hidden="1">1</definedName>
     <definedName name="solver_itr" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="2" hidden="1">2147483647</definedName>
@@ -145,6 +163,9 @@
     <definedName name="solver_itr" localSheetId="13" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="14" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="15" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="16" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="17" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="18" hidden="1">2147483647</definedName>
     <definedName name="solver_lhs1" localSheetId="0" hidden="1">ch_1_1!$B$3:$B$5</definedName>
     <definedName name="solver_lhs1" localSheetId="1" hidden="1">ch_1_2!$F$5:$F$7</definedName>
     <definedName name="solver_lhs1" localSheetId="2" hidden="1">ch_2_1!$B$4:$I$4</definedName>
@@ -161,6 +182,8 @@
     <definedName name="solver_lhs1" localSheetId="13" hidden="1">ch4_3!$B$2:$G$2</definedName>
     <definedName name="solver_lhs1" localSheetId="14" hidden="1">ch4_4!$B$2:$H$2</definedName>
     <definedName name="solver_lhs1" localSheetId="15" hidden="1">ch4_5!$B$14:$G$14</definedName>
+    <definedName name="solver_lhs1" localSheetId="17" hidden="1">ch5_2!$B$19:$C$19</definedName>
+    <definedName name="solver_lhs1" localSheetId="18" hidden="1">ch5_3!$I$3:$I$6</definedName>
     <definedName name="solver_lhs2" localSheetId="0" hidden="1">ch_1_1!$B$8:$B$9</definedName>
     <definedName name="solver_lhs2" localSheetId="2" hidden="1">ch_2_1!$O$2:$O$4</definedName>
     <definedName name="solver_lhs2" localSheetId="5" hidden="1">ch_2_4!$J$3</definedName>
@@ -174,10 +197,13 @@
     <definedName name="solver_lhs2" localSheetId="13" hidden="1">ch4_3!$H$4:$H$9</definedName>
     <definedName name="solver_lhs2" localSheetId="14" hidden="1">ch4_4!$I$4:$I$10</definedName>
     <definedName name="solver_lhs2" localSheetId="15" hidden="1">ch4_5!$B$15:$G$15</definedName>
+    <definedName name="solver_lhs2" localSheetId="18" hidden="1">ch5_3!$I$3:$I$6</definedName>
     <definedName name="solver_lhs3" localSheetId="8" hidden="1">ch_3_3!$B$20:$G$20</definedName>
     <definedName name="solver_lhs3" localSheetId="10" hidden="1">ch4_1!$B$16:$B$17</definedName>
     <definedName name="solver_lhs3" localSheetId="11" hidden="1">'ch4_1 (2)'!$B$16:$B$17</definedName>
     <definedName name="solver_lhs3" localSheetId="15" hidden="1">ch4_5!$B$24:$G$24</definedName>
+    <definedName name="solver_lhs3" localSheetId="18" hidden="1">ch5_3!$J$3:$J$6</definedName>
+    <definedName name="solver_lhs4" localSheetId="18" hidden="1">ch5_3!$J$3:$J$6</definedName>
     <definedName name="solver_mip" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="2" hidden="1">2147483647</definedName>
@@ -194,6 +220,9 @@
     <definedName name="solver_mip" localSheetId="13" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="14" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="15" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="16" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="17" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="18" hidden="1">2147483647</definedName>
     <definedName name="solver_mni" localSheetId="0" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="1" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="2" hidden="1">30</definedName>
@@ -210,6 +239,9 @@
     <definedName name="solver_mni" localSheetId="13" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="14" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="15" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="16" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="17" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="18" hidden="1">30</definedName>
     <definedName name="solver_mrt" localSheetId="0" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="1" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="2" hidden="1">0.075</definedName>
@@ -226,6 +258,9 @@
     <definedName name="solver_mrt" localSheetId="13" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="14" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="15" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="16" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="17" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="18" hidden="1">0.075</definedName>
     <definedName name="solver_msl" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="2" hidden="1">2</definedName>
@@ -242,6 +277,9 @@
     <definedName name="solver_msl" localSheetId="13" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="14" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="15" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="16" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="17" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="18" hidden="1">2</definedName>
     <definedName name="solver_neg" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="2" hidden="1">1</definedName>
@@ -258,6 +296,9 @@
     <definedName name="solver_neg" localSheetId="13" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="14" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="15" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="16" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="17" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="18" hidden="1">1</definedName>
     <definedName name="solver_nod" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="2" hidden="1">2147483647</definedName>
@@ -274,6 +315,9 @@
     <definedName name="solver_nod" localSheetId="13" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="14" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="15" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="16" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="17" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="18" hidden="1">2147483647</definedName>
     <definedName name="solver_num" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_num" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_num" localSheetId="2" hidden="1">2</definedName>
@@ -290,6 +334,9 @@
     <definedName name="solver_num" localSheetId="13" hidden="1">2</definedName>
     <definedName name="solver_num" localSheetId="14" hidden="1">2</definedName>
     <definedName name="solver_num" localSheetId="15" hidden="1">3</definedName>
+    <definedName name="solver_num" localSheetId="16" hidden="1">0</definedName>
+    <definedName name="solver_num" localSheetId="17" hidden="1">1</definedName>
+    <definedName name="solver_num" localSheetId="18" hidden="1">4</definedName>
     <definedName name="solver_nwt" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="2" hidden="1">1</definedName>
@@ -306,6 +353,9 @@
     <definedName name="solver_nwt" localSheetId="13" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="14" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="15" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="16" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="17" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="18" hidden="1">1</definedName>
     <definedName name="solver_opt" localSheetId="0" hidden="1">ch_1_1!$B$17</definedName>
     <definedName name="solver_opt" localSheetId="1" hidden="1">ch_1_2!$B$10</definedName>
     <definedName name="solver_opt" localSheetId="2" hidden="1">ch_2_1!$J$22</definedName>
@@ -322,6 +372,9 @@
     <definedName name="solver_opt" localSheetId="13" hidden="1">ch4_3!$H$2</definedName>
     <definedName name="solver_opt" localSheetId="14" hidden="1">ch4_4!$I$2</definedName>
     <definedName name="solver_opt" localSheetId="15" hidden="1">ch4_5!$H$33</definedName>
+    <definedName name="solver_opt" localSheetId="16" hidden="1">ch5_1!$B$7</definedName>
+    <definedName name="solver_opt" localSheetId="17" hidden="1">ch5_2!$B$26</definedName>
+    <definedName name="solver_opt" localSheetId="18" hidden="1">ch5_3!$B$8</definedName>
     <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="1" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="2" hidden="1">0.000001</definedName>
@@ -338,6 +391,9 @@
     <definedName name="solver_pre" localSheetId="13" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="14" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="15" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="16" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="17" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="18" hidden="1">0.000001</definedName>
     <definedName name="solver_rbv" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="2" hidden="1">1</definedName>
@@ -354,6 +410,9 @@
     <definedName name="solver_rbv" localSheetId="13" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="14" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="15" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="16" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="17" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="18" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="2" hidden="1">1</definedName>
@@ -370,6 +429,8 @@
     <definedName name="solver_rel1" localSheetId="13" hidden="1">5</definedName>
     <definedName name="solver_rel1" localSheetId="14" hidden="1">4</definedName>
     <definedName name="solver_rel1" localSheetId="15" hidden="1">5</definedName>
+    <definedName name="solver_rel1" localSheetId="17" hidden="1">1</definedName>
+    <definedName name="solver_rel1" localSheetId="18" hidden="1">3</definedName>
     <definedName name="solver_rel2" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rel2" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_rel2" localSheetId="5" hidden="1">1</definedName>
@@ -383,10 +444,13 @@
     <definedName name="solver_rel2" localSheetId="13" hidden="1">3</definedName>
     <definedName name="solver_rel2" localSheetId="14" hidden="1">3</definedName>
     <definedName name="solver_rel2" localSheetId="15" hidden="1">1</definedName>
+    <definedName name="solver_rel2" localSheetId="18" hidden="1">3</definedName>
     <definedName name="solver_rel3" localSheetId="8" hidden="1">3</definedName>
     <definedName name="solver_rel3" localSheetId="10" hidden="1">1</definedName>
     <definedName name="solver_rel3" localSheetId="11" hidden="1">1</definedName>
     <definedName name="solver_rel3" localSheetId="15" hidden="1">3</definedName>
+    <definedName name="solver_rel3" localSheetId="18" hidden="1">3</definedName>
+    <definedName name="solver_rel4" localSheetId="18" hidden="1">3</definedName>
     <definedName name="solver_rhs1" localSheetId="0" hidden="1">ch_1_1!$D$3:$D$5</definedName>
     <definedName name="solver_rhs1" localSheetId="1" hidden="1">ch_1_2!$H$5:$H$7</definedName>
     <definedName name="solver_rhs1" localSheetId="2" hidden="1">ch_2_1!$B$6:$I$6</definedName>
@@ -403,6 +467,8 @@
     <definedName name="solver_rhs1" localSheetId="13" hidden="1">"binary"</definedName>
     <definedName name="solver_rhs1" localSheetId="14" hidden="1">"integer"</definedName>
     <definedName name="solver_rhs1" localSheetId="15" hidden="1">"binary"</definedName>
+    <definedName name="solver_rhs1" localSheetId="17" hidden="1">ch5_2!$B$21:$C$21</definedName>
+    <definedName name="solver_rhs1" localSheetId="18" hidden="1">ch5_3!$E$3:$E$6</definedName>
     <definedName name="solver_rhs2" localSheetId="0" hidden="1">ch_1_1!$D$8:$D$9</definedName>
     <definedName name="solver_rhs2" localSheetId="2" hidden="1">ch_2_1!$Q$2:$Q$4</definedName>
     <definedName name="solver_rhs2" localSheetId="5" hidden="1">ch_2_4!$L$3</definedName>
@@ -416,10 +482,13 @@
     <definedName name="solver_rhs2" localSheetId="13" hidden="1">ch4_3!$J$4:$J$9</definedName>
     <definedName name="solver_rhs2" localSheetId="14" hidden="1">ch4_4!$K$4:$K$10</definedName>
     <definedName name="solver_rhs2" localSheetId="15" hidden="1">ch4_5!$B$18:$G$18</definedName>
+    <definedName name="solver_rhs2" localSheetId="18" hidden="1">ch5_3!$F$3:$F$6</definedName>
     <definedName name="solver_rhs3" localSheetId="8" hidden="1">0</definedName>
     <definedName name="solver_rhs3" localSheetId="10" hidden="1">ch4_1!$D$16:$D$17</definedName>
     <definedName name="solver_rhs3" localSheetId="11" hidden="1">'ch4_1 (2)'!$D$16:$D$17</definedName>
     <definedName name="solver_rhs3" localSheetId="15" hidden="1">0</definedName>
+    <definedName name="solver_rhs3" localSheetId="18" hidden="1">ch5_3!$G$3:$G$6</definedName>
+    <definedName name="solver_rhs4" localSheetId="18" hidden="1">ch5_3!$H$3:$H$6</definedName>
     <definedName name="solver_rlx" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="2" hidden="1">2</definedName>
@@ -436,6 +505,9 @@
     <definedName name="solver_rlx" localSheetId="13" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="14" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="15" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="16" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="17" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="18" hidden="1">2</definedName>
     <definedName name="solver_rsd" localSheetId="0" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="1" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="2" hidden="1">0</definedName>
@@ -452,6 +524,9 @@
     <definedName name="solver_rsd" localSheetId="13" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="14" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="15" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="16" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="17" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="18" hidden="1">0</definedName>
     <definedName name="solver_scl" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="2" hidden="1">1</definedName>
@@ -468,6 +543,9 @@
     <definedName name="solver_scl" localSheetId="13" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="14" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="15" hidden="1">1</definedName>
+    <definedName name="solver_scl" localSheetId="16" hidden="1">1</definedName>
+    <definedName name="solver_scl" localSheetId="17" hidden="1">1</definedName>
+    <definedName name="solver_scl" localSheetId="18" hidden="1">1</definedName>
     <definedName name="solver_sho" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="2" hidden="1">2</definedName>
@@ -484,6 +562,9 @@
     <definedName name="solver_sho" localSheetId="13" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="14" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="15" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="16" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="17" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="18" hidden="1">2</definedName>
     <definedName name="solver_ssz" localSheetId="0" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="1" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="2" hidden="1">100</definedName>
@@ -500,6 +581,9 @@
     <definedName name="solver_ssz" localSheetId="13" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="14" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="15" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="16" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="17" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="18" hidden="1">100</definedName>
     <definedName name="solver_tim" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="2" hidden="1">2147483647</definedName>
@@ -516,6 +600,9 @@
     <definedName name="solver_tim" localSheetId="13" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="14" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="15" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="16" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="17" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="18" hidden="1">2147483647</definedName>
     <definedName name="solver_tol" localSheetId="0" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="1" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="2" hidden="1">0.01</definedName>
@@ -532,6 +619,9 @@
     <definedName name="solver_tol" localSheetId="13" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="14" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="15" hidden="1">0</definedName>
+    <definedName name="solver_tol" localSheetId="16" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="17" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="18" hidden="1">0.01</definedName>
     <definedName name="solver_typ" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_typ" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_typ" localSheetId="2" hidden="1">1</definedName>
@@ -548,6 +638,9 @@
     <definedName name="solver_typ" localSheetId="13" hidden="1">2</definedName>
     <definedName name="solver_typ" localSheetId="14" hidden="1">2</definedName>
     <definedName name="solver_typ" localSheetId="15" hidden="1">2</definedName>
+    <definedName name="solver_typ" localSheetId="16" hidden="1">2</definedName>
+    <definedName name="solver_typ" localSheetId="17" hidden="1">1</definedName>
+    <definedName name="solver_typ" localSheetId="18" hidden="1">2</definedName>
     <definedName name="solver_val" localSheetId="0" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="1" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="2" hidden="1">0</definedName>
@@ -564,6 +657,9 @@
     <definedName name="solver_val" localSheetId="13" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="14" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="15" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="16" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="17" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="18" hidden="1">0</definedName>
     <definedName name="solver_ver" localSheetId="0" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="1" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="2" hidden="1">3</definedName>
@@ -580,6 +676,9 @@
     <definedName name="solver_ver" localSheetId="13" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="14" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="15" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="16" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="17" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="18" hidden="1">3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -603,7 +702,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="191">
   <si>
     <t xml:space="preserve">basic </t>
   </si>
@@ -1090,13 +1189,102 @@
   </si>
   <si>
     <t>Big M</t>
+  </si>
+  <si>
+    <t>customer</t>
+  </si>
+  <si>
+    <t>lat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">long </t>
+  </si>
+  <si>
+    <t xml:space="preserve"># shipment </t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>x0-xi</t>
+  </si>
+  <si>
+    <t>y0-yi</t>
+  </si>
+  <si>
+    <t>distance</t>
+  </si>
+  <si>
+    <t>total disctance</t>
+  </si>
+  <si>
+    <t>Florida Power &amp; Light peak-load pricing model</t>
+  </si>
+  <si>
+    <t>Coefficients of demand functions</t>
+  </si>
+  <si>
+    <t>Constant</t>
+  </si>
+  <si>
+    <t>Peak price</t>
+  </si>
+  <si>
+    <t>Off-peak price</t>
+  </si>
+  <si>
+    <t>Peak-load demand</t>
+  </si>
+  <si>
+    <t>Off-peak demand</t>
+  </si>
+  <si>
+    <t>Cost of capacity/kwh</t>
+  </si>
+  <si>
+    <t>Decisions</t>
+  </si>
+  <si>
+    <t>Peak-load</t>
+  </si>
+  <si>
+    <t>Off-peak</t>
+  </si>
+  <si>
+    <t>Prices</t>
+  </si>
+  <si>
+    <t>Capacity</t>
+  </si>
+  <si>
+    <t>Constraints on demand</t>
+  </si>
+  <si>
+    <t>Monetary summary</t>
+  </si>
+  <si>
+    <t>Revenue</t>
+  </si>
+  <si>
+    <t>Cost of capacity</t>
+  </si>
+  <si>
+    <t>Profit</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>T</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="6">
+  <numFmts count="8">
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="7" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="0.0000"/>
@@ -1243,7 +1431,7 @@
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1318,6 +1506,17 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="6" fontId="5" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="8" fontId="5" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="8" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="5" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="7" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="7" fontId="5" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="5" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="5" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Comma" xfId="4" builtinId="3"/>
@@ -1383,16 +1582,16 @@
       <sheetName val="Location"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
       <sheetData sheetId="10"/>
       <sheetData sheetId="11">
         <row r="6">
@@ -1466,17 +1665,17 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="12" refreshError="1"/>
-      <sheetData sheetId="13" refreshError="1"/>
-      <sheetData sheetId="14" refreshError="1"/>
-      <sheetData sheetId="15" refreshError="1"/>
-      <sheetData sheetId="16" refreshError="1"/>
-      <sheetData sheetId="17" refreshError="1"/>
-      <sheetData sheetId="18" refreshError="1"/>
-      <sheetData sheetId="19" refreshError="1"/>
-      <sheetData sheetId="20" refreshError="1"/>
-      <sheetData sheetId="21" refreshError="1"/>
-      <sheetData sheetId="22" refreshError="1"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
+      <sheetData sheetId="22"/>
       <sheetData sheetId="23">
         <row r="10">
           <cell r="B10">
@@ -1502,20 +1701,20 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="24" refreshError="1"/>
-      <sheetData sheetId="25" refreshError="1"/>
-      <sheetData sheetId="26" refreshError="1"/>
-      <sheetData sheetId="27" refreshError="1"/>
-      <sheetData sheetId="28" refreshError="1"/>
-      <sheetData sheetId="29" refreshError="1"/>
-      <sheetData sheetId="30" refreshError="1"/>
-      <sheetData sheetId="31" refreshError="1"/>
-      <sheetData sheetId="32" refreshError="1"/>
-      <sheetData sheetId="33" refreshError="1"/>
-      <sheetData sheetId="34" refreshError="1"/>
-      <sheetData sheetId="35" refreshError="1"/>
-      <sheetData sheetId="36" refreshError="1"/>
-      <sheetData sheetId="37" refreshError="1"/>
+      <sheetData sheetId="24"/>
+      <sheetData sheetId="25"/>
+      <sheetData sheetId="26"/>
+      <sheetData sheetId="27"/>
+      <sheetData sheetId="28"/>
+      <sheetData sheetId="29"/>
+      <sheetData sheetId="30"/>
+      <sheetData sheetId="31"/>
+      <sheetData sheetId="32"/>
+      <sheetData sheetId="33"/>
+      <sheetData sheetId="34"/>
+      <sheetData sheetId="35"/>
+      <sheetData sheetId="36"/>
+      <sheetData sheetId="37"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4082,27 +4281,27 @@
         <v>105</v>
       </c>
       <c r="B10" s="18">
-        <f>B9* $B$5</f>
+        <f t="shared" ref="B10:G10" si="0">B9* $B$5</f>
         <v>0.625</v>
       </c>
       <c r="C10" s="18">
-        <f>C9* $B$5</f>
+        <f t="shared" si="0"/>
         <v>0.62750000000000006</v>
       </c>
       <c r="D10" s="18">
-        <f>D9* $B$5</f>
+        <f t="shared" si="0"/>
         <v>0.63500000000000001</v>
       </c>
       <c r="E10" s="18">
-        <f>E9* $B$5</f>
+        <f t="shared" si="0"/>
         <v>0.64000000000000012</v>
       </c>
       <c r="F10" s="18">
-        <f>F9* $B$5</f>
+        <f t="shared" si="0"/>
         <v>0.64250000000000007</v>
       </c>
       <c r="G10" s="18">
-        <f>G9* $B$5</f>
+        <f t="shared" si="0"/>
         <v>0.64749999999999996</v>
       </c>
       <c r="H10" s="10"/>
@@ -4256,7 +4455,7 @@
         <v>125000</v>
       </c>
       <c r="C18" s="41">
-        <f t="shared" ref="C18:F18" si="0">$B$6*C14</f>
+        <f t="shared" ref="C18:F18" si="1">$B$6*C14</f>
         <v>0</v>
       </c>
       <c r="D18" s="41">
@@ -4264,11 +4463,11 @@
         <v>125000</v>
       </c>
       <c r="E18" s="41">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>125000</v>
       </c>
       <c r="F18" s="41">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>125000</v>
       </c>
       <c r="G18" s="41">
@@ -4370,7 +4569,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="27">
-        <f t="shared" ref="D24:G24" si="1">(E15)-E22+D24</f>
+        <f t="shared" ref="E24:G24" si="2">(E15)-E22+D24</f>
         <v>0</v>
       </c>
       <c r="F24" s="27">
@@ -4378,7 +4577,7 @@
         <v>10000</v>
       </c>
       <c r="G24" s="27">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H24" s="10"/>
@@ -4489,27 +4688,27 @@
         <v>119</v>
       </c>
       <c r="B30" s="35">
-        <f>B24*B10</f>
+        <f t="shared" ref="B30:G30" si="3">B24*B10</f>
         <v>9375</v>
       </c>
       <c r="C30" s="35">
-        <f>C24*C10</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D30" s="35">
-        <f>D24*D10</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E30" s="35">
-        <f>E24*E10</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F30" s="35">
-        <f>F24*F10</f>
+        <f t="shared" si="3"/>
         <v>6425.0000000000009</v>
       </c>
       <c r="G30" s="35">
-        <f>G24*G10</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H30" s="43">
@@ -4523,27 +4722,27 @@
         <v>120</v>
       </c>
       <c r="B31" s="35">
-        <f>B15*B9</f>
+        <f t="shared" ref="B31:G31" si="4">B15*B9</f>
         <v>250000</v>
       </c>
       <c r="C31" s="35">
-        <f>C15*C9</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D31" s="35">
-        <f>D15*D9</f>
+        <f t="shared" si="4"/>
         <v>381000</v>
       </c>
       <c r="E31" s="35">
-        <f>E15*E9</f>
+        <f t="shared" si="4"/>
         <v>448000</v>
       </c>
       <c r="F31" s="35">
-        <f>F15*F9</f>
+        <f t="shared" si="4"/>
         <v>449750</v>
       </c>
       <c r="G31" s="35">
-        <f>G15*G9</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H31" s="43">
@@ -4591,6 +4790,680 @@
       <c r="H33" s="44">
         <f>SUM(H30:H32)</f>
         <v>1604550</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FE38B91-F448-4184-8315-E5F01652B01A}">
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E1" t="s">
+        <v>167</v>
+      </c>
+      <c r="F1" t="s">
+        <v>168</v>
+      </c>
+      <c r="G1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>10</v>
+      </c>
+      <c r="D2">
+        <v>200</v>
+      </c>
+      <c r="E2">
+        <f>($B$6-B2)</f>
+        <v>4.3141630158538948</v>
+      </c>
+      <c r="F2">
+        <f>($C$6-C2)</f>
+        <v>-4.9712990159689436</v>
+      </c>
+      <c r="G2">
+        <f>SQRT(E2^2 +F2^2)</f>
+        <v>6.582234911755684</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>10</v>
+      </c>
+      <c r="C3">
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <v>150</v>
+      </c>
+      <c r="E3">
+        <f t="shared" ref="E3:E5" si="0">($B$6-B3)</f>
+        <v>-0.68583698414610517</v>
+      </c>
+      <c r="F3">
+        <f t="shared" ref="F3:F5" si="1">($C$6-C3)</f>
+        <v>2.8700984031056365E-2</v>
+      </c>
+      <c r="G3">
+        <f t="shared" ref="G3:G5" si="2">SQRT(E3^2 +F3^2)</f>
+        <v>0.68643726246975834</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>12</v>
+      </c>
+      <c r="D4">
+        <v>200</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="0"/>
+        <v>9.3141630158538948</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="1"/>
+        <v>-6.9712990159689436</v>
+      </c>
+      <c r="G4">
+        <f t="shared" si="2"/>
+        <v>11.634115465128842</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>12</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>300</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="0"/>
+        <v>-2.6858369841461052</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="1"/>
+        <v>5.0287009840310564</v>
+      </c>
+      <c r="G5">
+        <f t="shared" si="2"/>
+        <v>5.7010134092283948</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="31" t="s">
+        <v>166</v>
+      </c>
+      <c r="B6" s="1">
+        <v>9.3141630158538948</v>
+      </c>
+      <c r="C6" s="1">
+        <v>5.0287009840310564</v>
+      </c>
+      <c r="G6" s="32"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>170</v>
+      </c>
+      <c r="B7" s="2">
+        <f>SUMPRODUCT(D2:D5,G2:G5)</f>
+        <v>5456.5396875158876</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{573F87C3-C663-4007-B0D4-35BF49BC4D1B}">
+  <dimension ref="A1:E27"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="31.28515625" customWidth="1"/>
+    <col min="2" max="2" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="10"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="10"/>
+      <c r="B5" s="23" t="s">
+        <v>173</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>174</v>
+      </c>
+      <c r="D5" s="23" t="s">
+        <v>175</v>
+      </c>
+      <c r="E5" s="23"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="22" t="s">
+        <v>176</v>
+      </c>
+      <c r="B6" s="12">
+        <v>2.2530000000000001</v>
+      </c>
+      <c r="C6" s="12">
+        <v>-1.2999999999999999E-2</v>
+      </c>
+      <c r="D6" s="12">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="E6" s="10"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="B7" s="12">
+        <v>1.1419999999999999</v>
+      </c>
+      <c r="C7" s="12">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="D7" s="12">
+        <v>-1.4999999999999999E-2</v>
+      </c>
+      <c r="E7" s="10"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="10"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="B9" s="46">
+        <v>75</v>
+      </c>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="10"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="24" t="s">
+        <v>179</v>
+      </c>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="23"/>
+      <c r="B12" s="23" t="s">
+        <v>180</v>
+      </c>
+      <c r="C12" s="23" t="s">
+        <v>181</v>
+      </c>
+      <c r="D12" s="21"/>
+      <c r="E12" s="23"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="B13" s="47">
+        <v>137.57222139459847</v>
+      </c>
+      <c r="C13" s="47">
+        <v>75.849999204652676</v>
+      </c>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="10"/>
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="49"/>
+      <c r="E14" s="10"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="B15" s="50">
+        <v>0.69211111571181716</v>
+      </c>
+      <c r="C15" s="48"/>
+      <c r="D15" s="49"/>
+      <c r="E15" s="10"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="10"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="24" t="s">
+        <v>184</v>
+      </c>
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="10"/>
+      <c r="B18" s="23" t="s">
+        <v>180</v>
+      </c>
+      <c r="C18" s="23" t="s">
+        <v>181</v>
+      </c>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="B19" s="54">
+        <f>SUMPRODUCT(C6:D6,B13:C13) +B6</f>
+        <v>0.69211111948417825</v>
+      </c>
+      <c r="C19" s="54">
+        <f>SUMPRODUCT(C7:D7, B13:C13) + B7</f>
+        <v>0.6921111189032022</v>
+      </c>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="10"/>
+      <c r="B20" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="C20" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="10"/>
+      <c r="E20" s="10"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="B21" s="53">
+        <f>$B$15</f>
+        <v>0.69211111571181716</v>
+      </c>
+      <c r="C21" s="53">
+        <f>$B$15</f>
+        <v>0.69211111571181716</v>
+      </c>
+      <c r="D21" s="49"/>
+      <c r="E21" s="10"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="10"/>
+      <c r="B22" s="49"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="B23" s="10"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="B24" s="51">
+        <f>SUMPRODUCT(B19:C19,B13:C13)</f>
+        <v>147.71189197767993</v>
+      </c>
+      <c r="C24" s="51"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="B25" s="51">
+        <f>$B$9*B15</f>
+        <v>51.908333678386285</v>
+      </c>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="B26" s="52">
+        <f>B24-B25</f>
+        <v>95.803558299293641</v>
+      </c>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="10"/>
+      <c r="B27" s="10"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6829978-8C83-46EC-9B0D-95A12529CCF4}">
+  <dimension ref="A2:J8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="31" t="s">
+        <v>162</v>
+      </c>
+      <c r="B2" s="31" t="s">
+        <v>163</v>
+      </c>
+      <c r="C2" s="31" t="s">
+        <v>164</v>
+      </c>
+      <c r="D2" s="31" t="s">
+        <v>165</v>
+      </c>
+      <c r="E2" s="31" t="s">
+        <v>167</v>
+      </c>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31" t="s">
+        <v>168</v>
+      </c>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31" t="s">
+        <v>189</v>
+      </c>
+      <c r="J2" s="31" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>5</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+      <c r="D3">
+        <v>200</v>
+      </c>
+      <c r="E3">
+        <f>$B$7-B3</f>
+        <v>5</v>
+      </c>
+      <c r="F3">
+        <f>E3 * -1</f>
+        <v>-5</v>
+      </c>
+      <c r="G3">
+        <f>$C$7-C3</f>
+        <v>-5</v>
+      </c>
+      <c r="H3">
+        <f>G3 * -1</f>
+        <v>5</v>
+      </c>
+      <c r="I3" s="6">
+        <v>5</v>
+      </c>
+      <c r="J3" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>10</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+      <c r="D4">
+        <v>150</v>
+      </c>
+      <c r="E4">
+        <f t="shared" ref="E4:E7" si="0">$B$7-B4</f>
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <f t="shared" ref="F4:F6" si="1">E4 * -1</f>
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <f t="shared" ref="G4:G6" si="2">$C$7-C4</f>
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <f t="shared" ref="H4:H6" si="3">G4 * -1</f>
+        <v>0</v>
+      </c>
+      <c r="I4" s="6">
+        <v>0</v>
+      </c>
+      <c r="J4" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>12</v>
+      </c>
+      <c r="D5">
+        <v>200</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="1"/>
+        <v>-10</v>
+      </c>
+      <c r="G5">
+        <f t="shared" si="2"/>
+        <v>-7</v>
+      </c>
+      <c r="H5">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="I5" s="6">
+        <v>10</v>
+      </c>
+      <c r="J5" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>12</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>300</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="0"/>
+        <v>-2</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="3"/>
+        <v>-5</v>
+      </c>
+      <c r="I6" s="6">
+        <v>2</v>
+      </c>
+      <c r="J6" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="31" t="s">
+        <v>166</v>
+      </c>
+      <c r="B7" s="1">
+        <v>10</v>
+      </c>
+      <c r="C7" s="1">
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <f>SUMPRODUCT(D3:D6,I3:I6)</f>
+        <v>3600</v>
+      </c>
+      <c r="J7">
+        <f>SUMPRODUCT(D3:D6,J3:J6)</f>
+        <v>3900</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>170</v>
+      </c>
+      <c r="B8" s="2">
+        <f>SUM(I7:J7)</f>
+        <v>7500</v>
       </c>
     </row>
   </sheetData>

--- a/class_excel/temp_midterm.xlsx
+++ b/class_excel/temp_midterm.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\T00229\Documents\GitHub\DADS7102\class_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1FEE5B8-7AB4-4062-8876-16A21AC25CEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9176C054-1FD0-40C7-9D1F-62706308322C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="18" xr2:uid="{962D6ACA-47B2-4C7E-82D5-0F5476EE75BF}"/>
   </bookViews>
@@ -58,19 +58,19 @@
     <definedName name="solver_adj" localSheetId="3" hidden="1">ch_2_2!$B$2:$C$2</definedName>
     <definedName name="solver_adj" localSheetId="4" hidden="1">ch_2_3!$B$2:$E$4</definedName>
     <definedName name="solver_adj" localSheetId="5" hidden="1">ch_2_4!$B$2:$H$2</definedName>
-    <definedName name="solver_adj" localSheetId="6" hidden="1">ch_3_1!$D$3:$D$28</definedName>
+    <definedName name="solver_adj" localSheetId="6" hidden="1">ch_3_1!$D$2:$D$27</definedName>
     <definedName name="solver_adj" localSheetId="7" hidden="1">ch_3_2!$D$3:$D$8</definedName>
-    <definedName name="solver_adj" localSheetId="8" hidden="1">ch_3_3!$B$12:$G$12</definedName>
+    <definedName name="solver_adj" localSheetId="8" hidden="1">ch_3_3!$B$10:$G$10</definedName>
     <definedName name="solver_adj" localSheetId="9" hidden="1">ch_3_4!$E$2:$E$11</definedName>
-    <definedName name="solver_adj" localSheetId="10" hidden="1">ch4_1!$B$11:$F$12</definedName>
+    <definedName name="solver_adj" localSheetId="10" hidden="1">ch4_1!$B$10:$F$11</definedName>
     <definedName name="solver_adj" localSheetId="11" hidden="1">'ch4_1 (2)'!$B$11:$G$12</definedName>
     <definedName name="solver_adj" localSheetId="12" hidden="1">ch4_2!$B$2:$H$2</definedName>
     <definedName name="solver_adj" localSheetId="13" hidden="1">ch4_3!$B$2:$G$2</definedName>
     <definedName name="solver_adj" localSheetId="14" hidden="1">ch4_4!$B$2:$H$2</definedName>
-    <definedName name="solver_adj" localSheetId="15" hidden="1">ch4_5!$B$14:$G$15</definedName>
+    <definedName name="solver_adj" localSheetId="15" hidden="1">ch4_5!$B$12:$G$13</definedName>
     <definedName name="solver_adj" localSheetId="16" hidden="1">ch5_1!$B$6:$C$6</definedName>
-    <definedName name="solver_adj" localSheetId="17" hidden="1">ch5_2!$B$13:$C$13,ch5_2!$B$15</definedName>
-    <definedName name="solver_adj" localSheetId="18" hidden="1">ch5_3!$B$7:$C$7,ch5_3!$I$3:$J$6</definedName>
+    <definedName name="solver_adj" localSheetId="17" hidden="1">ch5_2!$B$11:$C$11,ch5_2!$B$13</definedName>
+    <definedName name="solver_adj" localSheetId="18" hidden="1">ch5_3!$B$6:$C$6,ch5_3!$I$2:$J$5</definedName>
     <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="1" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="2" hidden="1">0.0001</definedName>
@@ -170,40 +170,40 @@
     <definedName name="solver_lhs1" localSheetId="1" hidden="1">ch_1_2!$F$5:$F$7</definedName>
     <definedName name="solver_lhs1" localSheetId="2" hidden="1">ch_2_1!$B$4:$I$4</definedName>
     <definedName name="solver_lhs1" localSheetId="3" hidden="1">ch_2_2!$E$4:$E$6</definedName>
-    <definedName name="solver_lhs1" localSheetId="4" hidden="1">ch_2_3!$G$2:$G$6</definedName>
+    <definedName name="solver_lhs1" localSheetId="4" hidden="1">ch_2_3!$D$11:$D$15</definedName>
     <definedName name="solver_lhs1" localSheetId="5" hidden="1">ch_2_4!$B$2:$H$2</definedName>
-    <definedName name="solver_lhs1" localSheetId="6" hidden="1">ch_3_1!$D$3:$D$28</definedName>
+    <definedName name="solver_lhs1" localSheetId="6" hidden="1">ch_3_1!$D$2:$D$27</definedName>
     <definedName name="solver_lhs1" localSheetId="7" hidden="1">ch_3_2!$D$3:$D$8</definedName>
-    <definedName name="solver_lhs1" localSheetId="8" hidden="1">ch_3_3!$B$12:$G$12</definedName>
+    <definedName name="solver_lhs1" localSheetId="8" hidden="1">ch_3_3!$B$10:$G$10</definedName>
     <definedName name="solver_lhs1" localSheetId="9" hidden="1">ch_3_4!$E$2:$E$3</definedName>
-    <definedName name="solver_lhs1" localSheetId="10" hidden="1">ch4_1!$B$11:$F$11</definedName>
+    <definedName name="solver_lhs1" localSheetId="10" hidden="1">ch4_1!$B$10:$F$10</definedName>
     <definedName name="solver_lhs1" localSheetId="11" hidden="1">'ch4_1 (2)'!$B$11:$G$11</definedName>
     <definedName name="solver_lhs1" localSheetId="12" hidden="1">ch4_2!$B$2:$H$2</definedName>
     <definedName name="solver_lhs1" localSheetId="13" hidden="1">ch4_3!$B$2:$G$2</definedName>
     <definedName name="solver_lhs1" localSheetId="14" hidden="1">ch4_4!$B$2:$H$2</definedName>
-    <definedName name="solver_lhs1" localSheetId="15" hidden="1">ch4_5!$B$14:$G$14</definedName>
-    <definedName name="solver_lhs1" localSheetId="17" hidden="1">ch5_2!$B$19:$C$19</definedName>
-    <definedName name="solver_lhs1" localSheetId="18" hidden="1">ch5_3!$I$3:$I$6</definedName>
+    <definedName name="solver_lhs1" localSheetId="15" hidden="1">ch4_5!$B$12:$G$12</definedName>
+    <definedName name="solver_lhs1" localSheetId="17" hidden="1">ch5_2!$G$3:$H$3</definedName>
+    <definedName name="solver_lhs1" localSheetId="18" hidden="1">ch5_3!$I$2:$I$5</definedName>
     <definedName name="solver_lhs2" localSheetId="0" hidden="1">ch_1_1!$B$8:$B$9</definedName>
     <definedName name="solver_lhs2" localSheetId="2" hidden="1">ch_2_1!$O$2:$O$4</definedName>
-    <definedName name="solver_lhs2" localSheetId="5" hidden="1">ch_2_4!$J$3</definedName>
-    <definedName name="solver_lhs2" localSheetId="6" hidden="1">ch_3_1!$K$3:$K$9</definedName>
+    <definedName name="solver_lhs2" localSheetId="5" hidden="1">ch_2_4!$F$8</definedName>
+    <definedName name="solver_lhs2" localSheetId="6" hidden="1">ch_3_1!$K$2:$K$8</definedName>
     <definedName name="solver_lhs2" localSheetId="7" hidden="1">ch_3_2!$K$3:$K$7</definedName>
-    <definedName name="solver_lhs2" localSheetId="8" hidden="1">ch_3_3!$B$20:$G$20</definedName>
+    <definedName name="solver_lhs2" localSheetId="8" hidden="1">ch_3_3!$B$18:$G$18</definedName>
     <definedName name="solver_lhs2" localSheetId="9" hidden="1">ch_3_4!$L$2:$L$8</definedName>
-    <definedName name="solver_lhs2" localSheetId="10" hidden="1">ch4_1!$B$12:$F$12</definedName>
+    <definedName name="solver_lhs2" localSheetId="10" hidden="1">ch4_1!$B$11:$F$11</definedName>
     <definedName name="solver_lhs2" localSheetId="11" hidden="1">'ch4_1 (2)'!$B$12:$G$12</definedName>
-    <definedName name="solver_lhs2" localSheetId="12" hidden="1">ch4_2!$J$4</definedName>
+    <definedName name="solver_lhs2" localSheetId="12" hidden="1">ch4_2!$F$7</definedName>
     <definedName name="solver_lhs2" localSheetId="13" hidden="1">ch4_3!$H$4:$H$9</definedName>
     <definedName name="solver_lhs2" localSheetId="14" hidden="1">ch4_4!$I$4:$I$10</definedName>
-    <definedName name="solver_lhs2" localSheetId="15" hidden="1">ch4_5!$B$15:$G$15</definedName>
-    <definedName name="solver_lhs2" localSheetId="18" hidden="1">ch5_3!$I$3:$I$6</definedName>
-    <definedName name="solver_lhs3" localSheetId="8" hidden="1">ch_3_3!$B$20:$G$20</definedName>
-    <definedName name="solver_lhs3" localSheetId="10" hidden="1">ch4_1!$B$16:$B$17</definedName>
+    <definedName name="solver_lhs2" localSheetId="15" hidden="1">ch4_5!$B$13:$G$13</definedName>
+    <definedName name="solver_lhs2" localSheetId="18" hidden="1">ch5_3!$I$2:$I$5</definedName>
+    <definedName name="solver_lhs3" localSheetId="8" hidden="1">ch_3_3!$B$18:$G$18</definedName>
+    <definedName name="solver_lhs3" localSheetId="10" hidden="1">ch4_1!$I$1:$I$2</definedName>
     <definedName name="solver_lhs3" localSheetId="11" hidden="1">'ch4_1 (2)'!$B$16:$B$17</definedName>
-    <definedName name="solver_lhs3" localSheetId="15" hidden="1">ch4_5!$B$24:$G$24</definedName>
-    <definedName name="solver_lhs3" localSheetId="18" hidden="1">ch5_3!$J$3:$J$6</definedName>
-    <definedName name="solver_lhs4" localSheetId="18" hidden="1">ch5_3!$J$3:$J$6</definedName>
+    <definedName name="solver_lhs3" localSheetId="15" hidden="1">ch4_5!$B$20:$G$20</definedName>
+    <definedName name="solver_lhs3" localSheetId="18" hidden="1">ch5_3!$J$2:$J$5</definedName>
+    <definedName name="solver_lhs4" localSheetId="18" hidden="1">ch5_3!$J$2:$J$5</definedName>
     <definedName name="solver_mip" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="2" hidden="1">2147483647</definedName>
@@ -362,19 +362,19 @@
     <definedName name="solver_opt" localSheetId="3" hidden="1">ch_2_2!$B$10</definedName>
     <definedName name="solver_opt" localSheetId="4" hidden="1">ch_2_3!$B$14</definedName>
     <definedName name="solver_opt" localSheetId="5" hidden="1">ch_2_4!$B$8</definedName>
-    <definedName name="solver_opt" localSheetId="6" hidden="1">ch_3_1!$I$11</definedName>
+    <definedName name="solver_opt" localSheetId="6" hidden="1">ch_3_1!$I$10</definedName>
     <definedName name="solver_opt" localSheetId="7" hidden="1">ch_3_2!$B$11</definedName>
-    <definedName name="solver_opt" localSheetId="8" hidden="1">ch_3_3!$N$4</definedName>
+    <definedName name="solver_opt" localSheetId="8" hidden="1">ch_3_3!$H$26</definedName>
     <definedName name="solver_opt" localSheetId="9" hidden="1">ch_3_4!$E$13</definedName>
-    <definedName name="solver_opt" localSheetId="10" hidden="1">ch4_1!$B$22</definedName>
+    <definedName name="solver_opt" localSheetId="10" hidden="1">ch4_1!$I$7</definedName>
     <definedName name="solver_opt" localSheetId="11" hidden="1">'ch4_1 (2)'!$B$22</definedName>
-    <definedName name="solver_opt" localSheetId="12" hidden="1">ch4_2!$B$9</definedName>
+    <definedName name="solver_opt" localSheetId="12" hidden="1">ch4_2!$B$7</definedName>
     <definedName name="solver_opt" localSheetId="13" hidden="1">ch4_3!$H$2</definedName>
     <definedName name="solver_opt" localSheetId="14" hidden="1">ch4_4!$I$2</definedName>
-    <definedName name="solver_opt" localSheetId="15" hidden="1">ch4_5!$H$33</definedName>
+    <definedName name="solver_opt" localSheetId="15" hidden="1">ch4_5!$H$29</definedName>
     <definedName name="solver_opt" localSheetId="16" hidden="1">ch5_1!$B$7</definedName>
-    <definedName name="solver_opt" localSheetId="17" hidden="1">ch5_2!$B$26</definedName>
-    <definedName name="solver_opt" localSheetId="18" hidden="1">ch5_3!$B$8</definedName>
+    <definedName name="solver_opt" localSheetId="17" hidden="1">ch5_2!$G$10</definedName>
+    <definedName name="solver_opt" localSheetId="18" hidden="1">ch5_3!$B$7</definedName>
     <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="1" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="2" hidden="1">0.000001</definedName>
@@ -455,11 +455,11 @@
     <definedName name="solver_rhs1" localSheetId="1" hidden="1">ch_1_2!$H$5:$H$7</definedName>
     <definedName name="solver_rhs1" localSheetId="2" hidden="1">ch_2_1!$B$6:$I$6</definedName>
     <definedName name="solver_rhs1" localSheetId="3" hidden="1">ch_2_2!$G$4:$G$6</definedName>
-    <definedName name="solver_rhs1" localSheetId="4" hidden="1">ch_2_3!$I$2:$I$6</definedName>
+    <definedName name="solver_rhs1" localSheetId="4" hidden="1">ch_2_3!$F$11:$F$15</definedName>
     <definedName name="solver_rhs1" localSheetId="5" hidden="1">1</definedName>
-    <definedName name="solver_rhs1" localSheetId="6" hidden="1">ch_3_1!$F$3:$F$28</definedName>
+    <definedName name="solver_rhs1" localSheetId="6" hidden="1">ch_3_1!$F$2:$F$27</definedName>
     <definedName name="solver_rhs1" localSheetId="7" hidden="1">ch_3_2!$F$3:$F$8</definedName>
-    <definedName name="solver_rhs1" localSheetId="8" hidden="1">ch_3_3!$B$14:$G$14</definedName>
+    <definedName name="solver_rhs1" localSheetId="8" hidden="1">ch_3_3!$B$12:$G$12</definedName>
     <definedName name="solver_rhs1" localSheetId="9" hidden="1">ch_3_4!$G$2:$G$3</definedName>
     <definedName name="solver_rhs1" localSheetId="10" hidden="1">"binary"</definedName>
     <definedName name="solver_rhs1" localSheetId="11" hidden="1">"binary"</definedName>
@@ -467,28 +467,28 @@
     <definedName name="solver_rhs1" localSheetId="13" hidden="1">"binary"</definedName>
     <definedName name="solver_rhs1" localSheetId="14" hidden="1">"integer"</definedName>
     <definedName name="solver_rhs1" localSheetId="15" hidden="1">"binary"</definedName>
-    <definedName name="solver_rhs1" localSheetId="17" hidden="1">ch5_2!$B$21:$C$21</definedName>
-    <definedName name="solver_rhs1" localSheetId="18" hidden="1">ch5_3!$E$3:$E$6</definedName>
+    <definedName name="solver_rhs1" localSheetId="17" hidden="1">ch5_2!$G$5:$H$5</definedName>
+    <definedName name="solver_rhs1" localSheetId="18" hidden="1">ch5_3!$E$2:$E$5</definedName>
     <definedName name="solver_rhs2" localSheetId="0" hidden="1">ch_1_1!$D$8:$D$9</definedName>
     <definedName name="solver_rhs2" localSheetId="2" hidden="1">ch_2_1!$Q$2:$Q$4</definedName>
-    <definedName name="solver_rhs2" localSheetId="5" hidden="1">ch_2_4!$L$3</definedName>
-    <definedName name="solver_rhs2" localSheetId="6" hidden="1">ch_3_1!$M$3:$M$9</definedName>
+    <definedName name="solver_rhs2" localSheetId="5" hidden="1">ch_2_4!$H$8</definedName>
+    <definedName name="solver_rhs2" localSheetId="6" hidden="1">ch_3_1!$M$2:$M$8</definedName>
     <definedName name="solver_rhs2" localSheetId="7" hidden="1">ch_3_2!$M$3:$M$7</definedName>
-    <definedName name="solver_rhs2" localSheetId="8" hidden="1">ch_3_3!$B$22:$G$22</definedName>
+    <definedName name="solver_rhs2" localSheetId="8" hidden="1">ch_3_3!$B$20:$G$20</definedName>
     <definedName name="solver_rhs2" localSheetId="9" hidden="1">ch_3_4!$N$2:$N$8</definedName>
-    <definedName name="solver_rhs2" localSheetId="10" hidden="1">ch4_1!$B$14:$F$14</definedName>
+    <definedName name="solver_rhs2" localSheetId="10" hidden="1">ch4_1!$B$13:$F$13</definedName>
     <definedName name="solver_rhs2" localSheetId="11" hidden="1">'ch4_1 (2)'!$B$14:$G$14</definedName>
-    <definedName name="solver_rhs2" localSheetId="12" hidden="1">ch4_2!$L$4</definedName>
+    <definedName name="solver_rhs2" localSheetId="12" hidden="1">ch4_2!$H$7</definedName>
     <definedName name="solver_rhs2" localSheetId="13" hidden="1">ch4_3!$J$4:$J$9</definedName>
     <definedName name="solver_rhs2" localSheetId="14" hidden="1">ch4_4!$K$4:$K$10</definedName>
-    <definedName name="solver_rhs2" localSheetId="15" hidden="1">ch4_5!$B$18:$G$18</definedName>
-    <definedName name="solver_rhs2" localSheetId="18" hidden="1">ch5_3!$F$3:$F$6</definedName>
+    <definedName name="solver_rhs2" localSheetId="15" hidden="1">ch4_5!$B$16:$G$16</definedName>
+    <definedName name="solver_rhs2" localSheetId="18" hidden="1">ch5_3!$F$2:$F$5</definedName>
     <definedName name="solver_rhs3" localSheetId="8" hidden="1">0</definedName>
-    <definedName name="solver_rhs3" localSheetId="10" hidden="1">ch4_1!$D$16:$D$17</definedName>
+    <definedName name="solver_rhs3" localSheetId="10" hidden="1">ch4_1!$K$1:$K$2</definedName>
     <definedName name="solver_rhs3" localSheetId="11" hidden="1">'ch4_1 (2)'!$D$16:$D$17</definedName>
     <definedName name="solver_rhs3" localSheetId="15" hidden="1">0</definedName>
-    <definedName name="solver_rhs3" localSheetId="18" hidden="1">ch5_3!$G$3:$G$6</definedName>
-    <definedName name="solver_rhs4" localSheetId="18" hidden="1">ch5_3!$H$3:$H$6</definedName>
+    <definedName name="solver_rhs3" localSheetId="18" hidden="1">ch5_3!$G$2:$G$5</definedName>
+    <definedName name="solver_rhs4" localSheetId="18" hidden="1">ch5_3!$H$2:$H$5</definedName>
     <definedName name="solver_rlx" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="2" hidden="1">2</definedName>
@@ -702,7 +702,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="186">
   <si>
     <t xml:space="preserve">basic </t>
   </si>
@@ -1001,9 +1001,6 @@
     <t>net</t>
   </si>
   <si>
-    <t>Multiperiod production model</t>
-  </si>
-  <si>
     <t>Input data</t>
   </si>
   <si>
@@ -1031,9 +1028,6 @@
     <t>Production capacity</t>
   </si>
   <si>
-    <t xml:space="preserve">produce capacity </t>
-  </si>
-  <si>
     <t>On hand after production</t>
   </si>
   <si>
@@ -1043,16 +1037,7 @@
     <t>Ending inventory</t>
   </si>
   <si>
-    <t>&gt;= 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">for shortage condition </t>
-  </si>
-  <si>
     <t>Storage capacity</t>
-  </si>
-  <si>
-    <t>inventory condition</t>
   </si>
   <si>
     <t>Summary of costs (all costs are in hundreds of dollars)</t>
@@ -1218,9 +1203,6 @@
     <t>total disctance</t>
   </si>
   <si>
-    <t>Florida Power &amp; Light peak-load pricing model</t>
-  </si>
-  <si>
     <t>Coefficients of demand functions</t>
   </si>
   <si>
@@ -1276,13 +1258,16 @@
   </si>
   <si>
     <t>T</t>
+  </si>
+  <si>
+    <t>Ending inventory (&gt;=0)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="7" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
@@ -1291,6 +1276,7 @@
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.000_);\(&quot;$&quot;#,##0.000\)"/>
     <numFmt numFmtId="167" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="168" formatCode="0.0%"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -1332,7 +1318,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1399,6 +1385,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -1424,14 +1422,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="5">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="8" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1517,13 +1516,31 @@
     <xf numFmtId="7" fontId="5" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="5" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="5" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="5">
+  <cellStyles count="6">
     <cellStyle name="Comma" xfId="4" builtinId="3"/>
     <cellStyle name="Comma 2" xfId="3" xr:uid="{C9C68EFB-DC8B-4BBD-B2A4-694D3E58E673}"/>
     <cellStyle name="Currency 2" xfId="2" xr:uid="{A9BDFC23-AFF7-42B4-B5DA-AB895D831664}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{67581A20-F69A-473C-AA9B-FD9B097B2E83}"/>
+    <cellStyle name="Percent" xfId="5" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2264,19 +2281,19 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="B1" t="s">
         <v>94</v>
       </c>
       <c r="C1" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D1" t="s">
         <v>70</v>
       </c>
       <c r="E1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="I1" t="s">
         <v>88</v>
@@ -2285,13 +2302,13 @@
         <v>94</v>
       </c>
       <c r="K1" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="L1" t="s">
         <v>98</v>
       </c>
       <c r="N1" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
@@ -2609,317 +2626,327 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D286B17C-5944-46CA-B76E-D859AC09B597}">
-  <dimension ref="A2:F22"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.140625" customWidth="1"/>
-    <col min="3" max="3" width="10.42578125" customWidth="1"/>
+    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.85546875" customWidth="1"/>
+    <col min="8" max="8" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
-        <v>125</v>
-      </c>
-      <c r="C2" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C1" t="s">
         <v>56</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E1" t="s">
+        <v>122</v>
+      </c>
+      <c r="F1" t="s">
+        <v>123</v>
+      </c>
+      <c r="G1" s="60"/>
+      <c r="H1" t="s">
+        <v>135</v>
+      </c>
+      <c r="I1" s="4">
+        <f>SUMPRODUCT(B3:F3,B11:F11)</f>
+        <v>4000</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="K1" s="3">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>126</v>
       </c>
-      <c r="E2" t="s">
+      <c r="B2">
+        <v>1500</v>
+      </c>
+      <c r="C2">
+        <v>1200</v>
+      </c>
+      <c r="D2">
+        <v>1600</v>
+      </c>
+      <c r="E2">
+        <v>1500</v>
+      </c>
+      <c r="F2">
+        <v>1600</v>
+      </c>
+      <c r="G2" s="60"/>
+      <c r="H2" t="s">
+        <v>136</v>
+      </c>
+      <c r="I2" s="4">
+        <f xml:space="preserve"> SUMPRODUCT(B4:F4,B11:F11)</f>
+        <v>4500</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="K2" s="3">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="29" t="s">
         <v>127</v>
       </c>
-      <c r="F2" t="s">
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>6</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3">
+        <v>8</v>
+      </c>
+      <c r="G3" s="60"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>131</v>
-      </c>
-      <c r="B3">
-        <v>1500</v>
-      </c>
-      <c r="C3">
-        <v>1200</v>
-      </c>
-      <c r="D3">
-        <v>1600</v>
-      </c>
-      <c r="E3">
-        <v>1500</v>
-      </c>
-      <c r="F3">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="29" t="s">
-        <v>132</v>
-      </c>
       <c r="B4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="D4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="F4">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>133</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>2.5</v>
-      </c>
-      <c r="D5">
-        <v>4</v>
-      </c>
-      <c r="E5">
-        <v>4.5</v>
-      </c>
-      <c r="F5">
         <v>5.5</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="G4" s="60"/>
+      <c r="H4" t="s">
         <v>134</v>
       </c>
-      <c r="B6">
-        <v>35</v>
-      </c>
-      <c r="C6">
-        <v>40</v>
-      </c>
-      <c r="D6">
-        <v>65</v>
-      </c>
-      <c r="E6">
-        <v>70</v>
-      </c>
-      <c r="F6">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B7">
-        <v>20</v>
-      </c>
-      <c r="C7">
-        <v>10</v>
-      </c>
-      <c r="D7">
-        <v>25</v>
-      </c>
-      <c r="E7">
-        <v>30</v>
-      </c>
-      <c r="F7">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>138</v>
-      </c>
-      <c r="B8">
-        <f>B6-B7</f>
-        <v>15</v>
-      </c>
-      <c r="C8">
-        <f>C6-C7</f>
-        <v>30</v>
-      </c>
-      <c r="D8">
-        <f>D6-D7</f>
-        <v>40</v>
-      </c>
-      <c r="E8">
-        <f>E6-E7</f>
-        <v>40</v>
-      </c>
-      <c r="F8">
-        <f>F6-F7</f>
-        <v>75</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
-        <v>125</v>
-      </c>
-      <c r="C10" t="s">
-        <v>56</v>
-      </c>
-      <c r="D10" t="s">
-        <v>126</v>
-      </c>
-      <c r="E10" t="s">
-        <v>127</v>
-      </c>
-      <c r="F10" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>129</v>
-      </c>
-      <c r="B11" s="6">
-        <v>0</v>
-      </c>
-      <c r="C11" s="6">
-        <v>1</v>
-      </c>
-      <c r="D11" s="6">
-        <v>0</v>
-      </c>
-      <c r="E11" s="6">
-        <v>0</v>
-      </c>
-      <c r="F11" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>130</v>
-      </c>
-      <c r="B12" s="6">
-        <v>0</v>
-      </c>
-      <c r="C12" s="6">
-        <v>965.51724137931024</v>
-      </c>
-      <c r="D12" s="6">
-        <v>0</v>
-      </c>
-      <c r="E12" s="6">
-        <v>0</v>
-      </c>
-      <c r="F12" s="6">
-        <v>379.31034482758622</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B13" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B14">
-        <f>B11 * $B$19</f>
-        <v>0</v>
-      </c>
-      <c r="C14">
-        <f>C11 * $B$19</f>
-        <v>1000000</v>
-      </c>
-      <c r="D14">
-        <f>D11 * $B$19</f>
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <f>E11 * $B$19</f>
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <f>F11 * $B$19</f>
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>140</v>
-      </c>
-      <c r="B16" s="4">
-        <f>SUMPRODUCT(B4:F4,B12:F12)</f>
-        <v>4000</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D16" s="3">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>141</v>
-      </c>
-      <c r="B17" s="4">
-        <f>SUMPRODUCT(B5:F5, B12:F12)</f>
-        <v>4500</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D17" s="3">
-        <v>4500</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>139</v>
-      </c>
-      <c r="B19">
+      <c r="I4">
         <f>1000000</f>
         <v>1000000</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>136</v>
-      </c>
-      <c r="B20">
-        <f>SUMPRODUCT(B8:F8, B12:F12)</f>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B5">
+        <v>35</v>
+      </c>
+      <c r="C5">
+        <v>40</v>
+      </c>
+      <c r="D5">
+        <v>65</v>
+      </c>
+      <c r="E5">
+        <v>70</v>
+      </c>
+      <c r="F5">
+        <v>110</v>
+      </c>
+      <c r="G5" s="60"/>
+      <c r="H5" t="s">
+        <v>131</v>
+      </c>
+      <c r="I5" s="62">
+        <f xml:space="preserve"> SUMPRODUCT(B11:F11,B7:F7)</f>
         <v>57413.793103448275</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>137</v>
-      </c>
-      <c r="B21">
-        <f>SUMPRODUCT(B3:F3, B11:F11)</f>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>130</v>
+      </c>
+      <c r="B6">
+        <v>20</v>
+      </c>
+      <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="D6">
+        <v>25</v>
+      </c>
+      <c r="E6">
+        <v>30</v>
+      </c>
+      <c r="F6">
+        <v>35</v>
+      </c>
+      <c r="G6" s="60"/>
+      <c r="H6" t="s">
+        <v>132</v>
+      </c>
+      <c r="I6">
+        <f xml:space="preserve"> SUMPRODUCT(B10:F10,B2:F2)</f>
         <v>2800</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>133</v>
+      </c>
+      <c r="B7">
+        <f>B5-B6</f>
+        <v>15</v>
+      </c>
+      <c r="C7">
+        <f>C5-C6</f>
+        <v>30</v>
+      </c>
+      <c r="D7">
+        <f>D5-D6</f>
+        <v>40</v>
+      </c>
+      <c r="E7">
+        <f>E5-E6</f>
+        <v>40</v>
+      </c>
+      <c r="F7">
+        <f>F5-F6</f>
+        <v>75</v>
+      </c>
+      <c r="G7" s="60"/>
+      <c r="H7" t="s">
         <v>39</v>
       </c>
-      <c r="B22" s="2">
-        <f>B20-B21</f>
+      <c r="I7" s="61">
+        <f>I5-I6</f>
         <v>54613.793103448275</v>
       </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G8" s="60"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>120</v>
+      </c>
+      <c r="C9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E9" t="s">
+        <v>122</v>
+      </c>
+      <c r="F9" t="s">
+        <v>123</v>
+      </c>
+      <c r="G9" s="60"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>124</v>
+      </c>
+      <c r="B10" s="6">
+        <v>0</v>
+      </c>
+      <c r="C10" s="6">
+        <v>1</v>
+      </c>
+      <c r="D10" s="6">
+        <v>0</v>
+      </c>
+      <c r="E10" s="6">
+        <v>0</v>
+      </c>
+      <c r="F10" s="6">
+        <v>1</v>
+      </c>
+      <c r="G10" s="60"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>125</v>
+      </c>
+      <c r="B11" s="6">
+        <v>0</v>
+      </c>
+      <c r="C11" s="59">
+        <v>965.51724137931024</v>
+      </c>
+      <c r="D11" s="6">
+        <v>0</v>
+      </c>
+      <c r="E11" s="6">
+        <v>0</v>
+      </c>
+      <c r="F11" s="59">
+        <v>379.31034482758622</v>
+      </c>
+      <c r="G11" s="60"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B12" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="G12" s="60"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B13">
+        <f>B10 * $I$4</f>
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <f>C10 * $I$4</f>
+        <v>1000000</v>
+      </c>
+      <c r="D13">
+        <f>D10 * $I$4</f>
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <f>E10 * $I$4</f>
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <f>F10 * $I$4</f>
+        <v>1000000</v>
+      </c>
+      <c r="G13" s="60"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2940,27 +2967,27 @@
   <sheetData>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B2" s="31" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C2" s="31" t="s">
         <v>56</v>
       </c>
       <c r="D2" s="31" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="E2" s="31" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="F2" s="31" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="G2" s="31" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B3">
         <v>1500</v>
@@ -2983,7 +3010,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="29" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B4">
         <v>2</v>
@@ -3006,7 +3033,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B5">
         <v>3</v>
@@ -3029,7 +3056,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="B6">
         <v>35</v>
@@ -3052,7 +3079,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B7">
         <v>20</v>
@@ -3075,7 +3102,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B8">
         <f t="shared" ref="B8:G8" si="0">B6-B7</f>
@@ -3104,27 +3131,27 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C10" t="s">
         <v>56</v>
       </c>
       <c r="D10" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="E10" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="F10" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="G10" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="B11" s="6">
         <v>0</v>
@@ -3147,7 +3174,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B12" s="6">
         <v>0</v>
@@ -3216,7 +3243,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B16" s="4">
         <f>SUMPRODUCT(B4:G4,B12:G12)</f>
@@ -3231,7 +3258,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B17" s="4">
         <f>SUMPRODUCT(B5:G5, B12:G12)</f>
@@ -3246,7 +3273,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B19">
         <f>1000000</f>
@@ -3255,7 +3282,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B20">
         <f>SUMPRODUCT(B8:G8, B12:G12)</f>
@@ -3264,7 +3291,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B21">
         <f>SUMPRODUCT(B3:G3, B11:G11)</f>
@@ -3288,36 +3315,36 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA6CB6CF-31AC-43B2-BABC-B89D4F5C3C26}">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B1" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B1" s="31" t="s">
         <v>73</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="31" t="s">
         <v>75</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="31" t="s">
         <v>76</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="31" t="s">
         <v>77</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="31" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>82</v>
       </c>
@@ -3344,120 +3371,108 @@
       </c>
       <c r="K2" s="7"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
-      <c r="K3" s="7"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="J4" s="4">
-        <f>SUMPRODUCT(B2:H2, B5:H5)</f>
-        <v>14.8</v>
-      </c>
-      <c r="K4" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="L4" s="3">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3">
+        <v>5</v>
+      </c>
+      <c r="C3">
+        <v>2.4</v>
+      </c>
+      <c r="D3">
+        <v>3.5</v>
+      </c>
+      <c r="E3">
+        <v>5.9</v>
+      </c>
+      <c r="F3">
+        <v>6.9</v>
+      </c>
+      <c r="G3">
+        <v>4.5</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4">
+        <v>5.6</v>
+      </c>
+      <c r="C4">
+        <v>2.7</v>
+      </c>
+      <c r="D4">
+        <v>3.9</v>
+      </c>
+      <c r="E4">
+        <v>6.8</v>
+      </c>
+      <c r="F4">
+        <v>7.7</v>
+      </c>
+      <c r="G4">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="H4">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <f>(B4-B3)/B3</f>
+        <v>0.11999999999999993</v>
       </c>
       <c r="C5">
-        <v>2.4</v>
+        <f t="shared" ref="C5:G5" si="0">(C4-C3)/C3</f>
+        <v>0.12500000000000011</v>
       </c>
       <c r="D5">
-        <v>3.5</v>
-      </c>
-      <c r="E5">
-        <v>5.9</v>
-      </c>
-      <c r="F5">
-        <v>6.9</v>
-      </c>
-      <c r="G5">
-        <v>4.5</v>
-      </c>
-      <c r="H5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>80</v>
-      </c>
-      <c r="B6">
-        <v>5.6</v>
-      </c>
-      <c r="C6">
-        <v>2.7</v>
-      </c>
-      <c r="D6">
-        <v>3.9</v>
-      </c>
-      <c r="E6">
-        <v>6.8</v>
-      </c>
-      <c r="F6">
-        <v>7.7</v>
-      </c>
-      <c r="G6">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="H6">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>81</v>
-      </c>
-      <c r="B7">
-        <f>(B6-B5)/B5</f>
-        <v>0.11999999999999993</v>
-      </c>
-      <c r="C7">
-        <f t="shared" ref="C7:G7" si="0">(C6-C5)/C5</f>
-        <v>0.12500000000000011</v>
-      </c>
-      <c r="D7">
         <f t="shared" si="0"/>
         <v>0.11428571428571425</v>
       </c>
-      <c r="E7">
+      <c r="E5">
         <f t="shared" si="0"/>
         <v>0.15254237288135583</v>
       </c>
-      <c r="F7">
+      <c r="F5">
         <f t="shared" si="0"/>
         <v>0.11594202898550722</v>
       </c>
-      <c r="G7">
+      <c r="G5">
         <f t="shared" si="0"/>
         <v>0.13333333333333325</v>
       </c>
-      <c r="H7">
-        <f>(H6-H5)/H5</f>
+      <c r="H5">
+        <f>(H4-H3)/H3</f>
         <v>9.9999999999999936E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="2">
-        <f>SUMPRODUCT(B2:H2,B6:H6)</f>
+      <c r="B7" s="2">
+        <f>SUMPRODUCT(B2:H2,B4:H4)</f>
         <v>16.7</v>
+      </c>
+      <c r="F7" s="4">
+        <f>SUMPRODUCT(B2:H2, B3:H3)</f>
+        <v>14.8</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="H7" s="3">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -3468,36 +3483,45 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BF078DC-633E-40D6-9FA8-AC14046EFECF}">
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" customWidth="1"/>
+    <col min="2" max="2" width="7.42578125" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="4" max="4" width="7.5703125" customWidth="1"/>
+    <col min="5" max="5" width="8" customWidth="1"/>
+    <col min="6" max="6" width="7.85546875" customWidth="1"/>
+    <col min="7" max="7" width="9.85546875" customWidth="1"/>
+    <col min="8" max="8" width="6.5703125" customWidth="1"/>
+    <col min="9" max="9" width="3.85546875" customWidth="1"/>
+    <col min="10" max="10" width="6.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B1" t="s">
+      <c r="B1" s="31" t="s">
+        <v>137</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="D1" s="31" t="s">
+        <v>139</v>
+      </c>
+      <c r="E1" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="F1" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="G1" s="31" t="s">
         <v>142</v>
-      </c>
-      <c r="C1" t="s">
-        <v>143</v>
-      </c>
-      <c r="D1" t="s">
-        <v>144</v>
-      </c>
-      <c r="E1" t="s">
-        <v>145</v>
-      </c>
-      <c r="F1" t="s">
-        <v>146</v>
-      </c>
-      <c r="G1" t="s">
-        <v>147</v>
       </c>
       <c r="H1" s="31"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B2" s="6">
         <v>0</v>
@@ -3536,7 +3560,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -3569,7 +3593,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -3602,7 +3626,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -3635,7 +3659,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -3668,7 +3692,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -3701,7 +3725,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -3734,7 +3758,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -3755,9 +3779,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="33" t="s">
-        <v>149</v>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="33" t="s">
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -3768,55 +3792,67 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FFF8B83-9FAD-40FB-8E72-EC5CAC388E8C}">
   <dimension ref="A1:K12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="3.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="3.42578125" customWidth="1"/>
+    <col min="10" max="10" width="3.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="3.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="34" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B1" s="31" t="s">
+        <v>145</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>146</v>
+      </c>
+      <c r="D1" s="31" t="s">
+        <v>147</v>
+      </c>
+      <c r="E1" s="31" t="s">
+        <v>148</v>
+      </c>
+      <c r="F1" s="31" t="s">
+        <v>149</v>
+      </c>
+      <c r="G1" s="31" t="s">
+        <v>151</v>
+      </c>
+      <c r="H1" s="31" t="s">
         <v>150</v>
-      </c>
-      <c r="C1" s="31" t="s">
-        <v>151</v>
-      </c>
-      <c r="D1" s="31" t="s">
-        <v>152</v>
-      </c>
-      <c r="E1" s="31" t="s">
-        <v>153</v>
-      </c>
-      <c r="F1" s="31" t="s">
-        <v>154</v>
-      </c>
-      <c r="G1" s="31" t="s">
-        <v>156</v>
-      </c>
-      <c r="H1" s="31" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="B2" s="6">
+        <v>7</v>
+      </c>
+      <c r="C2" s="6">
+        <v>1</v>
+      </c>
+      <c r="D2" s="6">
+        <v>3</v>
+      </c>
+      <c r="E2" s="6">
+        <v>6</v>
+      </c>
+      <c r="F2" s="6">
+        <v>1</v>
+      </c>
+      <c r="G2" s="6">
         <v>5</v>
-      </c>
-      <c r="C2" s="6">
-        <v>1</v>
-      </c>
-      <c r="D2" s="6">
-        <v>7</v>
-      </c>
-      <c r="E2" s="6">
-        <v>1</v>
-      </c>
-      <c r="F2" s="6">
-        <v>3</v>
-      </c>
-      <c r="G2" s="6">
-        <v>6</v>
       </c>
       <c r="H2" s="6">
         <v>0</v>
@@ -3837,13 +3873,13 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="31" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -3855,14 +3891,14 @@
         <v>1</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" s="4">
         <f>SUMPRODUCT($B$2:$H$2, B4:H4)</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J4" t="s">
         <v>61</v>
@@ -3873,16 +3909,16 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="31" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -3894,11 +3930,11 @@
         <v>1</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" s="4">
         <f>SUMPRODUCT($B$2:$H$2, B5:H5)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J5" t="s">
         <v>61</v>
@@ -3909,19 +3945,19 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="31" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -3945,22 +3981,22 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="31" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -3981,7 +4017,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="31" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -3990,16 +4026,16 @@
         <v>1</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -4017,7 +4053,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="31" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -4029,20 +4065,20 @@
         <v>1</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" s="4">
         <f t="shared" ref="I9:I10" si="0">SUMPRODUCT($B$2:$H$2, B9:H9)</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J9" t="s">
         <v>61</v>
@@ -4053,10 +4089,10 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="31" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -4068,17 +4104,17 @@
         <v>1</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" s="4">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J10" t="s">
         <v>61</v>
@@ -4092,7 +4128,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="31" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -4123,13 +4159,12 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83770651-6A0E-4CA7-AD8F-E5D26ABE3557}">
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="50" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="7" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.7109375" customWidth="1"/>
+    <col min="2" max="7" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -4139,15 +4174,19 @@
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
+      <c r="E1" s="11"/>
       <c r="F1" s="10"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="10"/>
-      <c r="B2" s="10"/>
+      <c r="A2" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="B2" s="12">
+        <v>5000</v>
+      </c>
       <c r="C2" s="10"/>
       <c r="D2" s="10"/>
       <c r="E2" s="10"/>
@@ -4157,13 +4196,15 @@
       <c r="I2" s="10"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="B3" s="10"/>
+      <c r="A3" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="B3" s="13">
+        <v>0.05</v>
+      </c>
       <c r="C3" s="10"/>
       <c r="D3" s="10"/>
-      <c r="E3" s="11"/>
+      <c r="E3" s="10"/>
       <c r="F3" s="10"/>
       <c r="G3" s="10"/>
       <c r="H3" s="10"/>
@@ -4171,10 +4212,11 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="B4" s="12">
-        <v>5000</v>
+        <v>156</v>
+      </c>
+      <c r="B4" s="42">
+        <f>125000</f>
+        <v>125000</v>
       </c>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
@@ -4185,12 +4227,8 @@
       <c r="I4" s="10"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="B5" s="13">
-        <v>0.05</v>
-      </c>
+      <c r="A5" s="10"/>
+      <c r="B5" s="10"/>
       <c r="C5" s="10"/>
       <c r="D5" s="10"/>
       <c r="E5" s="10"/>
@@ -4201,174 +4239,195 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="B6" s="42">
-        <f>125000</f>
-        <v>125000</v>
-      </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
+        <v>102</v>
+      </c>
+      <c r="B6" s="14">
+        <v>1</v>
+      </c>
+      <c r="C6" s="14">
+        <v>2</v>
+      </c>
+      <c r="D6" s="14">
+        <v>3</v>
+      </c>
+      <c r="E6" s="14">
+        <v>4</v>
+      </c>
+      <c r="F6" s="14">
+        <v>5</v>
+      </c>
+      <c r="G6" s="14">
+        <v>6</v>
+      </c>
+      <c r="H6" s="15"/>
       <c r="I6" s="10"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="10"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
+      <c r="A7" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="B7" s="17">
+        <v>12.5</v>
+      </c>
+      <c r="C7" s="17">
+        <v>12.55</v>
+      </c>
+      <c r="D7" s="17">
+        <v>12.7</v>
+      </c>
+      <c r="E7" s="17">
+        <v>12.8</v>
+      </c>
+      <c r="F7" s="17">
+        <v>12.85</v>
+      </c>
+      <c r="G7" s="17">
+        <v>12.95</v>
+      </c>
       <c r="H7" s="10"/>
       <c r="I7" s="10"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="B8" s="14">
-        <v>1</v>
-      </c>
-      <c r="C8" s="14">
-        <v>2</v>
-      </c>
-      <c r="D8" s="14">
-        <v>3</v>
-      </c>
-      <c r="E8" s="14">
-        <v>4</v>
-      </c>
-      <c r="F8" s="14">
-        <v>5</v>
-      </c>
-      <c r="G8" s="14">
-        <v>6</v>
-      </c>
-      <c r="H8" s="15"/>
+      <c r="A8" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="B8" s="18">
+        <f t="shared" ref="B8:G8" si="0">B7* $B$3</f>
+        <v>0.625</v>
+      </c>
+      <c r="C8" s="18">
+        <f t="shared" si="0"/>
+        <v>0.62750000000000006</v>
+      </c>
+      <c r="D8" s="18">
+        <f t="shared" si="0"/>
+        <v>0.63500000000000001</v>
+      </c>
+      <c r="E8" s="18">
+        <f t="shared" si="0"/>
+        <v>0.64000000000000012</v>
+      </c>
+      <c r="F8" s="18">
+        <f t="shared" si="0"/>
+        <v>0.64250000000000007</v>
+      </c>
+      <c r="G8" s="18">
+        <f t="shared" si="0"/>
+        <v>0.64749999999999996</v>
+      </c>
+      <c r="H8" s="10"/>
       <c r="I8" s="10"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="B9" s="17">
-        <v>12.5</v>
-      </c>
-      <c r="C9" s="17">
-        <v>12.55</v>
-      </c>
-      <c r="D9" s="17">
-        <v>12.7</v>
-      </c>
-      <c r="E9" s="17">
-        <v>12.8</v>
-      </c>
-      <c r="F9" s="17">
-        <v>12.85</v>
-      </c>
-      <c r="G9" s="17">
-        <v>12.95</v>
-      </c>
       <c r="H9" s="10"/>
       <c r="I9" s="10"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="16" t="s">
+      <c r="A10" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="B10" s="18">
-        <f t="shared" ref="B10:G10" si="0">B9* $B$5</f>
-        <v>0.625</v>
-      </c>
-      <c r="C10" s="18">
-        <f t="shared" si="0"/>
-        <v>0.62750000000000006</v>
-      </c>
-      <c r="D10" s="18">
-        <f t="shared" si="0"/>
-        <v>0.63500000000000001</v>
-      </c>
-      <c r="E10" s="18">
-        <f t="shared" si="0"/>
-        <v>0.64000000000000012</v>
-      </c>
-      <c r="F10" s="18">
-        <f t="shared" si="0"/>
-        <v>0.64250000000000007</v>
-      </c>
-      <c r="G10" s="18">
-        <f t="shared" si="0"/>
-        <v>0.64749999999999996</v>
-      </c>
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
       <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="B11" s="14">
+        <v>1</v>
+      </c>
+      <c r="C11" s="14">
+        <v>2</v>
+      </c>
+      <c r="D11" s="14">
+        <v>3</v>
+      </c>
+      <c r="E11" s="14">
+        <v>4</v>
+      </c>
+      <c r="F11" s="14">
+        <v>5</v>
+      </c>
+      <c r="G11" s="14">
+        <v>6</v>
+      </c>
       <c r="H11" s="10"/>
       <c r="I11" s="10"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
+      <c r="A12" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="B12" s="39">
+        <v>1</v>
+      </c>
+      <c r="C12" s="39">
+        <v>0</v>
+      </c>
+      <c r="D12" s="39">
+        <v>1</v>
+      </c>
+      <c r="E12" s="39">
+        <v>1</v>
+      </c>
+      <c r="F12" s="39">
+        <v>1</v>
+      </c>
+      <c r="G12" s="39">
+        <v>0</v>
+      </c>
       <c r="H12" s="10"/>
+      <c r="I12" s="10"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="B13" s="14">
-        <v>1</v>
-      </c>
-      <c r="C13" s="14">
-        <v>2</v>
-      </c>
-      <c r="D13" s="14">
-        <v>3</v>
-      </c>
-      <c r="E13" s="14">
-        <v>4</v>
-      </c>
-      <c r="F13" s="14">
-        <v>5</v>
-      </c>
-      <c r="G13" s="14">
-        <v>6</v>
+        <v>106</v>
+      </c>
+      <c r="B13" s="40">
+        <v>20000</v>
+      </c>
+      <c r="C13" s="40">
+        <v>0</v>
+      </c>
+      <c r="D13" s="40">
+        <v>30000</v>
+      </c>
+      <c r="E13" s="40">
+        <v>35000</v>
+      </c>
+      <c r="F13" s="40">
+        <v>35000</v>
+      </c>
+      <c r="G13" s="40">
+        <v>0</v>
       </c>
       <c r="H13" s="10"/>
       <c r="I13" s="10"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="B14" s="39">
-        <v>1</v>
-      </c>
-      <c r="C14" s="39">
-        <v>0</v>
-      </c>
-      <c r="D14" s="39">
-        <v>1</v>
-      </c>
-      <c r="E14" s="39">
-        <v>1</v>
-      </c>
-      <c r="F14" s="39">
-        <v>1</v>
-      </c>
-      <c r="G14" s="39">
-        <v>0</v>
+      <c r="A14" s="10"/>
+      <c r="B14" s="45" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="45" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" s="45" t="s">
+        <v>2</v>
+      </c>
+      <c r="E14" s="45" t="s">
+        <v>2</v>
+      </c>
+      <c r="F14" s="45" t="s">
+        <v>2</v>
+      </c>
+      <c r="G14" s="45" t="s">
+        <v>2</v>
       </c>
       <c r="H14" s="10"/>
       <c r="I14" s="10"/>
@@ -4377,138 +4436,154 @@
       <c r="A15" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="B15" s="40">
-        <v>20000</v>
-      </c>
-      <c r="C15" s="40">
-        <v>0</v>
-      </c>
-      <c r="D15" s="40">
+      <c r="B15" s="38">
         <v>30000</v>
       </c>
-      <c r="E15" s="40">
-        <v>35000</v>
-      </c>
-      <c r="F15" s="40">
-        <v>35000</v>
-      </c>
-      <c r="G15" s="40">
-        <v>0</v>
+      <c r="C15" s="38">
+        <v>30000</v>
+      </c>
+      <c r="D15" s="38">
+        <v>30000</v>
+      </c>
+      <c r="E15" s="38">
+        <v>30000</v>
+      </c>
+      <c r="F15" s="38">
+        <v>30000</v>
+      </c>
+      <c r="G15" s="38">
+        <v>30000</v>
       </c>
       <c r="H15" s="10"/>
       <c r="I15" s="10"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="10"/>
-      <c r="B16" s="45" t="s">
-        <v>2</v>
-      </c>
-      <c r="C16" s="45" t="s">
-        <v>2</v>
-      </c>
-      <c r="D16" s="45" t="s">
-        <v>2</v>
-      </c>
-      <c r="E16" s="45" t="s">
-        <v>2</v>
-      </c>
-      <c r="F16" s="45" t="s">
-        <v>2</v>
-      </c>
-      <c r="G16" s="45" t="s">
-        <v>2</v>
+      <c r="B16" s="41">
+        <f>$B$4*B12</f>
+        <v>125000</v>
+      </c>
+      <c r="C16" s="41">
+        <f t="shared" ref="C16:F16" si="1">$B$4*C12</f>
+        <v>0</v>
+      </c>
+      <c r="D16" s="41">
+        <f>$B$4*D12</f>
+        <v>125000</v>
+      </c>
+      <c r="E16" s="41">
+        <f t="shared" si="1"/>
+        <v>125000</v>
+      </c>
+      <c r="F16" s="41">
+        <f t="shared" si="1"/>
+        <v>125000</v>
+      </c>
+      <c r="G16" s="41">
+        <f>$B$4*G12</f>
+        <v>0</v>
       </c>
       <c r="H16" s="10"/>
-      <c r="I16" s="10" t="s">
-        <v>109</v>
-      </c>
+      <c r="I16" s="10"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="B17" s="38">
-        <v>30000</v>
-      </c>
-      <c r="C17" s="38">
-        <v>30000</v>
-      </c>
-      <c r="D17" s="38">
-        <v>30000</v>
-      </c>
-      <c r="E17" s="38">
-        <v>30000</v>
-      </c>
-      <c r="F17" s="38">
-        <v>30000</v>
-      </c>
-      <c r="G17" s="38">
-        <v>30000</v>
-      </c>
+      <c r="A17" s="10"/>
+      <c r="B17" s="23"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="23"/>
       <c r="H17" s="10"/>
       <c r="I17" s="10"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="10"/>
-      <c r="B18" s="41">
-        <f>$B$6*B14</f>
-        <v>125000</v>
-      </c>
-      <c r="C18" s="41">
-        <f t="shared" ref="C18:F18" si="1">$B$6*C14</f>
-        <v>0</v>
-      </c>
-      <c r="D18" s="41">
-        <f>$B$6*D14</f>
-        <v>125000</v>
-      </c>
-      <c r="E18" s="41">
-        <f t="shared" si="1"/>
-        <v>125000</v>
-      </c>
-      <c r="F18" s="41">
-        <f t="shared" si="1"/>
-        <v>125000</v>
-      </c>
-      <c r="G18" s="41">
-        <f>$B$6*G14</f>
-        <v>0</v>
+      <c r="A18" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="B18" s="12">
+        <v>10000</v>
+      </c>
+      <c r="C18" s="12">
+        <v>15000</v>
+      </c>
+      <c r="D18" s="12">
+        <v>30000</v>
+      </c>
+      <c r="E18" s="12">
+        <v>35000</v>
+      </c>
+      <c r="F18" s="12">
+        <v>25000</v>
+      </c>
+      <c r="G18" s="12">
+        <v>10000</v>
       </c>
       <c r="H18" s="10"/>
       <c r="I18" s="10"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="10"/>
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
+      <c r="B19" s="21"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="23"/>
       <c r="I19" s="10"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="22" t="s">
+      <c r="A20" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
+      <c r="B20" s="27">
+        <f>(B13)-B18+B2</f>
+        <v>15000</v>
+      </c>
+      <c r="C20" s="27">
+        <f>(C13)-C18+B20</f>
+        <v>0</v>
+      </c>
+      <c r="D20" s="27">
+        <f>(D13)-D18+C20</f>
+        <v>0</v>
+      </c>
+      <c r="E20" s="27">
+        <f>(E13)-E18+D20</f>
+        <v>0</v>
+      </c>
+      <c r="F20" s="27">
+        <f>(F13)-F18+E20</f>
+        <v>10000</v>
+      </c>
+      <c r="G20" s="27">
+        <f>(G13)-G18+F20</f>
+        <v>0</v>
+      </c>
       <c r="H20" s="10"/>
       <c r="I20" s="10"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="10"/>
-      <c r="B21" s="23"/>
-      <c r="C21" s="23"/>
-      <c r="D21" s="23"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="23"/>
-      <c r="G21" s="23"/>
+      <c r="B21" s="36" t="s">
+        <v>2</v>
+      </c>
+      <c r="C21" s="36" t="s">
+        <v>2</v>
+      </c>
+      <c r="D21" s="36" t="s">
+        <v>2</v>
+      </c>
+      <c r="E21" s="36" t="s">
+        <v>2</v>
+      </c>
+      <c r="F21" s="36" t="s">
+        <v>2</v>
+      </c>
+      <c r="G21" s="36" t="s">
+        <v>2</v>
+      </c>
       <c r="H21" s="10"/>
       <c r="I21" s="10"/>
     </row>
@@ -4516,279 +4591,183 @@
       <c r="A22" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="B22" s="12">
+      <c r="B22" s="37">
         <v>10000</v>
       </c>
-      <c r="C22" s="12">
-        <v>15000</v>
-      </c>
-      <c r="D22" s="12">
-        <v>30000</v>
-      </c>
-      <c r="E22" s="12">
-        <v>35000</v>
-      </c>
-      <c r="F22" s="12">
-        <v>25000</v>
-      </c>
-      <c r="G22" s="12">
+      <c r="C22" s="37">
+        <v>10000</v>
+      </c>
+      <c r="D22" s="37">
+        <v>10000</v>
+      </c>
+      <c r="E22" s="37">
+        <v>10000</v>
+      </c>
+      <c r="F22" s="37">
+        <v>10000</v>
+      </c>
+      <c r="G22" s="37">
         <v>10000</v>
       </c>
       <c r="H22" s="10"/>
       <c r="I22" s="10"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="10"/>
-      <c r="B23" s="21"/>
-      <c r="C23" s="21"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="21"/>
-      <c r="G23" s="21"/>
-      <c r="H23" s="23" t="s">
+      <c r="A23" s="19"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10"/>
+      <c r="I23" s="10"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="B24" s="18"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="10"/>
+      <c r="I24" s="10"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="B25" s="14">
+        <v>1</v>
+      </c>
+      <c r="C25" s="14">
+        <v>2</v>
+      </c>
+      <c r="D25" s="14">
+        <v>3</v>
+      </c>
+      <c r="E25" s="14">
+        <v>4</v>
+      </c>
+      <c r="F25" s="14">
+        <v>5</v>
+      </c>
+      <c r="G25" s="14">
+        <v>6</v>
+      </c>
+      <c r="H25" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="I23" s="10" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="B24" s="27">
-        <f>(B15)-B22+B4</f>
-        <v>15000</v>
-      </c>
-      <c r="C24" s="27">
-        <f>(C15)-C22+B24</f>
-        <v>0</v>
-      </c>
-      <c r="D24" s="27">
-        <f>(D15)-D22+C24</f>
-        <v>0</v>
-      </c>
-      <c r="E24" s="27">
-        <f t="shared" ref="E24:G24" si="2">(E15)-E22+D24</f>
-        <v>0</v>
-      </c>
-      <c r="F24" s="27">
-        <f>(F15)-F22+E24</f>
-        <v>10000</v>
-      </c>
-      <c r="G24" s="27">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H24" s="10"/>
-      <c r="I24" s="10"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="10"/>
-      <c r="B25" s="36" t="s">
-        <v>2</v>
-      </c>
-      <c r="C25" s="36" t="s">
-        <v>2</v>
-      </c>
-      <c r="D25" s="36" t="s">
-        <v>2</v>
-      </c>
-      <c r="E25" s="36" t="s">
-        <v>2</v>
-      </c>
-      <c r="F25" s="36" t="s">
-        <v>2</v>
-      </c>
-      <c r="G25" s="36" t="s">
-        <v>2</v>
-      </c>
-      <c r="H25" s="10"/>
-      <c r="I25" s="10" t="s">
-        <v>116</v>
-      </c>
+      <c r="I25" s="10"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="B26" s="35">
+        <f>B20*B8</f>
+        <v>9375</v>
+      </c>
+      <c r="C26" s="35">
+        <f>C20*C8</f>
+        <v>0</v>
+      </c>
+      <c r="D26" s="35">
+        <f>D20*D8</f>
+        <v>0</v>
+      </c>
+      <c r="E26" s="35">
+        <f>E20*E8</f>
+        <v>0</v>
+      </c>
+      <c r="F26" s="35">
+        <f>F20*F8</f>
+        <v>6425.0000000000009</v>
+      </c>
+      <c r="G26" s="35">
+        <f>G20*G8</f>
+        <v>0</v>
+      </c>
+      <c r="H26" s="43">
+        <f>SUMPRODUCT(B20:G20,B8:G8)</f>
+        <v>15800</v>
+      </c>
+      <c r="I26" s="10"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="B26" s="37">
-        <v>10000</v>
-      </c>
-      <c r="C26" s="37">
-        <v>10000</v>
-      </c>
-      <c r="D26" s="37">
-        <v>10000</v>
-      </c>
-      <c r="E26" s="37">
-        <v>10000</v>
-      </c>
-      <c r="F26" s="37">
-        <v>10000</v>
-      </c>
-      <c r="G26" s="37">
-        <v>10000</v>
-      </c>
-      <c r="H26" s="10"/>
-      <c r="I26" s="10"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="19"/>
-      <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="10"/>
+      <c r="B27" s="35">
+        <f t="shared" ref="B27:G27" si="2">B13*B7</f>
+        <v>250000</v>
+      </c>
+      <c r="C27" s="35">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D27" s="35">
+        <f t="shared" si="2"/>
+        <v>381000</v>
+      </c>
+      <c r="E27" s="35">
+        <f t="shared" si="2"/>
+        <v>448000</v>
+      </c>
+      <c r="F27" s="35">
+        <f t="shared" si="2"/>
+        <v>449750</v>
+      </c>
+      <c r="G27" s="35">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H27" s="43">
+        <f>SUMPRODUCT(B13:G13,B7:G7)</f>
+        <v>1528750</v>
+      </c>
       <c r="I27" s="10"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="24" t="s">
-        <v>117</v>
-      </c>
-      <c r="B28" s="18"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="10"/>
+      <c r="A28" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="B28" s="35">
+        <v>15000</v>
+      </c>
+      <c r="C28" s="35">
+        <v>15000</v>
+      </c>
+      <c r="D28" s="35">
+        <v>15000</v>
+      </c>
+      <c r="E28" s="35">
+        <v>15000</v>
+      </c>
+      <c r="F28" s="35">
+        <v>15000</v>
+      </c>
+      <c r="G28" s="35">
+        <v>15000</v>
+      </c>
+      <c r="H28" s="43">
+        <f>SUMPRODUCT(B12:G12,B28:G28)</f>
+        <v>60000</v>
+      </c>
       <c r="I28" s="10"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="B29" s="14">
-        <v>1</v>
-      </c>
-      <c r="C29" s="14">
-        <v>2</v>
-      </c>
-      <c r="D29" s="14">
-        <v>3</v>
-      </c>
-      <c r="E29" s="14">
-        <v>4</v>
-      </c>
-      <c r="F29" s="14">
-        <v>5</v>
-      </c>
-      <c r="G29" s="14">
-        <v>6</v>
-      </c>
-      <c r="H29" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="I29" s="10"/>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="B30" s="35">
-        <f t="shared" ref="B30:G30" si="3">B24*B10</f>
-        <v>9375</v>
-      </c>
-      <c r="C30" s="35">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="D30" s="35">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="E30" s="35">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F30" s="35">
-        <f t="shared" si="3"/>
-        <v>6425.0000000000009</v>
-      </c>
-      <c r="G30" s="35">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H30" s="43">
-        <f>SUMPRODUCT(B24:G24,B10:G10)</f>
-        <v>15800</v>
-      </c>
-      <c r="I30" s="10"/>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="B31" s="35">
-        <f t="shared" ref="B31:G31" si="4">B15*B9</f>
-        <v>250000</v>
-      </c>
-      <c r="C31" s="35">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="D31" s="35">
-        <f t="shared" si="4"/>
-        <v>381000</v>
-      </c>
-      <c r="E31" s="35">
-        <f t="shared" si="4"/>
-        <v>448000</v>
-      </c>
-      <c r="F31" s="35">
-        <f t="shared" si="4"/>
-        <v>449750</v>
-      </c>
-      <c r="G31" s="35">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="H31" s="43">
-        <f>SUMPRODUCT(B15:G15,B9:G9)</f>
-        <v>1528750</v>
-      </c>
-      <c r="I31" s="10"/>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="16" t="s">
-        <v>131</v>
-      </c>
-      <c r="B32" s="35">
-        <v>15000</v>
-      </c>
-      <c r="C32" s="35">
-        <v>15000</v>
-      </c>
-      <c r="D32" s="35">
-        <v>15000</v>
-      </c>
-      <c r="E32" s="35">
-        <v>15000</v>
-      </c>
-      <c r="F32" s="35">
-        <v>15000</v>
-      </c>
-      <c r="G32" s="35">
-        <v>15000</v>
-      </c>
-      <c r="H32" s="43">
-        <f>SUMPRODUCT(B14:G14,B32:G32)</f>
-        <v>60000</v>
-      </c>
-      <c r="I32" s="10"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="10"/>
-      <c r="B33" s="10"/>
-      <c r="C33" s="10"/>
-      <c r="D33" s="10"/>
-      <c r="E33" s="10"/>
-      <c r="F33" s="10"/>
-      <c r="G33" s="10"/>
-      <c r="H33" s="44">
-        <f>SUM(H30:H32)</f>
+      <c r="A29" s="10"/>
+      <c r="B29" s="10"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="10"/>
+      <c r="H29" s="44">
+        <f>SUM(H26:H28)</f>
         <v>1604550</v>
       </c>
     </row>
@@ -4803,31 +4782,34 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.28515625" customWidth="1"/>
+    <col min="5" max="6" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="31" t="s">
+        <v>157</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>158</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>159</v>
+      </c>
+      <c r="D1" s="31" t="s">
+        <v>160</v>
+      </c>
+      <c r="E1" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="B1" t="s">
+      <c r="F1" s="31" t="s">
         <v>163</v>
       </c>
-      <c r="C1" t="s">
+      <c r="G1" s="31" t="s">
         <v>164</v>
-      </c>
-      <c r="D1" t="s">
-        <v>165</v>
-      </c>
-      <c r="E1" t="s">
-        <v>167</v>
-      </c>
-      <c r="F1" t="s">
-        <v>168</v>
-      </c>
-      <c r="G1" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -4843,15 +4825,15 @@
       <c r="D2">
         <v>200</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="62">
         <f>($B$6-B2)</f>
         <v>4.3141630158538948</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="62">
         <f>($C$6-C2)</f>
         <v>-4.9712990159689436</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="62">
         <f>SQRT(E2^2 +F2^2)</f>
         <v>6.582234911755684</v>
       </c>
@@ -4869,15 +4851,15 @@
       <c r="D3">
         <v>150</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="62">
         <f t="shared" ref="E3:E5" si="0">($B$6-B3)</f>
         <v>-0.68583698414610517</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="62">
         <f t="shared" ref="F3:F5" si="1">($C$6-C3)</f>
         <v>2.8700984031056365E-2</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="62">
         <f t="shared" ref="G3:G5" si="2">SQRT(E3^2 +F3^2)</f>
         <v>0.68643726246975834</v>
       </c>
@@ -4895,15 +4877,15 @@
       <c r="D4">
         <v>200</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="62">
         <f t="shared" si="0"/>
         <v>9.3141630158538948</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="62">
         <f t="shared" si="1"/>
         <v>-6.9712990159689436</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="62">
         <f t="shared" si="2"/>
         <v>11.634115465128842</v>
       </c>
@@ -4921,36 +4903,36 @@
       <c r="D5">
         <v>300</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="62">
         <f t="shared" si="0"/>
         <v>-2.6858369841461052</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="62">
         <f t="shared" si="1"/>
         <v>5.0287009840310564</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="62">
         <f t="shared" si="2"/>
         <v>5.7010134092283948</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="31" t="s">
-        <v>166</v>
-      </c>
-      <c r="B6" s="1">
+        <v>161</v>
+      </c>
+      <c r="B6" s="63">
         <v>9.3141630158538948</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" s="63">
         <v>5.0287009840310564</v>
       </c>
       <c r="G6" s="32"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>170</v>
-      </c>
-      <c r="B7" s="2">
+        <v>165</v>
+      </c>
+      <c r="B7" s="61">
         <f>SUMPRODUCT(D2:D5,G2:G5)</f>
         <v>5456.5396875158876</v>
       </c>
@@ -4962,294 +4944,282 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{573F87C3-C663-4007-B0D4-35BF49BC4D1B}">
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="31.28515625" customWidth="1"/>
+    <col min="1" max="1" width="31.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.42578125" customWidth="1"/>
+    <col min="6" max="6" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>171</v>
+        <v>99</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="10"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="24" t="s">
+        <v>178</v>
+      </c>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="16" t="s">
+        <v>166</v>
+      </c>
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
       <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="16" t="s">
+      <c r="E2" s="64"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="23" t="s">
+        <v>174</v>
+      </c>
+      <c r="H2" s="23" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="10"/>
+      <c r="B3" s="23" t="s">
+        <v>167</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>168</v>
+      </c>
+      <c r="D3" s="23" t="s">
+        <v>169</v>
+      </c>
+      <c r="E3" s="65"/>
+      <c r="F3" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3" s="54">
+        <f>SUMPRODUCT(C4:D4,B11:C11) +B4</f>
+        <v>0.69211111732132413</v>
+      </c>
+      <c r="H3" s="54">
+        <f>SUMPRODUCT(C5:D5, B11:C11) + B5</f>
+        <v>0.69211110893935746</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="22" t="s">
+        <v>170</v>
+      </c>
+      <c r="B4" s="12">
+        <v>2.2530000000000001</v>
+      </c>
+      <c r="C4" s="12">
+        <v>-1.2999999999999999E-2</v>
+      </c>
+      <c r="D4" s="12">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="E4" s="64"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="H4" s="23" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="B5" s="12">
+        <v>1.1419999999999999</v>
+      </c>
+      <c r="C5" s="12">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="D5" s="12">
+        <v>-1.4999999999999999E-2</v>
+      </c>
+      <c r="E5" s="64"/>
+      <c r="F5" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="G5" s="53">
+        <f>$B$13</f>
+        <v>0.69211111345885656</v>
+      </c>
+      <c r="H5" s="53">
+        <f>$B$13</f>
+        <v>0.69211111345885656</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="10"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="64"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="16" t="s">
         <v>172</v>
       </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="10"/>
-      <c r="B5" s="23" t="s">
-        <v>173</v>
-      </c>
-      <c r="C5" s="23" t="s">
-        <v>174</v>
-      </c>
-      <c r="D5" s="23" t="s">
-        <v>175</v>
-      </c>
-      <c r="E5" s="23"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="22" t="s">
-        <v>176</v>
-      </c>
-      <c r="B6" s="12">
-        <v>2.2530000000000001</v>
-      </c>
-      <c r="C6" s="12">
-        <v>-1.2999999999999999E-2</v>
-      </c>
-      <c r="D6" s="12">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="E6" s="10"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="B7" s="12">
-        <v>1.1419999999999999</v>
-      </c>
-      <c r="C7" s="12">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="D7" s="12">
-        <v>-1.4999999999999999E-2</v>
-      </c>
-      <c r="E7" s="10"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B7" s="46">
+        <v>75</v>
+      </c>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="64"/>
+      <c r="F7" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="G7" s="10"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="10"/>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
       <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="16" t="s">
-        <v>178</v>
-      </c>
-      <c r="B9" s="46">
-        <v>75</v>
-      </c>
+      <c r="E8" s="64"/>
+      <c r="F8" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="G8" s="51">
+        <f>SUMPRODUCT(G3:H3,B11:C11)</f>
+        <v>147.71189170368535</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="24" t="s">
+        <v>173</v>
+      </c>
+      <c r="B9" s="10"/>
       <c r="C9" s="10"/>
       <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="10"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="24" t="s">
-        <v>179</v>
-      </c>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
+      <c r="E9" s="64"/>
+      <c r="F9" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="G9" s="51">
+        <f>$B$7*B13</f>
+        <v>51.908333509414241</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="23"/>
+      <c r="B10" s="23" t="s">
+        <v>174</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>175</v>
+      </c>
+      <c r="D10" s="21"/>
+      <c r="E10" s="65"/>
+      <c r="F10" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="G10" s="52">
+        <f>G8-G9</f>
+        <v>95.803558194271119</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="B11" s="47">
+        <v>137.57222174090037</v>
+      </c>
+      <c r="C11" s="47">
+        <v>75.849999984342958</v>
+      </c>
       <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="23"/>
-      <c r="B12" s="23" t="s">
-        <v>180</v>
-      </c>
-      <c r="C12" s="23" t="s">
-        <v>181</v>
-      </c>
-      <c r="D12" s="21"/>
-      <c r="E12" s="23"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E11" s="64"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="10"/>
+      <c r="B12" s="48"/>
+      <c r="C12" s="48"/>
+      <c r="D12" s="49"/>
+      <c r="E12" s="64"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="B13" s="47">
-        <v>137.57222139459847</v>
-      </c>
-      <c r="C13" s="47">
-        <v>75.849999204652676</v>
-      </c>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+        <v>177</v>
+      </c>
+      <c r="B13" s="50">
+        <v>0.69211111345885656</v>
+      </c>
+      <c r="C13" s="48"/>
+      <c r="D13" s="49"/>
+      <c r="E13" s="64"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="10"/>
-      <c r="B14" s="48"/>
-      <c r="C14" s="48"/>
-      <c r="D14" s="49"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
       <c r="E14" s="10"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="B15" s="50">
-        <v>0.69211111571181716</v>
-      </c>
-      <c r="C15" s="48"/>
-      <c r="D15" s="49"/>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D15" s="10"/>
       <c r="E15" s="10"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="10"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="24" t="s">
-        <v>184</v>
-      </c>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
       <c r="D17" s="10"/>
       <c r="E17" s="10"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="10"/>
-      <c r="B18" s="23" t="s">
-        <v>180</v>
-      </c>
-      <c r="C18" s="23" t="s">
-        <v>181</v>
-      </c>
-      <c r="D18" s="23"/>
-      <c r="E18" s="23"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="B19" s="54">
-        <f>SUMPRODUCT(C6:D6,B13:C13) +B6</f>
-        <v>0.69211111948417825</v>
-      </c>
-      <c r="C19" s="54">
-        <f>SUMPRODUCT(C7:D7, B13:C13) + B7</f>
-        <v>0.6921111189032022</v>
-      </c>
-      <c r="D19" s="10"/>
+      <c r="D19" s="49"/>
       <c r="E19" s="10"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="10"/>
-      <c r="B20" s="23" t="s">
-        <v>2</v>
-      </c>
-      <c r="C20" s="23" t="s">
-        <v>2</v>
-      </c>
+      <c r="B20" s="49"/>
+      <c r="C20" s="10"/>
       <c r="D20" s="10"/>
       <c r="E20" s="10"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="B21" s="53">
-        <f>$B$15</f>
-        <v>0.69211111571181716</v>
-      </c>
-      <c r="C21" s="53">
-        <f>$B$15</f>
-        <v>0.69211111571181716</v>
-      </c>
-      <c r="D21" s="49"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
       <c r="E21" s="10"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="10"/>
-      <c r="B22" s="49"/>
-      <c r="C22" s="10"/>
+      <c r="C22" s="51"/>
       <c r="D22" s="10"/>
       <c r="E22" s="10"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="19" t="s">
-        <v>185</v>
-      </c>
-      <c r="B23" s="10"/>
       <c r="C23" s="10"/>
       <c r="D23" s="10"/>
       <c r="E23" s="10"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="B24" s="51">
-        <f>SUMPRODUCT(B19:C19,B13:C13)</f>
-        <v>147.71189197767993</v>
-      </c>
-      <c r="C24" s="51"/>
+      <c r="C24" s="10"/>
       <c r="D24" s="10"/>
       <c r="E24" s="10"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="B25" s="51">
-        <f>$B$9*B15</f>
-        <v>51.908333678386285</v>
-      </c>
+      <c r="A25" s="10"/>
+      <c r="B25" s="10"/>
       <c r="C25" s="10"/>
       <c r="D25" s="10"/>
       <c r="E25" s="10"/>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="B26" s="52">
-        <f>B24-B25</f>
-        <v>95.803558299293641</v>
-      </c>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="10"/>
-      <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5258,211 +5228,217 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6829978-8C83-46EC-9B0D-95A12529CCF4}">
-  <dimension ref="A2:J8"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="2.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="31" t="s">
+        <v>157</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>158</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>159</v>
+      </c>
+      <c r="D1" s="31" t="s">
+        <v>160</v>
+      </c>
+      <c r="E1" s="31" t="s">
+        <v>162</v>
+      </c>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31" t="s">
+        <v>163</v>
+      </c>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31" t="s">
+        <v>183</v>
+      </c>
+      <c r="J1" s="31" t="s">
+        <v>184</v>
+      </c>
+    </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
-        <v>162</v>
-      </c>
-      <c r="B2" s="31" t="s">
-        <v>163</v>
-      </c>
-      <c r="C2" s="31" t="s">
-        <v>164</v>
-      </c>
-      <c r="D2" s="31" t="s">
-        <v>165</v>
-      </c>
-      <c r="E2" s="31" t="s">
-        <v>167</v>
-      </c>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31" t="s">
-        <v>168</v>
-      </c>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31" t="s">
-        <v>189</v>
-      </c>
-      <c r="J2" s="31" t="s">
-        <v>190</v>
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>10</v>
+      </c>
+      <c r="D2">
+        <v>200</v>
+      </c>
+      <c r="E2">
+        <f>$B$6-B2</f>
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <f>E2 * -1</f>
+        <v>-5</v>
+      </c>
+      <c r="G2">
+        <f>$C$6-C2</f>
+        <v>-5</v>
+      </c>
+      <c r="H2">
+        <f>G2 * -1</f>
+        <v>5</v>
+      </c>
+      <c r="I2" s="6">
+        <v>5</v>
+      </c>
+      <c r="J2" s="6">
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3">
+        <v>10</v>
+      </c>
+      <c r="C3">
         <v>5</v>
       </c>
-      <c r="C3">
-        <v>10</v>
-      </c>
       <c r="D3">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="E3">
-        <f>$B$7-B3</f>
-        <v>5</v>
+        <f t="shared" ref="E3:E5" si="0">$B$6-B3</f>
+        <v>0</v>
       </c>
       <c r="F3">
-        <f>E3 * -1</f>
-        <v>-5</v>
+        <f t="shared" ref="F3:F5" si="1">E3 * -1</f>
+        <v>0</v>
       </c>
       <c r="G3">
-        <f>$C$7-C3</f>
-        <v>-5</v>
+        <f t="shared" ref="G3:G5" si="2">$C$6-C3</f>
+        <v>0</v>
       </c>
       <c r="H3">
-        <f>G3 * -1</f>
-        <v>5</v>
+        <f t="shared" ref="H3:H5" si="3">G3 * -1</f>
+        <v>0</v>
       </c>
       <c r="I3" s="6">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J3" s="6">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>12</v>
+      </c>
+      <c r="D4">
+        <v>200</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C4">
-        <v>5</v>
-      </c>
-      <c r="D4">
-        <v>150</v>
-      </c>
-      <c r="E4">
-        <f t="shared" ref="E4:E7" si="0">$B$7-B4</f>
-        <v>0</v>
-      </c>
       <c r="F4">
-        <f t="shared" ref="F4:F6" si="1">E4 * -1</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>-10</v>
       </c>
       <c r="G4">
-        <f t="shared" ref="G4:G6" si="2">$C$7-C4</f>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>-7</v>
       </c>
       <c r="H4">
-        <f t="shared" ref="H4:H6" si="3">G4 * -1</f>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>7</v>
       </c>
       <c r="I4" s="6">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J4" s="6">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C5">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E5">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>-2</v>
       </c>
       <c r="F5">
         <f t="shared" si="1"/>
-        <v>-10</v>
+        <v>2</v>
       </c>
       <c r="G5">
         <f t="shared" si="2"/>
-        <v>-7</v>
+        <v>5</v>
       </c>
       <c r="H5">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>-5</v>
       </c>
       <c r="I5" s="6">
+        <v>2</v>
+      </c>
+      <c r="J5" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="31" t="s">
+        <v>161</v>
+      </c>
+      <c r="B6" s="1">
         <v>10</v>
       </c>
-      <c r="J5" s="6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>4</v>
-      </c>
-      <c r="B6">
-        <v>12</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>300</v>
-      </c>
-      <c r="E6">
-        <f t="shared" si="0"/>
-        <v>-2</v>
-      </c>
-      <c r="F6">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="G6">
-        <f t="shared" si="2"/>
+      <c r="C6" s="1">
         <v>5</v>
       </c>
-      <c r="H6">
-        <f t="shared" si="3"/>
-        <v>-5</v>
-      </c>
-      <c r="I6" s="6">
-        <v>2</v>
-      </c>
-      <c r="J6" s="6">
-        <v>5</v>
+      <c r="I6">
+        <f>SUMPRODUCT(D2:D5,I2:I5)</f>
+        <v>3600</v>
+      </c>
+      <c r="J6">
+        <f>SUMPRODUCT(D2:D5,J2:J5)</f>
+        <v>3900</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="31" t="s">
-        <v>166</v>
-      </c>
-      <c r="B7" s="1">
-        <v>10</v>
-      </c>
-      <c r="C7" s="1">
-        <v>5</v>
-      </c>
-      <c r="I7">
-        <f>SUMPRODUCT(D3:D6,I3:I6)</f>
-        <v>3600</v>
-      </c>
-      <c r="J7">
-        <f>SUMPRODUCT(D3:D6,J3:J6)</f>
-        <v>3900</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>170</v>
-      </c>
-      <c r="B8" s="2">
-        <f>SUM(I7:J7)</f>
+      <c r="A7" t="s">
+        <v>165</v>
+      </c>
+      <c r="B7" s="2">
+        <f>SUM(I6:J6)</f>
         <v>7500</v>
       </c>
     </row>
@@ -6368,19 +6344,20 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{252464CB-7E70-452A-88CC-BE24E3E0118E}">
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.42578125" customWidth="1"/>
+    <col min="2" max="2" width="7" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8.42578125" customWidth="1"/>
     <col min="8" max="8" width="3" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>62</v>
       </c>
@@ -6394,7 +6371,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>64</v>
       </c>
@@ -6410,18 +6387,8 @@
       <c r="E2">
         <v>0</v>
       </c>
-      <c r="G2">
-        <f>SUM(B2:D2)</f>
-        <v>500</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="I2" s="3">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>30</v>
       </c>
@@ -6437,18 +6404,8 @@
       <c r="E3" s="1">
         <v>0</v>
       </c>
-      <c r="G3">
-        <f>-(B2 * B6) - B4 + B3</f>
-        <v>-200</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="I3" s="3">
-        <v>-200</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>65</v>
       </c>
@@ -6464,31 +6421,8 @@
       <c r="E4">
         <v>0</v>
       </c>
-      <c r="G4">
-        <f>-(C2*C6) - C4 + C3</f>
-        <v>-240</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="I4" s="3">
-        <v>-240</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G5">
-        <f>D3 + E3</f>
-        <v>6000</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="I5" s="3">
-        <f>D2*D6</f>
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>66</v>
       </c>
@@ -6501,18 +6435,8 @@
       <c r="D6">
         <v>20</v>
       </c>
-      <c r="G6">
-        <f>$D$3</f>
-        <v>6000</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="I6" s="3">
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>67</v>
       </c>
@@ -6526,7 +6450,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>68</v>
       </c>
@@ -6543,7 +6467,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>69</v>
       </c>
@@ -6554,7 +6478,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -6562,8 +6486,18 @@
         <f>SUMPRODUCT(B3:E3,B8:E8)</f>
         <v>233000</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D11" s="4">
+        <f>SUM(B2:D2)</f>
+        <v>500</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="F11" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>65</v>
       </c>
@@ -6571,8 +6505,18 @@
         <f>SUMPRODUCT(B4:C4,B9:C9)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D12" s="4">
+        <f>-(B2 * B6) - B4 + B3</f>
+        <v>-200</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="F12" s="3">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>70</v>
       </c>
@@ -6580,14 +6524,47 @@
         <f>SUMPRODUCT(B7:D7,B2:D2)</f>
         <v>114400</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D13" s="4">
+        <f>-(C2*C6) - C4 + C3</f>
+        <v>-240</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="F13" s="3">
+        <v>-240</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>39</v>
       </c>
       <c r="B14" s="2">
         <f>B11 - B12 - B13</f>
         <v>118600</v>
+      </c>
+      <c r="D14" s="4">
+        <f>D3 + E3</f>
+        <v>6000</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="F14" s="3">
+        <f>D2*D6</f>
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D15" s="4">
+        <f>$D$3</f>
+        <v>6000</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="F15" s="3">
+        <v>6000</v>
       </c>
     </row>
   </sheetData>
@@ -6598,14 +6575,14 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{663BCE4E-1681-441F-8DE6-2742A5A66B94}">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="8" width="8.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>73</v>
       </c>
@@ -6628,7 +6605,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>82</v>
       </c>
@@ -6653,21 +6630,9 @@
       <c r="H2" s="1">
         <v>0</v>
       </c>
-      <c r="K2" s="7"/>
-    </row>
-    <row r="3" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J3" s="4">
-        <f>SUMPRODUCT(B2:H2, B4:H4)</f>
-        <v>15.000000000000002</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="L3" s="3">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>70</v>
       </c>
@@ -6693,7 +6658,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>80</v>
       </c>
@@ -6719,46 +6684,58 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>81</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="56">
         <f>(B5-B4)/B4</f>
         <v>0.11999999999999993</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="56">
         <f t="shared" ref="C6:H6" si="0">(C5-C4)/C4</f>
         <v>0.12500000000000011</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="56">
         <f t="shared" si="0"/>
         <v>0.11428571428571425</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="56">
         <f t="shared" si="0"/>
         <v>0.15254237288135583</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="56">
         <f t="shared" si="0"/>
         <v>0.11594202898550722</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="56">
         <f t="shared" si="0"/>
         <v>0.13333333333333325</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="56">
         <f t="shared" si="0"/>
         <v>9.9999999999999936E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>39</v>
       </c>
       <c r="B8" s="2">
         <f>SUMPRODUCT(B2:H2,B5:H5)</f>
         <v>17.064</v>
+      </c>
+      <c r="D8" s="32"/>
+      <c r="E8" s="55"/>
+      <c r="F8" s="4">
+        <f xml:space="preserve"> SUMPRODUCT(B4:H4,B2:H2)</f>
+        <v>15.000000000000002</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="H8" s="3">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -6769,53 +6746,114 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9416A4A6-16E8-44A6-ABD2-65E95D8954DD}">
-  <dimension ref="A2:M28"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.42578125" customWidth="1"/>
+    <col min="8" max="8" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.5703125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="31" t="s">
         <v>83</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B1" s="31" t="s">
         <v>84</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C1" s="31" t="s">
         <v>85</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D1" s="31" t="s">
         <v>86</v>
       </c>
-      <c r="F2" t="s">
+      <c r="E1" s="31"/>
+      <c r="F1" s="31" t="s">
         <v>87</v>
       </c>
-      <c r="H2" t="s">
+      <c r="G1" s="57"/>
+      <c r="H1" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I1" s="31" t="s">
         <v>89</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J1" s="31" t="s">
         <v>90</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K1" s="31" t="s">
         <v>40</v>
       </c>
-      <c r="M2" t="s">
+      <c r="L1" s="31"/>
+      <c r="M1" s="31" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N1" s="31"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="3">
+        <v>200</v>
+      </c>
+      <c r="G2" s="58"/>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <f>SUMIF($A$2:$A$27,H2,$D$2:$D$27)</f>
+        <v>180</v>
+      </c>
+      <c r="J2">
+        <f>SUMIF($B$2:$B$27,H2,$D$2:$D$27)</f>
+        <v>0</v>
+      </c>
+      <c r="K2" s="4">
+        <f>I2-J2</f>
+        <v>180</v>
+      </c>
+      <c r="L2" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="M2" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D3" s="1">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>2</v>
@@ -6823,40 +6861,41 @@
       <c r="F3" s="3">
         <v>200</v>
       </c>
+      <c r="G3" s="58"/>
       <c r="H3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <f>SUMIF($A$3:$A$28,H3,$D$3:$D$28)</f>
-        <v>180</v>
+        <f>SUMIF($A$2:$A$27,H3,$D$2:$D$27)</f>
+        <v>300</v>
       </c>
       <c r="J3">
-        <f>SUMIF($B$3:$B$28,H3,$D$3:$D$28)</f>
+        <f>SUMIF($B$2:$B$27,H3,$D$2:$D$27)</f>
         <v>0</v>
       </c>
       <c r="K3" s="4">
-        <f>I3-J3</f>
-        <v>180</v>
+        <f t="shared" ref="K3:K8" si="0">I3-J3</f>
+        <v>300</v>
       </c>
       <c r="L3" s="7" t="s">
         <v>2</v>
       </c>
       <c r="M3" s="3">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D4" s="1">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>2</v>
@@ -6864,34 +6903,35 @@
       <c r="F4" s="3">
         <v>200</v>
       </c>
+      <c r="G4" s="58"/>
       <c r="H4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4">
-        <f>SUMIF($A$3:$A$28,H4,$D$3:$D$28)</f>
-        <v>300</v>
+        <f t="shared" ref="I4:I8" si="1">SUMIF($A$2:$A$27,H4,$D$2:$D$27)</f>
+        <v>280</v>
       </c>
       <c r="J4">
-        <f>SUMIF($B$3:$B$28,H4,$D$3:$D$28)</f>
-        <v>0</v>
+        <f t="shared" ref="J4:J8" si="2">SUMIF($B$2:$B$27,H4,$D$2:$D$27)</f>
+        <v>180</v>
       </c>
       <c r="K4" s="4">
-        <f t="shared" ref="K4:K9" si="0">I4-J4</f>
-        <v>300</v>
+        <f t="shared" si="0"/>
+        <v>100</v>
       </c>
       <c r="L4" s="7" t="s">
         <v>2</v>
       </c>
       <c r="M4" s="3">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5">
         <v>5</v>
@@ -6905,37 +6945,38 @@
       <c r="F5" s="3">
         <v>200</v>
       </c>
+      <c r="G5" s="58"/>
       <c r="H5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I5">
-        <f t="shared" ref="I5:I9" si="1">SUMIF($A$3:$A$28,H5,$D$3:$D$28)</f>
-        <v>280</v>
+        <f t="shared" si="1"/>
+        <v>200</v>
       </c>
       <c r="J5">
-        <f t="shared" ref="J5:J9" si="2">SUMIF($B$3:$B$28,H5,$D$3:$D$28)</f>
-        <v>180</v>
+        <f t="shared" si="2"/>
+        <v>200</v>
       </c>
       <c r="K5" s="4">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>2</v>
+        <v>92</v>
       </c>
       <c r="M5" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D6" s="1">
         <v>0</v>
@@ -6946,8 +6987,9 @@
       <c r="F6" s="3">
         <v>200</v>
       </c>
+      <c r="G6" s="58"/>
       <c r="H6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I6">
         <f t="shared" si="1"/>
@@ -6968,12 +7010,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>1</v>
       </c>
       <c r="B7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C7">
         <v>20</v>
@@ -6987,37 +7029,38 @@
       <c r="F7" s="3">
         <v>200</v>
       </c>
+      <c r="G7" s="58"/>
       <c r="H7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I7">
         <f t="shared" si="1"/>
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="J7">
         <f t="shared" si="2"/>
-        <v>200</v>
+        <v>580</v>
       </c>
       <c r="K7" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>92</v>
+        <v>2</v>
       </c>
       <c r="M7" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C8">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
@@ -7028,34 +7071,35 @@
       <c r="F8" s="3">
         <v>200</v>
       </c>
+      <c r="G8" s="58"/>
       <c r="H8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I8">
         <f t="shared" si="1"/>
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="J8">
         <f t="shared" si="2"/>
-        <v>580</v>
+        <v>180</v>
       </c>
       <c r="K8" s="4">
         <f t="shared" si="0"/>
-        <v>-400</v>
+        <v>-180</v>
       </c>
       <c r="L8" s="7" t="s">
         <v>2</v>
       </c>
       <c r="M8" s="3">
-        <v>-400</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+        <v>-180</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C9">
         <v>9</v>
@@ -7069,40 +7113,20 @@
       <c r="F9" s="3">
         <v>200</v>
       </c>
-      <c r="H9">
-        <v>7</v>
-      </c>
-      <c r="I9">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <f t="shared" si="2"/>
-        <v>180</v>
-      </c>
-      <c r="K9" s="4">
-        <f t="shared" si="0"/>
-        <v>-180</v>
-      </c>
-      <c r="L9" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="M9" s="3">
-        <v>-180</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="G9" s="58"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2</v>
       </c>
       <c r="B10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D10" s="1">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>2</v>
@@ -7110,19 +7134,27 @@
       <c r="F10" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="G10" s="58"/>
+      <c r="H10" t="s">
+        <v>70</v>
+      </c>
+      <c r="I10" s="2">
+        <f>SUMPRODUCT(C2:C27,D2:D27)</f>
+        <v>3260</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2</v>
       </c>
       <c r="B11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="D11" s="1">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>2</v>
@@ -7130,26 +7162,20 @@
       <c r="F11" s="3">
         <v>200</v>
       </c>
-      <c r="H11" t="s">
-        <v>70</v>
-      </c>
-      <c r="I11" s="2">
-        <f>SUMPRODUCT(C3:C28,D3:D28)</f>
-        <v>3260</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="G11" s="58"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2</v>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D12" s="1">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>2</v>
@@ -7157,19 +7183,20 @@
       <c r="F12" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="G12" s="58"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2</v>
       </c>
       <c r="B13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C13">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D13" s="1">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>2</v>
@@ -7177,16 +7204,17 @@
       <c r="F13" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="G13" s="58"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B14">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C14">
-        <v>15</v>
+        <v>0.4</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
@@ -7197,16 +7225,17 @@
       <c r="F14" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="G14" s="58"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>3</v>
       </c>
       <c r="B15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15">
-        <v>0.4</v>
+        <v>8</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -7217,19 +7246,20 @@
       <c r="F15" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="G15" s="58"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>3</v>
       </c>
       <c r="B16">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C16">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D16" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>2</v>
@@ -7237,19 +7267,20 @@
       <c r="F16" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" s="58"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>3</v>
       </c>
       <c r="B17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D17" s="1">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>2</v>
@@ -7257,19 +7288,20 @@
       <c r="F17" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" s="58"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>3</v>
       </c>
       <c r="B18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C18">
-        <v>0.5</v>
+        <v>10</v>
       </c>
       <c r="D18" s="1">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>2</v>
@@ -7277,16 +7309,17 @@
       <c r="F18" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" s="58"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>3</v>
       </c>
       <c r="B19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C19">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D19" s="1">
         <v>0</v>
@@ -7297,16 +7330,17 @@
       <c r="F19" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" s="58"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B20">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C20">
-        <v>12</v>
+        <v>1.2</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
@@ -7317,19 +7351,20 @@
       <c r="F20" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20" s="58"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>4</v>
       </c>
       <c r="B21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C21">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="D21" s="1">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>2</v>
@@ -7337,19 +7372,20 @@
       <c r="F21" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G21" s="58"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>4</v>
       </c>
       <c r="B22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C22">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D22" s="1">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>2</v>
@@ -7357,16 +7393,17 @@
       <c r="F22" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G22" s="58"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23">
+        <v>5</v>
+      </c>
+      <c r="B23">
         <v>4</v>
       </c>
-      <c r="B23">
-        <v>7</v>
-      </c>
       <c r="C23">
-        <v>12</v>
+        <v>0.8</v>
       </c>
       <c r="D23" s="1">
         <v>0</v>
@@ -7377,19 +7414,20 @@
       <c r="F23" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G23" s="58"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>5</v>
       </c>
       <c r="B24">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C24">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="D24" s="1">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>2</v>
@@ -7397,19 +7435,20 @@
       <c r="F24" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G24" s="58"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>5</v>
       </c>
       <c r="B25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C25">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D25" s="1">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E25" s="7" t="s">
         <v>2</v>
@@ -7417,19 +7456,20 @@
       <c r="F25" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G25" s="58"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B26">
         <v>7</v>
       </c>
       <c r="C26">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D26" s="1">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="E26" s="7" t="s">
         <v>2</v>
@@ -7437,19 +7477,20 @@
       <c r="F26" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G26" s="58"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27">
+        <v>7</v>
+      </c>
+      <c r="B27">
         <v>6</v>
       </c>
-      <c r="B27">
+      <c r="C27">
         <v>7</v>
       </c>
-      <c r="C27">
-        <v>1</v>
-      </c>
       <c r="D27" s="1">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>2</v>
@@ -7457,26 +7498,7 @@
       <c r="F27" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>7</v>
-      </c>
-      <c r="B28">
-        <v>6</v>
-      </c>
-      <c r="C28">
-        <v>7</v>
-      </c>
-      <c r="D28" s="1">
-        <v>0</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="F28" s="3">
-        <v>200</v>
-      </c>
+      <c r="G27" s="58"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7764,13 +7786,12 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E76634E4-7D20-4A0E-A622-BD83CBE54980}">
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.5703125" style="10" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" style="10" customWidth="1"/>
-    <col min="3" max="7" width="9" style="10"/>
-    <col min="8" max="8" width="12.85546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.140625" style="10" customWidth="1"/>
+    <col min="2" max="7" width="7.28515625" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" style="10" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19" style="10" bestFit="1" customWidth="1"/>
     <col min="10" max="243" width="9" style="10"/>
     <col min="244" max="244" width="26.5703125" style="10" customWidth="1"/>
@@ -8279,435 +8300,419 @@
     <col min="16127" max="16384" width="9" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
+      <c r="E1" s="11"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="E3" s="11"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
+      <c r="B2" s="12">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="B4" s="12">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B3" s="13">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="B5" s="13">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
+      <c r="B5" s="14">
+        <v>1</v>
+      </c>
+      <c r="C5" s="14">
+        <v>2</v>
+      </c>
+      <c r="D5" s="14">
+        <v>3</v>
+      </c>
+      <c r="E5" s="14">
+        <v>4</v>
+      </c>
+      <c r="F5" s="14">
+        <v>5</v>
+      </c>
+      <c r="G5" s="14">
+        <v>6</v>
+      </c>
+      <c r="H5" s="15"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="B7" s="14">
-        <v>1</v>
-      </c>
-      <c r="C7" s="14">
-        <v>2</v>
-      </c>
-      <c r="D7" s="14">
-        <v>3</v>
-      </c>
-      <c r="E7" s="14">
-        <v>4</v>
-      </c>
-      <c r="F7" s="14">
-        <v>5</v>
-      </c>
-      <c r="G7" s="14">
-        <v>6</v>
-      </c>
-      <c r="H7" s="15"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="16" t="s">
+      <c r="B6" s="17">
+        <v>12.5</v>
+      </c>
+      <c r="C6" s="17">
+        <v>12.55</v>
+      </c>
+      <c r="D6" s="17">
+        <v>12.7</v>
+      </c>
+      <c r="E6" s="17">
+        <v>12.8</v>
+      </c>
+      <c r="F6" s="17">
+        <v>12.85</v>
+      </c>
+      <c r="G6" s="17">
+        <v>12.95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="B8" s="17">
-        <v>12.5</v>
-      </c>
-      <c r="C8" s="17">
-        <v>12.55</v>
-      </c>
-      <c r="D8" s="17">
-        <v>12.7</v>
-      </c>
-      <c r="E8" s="17">
-        <v>12.8</v>
-      </c>
-      <c r="F8" s="17">
-        <v>12.85</v>
-      </c>
-      <c r="G8" s="17">
-        <v>12.95</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="B9" s="18">
-        <f>B8* $B$5</f>
+      <c r="B7" s="18">
+        <f>B6* $B$3</f>
         <v>0.625</v>
       </c>
-      <c r="C9" s="18">
-        <f t="shared" ref="C9:G9" si="0">C8* $B$5</f>
+      <c r="C7" s="18">
+        <f t="shared" ref="C7:G7" si="0">C6* $B$3</f>
         <v>0.62750000000000006</v>
       </c>
-      <c r="D9" s="18">
+      <c r="D7" s="18">
         <f t="shared" si="0"/>
         <v>0.63500000000000001</v>
       </c>
-      <c r="E9" s="18">
+      <c r="E7" s="18">
         <f t="shared" si="0"/>
         <v>0.64000000000000012</v>
       </c>
-      <c r="F9" s="18">
+      <c r="F7" s="18">
         <f t="shared" si="0"/>
         <v>0.64250000000000007</v>
       </c>
-      <c r="G9" s="18">
+      <c r="G7" s="18">
         <f t="shared" si="0"/>
         <v>0.64749999999999996</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="19" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="B9" s="14">
+        <v>1</v>
+      </c>
+      <c r="C9" s="14">
+        <v>2</v>
+      </c>
+      <c r="D9" s="14">
+        <v>3</v>
+      </c>
+      <c r="E9" s="14">
+        <v>4</v>
+      </c>
+      <c r="F9" s="14">
+        <v>5</v>
+      </c>
+      <c r="G9" s="14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="B11" s="14">
-        <v>1</v>
-      </c>
-      <c r="C11" s="14">
-        <v>2</v>
-      </c>
-      <c r="D11" s="14">
-        <v>3</v>
-      </c>
-      <c r="E11" s="14">
-        <v>4</v>
-      </c>
-      <c r="F11" s="14">
-        <v>5</v>
-      </c>
-      <c r="G11" s="14">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B10" s="20">
+        <v>5000</v>
+      </c>
+      <c r="C10" s="20">
+        <v>20000</v>
+      </c>
+      <c r="D10" s="20">
+        <v>30000</v>
+      </c>
+      <c r="E10" s="20">
+        <v>30000</v>
+      </c>
+      <c r="F10" s="20">
+        <v>25000</v>
+      </c>
+      <c r="G10" s="20">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B11" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="F11" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="G11" s="21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="B12" s="20">
+      <c r="B12" s="12">
+        <v>30000</v>
+      </c>
+      <c r="C12" s="12">
+        <v>30000</v>
+      </c>
+      <c r="D12" s="12">
+        <v>30000</v>
+      </c>
+      <c r="E12" s="12">
+        <v>30000</v>
+      </c>
+      <c r="F12" s="12">
+        <v>30000</v>
+      </c>
+      <c r="G12" s="12">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="22" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B15" s="23"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="B16" s="12">
+        <v>10000</v>
+      </c>
+      <c r="C16" s="12">
+        <v>15000</v>
+      </c>
+      <c r="D16" s="12">
+        <v>30000</v>
+      </c>
+      <c r="E16" s="12">
+        <v>35000</v>
+      </c>
+      <c r="F16" s="12">
+        <v>25000</v>
+      </c>
+      <c r="G16" s="12">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="21"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21"/>
+      <c r="G17" s="21"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="B18" s="27">
+        <f>B10-B16+B2</f>
+        <v>0</v>
+      </c>
+      <c r="C18" s="27">
+        <f>C10-C16+B18</f>
         <v>5000</v>
       </c>
-      <c r="C12" s="20">
-        <v>20000</v>
-      </c>
-      <c r="D12" s="20">
-        <v>30000</v>
-      </c>
-      <c r="E12" s="20">
-        <v>30000</v>
-      </c>
-      <c r="F12" s="20">
-        <v>25000</v>
-      </c>
-      <c r="G12" s="20">
+      <c r="D18" s="27">
+        <f t="shared" ref="D18:G18" si="1">D10-D16+C18</f>
+        <v>5000</v>
+      </c>
+      <c r="E18" s="27">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F18" s="27">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G18" s="27">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H18" s="23"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="C19" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="D19" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="E19" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="F19" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="G19" s="23" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="B20" s="12">
         <v>10000</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B13" s="21" t="s">
-        <v>2</v>
-      </c>
-      <c r="C13" s="21" t="s">
-        <v>2</v>
-      </c>
-      <c r="D13" s="21" t="s">
-        <v>2</v>
-      </c>
-      <c r="E13" s="21" t="s">
-        <v>2</v>
-      </c>
-      <c r="F13" s="21" t="s">
-        <v>2</v>
-      </c>
-      <c r="G13" s="21" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="B14" s="12">
-        <v>30000</v>
-      </c>
-      <c r="C14" s="12">
-        <v>30000</v>
-      </c>
-      <c r="D14" s="12">
-        <v>30000</v>
-      </c>
-      <c r="E14" s="12">
-        <v>30000</v>
-      </c>
-      <c r="F14" s="12">
-        <v>30000</v>
-      </c>
-      <c r="G14" s="12">
-        <v>30000</v>
-      </c>
-      <c r="I14" s="10" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="22" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B17" s="23"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="23"/>
-      <c r="G17" s="23"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="B18" s="12">
+      <c r="C20" s="12">
         <v>10000</v>
       </c>
-      <c r="C18" s="12">
-        <v>15000</v>
-      </c>
-      <c r="D18" s="12">
-        <v>30000</v>
-      </c>
-      <c r="E18" s="12">
-        <v>35000</v>
-      </c>
-      <c r="F18" s="12">
-        <v>25000</v>
-      </c>
-      <c r="G18" s="12">
+      <c r="D20" s="12">
         <v>10000</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B19" s="21"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="10" t="s">
+      <c r="E20" s="12">
+        <v>10000</v>
+      </c>
+      <c r="F20" s="12">
+        <v>10000</v>
+      </c>
+      <c r="G20" s="12">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="19"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="24" t="s">
         <v>112</v>
       </c>
-      <c r="B20" s="27">
-        <f>B12-B18+B4</f>
-        <v>0</v>
-      </c>
-      <c r="C20" s="27">
-        <f>C12-C18+B20</f>
-        <v>5000</v>
-      </c>
-      <c r="D20" s="27">
-        <f t="shared" ref="D20:G20" si="1">D12-D18+C20</f>
-        <v>5000</v>
-      </c>
-      <c r="E20" s="27">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F20" s="27">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G20" s="27">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H20" s="23" t="s">
+      <c r="B22" s="18"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="B23" s="14">
+        <v>1</v>
+      </c>
+      <c r="C23" s="14">
+        <v>2</v>
+      </c>
+      <c r="D23" s="14">
+        <v>3</v>
+      </c>
+      <c r="E23" s="14">
+        <v>4</v>
+      </c>
+      <c r="F23" s="14">
+        <v>5</v>
+      </c>
+      <c r="G23" s="14">
+        <v>6</v>
+      </c>
+      <c r="H23" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="I20" s="10" t="s">
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="10" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B21" s="23" t="s">
-        <v>2</v>
-      </c>
-      <c r="C21" s="23" t="s">
-        <v>2</v>
-      </c>
-      <c r="D21" s="23" t="s">
-        <v>2</v>
-      </c>
-      <c r="E21" s="23" t="s">
-        <v>2</v>
-      </c>
-      <c r="F21" s="23" t="s">
-        <v>2</v>
-      </c>
-      <c r="G21" s="23" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="B22" s="12">
-        <v>10000</v>
-      </c>
-      <c r="C22" s="12">
-        <v>10000</v>
-      </c>
-      <c r="D22" s="12">
-        <v>10000</v>
-      </c>
-      <c r="E22" s="12">
-        <v>10000</v>
-      </c>
-      <c r="F22" s="12">
-        <v>10000</v>
-      </c>
-      <c r="G22" s="12">
-        <v>10000</v>
-      </c>
-      <c r="I22" s="10" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="19"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="24" t="s">
-        <v>117</v>
-      </c>
-      <c r="B24" s="18"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="B25" s="14">
-        <v>1</v>
-      </c>
-      <c r="C25" s="14">
-        <v>2</v>
-      </c>
-      <c r="D25" s="14">
-        <v>3</v>
-      </c>
-      <c r="E25" s="14">
-        <v>4</v>
-      </c>
-      <c r="F25" s="14">
-        <v>5</v>
-      </c>
-      <c r="G25" s="14">
-        <v>6</v>
-      </c>
-      <c r="H25" s="23" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="B26" s="10">
-        <f>B20*B9</f>
-        <v>0</v>
-      </c>
-      <c r="C26" s="10">
-        <f t="shared" ref="C26:G26" si="2">C20*C9</f>
+      <c r="B24" s="10">
+        <f>B18*B7</f>
+        <v>0</v>
+      </c>
+      <c r="C24" s="10">
+        <f t="shared" ref="C24:G24" si="2">C18*C7</f>
         <v>3137.5000000000005</v>
       </c>
-      <c r="D26" s="10">
+      <c r="D24" s="10">
         <f t="shared" si="2"/>
         <v>3175</v>
       </c>
-      <c r="E26" s="10">
+      <c r="E24" s="10">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F26" s="10">
+      <c r="F24" s="10">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G26" s="10">
+      <c r="G24" s="10">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H26" s="25">
-        <f>SUM(B26:G26)</f>
+      <c r="H24" s="25">
+        <f>SUM(B24:G24)</f>
         <v>6312.5</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="B27" s="10">
-        <f>B12*B8</f>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="B25" s="10">
+        <f>B10*B6</f>
         <v>62500</v>
       </c>
-      <c r="C27" s="10">
-        <f t="shared" ref="C27:G27" si="3">C12*C8</f>
+      <c r="C25" s="10">
+        <f t="shared" ref="C25:G25" si="3">C10*C6</f>
         <v>251000</v>
       </c>
-      <c r="D27" s="10">
+      <c r="D25" s="10">
         <f t="shared" si="3"/>
         <v>381000</v>
       </c>
-      <c r="E27" s="10">
+      <c r="E25" s="10">
         <f t="shared" si="3"/>
         <v>384000</v>
       </c>
-      <c r="F27" s="10">
+      <c r="F25" s="10">
         <f t="shared" si="3"/>
         <v>321250</v>
       </c>
-      <c r="G27" s="10">
+      <c r="G25" s="10">
         <f t="shared" si="3"/>
         <v>129500</v>
       </c>
-      <c r="H27" s="25">
-        <f>SUM(B27:G27)</f>
+      <c r="H25" s="25">
+        <f>SUM(B25:G25)</f>
         <v>1529250</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="H28" s="26">
-        <f>SUM(H26:H27)</f>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H26" s="26">
+        <f>SUM(H24:H25)</f>
         <v>1535562.5</v>
       </c>
     </row>

--- a/class_excel/temp_midterm.xlsx
+++ b/class_excel/temp_midterm.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\T00229\Documents\GitHub\DADS7102\class_excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\DADS7102\class_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9176C054-1FD0-40C7-9D1F-62706308322C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{081F2990-7339-467B-BF6E-BDA906954E1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="18" xr2:uid="{962D6ACA-47B2-4C7E-82D5-0F5476EE75BF}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="9" activeTab="18" xr2:uid="{962D6ACA-47B2-4C7E-82D5-0F5476EE75BF}"/>
   </bookViews>
   <sheets>
     <sheet name="ch_1_1" sheetId="1" r:id="rId1"/>
@@ -366,7 +366,7 @@
     <definedName name="solver_opt" localSheetId="7" hidden="1">ch_3_2!$B$11</definedName>
     <definedName name="solver_opt" localSheetId="8" hidden="1">ch_3_3!$H$26</definedName>
     <definedName name="solver_opt" localSheetId="9" hidden="1">ch_3_4!$E$13</definedName>
-    <definedName name="solver_opt" localSheetId="10" hidden="1">ch4_1!$I$7</definedName>
+    <definedName name="solver_opt" localSheetId="10" hidden="1">ch4_1!$A$13</definedName>
     <definedName name="solver_opt" localSheetId="11" hidden="1">'ch4_1 (2)'!$B$22</definedName>
     <definedName name="solver_opt" localSheetId="12" hidden="1">ch4_2!$B$7</definedName>
     <definedName name="solver_opt" localSheetId="13" hidden="1">ch4_3!$H$2</definedName>
@@ -694,9 +694,6 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -1268,27 +1265,27 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="9">
-    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
-    <numFmt numFmtId="7" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\)"/>
-    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="0.0000"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
-    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.000_);\(&quot;$&quot;#,##0.000\)"/>
-    <numFmt numFmtId="167" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="168" formatCode="0.0%"/>
+    <numFmt numFmtId="187" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="188" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\)"/>
+    <numFmt numFmtId="189" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
+    <numFmt numFmtId="190" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="191" formatCode="0.0000"/>
+    <numFmt numFmtId="192" formatCode="0.000"/>
+    <numFmt numFmtId="193" formatCode="&quot;$&quot;#,##0.000_);\(&quot;$&quot;#,##0.000\)"/>
+    <numFmt numFmtId="194" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="195" formatCode="0.0%"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1300,20 +1297,20 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1425,12 +1422,12 @@
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="8" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="189" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="190" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="190" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1446,18 +1443,18 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="191" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="5" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="192" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="8" fontId="5" fillId="8" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="189" fontId="5" fillId="8" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="193" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -1472,21 +1469,18 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1"/>
-    <xf numFmtId="43" fontId="5" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="190" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="190" fontId="5" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="5" fillId="2" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="3" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="194" fontId="0" fillId="3" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1498,28 +1492,21 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="5" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="5" fillId="3" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="194" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="194" fontId="5" fillId="3" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="187" fontId="5" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="6" fontId="5" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="8" fontId="5" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="8" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="189" fontId="5" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="189" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="5" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="7" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="7" fontId="5" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="188" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="5" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="5" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="5" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="195" fontId="0" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1556,7 +1543,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Advertising "/>
@@ -1738,9 +1725,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1778,7 +1765,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1884,7 +1871,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2026,7 +2013,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2035,13 +2022,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C764809-11C3-4C28-A777-28C2126910BA}">
   <dimension ref="A1:N18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.6875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.4375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="H1" t="s">
         <v>0</v>
       </c>
@@ -2061,12 +2048,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="G2" t="s">
         <v>3</v>
       </c>
       <c r="H2">
-        <v>316</v>
+        <v>300</v>
       </c>
       <c r="I2">
         <v>450</v>
@@ -2084,7 +2071,7 @@
         <v>28.571428571428573</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -2111,7 +2098,7 @@
         <v>275</v>
       </c>
       <c r="L3">
-        <v>514.28571428571422</v>
+        <v>514.28571428571399</v>
       </c>
       <c r="M3">
         <v>1200</v>
@@ -2120,7 +2107,7 @@
         <v>28.571428571428573</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -2147,7 +2134,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -2174,7 +2161,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -2195,7 +2182,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -2216,16 +2203,16 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>11</v>
       </c>
       <c r="B13">
         <f>SUMPRODUCT(H2:J2,L2:N2)</f>
-        <v>718514.28571428568</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+        <v>710285.71428571432</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -2234,34 +2221,34 @@
         <v>355000</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>14</v>
       </c>
       <c r="B15">
-        <f>$B$8*11</f>
+        <f>$B$8*$H$8</f>
         <v>110000</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>15</v>
       </c>
       <c r="B16">
-        <f>$B$9 * 15</f>
+        <f>$B$9 * $H$9</f>
         <v>45000</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>12</v>
       </c>
       <c r="B17" s="2">
         <f>B13 - (B14+B15+B16)</f>
-        <v>208514.28571428568</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+        <v>200285.71428571432</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B18">
         <v>200285.71428571432</v>
       </c>
@@ -2274,12 +2261,12 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68278018-F2A2-4894-8531-388098B52F99}">
   <dimension ref="A1:N13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="5" max="5" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.3125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>116</v>
       </c>
@@ -2311,7 +2298,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B2">
         <v>1</v>
       </c>
@@ -2352,7 +2339,7 @@
         <v>290000</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B3">
         <v>1</v>
       </c>
@@ -2393,7 +2380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B4">
         <v>2</v>
       </c>
@@ -2428,7 +2415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B5">
         <v>2</v>
       </c>
@@ -2463,7 +2450,7 @@
         <v>-90000</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B6">
         <v>2</v>
       </c>
@@ -2498,7 +2485,7 @@
         <v>-80000</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B7">
         <v>2</v>
       </c>
@@ -2533,7 +2520,7 @@
         <v>-50000</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B8">
         <v>3</v>
       </c>
@@ -2568,7 +2555,7 @@
         <v>-70000</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B9">
         <v>3</v>
       </c>
@@ -2582,7 +2569,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B10">
         <v>3</v>
       </c>
@@ -2596,7 +2583,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B11">
         <v>3</v>
       </c>
@@ -2610,7 +2597,7 @@
         <v>70000</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="D13" t="s">
         <v>70</v>
       </c>
@@ -2627,21 +2614,21 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D286B17C-5944-46CA-B76E-D859AC09B597}">
   <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="3.85546875" customWidth="1"/>
-    <col min="8" max="8" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.875" customWidth="1"/>
+    <col min="8" max="8" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.5625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="3" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
         <v>120</v>
       </c>
@@ -2657,7 +2644,7 @@
       <c r="F1" t="s">
         <v>123</v>
       </c>
-      <c r="G1" s="60"/>
+      <c r="G1" s="54"/>
       <c r="H1" t="s">
         <v>135</v>
       </c>
@@ -2672,7 +2659,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>126</v>
       </c>
@@ -2691,7 +2678,7 @@
       <c r="F2">
         <v>1600</v>
       </c>
-      <c r="G2" s="60"/>
+      <c r="G2" s="54"/>
       <c r="H2" t="s">
         <v>136</v>
       </c>
@@ -2706,7 +2693,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="29" t="s">
         <v>127</v>
       </c>
@@ -2725,9 +2712,9 @@
       <c r="F3">
         <v>8</v>
       </c>
-      <c r="G3" s="60"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G3" s="54"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>128</v>
       </c>
@@ -2746,7 +2733,7 @@
       <c r="F4">
         <v>5.5</v>
       </c>
-      <c r="G4" s="60"/>
+      <c r="G4" s="54"/>
       <c r="H4" t="s">
         <v>134</v>
       </c>
@@ -2755,7 +2742,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>129</v>
       </c>
@@ -2774,16 +2761,16 @@
       <c r="F5">
         <v>110</v>
       </c>
-      <c r="G5" s="60"/>
+      <c r="G5" s="54"/>
       <c r="H5" t="s">
         <v>131</v>
       </c>
-      <c r="I5" s="62">
+      <c r="I5" s="56">
         <f xml:space="preserve"> SUMPRODUCT(B11:F11,B7:F7)</f>
         <v>57413.793103448275</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>130</v>
       </c>
@@ -2802,7 +2789,7 @@
       <c r="F6">
         <v>35</v>
       </c>
-      <c r="G6" s="60"/>
+      <c r="G6" s="54"/>
       <c r="H6" t="s">
         <v>132</v>
       </c>
@@ -2811,7 +2798,7 @@
         <v>2800</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>133</v>
       </c>
@@ -2835,19 +2822,19 @@
         <f>F5-F6</f>
         <v>75</v>
       </c>
-      <c r="G7" s="60"/>
+      <c r="G7" s="54"/>
       <c r="H7" t="s">
         <v>39</v>
       </c>
-      <c r="I7" s="61">
+      <c r="I7" s="55">
         <f>I5-I6</f>
         <v>54613.793103448275</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="G8" s="60"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="G8" s="54"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>120</v>
       </c>
@@ -2863,9 +2850,9 @@
       <c r="F9" t="s">
         <v>123</v>
       </c>
-      <c r="G9" s="60"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G9" s="54"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>124</v>
       </c>
@@ -2884,16 +2871,16 @@
       <c r="F10" s="6">
         <v>1</v>
       </c>
-      <c r="G10" s="60"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G10" s="54"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>125</v>
       </c>
       <c r="B11" s="6">
         <v>0</v>
       </c>
-      <c r="C11" s="59">
+      <c r="C11" s="53">
         <v>965.51724137931024</v>
       </c>
       <c r="D11" s="6">
@@ -2902,12 +2889,12 @@
       <c r="E11" s="6">
         <v>0</v>
       </c>
-      <c r="F11" s="59">
+      <c r="F11" s="53">
         <v>379.31034482758622</v>
       </c>
-      <c r="G11" s="60"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G11" s="54"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B12" s="7" t="s">
         <v>2</v>
       </c>
@@ -2923,9 +2910,9 @@
       <c r="F12" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="G12" s="60"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G12" s="54"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B13">
         <f>B10 * $I$4</f>
         <v>0</v>
@@ -2946,7 +2933,7 @@
         <f>F10 * $I$4</f>
         <v>1000000</v>
       </c>
-      <c r="G13" s="60"/>
+      <c r="G13" s="54"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2958,34 +2945,34 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A8A5270-313A-4FDD-8229-6559A071CFF2}">
   <dimension ref="A2:G22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.140625" customWidth="1"/>
-    <col min="3" max="3" width="10.42578125" customWidth="1"/>
+    <col min="1" max="1" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.125" customWidth="1"/>
+    <col min="3" max="3" width="10.4375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B2" s="31" t="s">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B2" s="30" t="s">
         <v>120</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="C2" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="D2" s="31" t="s">
+      <c r="D2" s="30" t="s">
         <v>121</v>
       </c>
-      <c r="E2" s="31" t="s">
+      <c r="E2" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="F2" s="31" t="s">
+      <c r="F2" s="30" t="s">
         <v>123</v>
       </c>
-      <c r="G2" s="31" t="s">
+      <c r="G2" s="30" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>126</v>
       </c>
@@ -3008,7 +2995,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="29" t="s">
         <v>127</v>
       </c>
@@ -3031,7 +3018,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>128</v>
       </c>
@@ -3054,7 +3041,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>129</v>
       </c>
@@ -3077,7 +3064,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>130</v>
       </c>
@@ -3100,7 +3087,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>133</v>
       </c>
@@ -3129,7 +3116,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>120</v>
       </c>
@@ -3149,7 +3136,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>124</v>
       </c>
@@ -3172,7 +3159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>125</v>
       </c>
@@ -3195,7 +3182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B13" s="7" t="s">
         <v>2</v>
       </c>
@@ -3215,7 +3202,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B14">
         <f t="shared" ref="B14:G14" si="1">B11 * $B$19</f>
         <v>0</v>
@@ -3241,7 +3228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>135</v>
       </c>
@@ -3256,7 +3243,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>136</v>
       </c>
@@ -3271,7 +3258,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>134</v>
       </c>
@@ -3280,7 +3267,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>131</v>
       </c>
@@ -3289,7 +3276,7 @@
         <v>57413.793103448275</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>132</v>
       </c>
@@ -3298,7 +3285,7 @@
         <v>2800</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>39</v>
       </c>
@@ -3316,35 +3303,35 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA6CB6CF-31AC-43B2-BABC-B89D4F5C3C26}">
   <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.5625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B1" s="31" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B1" s="30" t="s">
         <v>73</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="30" t="s">
         <v>74</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="30" t="s">
         <v>75</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="H1" s="31" t="s">
+      <c r="H1" s="30" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>82</v>
       </c>
@@ -3371,7 +3358,7 @@
       </c>
       <c r="K2" s="7"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>70</v>
       </c>
@@ -3397,7 +3384,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>80</v>
       </c>
@@ -3423,7 +3410,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>81</v>
       </c>
@@ -3456,7 +3443,7 @@
         <v>9.9999999999999936E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>39</v>
       </c>
@@ -3484,42 +3471,42 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BF078DC-633E-40D6-9FA8-AC14046EFECF}">
   <dimension ref="A1:J12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.140625" customWidth="1"/>
-    <col min="2" max="2" width="7.42578125" customWidth="1"/>
+    <col min="1" max="1" width="9.125" customWidth="1"/>
+    <col min="2" max="2" width="7.4375" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="7.5703125" customWidth="1"/>
+    <col min="4" max="4" width="7.5625" customWidth="1"/>
     <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="7.85546875" customWidth="1"/>
-    <col min="7" max="7" width="9.85546875" customWidth="1"/>
-    <col min="8" max="8" width="6.5703125" customWidth="1"/>
-    <col min="9" max="9" width="3.85546875" customWidth="1"/>
-    <col min="10" max="10" width="6.42578125" customWidth="1"/>
+    <col min="6" max="6" width="7.875" customWidth="1"/>
+    <col min="7" max="7" width="9.875" customWidth="1"/>
+    <col min="8" max="8" width="6.5625" customWidth="1"/>
+    <col min="9" max="9" width="3.875" customWidth="1"/>
+    <col min="10" max="10" width="6.4375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B1" s="31" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B1" s="30" t="s">
         <v>137</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="30" t="s">
         <v>138</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="30" t="s">
         <v>139</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="30" t="s">
         <v>140</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="30" t="s">
         <v>141</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="30" t="s">
         <v>142</v>
       </c>
-      <c r="H1" s="31"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H1" s="30"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>143</v>
       </c>
@@ -3546,19 +3533,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="32"/>
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
-      <c r="J3" s="32"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>137</v>
       </c>
@@ -3591,7 +3566,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>138</v>
       </c>
@@ -3624,7 +3599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>139</v>
       </c>
@@ -3657,7 +3632,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>140</v>
       </c>
@@ -3690,7 +3665,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>141</v>
       </c>
@@ -3723,7 +3698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>142</v>
       </c>
@@ -3756,7 +3731,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>126</v>
       </c>
@@ -3779,8 +3754,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="33" t="s">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>144</v>
       </c>
     </row>
@@ -3792,47 +3767,47 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FFF8B83-9FAD-40FB-8E72-EC5CAC388E8C}">
   <dimension ref="A1:K12"/>
-  <sheetFormatPr defaultColWidth="10.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.3125" defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.3125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.6875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="3.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="4.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="3.42578125" customWidth="1"/>
-    <col min="10" max="10" width="3.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="3.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="4.4375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="3.4375" customWidth="1"/>
+    <col min="10" max="10" width="3.125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="3.4375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="34" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A1" s="31" t="s">
         <v>154</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="30" t="s">
         <v>145</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="30" t="s">
         <v>146</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="30" t="s">
         <v>147</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="30" t="s">
         <v>148</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="30" t="s">
         <v>149</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="30" t="s">
         <v>151</v>
       </c>
-      <c r="H1" s="31" t="s">
+      <c r="H1" s="30" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>152</v>
       </c>
@@ -3862,17 +3837,17 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="31" t="s">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A4" s="30" t="s">
         <v>145</v>
       </c>
       <c r="B4">
@@ -3907,8 +3882,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="31" t="s">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A5" s="30" t="s">
         <v>146</v>
       </c>
       <c r="B5">
@@ -3943,8 +3918,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="31" t="s">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A6" s="30" t="s">
         <v>147</v>
       </c>
       <c r="B6">
@@ -3979,8 +3954,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="31" t="s">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A7" s="30" t="s">
         <v>148</v>
       </c>
       <c r="B7">
@@ -4015,8 +3990,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A8" s="30" t="s">
         <v>149</v>
       </c>
       <c r="B8">
@@ -4051,8 +4026,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="31" t="s">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A9" s="30" t="s">
         <v>151</v>
       </c>
       <c r="B9">
@@ -4087,8 +4062,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A10" s="30" t="s">
         <v>150</v>
       </c>
       <c r="B10">
@@ -4123,11 +4098,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="I11" s="32"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="31" t="s">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A12" s="30" t="s">
         <v>153</v>
       </c>
       <c r="B12">
@@ -4160,14 +4132,14 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83770651-6A0E-4CA7-AD8F-E5D26ABE3557}">
   <dimension ref="A1:I29"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.7109375" customWidth="1"/>
-    <col min="2" max="7" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.6875" customWidth="1"/>
+    <col min="2" max="7" width="7.3125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="9" t="s">
         <v>99</v>
       </c>
@@ -4180,7 +4152,7 @@
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
         <v>100</v>
       </c>
@@ -4195,7 +4167,7 @@
       <c r="H2" s="10"/>
       <c r="I2" s="10"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="10" t="s">
         <v>101</v>
       </c>
@@ -4210,11 +4182,11 @@
       <c r="H3" s="10"/>
       <c r="I3" s="10"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="B4" s="42">
+      <c r="B4" s="38">
         <f>125000</f>
         <v>125000</v>
       </c>
@@ -4226,7 +4198,7 @@
       <c r="H4" s="10"/>
       <c r="I4" s="10"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="10"/>
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
@@ -4237,7 +4209,7 @@
       <c r="H5" s="10"/>
       <c r="I5" s="10"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="10" t="s">
         <v>102</v>
       </c>
@@ -4262,7 +4234,7 @@
       <c r="H6" s="15"/>
       <c r="I6" s="10"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
         <v>103</v>
       </c>
@@ -4287,7 +4259,7 @@
       <c r="H7" s="10"/>
       <c r="I7" s="10"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" s="16" t="s">
         <v>104</v>
       </c>
@@ -4318,11 +4290,11 @@
       <c r="H8" s="10"/>
       <c r="I8" s="10"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="H9" s="10"/>
       <c r="I9" s="10"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="19" t="s">
         <v>105</v>
       </c>
@@ -4334,7 +4306,7 @@
       <c r="G10" s="10"/>
       <c r="H10" s="10"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="10" t="s">
         <v>102</v>
       </c>
@@ -4359,134 +4331,134 @@
       <c r="H11" s="10"/>
       <c r="I11" s="10"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="B12" s="39">
-        <v>1</v>
-      </c>
-      <c r="C12" s="39">
-        <v>0</v>
-      </c>
-      <c r="D12" s="39">
-        <v>1</v>
-      </c>
-      <c r="E12" s="39">
-        <v>1</v>
-      </c>
-      <c r="F12" s="39">
-        <v>1</v>
-      </c>
-      <c r="G12" s="39">
+      <c r="B12" s="36">
+        <v>1</v>
+      </c>
+      <c r="C12" s="36">
+        <v>0</v>
+      </c>
+      <c r="D12" s="36">
+        <v>1</v>
+      </c>
+      <c r="E12" s="36">
+        <v>1</v>
+      </c>
+      <c r="F12" s="36">
+        <v>1</v>
+      </c>
+      <c r="G12" s="36">
         <v>0</v>
       </c>
       <c r="H12" s="10"/>
       <c r="I12" s="10"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="B13" s="40">
+      <c r="B13" s="37">
         <v>20000</v>
       </c>
-      <c r="C13" s="40">
-        <v>0</v>
-      </c>
-      <c r="D13" s="40">
+      <c r="C13" s="37">
+        <v>0</v>
+      </c>
+      <c r="D13" s="37">
         <v>30000</v>
       </c>
-      <c r="E13" s="40">
+      <c r="E13" s="37">
         <v>35000</v>
       </c>
-      <c r="F13" s="40">
+      <c r="F13" s="37">
         <v>35000</v>
       </c>
-      <c r="G13" s="40">
+      <c r="G13" s="37">
         <v>0</v>
       </c>
       <c r="H13" s="10"/>
       <c r="I13" s="10"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" s="10"/>
-      <c r="B14" s="45" t="s">
-        <v>2</v>
-      </c>
-      <c r="C14" s="45" t="s">
-        <v>2</v>
-      </c>
-      <c r="D14" s="45" t="s">
-        <v>2</v>
-      </c>
-      <c r="E14" s="45" t="s">
-        <v>2</v>
-      </c>
-      <c r="F14" s="45" t="s">
-        <v>2</v>
-      </c>
-      <c r="G14" s="45" t="s">
+      <c r="B14" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="F14" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="G14" s="21" t="s">
         <v>2</v>
       </c>
       <c r="H14" s="10"/>
       <c r="I14" s="10"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="B15" s="38">
+      <c r="B15" s="35">
         <v>30000</v>
       </c>
-      <c r="C15" s="38">
+      <c r="C15" s="35">
         <v>30000</v>
       </c>
-      <c r="D15" s="38">
+      <c r="D15" s="35">
         <v>30000</v>
       </c>
-      <c r="E15" s="38">
+      <c r="E15" s="35">
         <v>30000</v>
       </c>
-      <c r="F15" s="38">
+      <c r="F15" s="35">
         <v>30000</v>
       </c>
-      <c r="G15" s="38">
+      <c r="G15" s="35">
         <v>30000</v>
       </c>
       <c r="H15" s="10"/>
       <c r="I15" s="10"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" s="10"/>
-      <c r="B16" s="41">
+      <c r="B16" s="10">
         <f>$B$4*B12</f>
         <v>125000</v>
       </c>
-      <c r="C16" s="41">
+      <c r="C16" s="10">
         <f t="shared" ref="C16:F16" si="1">$B$4*C12</f>
         <v>0</v>
       </c>
-      <c r="D16" s="41">
+      <c r="D16" s="10">
         <f>$B$4*D12</f>
         <v>125000</v>
       </c>
-      <c r="E16" s="41">
+      <c r="E16" s="10">
         <f t="shared" si="1"/>
         <v>125000</v>
       </c>
-      <c r="F16" s="41">
+      <c r="F16" s="10">
         <f t="shared" si="1"/>
         <v>125000</v>
       </c>
-      <c r="G16" s="41">
+      <c r="G16" s="10">
         <f>$B$4*G12</f>
         <v>0</v>
       </c>
       <c r="H16" s="10"/>
       <c r="I16" s="10"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" s="10"/>
       <c r="B17" s="23"/>
       <c r="C17" s="23"/>
@@ -4497,7 +4469,7 @@
       <c r="H17" s="10"/>
       <c r="I17" s="10"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" s="10" t="s">
         <v>109</v>
       </c>
@@ -4522,7 +4494,7 @@
       <c r="H18" s="10"/>
       <c r="I18" s="10"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" s="10"/>
       <c r="B19" s="21"/>
       <c r="C19" s="21"/>
@@ -4533,7 +4505,7 @@
       <c r="H19" s="23"/>
       <c r="I19" s="10"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" s="10" t="s">
         <v>110</v>
       </c>
@@ -4564,55 +4536,55 @@
       <c r="H20" s="10"/>
       <c r="I20" s="10"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" s="10"/>
-      <c r="B21" s="36" t="s">
-        <v>2</v>
-      </c>
-      <c r="C21" s="36" t="s">
-        <v>2</v>
-      </c>
-      <c r="D21" s="36" t="s">
-        <v>2</v>
-      </c>
-      <c r="E21" s="36" t="s">
-        <v>2</v>
-      </c>
-      <c r="F21" s="36" t="s">
-        <v>2</v>
-      </c>
-      <c r="G21" s="36" t="s">
+      <c r="B21" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="C21" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="D21" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="E21" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="F21" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="G21" s="33" t="s">
         <v>2</v>
       </c>
       <c r="H21" s="10"/>
       <c r="I21" s="10"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="B22" s="37">
+      <c r="B22" s="34">
         <v>10000</v>
       </c>
-      <c r="C22" s="37">
+      <c r="C22" s="34">
         <v>10000</v>
       </c>
-      <c r="D22" s="37">
+      <c r="D22" s="34">
         <v>10000</v>
       </c>
-      <c r="E22" s="37">
+      <c r="E22" s="34">
         <v>10000</v>
       </c>
-      <c r="F22" s="37">
+      <c r="F22" s="34">
         <v>10000</v>
       </c>
-      <c r="G22" s="37">
+      <c r="G22" s="34">
         <v>10000</v>
       </c>
       <c r="H22" s="10"/>
       <c r="I22" s="10"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" s="19"/>
       <c r="B23" s="10"/>
       <c r="C23" s="10"/>
@@ -4623,7 +4595,7 @@
       <c r="H23" s="10"/>
       <c r="I23" s="10"/>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" s="24" t="s">
         <v>112</v>
       </c>
@@ -4635,7 +4607,7 @@
       <c r="G24" s="10"/>
       <c r="I24" s="10"/>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" s="10" t="s">
         <v>102</v>
       </c>
@@ -4662,103 +4634,103 @@
       </c>
       <c r="I25" s="10"/>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="B26" s="35">
-        <f>B20*B8</f>
+      <c r="B26" s="32">
+        <f t="shared" ref="B26:G26" si="2">B20*B8</f>
         <v>9375</v>
       </c>
-      <c r="C26" s="35">
-        <f>C20*C8</f>
-        <v>0</v>
-      </c>
-      <c r="D26" s="35">
-        <f>D20*D8</f>
-        <v>0</v>
-      </c>
-      <c r="E26" s="35">
-        <f>E20*E8</f>
-        <v>0</v>
-      </c>
-      <c r="F26" s="35">
-        <f>F20*F8</f>
+      <c r="C26" s="32">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D26" s="32">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E26" s="32">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F26" s="32">
+        <f t="shared" si="2"/>
         <v>6425.0000000000009</v>
       </c>
-      <c r="G26" s="35">
-        <f>G20*G8</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="43">
+      <c r="G26" s="32">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H26" s="39">
         <f>SUMPRODUCT(B20:G20,B8:G8)</f>
         <v>15800</v>
       </c>
       <c r="I26" s="10"/>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="B27" s="35">
-        <f t="shared" ref="B27:G27" si="2">B13*B7</f>
+      <c r="B27" s="32">
+        <f t="shared" ref="B27:G27" si="3">B13*B7</f>
         <v>250000</v>
       </c>
-      <c r="C27" s="35">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D27" s="35">
-        <f t="shared" si="2"/>
+      <c r="C27" s="32">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="D27" s="32">
+        <f t="shared" si="3"/>
         <v>381000</v>
       </c>
-      <c r="E27" s="35">
-        <f t="shared" si="2"/>
+      <c r="E27" s="32">
+        <f t="shared" si="3"/>
         <v>448000</v>
       </c>
-      <c r="F27" s="35">
-        <f t="shared" si="2"/>
+      <c r="F27" s="32">
+        <f t="shared" si="3"/>
         <v>449750</v>
       </c>
-      <c r="G27" s="35">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H27" s="43">
+      <c r="G27" s="32">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H27" s="39">
         <f>SUMPRODUCT(B13:G13,B7:G7)</f>
         <v>1528750</v>
       </c>
       <c r="I27" s="10"/>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="B28" s="35">
+      <c r="B28" s="32">
         <v>15000</v>
       </c>
-      <c r="C28" s="35">
+      <c r="C28" s="32">
         <v>15000</v>
       </c>
-      <c r="D28" s="35">
+      <c r="D28" s="32">
         <v>15000</v>
       </c>
-      <c r="E28" s="35">
+      <c r="E28" s="32">
         <v>15000</v>
       </c>
-      <c r="F28" s="35">
+      <c r="F28" s="32">
         <v>15000</v>
       </c>
-      <c r="G28" s="35">
+      <c r="G28" s="32">
         <v>15000</v>
       </c>
-      <c r="H28" s="43">
+      <c r="H28" s="39">
         <f>SUMPRODUCT(B12:G12,B28:G28)</f>
         <v>60000</v>
       </c>
       <c r="I28" s="10"/>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" s="10"/>
       <c r="B29" s="10"/>
       <c r="C29" s="10"/>
@@ -4766,7 +4738,7 @@
       <c r="E29" s="10"/>
       <c r="F29" s="10"/>
       <c r="G29" s="10"/>
-      <c r="H29" s="44">
+      <c r="H29" s="40">
         <f>SUM(H26:H28)</f>
         <v>1604550</v>
       </c>
@@ -4779,40 +4751,40 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FE38B91-F448-4184-8315-E5F01652B01A}">
   <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.5625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.3125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.3125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="5.3125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.4375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" s="30" t="s">
         <v>157</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="30" t="s">
         <v>158</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="30" t="s">
         <v>159</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="30" t="s">
         <v>160</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="30" t="s">
         <v>162</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="30" t="s">
         <v>163</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="30" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4825,20 +4797,20 @@
       <c r="D2">
         <v>200</v>
       </c>
-      <c r="E2" s="62">
+      <c r="E2" s="56">
         <f>($B$6-B2)</f>
         <v>4.3141630158538948</v>
       </c>
-      <c r="F2" s="62">
+      <c r="F2" s="56">
         <f>($C$6-C2)</f>
         <v>-4.9712990159689436</v>
       </c>
-      <c r="G2" s="62">
+      <c r="G2" s="56">
         <f>SQRT(E2^2 +F2^2)</f>
         <v>6.582234911755684</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4851,20 +4823,20 @@
       <c r="D3">
         <v>150</v>
       </c>
-      <c r="E3" s="62">
+      <c r="E3" s="56">
         <f t="shared" ref="E3:E5" si="0">($B$6-B3)</f>
         <v>-0.68583698414610517</v>
       </c>
-      <c r="F3" s="62">
+      <c r="F3" s="56">
         <f t="shared" ref="F3:F5" si="1">($C$6-C3)</f>
         <v>2.8700984031056365E-2</v>
       </c>
-      <c r="G3" s="62">
+      <c r="G3" s="56">
         <f t="shared" ref="G3:G5" si="2">SQRT(E3^2 +F3^2)</f>
         <v>0.68643726246975834</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4877,20 +4849,20 @@
       <c r="D4">
         <v>200</v>
       </c>
-      <c r="E4" s="62">
+      <c r="E4" s="56">
         <f t="shared" si="0"/>
         <v>9.3141630158538948</v>
       </c>
-      <c r="F4" s="62">
+      <c r="F4" s="56">
         <f t="shared" si="1"/>
         <v>-6.9712990159689436</v>
       </c>
-      <c r="G4" s="62">
+      <c r="G4" s="56">
         <f t="shared" si="2"/>
         <v>11.634115465128842</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4903,36 +4875,35 @@
       <c r="D5">
         <v>300</v>
       </c>
-      <c r="E5" s="62">
+      <c r="E5" s="56">
         <f t="shared" si="0"/>
         <v>-2.6858369841461052</v>
       </c>
-      <c r="F5" s="62">
+      <c r="F5" s="56">
         <f t="shared" si="1"/>
         <v>5.0287009840310564</v>
       </c>
-      <c r="G5" s="62">
+      <c r="G5" s="56">
         <f t="shared" si="2"/>
         <v>5.7010134092283948</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="31" t="s">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="B6" s="63">
+      <c r="B6" s="57">
         <v>9.3141630158538948</v>
       </c>
-      <c r="C6" s="63">
+      <c r="C6" s="57">
         <v>5.0287009840310564</v>
       </c>
-      <c r="G6" s="32"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>165</v>
       </c>
-      <c r="B7" s="61">
+      <c r="B7" s="55">
         <f>SUMPRODUCT(D2:D5,G2:G5)</f>
         <v>5456.5396875158876</v>
       </c>
@@ -4945,40 +4916,40 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{573F87C3-C663-4007-B0D4-35BF49BC4D1B}">
   <dimension ref="A1:H25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="31.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.42578125" customWidth="1"/>
-    <col min="6" max="6" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.4375" customWidth="1"/>
+    <col min="6" max="6" width="21.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="19" t="s">
         <v>99</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
-      <c r="E1" s="64"/>
+      <c r="E1" s="58"/>
       <c r="F1" s="24" t="s">
         <v>178</v>
       </c>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
         <v>166</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
       <c r="D2" s="10"/>
-      <c r="E2" s="64"/>
+      <c r="E2" s="58"/>
       <c r="F2" s="10"/>
       <c r="G2" s="23" t="s">
         <v>174</v>
@@ -4987,7 +4958,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="10"/>
       <c r="B3" s="23" t="s">
         <v>167</v>
@@ -4998,20 +4969,20 @@
       <c r="D3" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="E3" s="65"/>
+      <c r="E3" s="59"/>
       <c r="F3" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="G3" s="54">
+      <c r="G3" s="49">
         <f>SUMPRODUCT(C4:D4,B11:C11) +B4</f>
         <v>0.69211111732132413</v>
       </c>
-      <c r="H3" s="54">
+      <c r="H3" s="49">
         <f>SUMPRODUCT(C5:D5, B11:C11) + B5</f>
         <v>0.69211110893935746</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="22" t="s">
         <v>170</v>
       </c>
@@ -5024,7 +4995,7 @@
       <c r="D4" s="12">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="E4" s="64"/>
+      <c r="E4" s="58"/>
       <c r="F4" s="10"/>
       <c r="G4" s="23" t="s">
         <v>2</v>
@@ -5033,7 +5004,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="10" t="s">
         <v>171</v>
       </c>
@@ -5046,72 +5017,72 @@
       <c r="D5" s="12">
         <v>-1.4999999999999999E-2</v>
       </c>
-      <c r="E5" s="64"/>
+      <c r="E5" s="58"/>
       <c r="F5" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="G5" s="53">
+      <c r="G5" s="48">
         <f>$B$13</f>
         <v>0.69211111345885656</v>
       </c>
-      <c r="H5" s="53">
+      <c r="H5" s="48">
         <f>$B$13</f>
         <v>0.69211111345885656</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="10"/>
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
       <c r="D6" s="10"/>
-      <c r="E6" s="64"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E6" s="58"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
         <v>172</v>
       </c>
-      <c r="B7" s="46">
+      <c r="B7" s="41">
         <v>75</v>
       </c>
       <c r="C7" s="10"/>
       <c r="D7" s="10"/>
-      <c r="E7" s="64"/>
+      <c r="E7" s="58"/>
       <c r="F7" s="19" t="s">
         <v>179</v>
       </c>
       <c r="G7" s="10"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="10"/>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
       <c r="D8" s="10"/>
-      <c r="E8" s="64"/>
+      <c r="E8" s="58"/>
       <c r="F8" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="G8" s="51">
+      <c r="G8" s="46">
         <f>SUMPRODUCT(G3:H3,B11:C11)</f>
         <v>147.71189170368535</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="24" t="s">
         <v>173</v>
       </c>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
       <c r="D9" s="10"/>
-      <c r="E9" s="64"/>
+      <c r="E9" s="58"/>
       <c r="F9" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="G9" s="51">
+      <c r="G9" s="46">
         <f>$B$7*B13</f>
         <v>51.908333509414241</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="23"/>
       <c r="B10" s="23" t="s">
         <v>174</v>
@@ -5120,101 +5091,101 @@
         <v>175</v>
       </c>
       <c r="D10" s="21"/>
-      <c r="E10" s="65"/>
+      <c r="E10" s="59"/>
       <c r="F10" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="G10" s="52">
+      <c r="G10" s="47">
         <f>G8-G9</f>
         <v>95.803558194271119</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="B11" s="47">
+      <c r="B11" s="42">
         <v>137.57222174090037</v>
       </c>
-      <c r="C11" s="47">
+      <c r="C11" s="42">
         <v>75.849999984342958</v>
       </c>
       <c r="D11" s="10"/>
-      <c r="E11" s="64"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E11" s="58"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="10"/>
-      <c r="B12" s="48"/>
-      <c r="C12" s="48"/>
-      <c r="D12" s="49"/>
-      <c r="E12" s="64"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B12" s="43"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="58"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="B13" s="50">
+      <c r="B13" s="45">
         <v>0.69211111345885656</v>
       </c>
-      <c r="C13" s="48"/>
-      <c r="D13" s="49"/>
-      <c r="E13" s="64"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C13" s="43"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="58"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="10"/>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
       <c r="D14" s="10"/>
       <c r="E14" s="10"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="D15" s="10"/>
       <c r="E15" s="10"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="D16" s="23"/>
       <c r="E16" s="23"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="D17" s="10"/>
       <c r="E17" s="10"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="D18" s="10"/>
       <c r="E18" s="10"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D19" s="49"/>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="D19" s="44"/>
       <c r="E19" s="10"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="10"/>
-      <c r="B20" s="49"/>
+      <c r="B20" s="44"/>
       <c r="C20" s="10"/>
       <c r="D20" s="10"/>
       <c r="E20" s="10"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="C21" s="10"/>
       <c r="D21" s="10"/>
       <c r="E21" s="10"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C22" s="51"/>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="C22" s="46"/>
       <c r="D22" s="10"/>
       <c r="E22" s="10"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="C23" s="10"/>
       <c r="D23" s="10"/>
       <c r="E23" s="10"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
       <c r="E24" s="10"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="10"/>
       <c r="B25" s="10"/>
       <c r="C25" s="10"/>
@@ -5229,48 +5200,48 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6829978-8C83-46EC-9B0D-95A12529CCF4}">
   <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="3.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="2.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.3125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.3125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.3125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.6875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.3125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="2.6875" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" s="30" t="s">
         <v>157</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="30" t="s">
         <v>158</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="30" t="s">
         <v>159</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="30" t="s">
         <v>160</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="30" t="s">
         <v>162</v>
       </c>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31" t="s">
+      <c r="F1" s="30"/>
+      <c r="G1" s="30" t="s">
         <v>163</v>
       </c>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31" t="s">
+      <c r="H1" s="30"/>
+      <c r="I1" s="30" t="s">
         <v>183</v>
       </c>
-      <c r="J1" s="31" t="s">
+      <c r="J1" s="30" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -5306,7 +5277,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -5342,7 +5313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -5378,7 +5349,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -5414,8 +5385,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="31" t="s">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6" s="30" t="s">
         <v>161</v>
       </c>
       <c r="B6" s="1">
@@ -5433,7 +5404,7 @@
         <v>3900</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>165</v>
       </c>
@@ -5450,12 +5421,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8ED592CD-86CB-44D4-97B2-69C4BC78FBD6}">
   <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
         <v>47</v>
       </c>
@@ -5463,7 +5434,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>46</v>
       </c>
@@ -5474,7 +5445,7 @@
         <v>0.25000000000000072</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>47</v>
       </c>
@@ -5482,7 +5453,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>54</v>
       </c>
@@ -5507,7 +5478,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>49</v>
       </c>
@@ -5531,7 +5502,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>50</v>
       </c>
@@ -5556,7 +5527,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>52</v>
       </c>
@@ -5567,7 +5538,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>53</v>
       </c>
@@ -5584,14 +5555,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{383545CA-8758-49BF-B735-9E5D292B0FF0}">
   <dimension ref="A1:Q22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.6875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.4375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
         <v>19</v>
       </c>
@@ -5618,7 +5589,7 @@
       </c>
       <c r="M1" s="8"/>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>27</v>
       </c>
@@ -5661,7 +5632,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>28</v>
       </c>
@@ -5704,7 +5675,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>40</v>
       </c>
@@ -5713,11 +5684,11 @@
         <v>1500</v>
       </c>
       <c r="C4">
-        <f t="shared" ref="C4:H4" si="0">SUM(C2:C3)</f>
+        <f>SUM(C2:C3)</f>
         <v>0</v>
       </c>
       <c r="D4">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="C4:H4" si="0">SUM(D2:D3)</f>
         <v>0</v>
       </c>
       <c r="E4">
@@ -5755,7 +5726,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B5" s="7" t="s">
         <v>2</v>
       </c>
@@ -5782,7 +5753,7 @@
       </c>
       <c r="M5" s="8"/>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6" s="3">
         <v>1500</v>
       </c>
@@ -5809,13 +5780,13 @@
       </c>
       <c r="M6" s="8"/>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="M7" s="8"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="M8" s="8"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -5851,7 +5822,7 @@
       </c>
       <c r="M9" s="8"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>42</v>
       </c>
@@ -5887,7 +5858,7 @@
       </c>
       <c r="M10" s="8"/>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>43</v>
       </c>
@@ -5923,10 +5894,10 @@
       </c>
       <c r="M11" s="8"/>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="M12" s="8"/>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>29</v>
       </c>
@@ -5956,7 +5927,7 @@
       </c>
       <c r="M13" s="8"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>30</v>
       </c>
@@ -5986,7 +5957,7 @@
       </c>
       <c r="M14" s="8"/>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -6024,7 +5995,7 @@
       </c>
       <c r="M15" s="8"/>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>37</v>
       </c>
@@ -6062,7 +6033,7 @@
       </c>
       <c r="M16" s="8"/>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>38</v>
       </c>
@@ -6100,10 +6071,10 @@
       </c>
       <c r="M17" s="8"/>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="M18" s="8"/>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>31</v>
       </c>
@@ -6141,7 +6112,7 @@
       </c>
       <c r="M19" s="8"/>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>32</v>
       </c>
@@ -6179,10 +6150,10 @@
       </c>
       <c r="M20" s="8"/>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
       <c r="M21" s="8"/>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>39</v>
       </c>
@@ -6233,9 +6204,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0E7EC63-9A54-4477-BBCB-EE695471FCE4}">
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
         <v>55</v>
       </c>
@@ -6243,15 +6214,15 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B2" s="1">
-        <v>4.3333333333333339</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="C2" s="1">
-        <v>3.333333333333333</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>57</v>
       </c>
@@ -6263,7 +6234,7 @@
       </c>
       <c r="E4" s="4">
         <f>SUMPRODUCT(B4:C4,$B$2:$C$2)</f>
-        <v>40.333333333333336</v>
+        <v>41.199999999999996</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>61</v>
@@ -6272,7 +6243,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>58</v>
       </c>
@@ -6284,7 +6255,7 @@
       </c>
       <c r="E5" s="4">
         <f t="shared" ref="E5:E6" si="0">SUMPRODUCT(B5:C5,$B$2:$C$2)</f>
-        <v>60.000000000000007</v>
+        <v>61</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>61</v>
@@ -6293,7 +6264,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>59</v>
       </c>
@@ -6314,10 +6285,10 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="F7" s="7"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -6328,13 +6299,13 @@
         <v>60</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>60</v>
       </c>
       <c r="B10" s="2">
         <f>SUMPRODUCT(B9:C9,B2:C2)</f>
-        <v>633.33333333333337</v>
+        <v>640</v>
       </c>
     </row>
   </sheetData>
@@ -6345,19 +6316,19 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{252464CB-7E70-452A-88CC-BE24E3E0118E}">
   <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="7.6875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.42578125" customWidth="1"/>
+    <col min="7" max="7" width="8.4375" customWidth="1"/>
     <col min="8" max="8" width="3" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
         <v>62</v>
       </c>
@@ -6371,7 +6342,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>64</v>
       </c>
@@ -6388,7 +6359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>30</v>
       </c>
@@ -6405,7 +6376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>65</v>
       </c>
@@ -6422,7 +6393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>66</v>
       </c>
@@ -6436,7 +6407,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>67</v>
       </c>
@@ -6450,7 +6421,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>68</v>
       </c>
@@ -6467,7 +6438,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>69</v>
       </c>
@@ -6478,7 +6449,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -6497,7 +6468,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>65</v>
       </c>
@@ -6516,7 +6487,7 @@
         <v>-200</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>70</v>
       </c>
@@ -6535,7 +6506,7 @@
         <v>-240</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -6555,7 +6526,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="D15" s="4">
         <f>$D$3</f>
         <v>6000</v>
@@ -6576,13 +6547,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{663BCE4E-1681-441F-8DE6-2742A5A66B94}">
   <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="8" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.5625" bestFit="1" customWidth="1"/>
+    <col min="2" max="8" width="8.4375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
         <v>73</v>
       </c>
@@ -6605,7 +6576,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>82</v>
       </c>
@@ -6631,8 +6602,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>70</v>
       </c>
@@ -6658,7 +6629,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>80</v>
       </c>
@@ -6684,40 +6655,40 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>81</v>
       </c>
-      <c r="B6" s="56">
+      <c r="B6" s="50">
         <f>(B5-B4)/B4</f>
         <v>0.11999999999999993</v>
       </c>
-      <c r="C6" s="56">
+      <c r="C6" s="50">
         <f t="shared" ref="C6:H6" si="0">(C5-C4)/C4</f>
         <v>0.12500000000000011</v>
       </c>
-      <c r="D6" s="56">
+      <c r="D6" s="50">
         <f t="shared" si="0"/>
         <v>0.11428571428571425</v>
       </c>
-      <c r="E6" s="56">
+      <c r="E6" s="50">
         <f t="shared" si="0"/>
         <v>0.15254237288135583</v>
       </c>
-      <c r="F6" s="56">
+      <c r="F6" s="50">
         <f t="shared" si="0"/>
         <v>0.11594202898550722</v>
       </c>
-      <c r="G6" s="56">
+      <c r="G6" s="50">
         <f t="shared" si="0"/>
         <v>0.13333333333333325</v>
       </c>
-      <c r="H6" s="56">
+      <c r="H6" s="50">
         <f t="shared" si="0"/>
         <v>9.9999999999999936E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>39</v>
       </c>
@@ -6725,8 +6696,7 @@
         <f>SUMPRODUCT(B2:H2,B5:H5)</f>
         <v>17.064</v>
       </c>
-      <c r="D8" s="32"/>
-      <c r="E8" s="55"/>
+      <c r="E8" s="7"/>
       <c r="F8" s="4">
         <f xml:space="preserve"> SUMPRODUCT(B4:H4,B2:H2)</f>
         <v>15.000000000000002</v>
@@ -6747,60 +6717,60 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9416A4A6-16E8-44A6-ABD2-65E95D8954DD}">
   <dimension ref="A1:N27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.4375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.3125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.3125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="3.42578125" customWidth="1"/>
-    <col min="8" max="8" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.6875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.4375" customWidth="1"/>
+    <col min="8" max="8" width="5.5625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="4" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.5625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A1" s="30" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="30" t="s">
         <v>85</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="30" t="s">
         <v>86</v>
       </c>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31" t="s">
+      <c r="E1" s="30"/>
+      <c r="F1" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="57"/>
-      <c r="H1" s="31" t="s">
+      <c r="G1" s="51"/>
+      <c r="H1" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="I1" s="31" t="s">
+      <c r="I1" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="J1" s="31" t="s">
+      <c r="J1" s="30" t="s">
         <v>90</v>
       </c>
-      <c r="K1" s="31" t="s">
+      <c r="K1" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31" t="s">
+      <c r="L1" s="30"/>
+      <c r="M1" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="N1" s="31"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N1" s="30"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -6819,7 +6789,7 @@
       <c r="F2" s="3">
         <v>200</v>
       </c>
-      <c r="G2" s="58"/>
+      <c r="G2" s="52"/>
       <c r="H2">
         <v>1</v>
       </c>
@@ -6842,7 +6812,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>
@@ -6861,7 +6831,7 @@
       <c r="F3" s="3">
         <v>200</v>
       </c>
-      <c r="G3" s="58"/>
+      <c r="G3" s="52"/>
       <c r="H3">
         <v>2</v>
       </c>
@@ -6884,7 +6854,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>1</v>
       </c>
@@ -6903,7 +6873,7 @@
       <c r="F4" s="3">
         <v>200</v>
       </c>
-      <c r="G4" s="58"/>
+      <c r="G4" s="52"/>
       <c r="H4">
         <v>3</v>
       </c>
@@ -6926,7 +6896,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>1</v>
       </c>
@@ -6945,12 +6915,12 @@
       <c r="F5" s="3">
         <v>200</v>
       </c>
-      <c r="G5" s="58"/>
+      <c r="G5" s="52"/>
       <c r="H5">
         <v>4</v>
       </c>
       <c r="I5">
-        <f t="shared" si="1"/>
+        <f>SUMIF($A$2:$A$27,H5,$D$2:$D$27)</f>
         <v>200</v>
       </c>
       <c r="J5">
@@ -6968,7 +6938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>1</v>
       </c>
@@ -6987,7 +6957,7 @@
       <c r="F6" s="3">
         <v>200</v>
       </c>
-      <c r="G6" s="58"/>
+      <c r="G6" s="52"/>
       <c r="H6">
         <v>5</v>
       </c>
@@ -7010,7 +6980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>1</v>
       </c>
@@ -7029,12 +6999,12 @@
       <c r="F7" s="3">
         <v>200</v>
       </c>
-      <c r="G7" s="58"/>
+      <c r="G7" s="52"/>
       <c r="H7">
         <v>6</v>
       </c>
       <c r="I7">
-        <f t="shared" si="1"/>
+        <f>SUMIF($A$2:$A$27,H7,$D$2:$D$27)</f>
         <v>180</v>
       </c>
       <c r="J7">
@@ -7052,7 +7022,7 @@
         <v>-400</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>2</v>
       </c>
@@ -7071,7 +7041,7 @@
       <c r="F8" s="3">
         <v>200</v>
       </c>
-      <c r="G8" s="58"/>
+      <c r="G8" s="52"/>
       <c r="H8">
         <v>7</v>
       </c>
@@ -7094,7 +7064,7 @@
         <v>-180</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>2</v>
       </c>
@@ -7113,9 +7083,9 @@
       <c r="F9" s="3">
         <v>200</v>
       </c>
-      <c r="G9" s="58"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G9" s="52"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>2</v>
       </c>
@@ -7134,7 +7104,7 @@
       <c r="F10" s="3">
         <v>200</v>
       </c>
-      <c r="G10" s="58"/>
+      <c r="G10" s="52"/>
       <c r="H10" t="s">
         <v>70</v>
       </c>
@@ -7143,7 +7113,7 @@
         <v>3260</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>2</v>
       </c>
@@ -7162,9 +7132,9 @@
       <c r="F11" s="3">
         <v>200</v>
       </c>
-      <c r="G11" s="58"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G11" s="52"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>2</v>
       </c>
@@ -7183,9 +7153,9 @@
       <c r="F12" s="3">
         <v>200</v>
       </c>
-      <c r="G12" s="58"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G12" s="52"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>2</v>
       </c>
@@ -7204,9 +7174,9 @@
       <c r="F13" s="3">
         <v>200</v>
       </c>
-      <c r="G13" s="58"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G13" s="52"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>3</v>
       </c>
@@ -7225,9 +7195,9 @@
       <c r="F14" s="3">
         <v>200</v>
       </c>
-      <c r="G14" s="58"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G14" s="52"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>3</v>
       </c>
@@ -7246,9 +7216,9 @@
       <c r="F15" s="3">
         <v>200</v>
       </c>
-      <c r="G15" s="58"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G15" s="52"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>3</v>
       </c>
@@ -7267,9 +7237,9 @@
       <c r="F16" s="3">
         <v>200</v>
       </c>
-      <c r="G16" s="58"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G16" s="52"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>3</v>
       </c>
@@ -7288,9 +7258,9 @@
       <c r="F17" s="3">
         <v>200</v>
       </c>
-      <c r="G17" s="58"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G17" s="52"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>3</v>
       </c>
@@ -7309,9 +7279,9 @@
       <c r="F18" s="3">
         <v>200</v>
       </c>
-      <c r="G18" s="58"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G18" s="52"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>3</v>
       </c>
@@ -7330,9 +7300,9 @@
       <c r="F19" s="3">
         <v>200</v>
       </c>
-      <c r="G19" s="58"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G19" s="52"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>4</v>
       </c>
@@ -7351,9 +7321,9 @@
       <c r="F20" s="3">
         <v>200</v>
       </c>
-      <c r="G20" s="58"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G20" s="52"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>4</v>
       </c>
@@ -7372,9 +7342,9 @@
       <c r="F21" s="3">
         <v>200</v>
       </c>
-      <c r="G21" s="58"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G21" s="52"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>4</v>
       </c>
@@ -7393,9 +7363,9 @@
       <c r="F22" s="3">
         <v>200</v>
       </c>
-      <c r="G22" s="58"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G22" s="52"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>5</v>
       </c>
@@ -7414,9 +7384,9 @@
       <c r="F23" s="3">
         <v>200</v>
       </c>
-      <c r="G23" s="58"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G23" s="52"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>5</v>
       </c>
@@ -7435,9 +7405,9 @@
       <c r="F24" s="3">
         <v>200</v>
       </c>
-      <c r="G24" s="58"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G24" s="52"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>5</v>
       </c>
@@ -7456,9 +7426,9 @@
       <c r="F25" s="3">
         <v>200</v>
       </c>
-      <c r="G25" s="58"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G25" s="52"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>6</v>
       </c>
@@ -7477,9 +7447,9 @@
       <c r="F26" s="3">
         <v>200</v>
       </c>
-      <c r="G26" s="58"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G26" s="52"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>7</v>
       </c>
@@ -7498,7 +7468,7 @@
       <c r="F27" s="3">
         <v>200</v>
       </c>
-      <c r="G27" s="58"/>
+      <c r="G27" s="52"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7508,9 +7478,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B2F4BAA-45A2-4B9F-8DB4-EA5599549413}">
   <dimension ref="A2:M11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>94</v>
       </c>
@@ -7542,7 +7512,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>
@@ -7583,7 +7553,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>1</v>
       </c>
@@ -7625,7 +7595,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>2</v>
       </c>
@@ -7666,7 +7636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>2</v>
       </c>
@@ -7708,7 +7678,7 @@
         <v>-60</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>3</v>
       </c>
@@ -7749,7 +7719,7 @@
         <v>-90</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>3</v>
       </c>
@@ -7770,7 +7740,7 @@
       </c>
       <c r="L8" s="7"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>70</v>
       </c>
@@ -7787,526 +7757,526 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E76634E4-7D20-4A0E-A622-BD83CBE54980}">
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="27.140625" style="10" customWidth="1"/>
-    <col min="2" max="7" width="7.28515625" style="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.28515625" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.125" style="10" customWidth="1"/>
+    <col min="2" max="7" width="7.3125" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.3125" style="10" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19" style="10" bestFit="1" customWidth="1"/>
     <col min="10" max="243" width="9" style="10"/>
-    <col min="244" max="244" width="26.5703125" style="10" customWidth="1"/>
-    <col min="245" max="245" width="13.140625" style="10" customWidth="1"/>
+    <col min="244" max="244" width="26.5625" style="10" customWidth="1"/>
+    <col min="245" max="245" width="13.125" style="10" customWidth="1"/>
     <col min="246" max="250" width="9" style="10"/>
-    <col min="251" max="251" width="10.85546875" style="10" customWidth="1"/>
+    <col min="251" max="251" width="10.875" style="10" customWidth="1"/>
     <col min="252" max="252" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="253" max="253" width="10.5703125" style="10" customWidth="1"/>
-    <col min="254" max="254" width="10.85546875" style="10" customWidth="1"/>
+    <col min="253" max="253" width="10.5625" style="10" customWidth="1"/>
+    <col min="254" max="254" width="10.875" style="10" customWidth="1"/>
     <col min="255" max="499" width="9" style="10"/>
-    <col min="500" max="500" width="26.5703125" style="10" customWidth="1"/>
-    <col min="501" max="501" width="13.140625" style="10" customWidth="1"/>
+    <col min="500" max="500" width="26.5625" style="10" customWidth="1"/>
+    <col min="501" max="501" width="13.125" style="10" customWidth="1"/>
     <col min="502" max="506" width="9" style="10"/>
-    <col min="507" max="507" width="10.85546875" style="10" customWidth="1"/>
+    <col min="507" max="507" width="10.875" style="10" customWidth="1"/>
     <col min="508" max="508" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="509" max="509" width="10.5703125" style="10" customWidth="1"/>
-    <col min="510" max="510" width="10.85546875" style="10" customWidth="1"/>
+    <col min="509" max="509" width="10.5625" style="10" customWidth="1"/>
+    <col min="510" max="510" width="10.875" style="10" customWidth="1"/>
     <col min="511" max="755" width="9" style="10"/>
-    <col min="756" max="756" width="26.5703125" style="10" customWidth="1"/>
-    <col min="757" max="757" width="13.140625" style="10" customWidth="1"/>
+    <col min="756" max="756" width="26.5625" style="10" customWidth="1"/>
+    <col min="757" max="757" width="13.125" style="10" customWidth="1"/>
     <col min="758" max="762" width="9" style="10"/>
-    <col min="763" max="763" width="10.85546875" style="10" customWidth="1"/>
+    <col min="763" max="763" width="10.875" style="10" customWidth="1"/>
     <col min="764" max="764" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="765" max="765" width="10.5703125" style="10" customWidth="1"/>
-    <col min="766" max="766" width="10.85546875" style="10" customWidth="1"/>
+    <col min="765" max="765" width="10.5625" style="10" customWidth="1"/>
+    <col min="766" max="766" width="10.875" style="10" customWidth="1"/>
     <col min="767" max="1011" width="9" style="10"/>
-    <col min="1012" max="1012" width="26.5703125" style="10" customWidth="1"/>
-    <col min="1013" max="1013" width="13.140625" style="10" customWidth="1"/>
+    <col min="1012" max="1012" width="26.5625" style="10" customWidth="1"/>
+    <col min="1013" max="1013" width="13.125" style="10" customWidth="1"/>
     <col min="1014" max="1018" width="9" style="10"/>
-    <col min="1019" max="1019" width="10.85546875" style="10" customWidth="1"/>
+    <col min="1019" max="1019" width="10.875" style="10" customWidth="1"/>
     <col min="1020" max="1020" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="1021" max="1021" width="10.5703125" style="10" customWidth="1"/>
-    <col min="1022" max="1022" width="10.85546875" style="10" customWidth="1"/>
+    <col min="1021" max="1021" width="10.5625" style="10" customWidth="1"/>
+    <col min="1022" max="1022" width="10.875" style="10" customWidth="1"/>
     <col min="1023" max="1267" width="9" style="10"/>
-    <col min="1268" max="1268" width="26.5703125" style="10" customWidth="1"/>
-    <col min="1269" max="1269" width="13.140625" style="10" customWidth="1"/>
+    <col min="1268" max="1268" width="26.5625" style="10" customWidth="1"/>
+    <col min="1269" max="1269" width="13.125" style="10" customWidth="1"/>
     <col min="1270" max="1274" width="9" style="10"/>
-    <col min="1275" max="1275" width="10.85546875" style="10" customWidth="1"/>
+    <col min="1275" max="1275" width="10.875" style="10" customWidth="1"/>
     <col min="1276" max="1276" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="1277" max="1277" width="10.5703125" style="10" customWidth="1"/>
-    <col min="1278" max="1278" width="10.85546875" style="10" customWidth="1"/>
+    <col min="1277" max="1277" width="10.5625" style="10" customWidth="1"/>
+    <col min="1278" max="1278" width="10.875" style="10" customWidth="1"/>
     <col min="1279" max="1523" width="9" style="10"/>
-    <col min="1524" max="1524" width="26.5703125" style="10" customWidth="1"/>
-    <col min="1525" max="1525" width="13.140625" style="10" customWidth="1"/>
+    <col min="1524" max="1524" width="26.5625" style="10" customWidth="1"/>
+    <col min="1525" max="1525" width="13.125" style="10" customWidth="1"/>
     <col min="1526" max="1530" width="9" style="10"/>
-    <col min="1531" max="1531" width="10.85546875" style="10" customWidth="1"/>
+    <col min="1531" max="1531" width="10.875" style="10" customWidth="1"/>
     <col min="1532" max="1532" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="1533" max="1533" width="10.5703125" style="10" customWidth="1"/>
-    <col min="1534" max="1534" width="10.85546875" style="10" customWidth="1"/>
+    <col min="1533" max="1533" width="10.5625" style="10" customWidth="1"/>
+    <col min="1534" max="1534" width="10.875" style="10" customWidth="1"/>
     <col min="1535" max="1779" width="9" style="10"/>
-    <col min="1780" max="1780" width="26.5703125" style="10" customWidth="1"/>
-    <col min="1781" max="1781" width="13.140625" style="10" customWidth="1"/>
+    <col min="1780" max="1780" width="26.5625" style="10" customWidth="1"/>
+    <col min="1781" max="1781" width="13.125" style="10" customWidth="1"/>
     <col min="1782" max="1786" width="9" style="10"/>
-    <col min="1787" max="1787" width="10.85546875" style="10" customWidth="1"/>
+    <col min="1787" max="1787" width="10.875" style="10" customWidth="1"/>
     <col min="1788" max="1788" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="1789" max="1789" width="10.5703125" style="10" customWidth="1"/>
-    <col min="1790" max="1790" width="10.85546875" style="10" customWidth="1"/>
+    <col min="1789" max="1789" width="10.5625" style="10" customWidth="1"/>
+    <col min="1790" max="1790" width="10.875" style="10" customWidth="1"/>
     <col min="1791" max="2035" width="9" style="10"/>
-    <col min="2036" max="2036" width="26.5703125" style="10" customWidth="1"/>
-    <col min="2037" max="2037" width="13.140625" style="10" customWidth="1"/>
+    <col min="2036" max="2036" width="26.5625" style="10" customWidth="1"/>
+    <col min="2037" max="2037" width="13.125" style="10" customWidth="1"/>
     <col min="2038" max="2042" width="9" style="10"/>
-    <col min="2043" max="2043" width="10.85546875" style="10" customWidth="1"/>
+    <col min="2043" max="2043" width="10.875" style="10" customWidth="1"/>
     <col min="2044" max="2044" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="2045" max="2045" width="10.5703125" style="10" customWidth="1"/>
-    <col min="2046" max="2046" width="10.85546875" style="10" customWidth="1"/>
+    <col min="2045" max="2045" width="10.5625" style="10" customWidth="1"/>
+    <col min="2046" max="2046" width="10.875" style="10" customWidth="1"/>
     <col min="2047" max="2291" width="9" style="10"/>
-    <col min="2292" max="2292" width="26.5703125" style="10" customWidth="1"/>
-    <col min="2293" max="2293" width="13.140625" style="10" customWidth="1"/>
+    <col min="2292" max="2292" width="26.5625" style="10" customWidth="1"/>
+    <col min="2293" max="2293" width="13.125" style="10" customWidth="1"/>
     <col min="2294" max="2298" width="9" style="10"/>
-    <col min="2299" max="2299" width="10.85546875" style="10" customWidth="1"/>
+    <col min="2299" max="2299" width="10.875" style="10" customWidth="1"/>
     <col min="2300" max="2300" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="2301" max="2301" width="10.5703125" style="10" customWidth="1"/>
-    <col min="2302" max="2302" width="10.85546875" style="10" customWidth="1"/>
+    <col min="2301" max="2301" width="10.5625" style="10" customWidth="1"/>
+    <col min="2302" max="2302" width="10.875" style="10" customWidth="1"/>
     <col min="2303" max="2547" width="9" style="10"/>
-    <col min="2548" max="2548" width="26.5703125" style="10" customWidth="1"/>
-    <col min="2549" max="2549" width="13.140625" style="10" customWidth="1"/>
+    <col min="2548" max="2548" width="26.5625" style="10" customWidth="1"/>
+    <col min="2549" max="2549" width="13.125" style="10" customWidth="1"/>
     <col min="2550" max="2554" width="9" style="10"/>
-    <col min="2555" max="2555" width="10.85546875" style="10" customWidth="1"/>
+    <col min="2555" max="2555" width="10.875" style="10" customWidth="1"/>
     <col min="2556" max="2556" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="2557" max="2557" width="10.5703125" style="10" customWidth="1"/>
-    <col min="2558" max="2558" width="10.85546875" style="10" customWidth="1"/>
+    <col min="2557" max="2557" width="10.5625" style="10" customWidth="1"/>
+    <col min="2558" max="2558" width="10.875" style="10" customWidth="1"/>
     <col min="2559" max="2803" width="9" style="10"/>
-    <col min="2804" max="2804" width="26.5703125" style="10" customWidth="1"/>
-    <col min="2805" max="2805" width="13.140625" style="10" customWidth="1"/>
+    <col min="2804" max="2804" width="26.5625" style="10" customWidth="1"/>
+    <col min="2805" max="2805" width="13.125" style="10" customWidth="1"/>
     <col min="2806" max="2810" width="9" style="10"/>
-    <col min="2811" max="2811" width="10.85546875" style="10" customWidth="1"/>
+    <col min="2811" max="2811" width="10.875" style="10" customWidth="1"/>
     <col min="2812" max="2812" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="2813" max="2813" width="10.5703125" style="10" customWidth="1"/>
-    <col min="2814" max="2814" width="10.85546875" style="10" customWidth="1"/>
+    <col min="2813" max="2813" width="10.5625" style="10" customWidth="1"/>
+    <col min="2814" max="2814" width="10.875" style="10" customWidth="1"/>
     <col min="2815" max="3059" width="9" style="10"/>
-    <col min="3060" max="3060" width="26.5703125" style="10" customWidth="1"/>
-    <col min="3061" max="3061" width="13.140625" style="10" customWidth="1"/>
+    <col min="3060" max="3060" width="26.5625" style="10" customWidth="1"/>
+    <col min="3061" max="3061" width="13.125" style="10" customWidth="1"/>
     <col min="3062" max="3066" width="9" style="10"/>
-    <col min="3067" max="3067" width="10.85546875" style="10" customWidth="1"/>
+    <col min="3067" max="3067" width="10.875" style="10" customWidth="1"/>
     <col min="3068" max="3068" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="3069" max="3069" width="10.5703125" style="10" customWidth="1"/>
-    <col min="3070" max="3070" width="10.85546875" style="10" customWidth="1"/>
+    <col min="3069" max="3069" width="10.5625" style="10" customWidth="1"/>
+    <col min="3070" max="3070" width="10.875" style="10" customWidth="1"/>
     <col min="3071" max="3315" width="9" style="10"/>
-    <col min="3316" max="3316" width="26.5703125" style="10" customWidth="1"/>
-    <col min="3317" max="3317" width="13.140625" style="10" customWidth="1"/>
+    <col min="3316" max="3316" width="26.5625" style="10" customWidth="1"/>
+    <col min="3317" max="3317" width="13.125" style="10" customWidth="1"/>
     <col min="3318" max="3322" width="9" style="10"/>
-    <col min="3323" max="3323" width="10.85546875" style="10" customWidth="1"/>
+    <col min="3323" max="3323" width="10.875" style="10" customWidth="1"/>
     <col min="3324" max="3324" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="3325" max="3325" width="10.5703125" style="10" customWidth="1"/>
-    <col min="3326" max="3326" width="10.85546875" style="10" customWidth="1"/>
+    <col min="3325" max="3325" width="10.5625" style="10" customWidth="1"/>
+    <col min="3326" max="3326" width="10.875" style="10" customWidth="1"/>
     <col min="3327" max="3571" width="9" style="10"/>
-    <col min="3572" max="3572" width="26.5703125" style="10" customWidth="1"/>
-    <col min="3573" max="3573" width="13.140625" style="10" customWidth="1"/>
+    <col min="3572" max="3572" width="26.5625" style="10" customWidth="1"/>
+    <col min="3573" max="3573" width="13.125" style="10" customWidth="1"/>
     <col min="3574" max="3578" width="9" style="10"/>
-    <col min="3579" max="3579" width="10.85546875" style="10" customWidth="1"/>
+    <col min="3579" max="3579" width="10.875" style="10" customWidth="1"/>
     <col min="3580" max="3580" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="3581" max="3581" width="10.5703125" style="10" customWidth="1"/>
-    <col min="3582" max="3582" width="10.85546875" style="10" customWidth="1"/>
+    <col min="3581" max="3581" width="10.5625" style="10" customWidth="1"/>
+    <col min="3582" max="3582" width="10.875" style="10" customWidth="1"/>
     <col min="3583" max="3827" width="9" style="10"/>
-    <col min="3828" max="3828" width="26.5703125" style="10" customWidth="1"/>
-    <col min="3829" max="3829" width="13.140625" style="10" customWidth="1"/>
+    <col min="3828" max="3828" width="26.5625" style="10" customWidth="1"/>
+    <col min="3829" max="3829" width="13.125" style="10" customWidth="1"/>
     <col min="3830" max="3834" width="9" style="10"/>
-    <col min="3835" max="3835" width="10.85546875" style="10" customWidth="1"/>
+    <col min="3835" max="3835" width="10.875" style="10" customWidth="1"/>
     <col min="3836" max="3836" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="3837" max="3837" width="10.5703125" style="10" customWidth="1"/>
-    <col min="3838" max="3838" width="10.85546875" style="10" customWidth="1"/>
+    <col min="3837" max="3837" width="10.5625" style="10" customWidth="1"/>
+    <col min="3838" max="3838" width="10.875" style="10" customWidth="1"/>
     <col min="3839" max="4083" width="9" style="10"/>
-    <col min="4084" max="4084" width="26.5703125" style="10" customWidth="1"/>
-    <col min="4085" max="4085" width="13.140625" style="10" customWidth="1"/>
+    <col min="4084" max="4084" width="26.5625" style="10" customWidth="1"/>
+    <col min="4085" max="4085" width="13.125" style="10" customWidth="1"/>
     <col min="4086" max="4090" width="9" style="10"/>
-    <col min="4091" max="4091" width="10.85546875" style="10" customWidth="1"/>
+    <col min="4091" max="4091" width="10.875" style="10" customWidth="1"/>
     <col min="4092" max="4092" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="4093" max="4093" width="10.5703125" style="10" customWidth="1"/>
-    <col min="4094" max="4094" width="10.85546875" style="10" customWidth="1"/>
+    <col min="4093" max="4093" width="10.5625" style="10" customWidth="1"/>
+    <col min="4094" max="4094" width="10.875" style="10" customWidth="1"/>
     <col min="4095" max="4339" width="9" style="10"/>
-    <col min="4340" max="4340" width="26.5703125" style="10" customWidth="1"/>
-    <col min="4341" max="4341" width="13.140625" style="10" customWidth="1"/>
+    <col min="4340" max="4340" width="26.5625" style="10" customWidth="1"/>
+    <col min="4341" max="4341" width="13.125" style="10" customWidth="1"/>
     <col min="4342" max="4346" width="9" style="10"/>
-    <col min="4347" max="4347" width="10.85546875" style="10" customWidth="1"/>
+    <col min="4347" max="4347" width="10.875" style="10" customWidth="1"/>
     <col min="4348" max="4348" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="4349" max="4349" width="10.5703125" style="10" customWidth="1"/>
-    <col min="4350" max="4350" width="10.85546875" style="10" customWidth="1"/>
+    <col min="4349" max="4349" width="10.5625" style="10" customWidth="1"/>
+    <col min="4350" max="4350" width="10.875" style="10" customWidth="1"/>
     <col min="4351" max="4595" width="9" style="10"/>
-    <col min="4596" max="4596" width="26.5703125" style="10" customWidth="1"/>
-    <col min="4597" max="4597" width="13.140625" style="10" customWidth="1"/>
+    <col min="4596" max="4596" width="26.5625" style="10" customWidth="1"/>
+    <col min="4597" max="4597" width="13.125" style="10" customWidth="1"/>
     <col min="4598" max="4602" width="9" style="10"/>
-    <col min="4603" max="4603" width="10.85546875" style="10" customWidth="1"/>
+    <col min="4603" max="4603" width="10.875" style="10" customWidth="1"/>
     <col min="4604" max="4604" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="4605" max="4605" width="10.5703125" style="10" customWidth="1"/>
-    <col min="4606" max="4606" width="10.85546875" style="10" customWidth="1"/>
+    <col min="4605" max="4605" width="10.5625" style="10" customWidth="1"/>
+    <col min="4606" max="4606" width="10.875" style="10" customWidth="1"/>
     <col min="4607" max="4851" width="9" style="10"/>
-    <col min="4852" max="4852" width="26.5703125" style="10" customWidth="1"/>
-    <col min="4853" max="4853" width="13.140625" style="10" customWidth="1"/>
+    <col min="4852" max="4852" width="26.5625" style="10" customWidth="1"/>
+    <col min="4853" max="4853" width="13.125" style="10" customWidth="1"/>
     <col min="4854" max="4858" width="9" style="10"/>
-    <col min="4859" max="4859" width="10.85546875" style="10" customWidth="1"/>
+    <col min="4859" max="4859" width="10.875" style="10" customWidth="1"/>
     <col min="4860" max="4860" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="4861" max="4861" width="10.5703125" style="10" customWidth="1"/>
-    <col min="4862" max="4862" width="10.85546875" style="10" customWidth="1"/>
+    <col min="4861" max="4861" width="10.5625" style="10" customWidth="1"/>
+    <col min="4862" max="4862" width="10.875" style="10" customWidth="1"/>
     <col min="4863" max="5107" width="9" style="10"/>
-    <col min="5108" max="5108" width="26.5703125" style="10" customWidth="1"/>
-    <col min="5109" max="5109" width="13.140625" style="10" customWidth="1"/>
+    <col min="5108" max="5108" width="26.5625" style="10" customWidth="1"/>
+    <col min="5109" max="5109" width="13.125" style="10" customWidth="1"/>
     <col min="5110" max="5114" width="9" style="10"/>
-    <col min="5115" max="5115" width="10.85546875" style="10" customWidth="1"/>
+    <col min="5115" max="5115" width="10.875" style="10" customWidth="1"/>
     <col min="5116" max="5116" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="5117" max="5117" width="10.5703125" style="10" customWidth="1"/>
-    <col min="5118" max="5118" width="10.85546875" style="10" customWidth="1"/>
+    <col min="5117" max="5117" width="10.5625" style="10" customWidth="1"/>
+    <col min="5118" max="5118" width="10.875" style="10" customWidth="1"/>
     <col min="5119" max="5363" width="9" style="10"/>
-    <col min="5364" max="5364" width="26.5703125" style="10" customWidth="1"/>
-    <col min="5365" max="5365" width="13.140625" style="10" customWidth="1"/>
+    <col min="5364" max="5364" width="26.5625" style="10" customWidth="1"/>
+    <col min="5365" max="5365" width="13.125" style="10" customWidth="1"/>
     <col min="5366" max="5370" width="9" style="10"/>
-    <col min="5371" max="5371" width="10.85546875" style="10" customWidth="1"/>
+    <col min="5371" max="5371" width="10.875" style="10" customWidth="1"/>
     <col min="5372" max="5372" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="5373" max="5373" width="10.5703125" style="10" customWidth="1"/>
-    <col min="5374" max="5374" width="10.85546875" style="10" customWidth="1"/>
+    <col min="5373" max="5373" width="10.5625" style="10" customWidth="1"/>
+    <col min="5374" max="5374" width="10.875" style="10" customWidth="1"/>
     <col min="5375" max="5619" width="9" style="10"/>
-    <col min="5620" max="5620" width="26.5703125" style="10" customWidth="1"/>
-    <col min="5621" max="5621" width="13.140625" style="10" customWidth="1"/>
+    <col min="5620" max="5620" width="26.5625" style="10" customWidth="1"/>
+    <col min="5621" max="5621" width="13.125" style="10" customWidth="1"/>
     <col min="5622" max="5626" width="9" style="10"/>
-    <col min="5627" max="5627" width="10.85546875" style="10" customWidth="1"/>
+    <col min="5627" max="5627" width="10.875" style="10" customWidth="1"/>
     <col min="5628" max="5628" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="5629" max="5629" width="10.5703125" style="10" customWidth="1"/>
-    <col min="5630" max="5630" width="10.85546875" style="10" customWidth="1"/>
+    <col min="5629" max="5629" width="10.5625" style="10" customWidth="1"/>
+    <col min="5630" max="5630" width="10.875" style="10" customWidth="1"/>
     <col min="5631" max="5875" width="9" style="10"/>
-    <col min="5876" max="5876" width="26.5703125" style="10" customWidth="1"/>
-    <col min="5877" max="5877" width="13.140625" style="10" customWidth="1"/>
+    <col min="5876" max="5876" width="26.5625" style="10" customWidth="1"/>
+    <col min="5877" max="5877" width="13.125" style="10" customWidth="1"/>
     <col min="5878" max="5882" width="9" style="10"/>
-    <col min="5883" max="5883" width="10.85546875" style="10" customWidth="1"/>
+    <col min="5883" max="5883" width="10.875" style="10" customWidth="1"/>
     <col min="5884" max="5884" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="5885" max="5885" width="10.5703125" style="10" customWidth="1"/>
-    <col min="5886" max="5886" width="10.85546875" style="10" customWidth="1"/>
+    <col min="5885" max="5885" width="10.5625" style="10" customWidth="1"/>
+    <col min="5886" max="5886" width="10.875" style="10" customWidth="1"/>
     <col min="5887" max="6131" width="9" style="10"/>
-    <col min="6132" max="6132" width="26.5703125" style="10" customWidth="1"/>
-    <col min="6133" max="6133" width="13.140625" style="10" customWidth="1"/>
+    <col min="6132" max="6132" width="26.5625" style="10" customWidth="1"/>
+    <col min="6133" max="6133" width="13.125" style="10" customWidth="1"/>
     <col min="6134" max="6138" width="9" style="10"/>
-    <col min="6139" max="6139" width="10.85546875" style="10" customWidth="1"/>
+    <col min="6139" max="6139" width="10.875" style="10" customWidth="1"/>
     <col min="6140" max="6140" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="6141" max="6141" width="10.5703125" style="10" customWidth="1"/>
-    <col min="6142" max="6142" width="10.85546875" style="10" customWidth="1"/>
+    <col min="6141" max="6141" width="10.5625" style="10" customWidth="1"/>
+    <col min="6142" max="6142" width="10.875" style="10" customWidth="1"/>
     <col min="6143" max="6387" width="9" style="10"/>
-    <col min="6388" max="6388" width="26.5703125" style="10" customWidth="1"/>
-    <col min="6389" max="6389" width="13.140625" style="10" customWidth="1"/>
+    <col min="6388" max="6388" width="26.5625" style="10" customWidth="1"/>
+    <col min="6389" max="6389" width="13.125" style="10" customWidth="1"/>
     <col min="6390" max="6394" width="9" style="10"/>
-    <col min="6395" max="6395" width="10.85546875" style="10" customWidth="1"/>
+    <col min="6395" max="6395" width="10.875" style="10" customWidth="1"/>
     <col min="6396" max="6396" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="6397" max="6397" width="10.5703125" style="10" customWidth="1"/>
-    <col min="6398" max="6398" width="10.85546875" style="10" customWidth="1"/>
+    <col min="6397" max="6397" width="10.5625" style="10" customWidth="1"/>
+    <col min="6398" max="6398" width="10.875" style="10" customWidth="1"/>
     <col min="6399" max="6643" width="9" style="10"/>
-    <col min="6644" max="6644" width="26.5703125" style="10" customWidth="1"/>
-    <col min="6645" max="6645" width="13.140625" style="10" customWidth="1"/>
+    <col min="6644" max="6644" width="26.5625" style="10" customWidth="1"/>
+    <col min="6645" max="6645" width="13.125" style="10" customWidth="1"/>
     <col min="6646" max="6650" width="9" style="10"/>
-    <col min="6651" max="6651" width="10.85546875" style="10" customWidth="1"/>
+    <col min="6651" max="6651" width="10.875" style="10" customWidth="1"/>
     <col min="6652" max="6652" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="6653" max="6653" width="10.5703125" style="10" customWidth="1"/>
-    <col min="6654" max="6654" width="10.85546875" style="10" customWidth="1"/>
+    <col min="6653" max="6653" width="10.5625" style="10" customWidth="1"/>
+    <col min="6654" max="6654" width="10.875" style="10" customWidth="1"/>
     <col min="6655" max="6899" width="9" style="10"/>
-    <col min="6900" max="6900" width="26.5703125" style="10" customWidth="1"/>
-    <col min="6901" max="6901" width="13.140625" style="10" customWidth="1"/>
+    <col min="6900" max="6900" width="26.5625" style="10" customWidth="1"/>
+    <col min="6901" max="6901" width="13.125" style="10" customWidth="1"/>
     <col min="6902" max="6906" width="9" style="10"/>
-    <col min="6907" max="6907" width="10.85546875" style="10" customWidth="1"/>
+    <col min="6907" max="6907" width="10.875" style="10" customWidth="1"/>
     <col min="6908" max="6908" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="6909" max="6909" width="10.5703125" style="10" customWidth="1"/>
-    <col min="6910" max="6910" width="10.85546875" style="10" customWidth="1"/>
+    <col min="6909" max="6909" width="10.5625" style="10" customWidth="1"/>
+    <col min="6910" max="6910" width="10.875" style="10" customWidth="1"/>
     <col min="6911" max="7155" width="9" style="10"/>
-    <col min="7156" max="7156" width="26.5703125" style="10" customWidth="1"/>
-    <col min="7157" max="7157" width="13.140625" style="10" customWidth="1"/>
+    <col min="7156" max="7156" width="26.5625" style="10" customWidth="1"/>
+    <col min="7157" max="7157" width="13.125" style="10" customWidth="1"/>
     <col min="7158" max="7162" width="9" style="10"/>
-    <col min="7163" max="7163" width="10.85546875" style="10" customWidth="1"/>
+    <col min="7163" max="7163" width="10.875" style="10" customWidth="1"/>
     <col min="7164" max="7164" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="7165" max="7165" width="10.5703125" style="10" customWidth="1"/>
-    <col min="7166" max="7166" width="10.85546875" style="10" customWidth="1"/>
+    <col min="7165" max="7165" width="10.5625" style="10" customWidth="1"/>
+    <col min="7166" max="7166" width="10.875" style="10" customWidth="1"/>
     <col min="7167" max="7411" width="9" style="10"/>
-    <col min="7412" max="7412" width="26.5703125" style="10" customWidth="1"/>
-    <col min="7413" max="7413" width="13.140625" style="10" customWidth="1"/>
+    <col min="7412" max="7412" width="26.5625" style="10" customWidth="1"/>
+    <col min="7413" max="7413" width="13.125" style="10" customWidth="1"/>
     <col min="7414" max="7418" width="9" style="10"/>
-    <col min="7419" max="7419" width="10.85546875" style="10" customWidth="1"/>
+    <col min="7419" max="7419" width="10.875" style="10" customWidth="1"/>
     <col min="7420" max="7420" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="7421" max="7421" width="10.5703125" style="10" customWidth="1"/>
-    <col min="7422" max="7422" width="10.85546875" style="10" customWidth="1"/>
+    <col min="7421" max="7421" width="10.5625" style="10" customWidth="1"/>
+    <col min="7422" max="7422" width="10.875" style="10" customWidth="1"/>
     <col min="7423" max="7667" width="9" style="10"/>
-    <col min="7668" max="7668" width="26.5703125" style="10" customWidth="1"/>
-    <col min="7669" max="7669" width="13.140625" style="10" customWidth="1"/>
+    <col min="7668" max="7668" width="26.5625" style="10" customWidth="1"/>
+    <col min="7669" max="7669" width="13.125" style="10" customWidth="1"/>
     <col min="7670" max="7674" width="9" style="10"/>
-    <col min="7675" max="7675" width="10.85546875" style="10" customWidth="1"/>
+    <col min="7675" max="7675" width="10.875" style="10" customWidth="1"/>
     <col min="7676" max="7676" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="7677" max="7677" width="10.5703125" style="10" customWidth="1"/>
-    <col min="7678" max="7678" width="10.85546875" style="10" customWidth="1"/>
+    <col min="7677" max="7677" width="10.5625" style="10" customWidth="1"/>
+    <col min="7678" max="7678" width="10.875" style="10" customWidth="1"/>
     <col min="7679" max="7923" width="9" style="10"/>
-    <col min="7924" max="7924" width="26.5703125" style="10" customWidth="1"/>
-    <col min="7925" max="7925" width="13.140625" style="10" customWidth="1"/>
+    <col min="7924" max="7924" width="26.5625" style="10" customWidth="1"/>
+    <col min="7925" max="7925" width="13.125" style="10" customWidth="1"/>
     <col min="7926" max="7930" width="9" style="10"/>
-    <col min="7931" max="7931" width="10.85546875" style="10" customWidth="1"/>
+    <col min="7931" max="7931" width="10.875" style="10" customWidth="1"/>
     <col min="7932" max="7932" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="7933" max="7933" width="10.5703125" style="10" customWidth="1"/>
-    <col min="7934" max="7934" width="10.85546875" style="10" customWidth="1"/>
+    <col min="7933" max="7933" width="10.5625" style="10" customWidth="1"/>
+    <col min="7934" max="7934" width="10.875" style="10" customWidth="1"/>
     <col min="7935" max="8179" width="9" style="10"/>
-    <col min="8180" max="8180" width="26.5703125" style="10" customWidth="1"/>
-    <col min="8181" max="8181" width="13.140625" style="10" customWidth="1"/>
+    <col min="8180" max="8180" width="26.5625" style="10" customWidth="1"/>
+    <col min="8181" max="8181" width="13.125" style="10" customWidth="1"/>
     <col min="8182" max="8186" width="9" style="10"/>
-    <col min="8187" max="8187" width="10.85546875" style="10" customWidth="1"/>
+    <col min="8187" max="8187" width="10.875" style="10" customWidth="1"/>
     <col min="8188" max="8188" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="8189" max="8189" width="10.5703125" style="10" customWidth="1"/>
-    <col min="8190" max="8190" width="10.85546875" style="10" customWidth="1"/>
+    <col min="8189" max="8189" width="10.5625" style="10" customWidth="1"/>
+    <col min="8190" max="8190" width="10.875" style="10" customWidth="1"/>
     <col min="8191" max="8435" width="9" style="10"/>
-    <col min="8436" max="8436" width="26.5703125" style="10" customWidth="1"/>
-    <col min="8437" max="8437" width="13.140625" style="10" customWidth="1"/>
+    <col min="8436" max="8436" width="26.5625" style="10" customWidth="1"/>
+    <col min="8437" max="8437" width="13.125" style="10" customWidth="1"/>
     <col min="8438" max="8442" width="9" style="10"/>
-    <col min="8443" max="8443" width="10.85546875" style="10" customWidth="1"/>
+    <col min="8443" max="8443" width="10.875" style="10" customWidth="1"/>
     <col min="8444" max="8444" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="8445" max="8445" width="10.5703125" style="10" customWidth="1"/>
-    <col min="8446" max="8446" width="10.85546875" style="10" customWidth="1"/>
+    <col min="8445" max="8445" width="10.5625" style="10" customWidth="1"/>
+    <col min="8446" max="8446" width="10.875" style="10" customWidth="1"/>
     <col min="8447" max="8691" width="9" style="10"/>
-    <col min="8692" max="8692" width="26.5703125" style="10" customWidth="1"/>
-    <col min="8693" max="8693" width="13.140625" style="10" customWidth="1"/>
+    <col min="8692" max="8692" width="26.5625" style="10" customWidth="1"/>
+    <col min="8693" max="8693" width="13.125" style="10" customWidth="1"/>
     <col min="8694" max="8698" width="9" style="10"/>
-    <col min="8699" max="8699" width="10.85546875" style="10" customWidth="1"/>
+    <col min="8699" max="8699" width="10.875" style="10" customWidth="1"/>
     <col min="8700" max="8700" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="8701" max="8701" width="10.5703125" style="10" customWidth="1"/>
-    <col min="8702" max="8702" width="10.85546875" style="10" customWidth="1"/>
+    <col min="8701" max="8701" width="10.5625" style="10" customWidth="1"/>
+    <col min="8702" max="8702" width="10.875" style="10" customWidth="1"/>
     <col min="8703" max="8947" width="9" style="10"/>
-    <col min="8948" max="8948" width="26.5703125" style="10" customWidth="1"/>
-    <col min="8949" max="8949" width="13.140625" style="10" customWidth="1"/>
+    <col min="8948" max="8948" width="26.5625" style="10" customWidth="1"/>
+    <col min="8949" max="8949" width="13.125" style="10" customWidth="1"/>
     <col min="8950" max="8954" width="9" style="10"/>
-    <col min="8955" max="8955" width="10.85546875" style="10" customWidth="1"/>
+    <col min="8955" max="8955" width="10.875" style="10" customWidth="1"/>
     <col min="8956" max="8956" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="8957" max="8957" width="10.5703125" style="10" customWidth="1"/>
-    <col min="8958" max="8958" width="10.85546875" style="10" customWidth="1"/>
+    <col min="8957" max="8957" width="10.5625" style="10" customWidth="1"/>
+    <col min="8958" max="8958" width="10.875" style="10" customWidth="1"/>
     <col min="8959" max="9203" width="9" style="10"/>
-    <col min="9204" max="9204" width="26.5703125" style="10" customWidth="1"/>
-    <col min="9205" max="9205" width="13.140625" style="10" customWidth="1"/>
+    <col min="9204" max="9204" width="26.5625" style="10" customWidth="1"/>
+    <col min="9205" max="9205" width="13.125" style="10" customWidth="1"/>
     <col min="9206" max="9210" width="9" style="10"/>
-    <col min="9211" max="9211" width="10.85546875" style="10" customWidth="1"/>
+    <col min="9211" max="9211" width="10.875" style="10" customWidth="1"/>
     <col min="9212" max="9212" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="9213" max="9213" width="10.5703125" style="10" customWidth="1"/>
-    <col min="9214" max="9214" width="10.85546875" style="10" customWidth="1"/>
+    <col min="9213" max="9213" width="10.5625" style="10" customWidth="1"/>
+    <col min="9214" max="9214" width="10.875" style="10" customWidth="1"/>
     <col min="9215" max="9459" width="9" style="10"/>
-    <col min="9460" max="9460" width="26.5703125" style="10" customWidth="1"/>
-    <col min="9461" max="9461" width="13.140625" style="10" customWidth="1"/>
+    <col min="9460" max="9460" width="26.5625" style="10" customWidth="1"/>
+    <col min="9461" max="9461" width="13.125" style="10" customWidth="1"/>
     <col min="9462" max="9466" width="9" style="10"/>
-    <col min="9467" max="9467" width="10.85546875" style="10" customWidth="1"/>
+    <col min="9467" max="9467" width="10.875" style="10" customWidth="1"/>
     <col min="9468" max="9468" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="9469" max="9469" width="10.5703125" style="10" customWidth="1"/>
-    <col min="9470" max="9470" width="10.85546875" style="10" customWidth="1"/>
+    <col min="9469" max="9469" width="10.5625" style="10" customWidth="1"/>
+    <col min="9470" max="9470" width="10.875" style="10" customWidth="1"/>
     <col min="9471" max="9715" width="9" style="10"/>
-    <col min="9716" max="9716" width="26.5703125" style="10" customWidth="1"/>
-    <col min="9717" max="9717" width="13.140625" style="10" customWidth="1"/>
+    <col min="9716" max="9716" width="26.5625" style="10" customWidth="1"/>
+    <col min="9717" max="9717" width="13.125" style="10" customWidth="1"/>
     <col min="9718" max="9722" width="9" style="10"/>
-    <col min="9723" max="9723" width="10.85546875" style="10" customWidth="1"/>
+    <col min="9723" max="9723" width="10.875" style="10" customWidth="1"/>
     <col min="9724" max="9724" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="9725" max="9725" width="10.5703125" style="10" customWidth="1"/>
-    <col min="9726" max="9726" width="10.85546875" style="10" customWidth="1"/>
+    <col min="9725" max="9725" width="10.5625" style="10" customWidth="1"/>
+    <col min="9726" max="9726" width="10.875" style="10" customWidth="1"/>
     <col min="9727" max="9971" width="9" style="10"/>
-    <col min="9972" max="9972" width="26.5703125" style="10" customWidth="1"/>
-    <col min="9973" max="9973" width="13.140625" style="10" customWidth="1"/>
+    <col min="9972" max="9972" width="26.5625" style="10" customWidth="1"/>
+    <col min="9973" max="9973" width="13.125" style="10" customWidth="1"/>
     <col min="9974" max="9978" width="9" style="10"/>
-    <col min="9979" max="9979" width="10.85546875" style="10" customWidth="1"/>
+    <col min="9979" max="9979" width="10.875" style="10" customWidth="1"/>
     <col min="9980" max="9980" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="9981" max="9981" width="10.5703125" style="10" customWidth="1"/>
-    <col min="9982" max="9982" width="10.85546875" style="10" customWidth="1"/>
+    <col min="9981" max="9981" width="10.5625" style="10" customWidth="1"/>
+    <col min="9982" max="9982" width="10.875" style="10" customWidth="1"/>
     <col min="9983" max="10227" width="9" style="10"/>
-    <col min="10228" max="10228" width="26.5703125" style="10" customWidth="1"/>
-    <col min="10229" max="10229" width="13.140625" style="10" customWidth="1"/>
+    <col min="10228" max="10228" width="26.5625" style="10" customWidth="1"/>
+    <col min="10229" max="10229" width="13.125" style="10" customWidth="1"/>
     <col min="10230" max="10234" width="9" style="10"/>
-    <col min="10235" max="10235" width="10.85546875" style="10" customWidth="1"/>
+    <col min="10235" max="10235" width="10.875" style="10" customWidth="1"/>
     <col min="10236" max="10236" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="10237" max="10237" width="10.5703125" style="10" customWidth="1"/>
-    <col min="10238" max="10238" width="10.85546875" style="10" customWidth="1"/>
+    <col min="10237" max="10237" width="10.5625" style="10" customWidth="1"/>
+    <col min="10238" max="10238" width="10.875" style="10" customWidth="1"/>
     <col min="10239" max="10483" width="9" style="10"/>
-    <col min="10484" max="10484" width="26.5703125" style="10" customWidth="1"/>
-    <col min="10485" max="10485" width="13.140625" style="10" customWidth="1"/>
+    <col min="10484" max="10484" width="26.5625" style="10" customWidth="1"/>
+    <col min="10485" max="10485" width="13.125" style="10" customWidth="1"/>
     <col min="10486" max="10490" width="9" style="10"/>
-    <col min="10491" max="10491" width="10.85546875" style="10" customWidth="1"/>
+    <col min="10491" max="10491" width="10.875" style="10" customWidth="1"/>
     <col min="10492" max="10492" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="10493" max="10493" width="10.5703125" style="10" customWidth="1"/>
-    <col min="10494" max="10494" width="10.85546875" style="10" customWidth="1"/>
+    <col min="10493" max="10493" width="10.5625" style="10" customWidth="1"/>
+    <col min="10494" max="10494" width="10.875" style="10" customWidth="1"/>
     <col min="10495" max="10739" width="9" style="10"/>
-    <col min="10740" max="10740" width="26.5703125" style="10" customWidth="1"/>
-    <col min="10741" max="10741" width="13.140625" style="10" customWidth="1"/>
+    <col min="10740" max="10740" width="26.5625" style="10" customWidth="1"/>
+    <col min="10741" max="10741" width="13.125" style="10" customWidth="1"/>
     <col min="10742" max="10746" width="9" style="10"/>
-    <col min="10747" max="10747" width="10.85546875" style="10" customWidth="1"/>
+    <col min="10747" max="10747" width="10.875" style="10" customWidth="1"/>
     <col min="10748" max="10748" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="10749" max="10749" width="10.5703125" style="10" customWidth="1"/>
-    <col min="10750" max="10750" width="10.85546875" style="10" customWidth="1"/>
+    <col min="10749" max="10749" width="10.5625" style="10" customWidth="1"/>
+    <col min="10750" max="10750" width="10.875" style="10" customWidth="1"/>
     <col min="10751" max="10995" width="9" style="10"/>
-    <col min="10996" max="10996" width="26.5703125" style="10" customWidth="1"/>
-    <col min="10997" max="10997" width="13.140625" style="10" customWidth="1"/>
+    <col min="10996" max="10996" width="26.5625" style="10" customWidth="1"/>
+    <col min="10997" max="10997" width="13.125" style="10" customWidth="1"/>
     <col min="10998" max="11002" width="9" style="10"/>
-    <col min="11003" max="11003" width="10.85546875" style="10" customWidth="1"/>
+    <col min="11003" max="11003" width="10.875" style="10" customWidth="1"/>
     <col min="11004" max="11004" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="11005" max="11005" width="10.5703125" style="10" customWidth="1"/>
-    <col min="11006" max="11006" width="10.85546875" style="10" customWidth="1"/>
+    <col min="11005" max="11005" width="10.5625" style="10" customWidth="1"/>
+    <col min="11006" max="11006" width="10.875" style="10" customWidth="1"/>
     <col min="11007" max="11251" width="9" style="10"/>
-    <col min="11252" max="11252" width="26.5703125" style="10" customWidth="1"/>
-    <col min="11253" max="11253" width="13.140625" style="10" customWidth="1"/>
+    <col min="11252" max="11252" width="26.5625" style="10" customWidth="1"/>
+    <col min="11253" max="11253" width="13.125" style="10" customWidth="1"/>
     <col min="11254" max="11258" width="9" style="10"/>
-    <col min="11259" max="11259" width="10.85546875" style="10" customWidth="1"/>
+    <col min="11259" max="11259" width="10.875" style="10" customWidth="1"/>
     <col min="11260" max="11260" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="11261" max="11261" width="10.5703125" style="10" customWidth="1"/>
-    <col min="11262" max="11262" width="10.85546875" style="10" customWidth="1"/>
+    <col min="11261" max="11261" width="10.5625" style="10" customWidth="1"/>
+    <col min="11262" max="11262" width="10.875" style="10" customWidth="1"/>
     <col min="11263" max="11507" width="9" style="10"/>
-    <col min="11508" max="11508" width="26.5703125" style="10" customWidth="1"/>
-    <col min="11509" max="11509" width="13.140625" style="10" customWidth="1"/>
+    <col min="11508" max="11508" width="26.5625" style="10" customWidth="1"/>
+    <col min="11509" max="11509" width="13.125" style="10" customWidth="1"/>
     <col min="11510" max="11514" width="9" style="10"/>
-    <col min="11515" max="11515" width="10.85546875" style="10" customWidth="1"/>
+    <col min="11515" max="11515" width="10.875" style="10" customWidth="1"/>
     <col min="11516" max="11516" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="11517" max="11517" width="10.5703125" style="10" customWidth="1"/>
-    <col min="11518" max="11518" width="10.85546875" style="10" customWidth="1"/>
+    <col min="11517" max="11517" width="10.5625" style="10" customWidth="1"/>
+    <col min="11518" max="11518" width="10.875" style="10" customWidth="1"/>
     <col min="11519" max="11763" width="9" style="10"/>
-    <col min="11764" max="11764" width="26.5703125" style="10" customWidth="1"/>
-    <col min="11765" max="11765" width="13.140625" style="10" customWidth="1"/>
+    <col min="11764" max="11764" width="26.5625" style="10" customWidth="1"/>
+    <col min="11765" max="11765" width="13.125" style="10" customWidth="1"/>
     <col min="11766" max="11770" width="9" style="10"/>
-    <col min="11771" max="11771" width="10.85546875" style="10" customWidth="1"/>
+    <col min="11771" max="11771" width="10.875" style="10" customWidth="1"/>
     <col min="11772" max="11772" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="11773" max="11773" width="10.5703125" style="10" customWidth="1"/>
-    <col min="11774" max="11774" width="10.85546875" style="10" customWidth="1"/>
+    <col min="11773" max="11773" width="10.5625" style="10" customWidth="1"/>
+    <col min="11774" max="11774" width="10.875" style="10" customWidth="1"/>
     <col min="11775" max="12019" width="9" style="10"/>
-    <col min="12020" max="12020" width="26.5703125" style="10" customWidth="1"/>
-    <col min="12021" max="12021" width="13.140625" style="10" customWidth="1"/>
+    <col min="12020" max="12020" width="26.5625" style="10" customWidth="1"/>
+    <col min="12021" max="12021" width="13.125" style="10" customWidth="1"/>
     <col min="12022" max="12026" width="9" style="10"/>
-    <col min="12027" max="12027" width="10.85546875" style="10" customWidth="1"/>
+    <col min="12027" max="12027" width="10.875" style="10" customWidth="1"/>
     <col min="12028" max="12028" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="12029" max="12029" width="10.5703125" style="10" customWidth="1"/>
-    <col min="12030" max="12030" width="10.85546875" style="10" customWidth="1"/>
+    <col min="12029" max="12029" width="10.5625" style="10" customWidth="1"/>
+    <col min="12030" max="12030" width="10.875" style="10" customWidth="1"/>
     <col min="12031" max="12275" width="9" style="10"/>
-    <col min="12276" max="12276" width="26.5703125" style="10" customWidth="1"/>
-    <col min="12277" max="12277" width="13.140625" style="10" customWidth="1"/>
+    <col min="12276" max="12276" width="26.5625" style="10" customWidth="1"/>
+    <col min="12277" max="12277" width="13.125" style="10" customWidth="1"/>
     <col min="12278" max="12282" width="9" style="10"/>
-    <col min="12283" max="12283" width="10.85546875" style="10" customWidth="1"/>
+    <col min="12283" max="12283" width="10.875" style="10" customWidth="1"/>
     <col min="12284" max="12284" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="12285" max="12285" width="10.5703125" style="10" customWidth="1"/>
-    <col min="12286" max="12286" width="10.85546875" style="10" customWidth="1"/>
+    <col min="12285" max="12285" width="10.5625" style="10" customWidth="1"/>
+    <col min="12286" max="12286" width="10.875" style="10" customWidth="1"/>
     <col min="12287" max="12531" width="9" style="10"/>
-    <col min="12532" max="12532" width="26.5703125" style="10" customWidth="1"/>
-    <col min="12533" max="12533" width="13.140625" style="10" customWidth="1"/>
+    <col min="12532" max="12532" width="26.5625" style="10" customWidth="1"/>
+    <col min="12533" max="12533" width="13.125" style="10" customWidth="1"/>
     <col min="12534" max="12538" width="9" style="10"/>
-    <col min="12539" max="12539" width="10.85546875" style="10" customWidth="1"/>
+    <col min="12539" max="12539" width="10.875" style="10" customWidth="1"/>
     <col min="12540" max="12540" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="12541" max="12541" width="10.5703125" style="10" customWidth="1"/>
-    <col min="12542" max="12542" width="10.85546875" style="10" customWidth="1"/>
+    <col min="12541" max="12541" width="10.5625" style="10" customWidth="1"/>
+    <col min="12542" max="12542" width="10.875" style="10" customWidth="1"/>
     <col min="12543" max="12787" width="9" style="10"/>
-    <col min="12788" max="12788" width="26.5703125" style="10" customWidth="1"/>
-    <col min="12789" max="12789" width="13.140625" style="10" customWidth="1"/>
+    <col min="12788" max="12788" width="26.5625" style="10" customWidth="1"/>
+    <col min="12789" max="12789" width="13.125" style="10" customWidth="1"/>
     <col min="12790" max="12794" width="9" style="10"/>
-    <col min="12795" max="12795" width="10.85546875" style="10" customWidth="1"/>
+    <col min="12795" max="12795" width="10.875" style="10" customWidth="1"/>
     <col min="12796" max="12796" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="12797" max="12797" width="10.5703125" style="10" customWidth="1"/>
-    <col min="12798" max="12798" width="10.85546875" style="10" customWidth="1"/>
+    <col min="12797" max="12797" width="10.5625" style="10" customWidth="1"/>
+    <col min="12798" max="12798" width="10.875" style="10" customWidth="1"/>
     <col min="12799" max="13043" width="9" style="10"/>
-    <col min="13044" max="13044" width="26.5703125" style="10" customWidth="1"/>
-    <col min="13045" max="13045" width="13.140625" style="10" customWidth="1"/>
+    <col min="13044" max="13044" width="26.5625" style="10" customWidth="1"/>
+    <col min="13045" max="13045" width="13.125" style="10" customWidth="1"/>
     <col min="13046" max="13050" width="9" style="10"/>
-    <col min="13051" max="13051" width="10.85546875" style="10" customWidth="1"/>
+    <col min="13051" max="13051" width="10.875" style="10" customWidth="1"/>
     <col min="13052" max="13052" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="13053" max="13053" width="10.5703125" style="10" customWidth="1"/>
-    <col min="13054" max="13054" width="10.85546875" style="10" customWidth="1"/>
+    <col min="13053" max="13053" width="10.5625" style="10" customWidth="1"/>
+    <col min="13054" max="13054" width="10.875" style="10" customWidth="1"/>
     <col min="13055" max="13299" width="9" style="10"/>
-    <col min="13300" max="13300" width="26.5703125" style="10" customWidth="1"/>
-    <col min="13301" max="13301" width="13.140625" style="10" customWidth="1"/>
+    <col min="13300" max="13300" width="26.5625" style="10" customWidth="1"/>
+    <col min="13301" max="13301" width="13.125" style="10" customWidth="1"/>
     <col min="13302" max="13306" width="9" style="10"/>
-    <col min="13307" max="13307" width="10.85546875" style="10" customWidth="1"/>
+    <col min="13307" max="13307" width="10.875" style="10" customWidth="1"/>
     <col min="13308" max="13308" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="13309" max="13309" width="10.5703125" style="10" customWidth="1"/>
-    <col min="13310" max="13310" width="10.85546875" style="10" customWidth="1"/>
+    <col min="13309" max="13309" width="10.5625" style="10" customWidth="1"/>
+    <col min="13310" max="13310" width="10.875" style="10" customWidth="1"/>
     <col min="13311" max="13555" width="9" style="10"/>
-    <col min="13556" max="13556" width="26.5703125" style="10" customWidth="1"/>
-    <col min="13557" max="13557" width="13.140625" style="10" customWidth="1"/>
+    <col min="13556" max="13556" width="26.5625" style="10" customWidth="1"/>
+    <col min="13557" max="13557" width="13.125" style="10" customWidth="1"/>
     <col min="13558" max="13562" width="9" style="10"/>
-    <col min="13563" max="13563" width="10.85546875" style="10" customWidth="1"/>
+    <col min="13563" max="13563" width="10.875" style="10" customWidth="1"/>
     <col min="13564" max="13564" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="13565" max="13565" width="10.5703125" style="10" customWidth="1"/>
-    <col min="13566" max="13566" width="10.85546875" style="10" customWidth="1"/>
+    <col min="13565" max="13565" width="10.5625" style="10" customWidth="1"/>
+    <col min="13566" max="13566" width="10.875" style="10" customWidth="1"/>
     <col min="13567" max="13811" width="9" style="10"/>
-    <col min="13812" max="13812" width="26.5703125" style="10" customWidth="1"/>
-    <col min="13813" max="13813" width="13.140625" style="10" customWidth="1"/>
+    <col min="13812" max="13812" width="26.5625" style="10" customWidth="1"/>
+    <col min="13813" max="13813" width="13.125" style="10" customWidth="1"/>
     <col min="13814" max="13818" width="9" style="10"/>
-    <col min="13819" max="13819" width="10.85546875" style="10" customWidth="1"/>
+    <col min="13819" max="13819" width="10.875" style="10" customWidth="1"/>
     <col min="13820" max="13820" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="13821" max="13821" width="10.5703125" style="10" customWidth="1"/>
-    <col min="13822" max="13822" width="10.85546875" style="10" customWidth="1"/>
+    <col min="13821" max="13821" width="10.5625" style="10" customWidth="1"/>
+    <col min="13822" max="13822" width="10.875" style="10" customWidth="1"/>
     <col min="13823" max="14067" width="9" style="10"/>
-    <col min="14068" max="14068" width="26.5703125" style="10" customWidth="1"/>
-    <col min="14069" max="14069" width="13.140625" style="10" customWidth="1"/>
+    <col min="14068" max="14068" width="26.5625" style="10" customWidth="1"/>
+    <col min="14069" max="14069" width="13.125" style="10" customWidth="1"/>
     <col min="14070" max="14074" width="9" style="10"/>
-    <col min="14075" max="14075" width="10.85546875" style="10" customWidth="1"/>
+    <col min="14075" max="14075" width="10.875" style="10" customWidth="1"/>
     <col min="14076" max="14076" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="14077" max="14077" width="10.5703125" style="10" customWidth="1"/>
-    <col min="14078" max="14078" width="10.85546875" style="10" customWidth="1"/>
+    <col min="14077" max="14077" width="10.5625" style="10" customWidth="1"/>
+    <col min="14078" max="14078" width="10.875" style="10" customWidth="1"/>
     <col min="14079" max="14323" width="9" style="10"/>
-    <col min="14324" max="14324" width="26.5703125" style="10" customWidth="1"/>
-    <col min="14325" max="14325" width="13.140625" style="10" customWidth="1"/>
+    <col min="14324" max="14324" width="26.5625" style="10" customWidth="1"/>
+    <col min="14325" max="14325" width="13.125" style="10" customWidth="1"/>
     <col min="14326" max="14330" width="9" style="10"/>
-    <col min="14331" max="14331" width="10.85546875" style="10" customWidth="1"/>
+    <col min="14331" max="14331" width="10.875" style="10" customWidth="1"/>
     <col min="14332" max="14332" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="14333" max="14333" width="10.5703125" style="10" customWidth="1"/>
-    <col min="14334" max="14334" width="10.85546875" style="10" customWidth="1"/>
+    <col min="14333" max="14333" width="10.5625" style="10" customWidth="1"/>
+    <col min="14334" max="14334" width="10.875" style="10" customWidth="1"/>
     <col min="14335" max="14579" width="9" style="10"/>
-    <col min="14580" max="14580" width="26.5703125" style="10" customWidth="1"/>
-    <col min="14581" max="14581" width="13.140625" style="10" customWidth="1"/>
+    <col min="14580" max="14580" width="26.5625" style="10" customWidth="1"/>
+    <col min="14581" max="14581" width="13.125" style="10" customWidth="1"/>
     <col min="14582" max="14586" width="9" style="10"/>
-    <col min="14587" max="14587" width="10.85546875" style="10" customWidth="1"/>
+    <col min="14587" max="14587" width="10.875" style="10" customWidth="1"/>
     <col min="14588" max="14588" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="14589" max="14589" width="10.5703125" style="10" customWidth="1"/>
-    <col min="14590" max="14590" width="10.85546875" style="10" customWidth="1"/>
+    <col min="14589" max="14589" width="10.5625" style="10" customWidth="1"/>
+    <col min="14590" max="14590" width="10.875" style="10" customWidth="1"/>
     <col min="14591" max="14835" width="9" style="10"/>
-    <col min="14836" max="14836" width="26.5703125" style="10" customWidth="1"/>
-    <col min="14837" max="14837" width="13.140625" style="10" customWidth="1"/>
+    <col min="14836" max="14836" width="26.5625" style="10" customWidth="1"/>
+    <col min="14837" max="14837" width="13.125" style="10" customWidth="1"/>
     <col min="14838" max="14842" width="9" style="10"/>
-    <col min="14843" max="14843" width="10.85546875" style="10" customWidth="1"/>
+    <col min="14843" max="14843" width="10.875" style="10" customWidth="1"/>
     <col min="14844" max="14844" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="14845" max="14845" width="10.5703125" style="10" customWidth="1"/>
-    <col min="14846" max="14846" width="10.85546875" style="10" customWidth="1"/>
+    <col min="14845" max="14845" width="10.5625" style="10" customWidth="1"/>
+    <col min="14846" max="14846" width="10.875" style="10" customWidth="1"/>
     <col min="14847" max="15091" width="9" style="10"/>
-    <col min="15092" max="15092" width="26.5703125" style="10" customWidth="1"/>
-    <col min="15093" max="15093" width="13.140625" style="10" customWidth="1"/>
+    <col min="15092" max="15092" width="26.5625" style="10" customWidth="1"/>
+    <col min="15093" max="15093" width="13.125" style="10" customWidth="1"/>
     <col min="15094" max="15098" width="9" style="10"/>
-    <col min="15099" max="15099" width="10.85546875" style="10" customWidth="1"/>
+    <col min="15099" max="15099" width="10.875" style="10" customWidth="1"/>
     <col min="15100" max="15100" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="15101" max="15101" width="10.5703125" style="10" customWidth="1"/>
-    <col min="15102" max="15102" width="10.85546875" style="10" customWidth="1"/>
+    <col min="15101" max="15101" width="10.5625" style="10" customWidth="1"/>
+    <col min="15102" max="15102" width="10.875" style="10" customWidth="1"/>
     <col min="15103" max="15347" width="9" style="10"/>
-    <col min="15348" max="15348" width="26.5703125" style="10" customWidth="1"/>
-    <col min="15349" max="15349" width="13.140625" style="10" customWidth="1"/>
+    <col min="15348" max="15348" width="26.5625" style="10" customWidth="1"/>
+    <col min="15349" max="15349" width="13.125" style="10" customWidth="1"/>
     <col min="15350" max="15354" width="9" style="10"/>
-    <col min="15355" max="15355" width="10.85546875" style="10" customWidth="1"/>
+    <col min="15355" max="15355" width="10.875" style="10" customWidth="1"/>
     <col min="15356" max="15356" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="15357" max="15357" width="10.5703125" style="10" customWidth="1"/>
-    <col min="15358" max="15358" width="10.85546875" style="10" customWidth="1"/>
+    <col min="15357" max="15357" width="10.5625" style="10" customWidth="1"/>
+    <col min="15358" max="15358" width="10.875" style="10" customWidth="1"/>
     <col min="15359" max="15603" width="9" style="10"/>
-    <col min="15604" max="15604" width="26.5703125" style="10" customWidth="1"/>
-    <col min="15605" max="15605" width="13.140625" style="10" customWidth="1"/>
+    <col min="15604" max="15604" width="26.5625" style="10" customWidth="1"/>
+    <col min="15605" max="15605" width="13.125" style="10" customWidth="1"/>
     <col min="15606" max="15610" width="9" style="10"/>
-    <col min="15611" max="15611" width="10.85546875" style="10" customWidth="1"/>
+    <col min="15611" max="15611" width="10.875" style="10" customWidth="1"/>
     <col min="15612" max="15612" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="15613" max="15613" width="10.5703125" style="10" customWidth="1"/>
-    <col min="15614" max="15614" width="10.85546875" style="10" customWidth="1"/>
+    <col min="15613" max="15613" width="10.5625" style="10" customWidth="1"/>
+    <col min="15614" max="15614" width="10.875" style="10" customWidth="1"/>
     <col min="15615" max="15859" width="9" style="10"/>
-    <col min="15860" max="15860" width="26.5703125" style="10" customWidth="1"/>
-    <col min="15861" max="15861" width="13.140625" style="10" customWidth="1"/>
+    <col min="15860" max="15860" width="26.5625" style="10" customWidth="1"/>
+    <col min="15861" max="15861" width="13.125" style="10" customWidth="1"/>
     <col min="15862" max="15866" width="9" style="10"/>
-    <col min="15867" max="15867" width="10.85546875" style="10" customWidth="1"/>
+    <col min="15867" max="15867" width="10.875" style="10" customWidth="1"/>
     <col min="15868" max="15868" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="15869" max="15869" width="10.5703125" style="10" customWidth="1"/>
-    <col min="15870" max="15870" width="10.85546875" style="10" customWidth="1"/>
+    <col min="15869" max="15869" width="10.5625" style="10" customWidth="1"/>
+    <col min="15870" max="15870" width="10.875" style="10" customWidth="1"/>
     <col min="15871" max="16115" width="9" style="10"/>
-    <col min="16116" max="16116" width="26.5703125" style="10" customWidth="1"/>
-    <col min="16117" max="16117" width="13.140625" style="10" customWidth="1"/>
+    <col min="16116" max="16116" width="26.5625" style="10" customWidth="1"/>
+    <col min="16117" max="16117" width="13.125" style="10" customWidth="1"/>
     <col min="16118" max="16122" width="9" style="10"/>
-    <col min="16123" max="16123" width="10.85546875" style="10" customWidth="1"/>
+    <col min="16123" max="16123" width="10.875" style="10" customWidth="1"/>
     <col min="16124" max="16124" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="16125" max="16125" width="10.5703125" style="10" customWidth="1"/>
-    <col min="16126" max="16126" width="10.85546875" style="10" customWidth="1"/>
+    <col min="16125" max="16125" width="10.5625" style="10" customWidth="1"/>
+    <col min="16126" max="16126" width="10.875" style="10" customWidth="1"/>
     <col min="16127" max="16384" width="9" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="9" t="s">
         <v>99</v>
       </c>
       <c r="E1" s="11"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
         <v>100</v>
       </c>
@@ -8314,7 +8284,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="10" t="s">
         <v>101</v>
       </c>
@@ -8322,7 +8292,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="10" t="s">
         <v>102</v>
       </c>
@@ -8346,7 +8316,7 @@
       </c>
       <c r="H5" s="15"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="16" t="s">
         <v>103</v>
       </c>
@@ -8369,7 +8339,7 @@
         <v>12.95</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
         <v>104</v>
       </c>
@@ -8398,12 +8368,12 @@
         <v>0.64749999999999996</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="19" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="10" t="s">
         <v>102</v>
       </c>
@@ -8426,7 +8396,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="10" t="s">
         <v>106</v>
       </c>
@@ -8449,7 +8419,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B11" s="21" t="s">
         <v>2</v>
       </c>
@@ -8469,7 +8439,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="10" t="s">
         <v>107</v>
       </c>
@@ -8492,12 +8462,12 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="22" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B15" s="23"/>
       <c r="C15" s="23"/>
       <c r="D15" s="23"/>
@@ -8505,7 +8475,7 @@
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="10" t="s">
         <v>109</v>
       </c>
@@ -8528,7 +8498,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B17" s="21"/>
       <c r="C17" s="21"/>
       <c r="D17" s="21"/>
@@ -8536,7 +8506,7 @@
       <c r="F17" s="21"/>
       <c r="G17" s="21"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="10" t="s">
         <v>185</v>
       </c>
@@ -8566,7 +8536,7 @@
       </c>
       <c r="H18" s="23"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B19" s="23" t="s">
         <v>2</v>
       </c>
@@ -8586,7 +8556,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="10" t="s">
         <v>111</v>
       </c>
@@ -8609,16 +8579,16 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="19"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="24" t="s">
         <v>112</v>
       </c>
       <c r="B22" s="18"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="10" t="s">
         <v>102</v>
       </c>
@@ -8644,7 +8614,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="10" t="s">
         <v>114</v>
       </c>
@@ -8665,7 +8635,7 @@
         <v>0</v>
       </c>
       <c r="F24" s="10">
-        <f t="shared" si="2"/>
+        <f>F18*F7</f>
         <v>0</v>
       </c>
       <c r="G24" s="10">
@@ -8677,7 +8647,7 @@
         <v>6312.5</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="10" t="s">
         <v>115</v>
       </c>
@@ -8710,7 +8680,7 @@
         <v>1529250</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="H26" s="26">
         <f>SUM(H24:H25)</f>
         <v>1535562.5</v>

--- a/class_excel/temp_midterm.xlsx
+++ b/class_excel/temp_midterm.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\DADS7102\class_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{081F2990-7339-467B-BF6E-BDA906954E1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76356BB0-B23B-4A38-A687-D9E067890355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="9" activeTab="18" xr2:uid="{962D6ACA-47B2-4C7E-82D5-0F5476EE75BF}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="4" activeTab="6" xr2:uid="{962D6ACA-47B2-4C7E-82D5-0F5476EE75BF}"/>
   </bookViews>
   <sheets>
     <sheet name="ch_1_1" sheetId="1" r:id="rId1"/>
@@ -5688,7 +5688,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <f t="shared" ref="C4:H4" si="0">SUM(D2:D3)</f>
+        <f t="shared" ref="D4:H4" si="0">SUM(D2:D3)</f>
         <v>0</v>
       </c>
       <c r="E4">
@@ -6716,7 +6716,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9416A4A6-16E8-44A6-ABD2-65E95D8954DD}">
-  <dimension ref="A1:N27"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6.4375" bestFit="1" customWidth="1"/>
@@ -6734,7 +6734,7 @@
     <col min="13" max="13" width="5.5625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" s="30" t="s">
         <v>83</v>
       </c>
@@ -6768,9 +6768,8 @@
       <c r="M1" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="N1" s="30"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -6812,7 +6811,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>
@@ -6854,7 +6853,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>1</v>
       </c>
@@ -6896,7 +6895,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>1</v>
       </c>
@@ -6938,7 +6937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>1</v>
       </c>
@@ -6980,7 +6979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>1</v>
       </c>
@@ -7022,7 +7021,7 @@
         <v>-400</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>2</v>
       </c>
@@ -7064,7 +7063,7 @@
         <v>-180</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>2</v>
       </c>
@@ -7085,7 +7084,7 @@
       </c>
       <c r="G9" s="52"/>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>2</v>
       </c>
@@ -7113,7 +7112,7 @@
         <v>3260</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>2</v>
       </c>
@@ -7134,7 +7133,7 @@
       </c>
       <c r="G11" s="52"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>2</v>
       </c>
@@ -7155,7 +7154,7 @@
       </c>
       <c r="G12" s="52"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>2</v>
       </c>
@@ -7176,7 +7175,7 @@
       </c>
       <c r="G13" s="52"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>3</v>
       </c>
@@ -7197,7 +7196,7 @@
       </c>
       <c r="G14" s="52"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>3</v>
       </c>
@@ -7218,7 +7217,7 @@
       </c>
       <c r="G15" s="52"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>3</v>
       </c>
